--- a/DB Flotte ETR1000 Ver_1.7_00.xlsx
+++ b/DB Flotte ETR1000 Ver_1.7_00.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-410]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -318,36 +318,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <color indexed="81"/>
-      <sz val="9"/>
+      <color rgb="FF00AA00"/>
+      <sz val="11"/>
     </font>
     <font>
       <color rgb="0000AA00"/>
@@ -2019,7 +1991,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="638">
+  <cellXfs count="626">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3461,6 +3433,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3507,49 +3482,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3559,6 +3503,7 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3570,14 +3515,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3611,6 +3554,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3621,31 +3577,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3653,6 +3596,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3665,20 +3614,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3688,6 +3635,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3697,29 +3647,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4678,8 +4612,8 @@
   <cols>
     <col width="10.85546875" customWidth="1" style="13" min="1" max="2"/>
     <col width="59" customWidth="1" style="13" min="3" max="3"/>
-    <col width="8.7109375" customWidth="1" style="13" min="4" max="9"/>
-    <col width="8.7109375" customWidth="1" style="13" min="10" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="4" max="10"/>
+    <col width="8.7109375" customWidth="1" style="13" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="188">
@@ -4761,100 +4695,100 @@
     <col width="8.7109375" customWidth="1" style="260" min="20" max="20"/>
     <col width="6.7109375" customWidth="1" style="260" min="21" max="21"/>
     <col width="8.7109375" customWidth="1" style="260" min="22" max="22"/>
-    <col width="8.7109375" customWidth="1" style="103" min="23" max="28"/>
-    <col width="8.7109375" customWidth="1" style="103" min="29" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="23" max="29"/>
+    <col width="8.7109375" customWidth="1" style="103" min="30" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customFormat="1" customHeight="1" s="105">
-      <c r="A1" s="562" t="inlineStr">
+      <c r="A1" s="554" t="inlineStr">
         <is>
           <t>Impianto</t>
         </is>
       </c>
-      <c r="B1" s="568" t="inlineStr">
+      <c r="B1" s="561" t="inlineStr">
         <is>
           <t>Gruppo/Componente</t>
         </is>
       </c>
-      <c r="C1" s="567" t="inlineStr">
+      <c r="C1" s="560" t="inlineStr">
         <is>
           <t>P/N</t>
         </is>
       </c>
-      <c r="D1" s="571" t="inlineStr">
+      <c r="D1" s="563" t="inlineStr">
         <is>
           <t>Applicabilità flotte</t>
         </is>
       </c>
-      <c r="E1" s="570" t="n"/>
-      <c r="F1" s="570" t="n"/>
-      <c r="G1" s="570" t="n"/>
-      <c r="H1" s="570" t="n"/>
-      <c r="I1" s="570" t="n"/>
-      <c r="J1" s="565" t="n"/>
-      <c r="K1" s="564" t="inlineStr">
+      <c r="E1" s="557" t="n"/>
+      <c r="F1" s="557" t="n"/>
+      <c r="G1" s="557" t="n"/>
+      <c r="H1" s="557" t="n"/>
+      <c r="I1" s="557" t="n"/>
+      <c r="J1" s="558" t="n"/>
+      <c r="K1" s="556" t="inlineStr">
         <is>
           <t>Manuale</t>
         </is>
       </c>
-      <c r="L1" s="570" t="n"/>
-      <c r="M1" s="565" t="n"/>
-      <c r="N1" s="564" t="inlineStr">
+      <c r="L1" s="557" t="n"/>
+      <c r="M1" s="558" t="n"/>
+      <c r="N1" s="556" t="inlineStr">
         <is>
           <t>CPR</t>
         </is>
       </c>
-      <c r="O1" s="570" t="n"/>
-      <c r="P1" s="565" t="n"/>
-      <c r="Q1" s="564" t="inlineStr">
+      <c r="O1" s="557" t="n"/>
+      <c r="P1" s="558" t="n"/>
+      <c r="Q1" s="556" t="inlineStr">
         <is>
           <t>Raccolta doc</t>
         </is>
       </c>
-      <c r="R1" s="565" t="n"/>
-      <c r="S1" s="566" t="inlineStr">
+      <c r="R1" s="558" t="n"/>
+      <c r="S1" s="559" t="inlineStr">
         <is>
           <t>Schema elettrico</t>
         </is>
       </c>
-      <c r="T1" s="565" t="n"/>
-      <c r="U1" s="566" t="inlineStr">
+      <c r="T1" s="558" t="n"/>
+      <c r="U1" s="559" t="inlineStr">
         <is>
           <t>Schema Pneumatico</t>
         </is>
       </c>
-      <c r="V1" s="565" t="n"/>
+      <c r="V1" s="558" t="n"/>
     </row>
     <row r="2" ht="31.5" customFormat="1" customHeight="1" s="105">
-      <c r="A2" s="563" t="n"/>
-      <c r="B2" s="569" t="n"/>
-      <c r="C2" s="527" t="n"/>
+      <c r="A2" s="555" t="n"/>
+      <c r="B2" s="562" t="n"/>
+      <c r="C2" s="528" t="n"/>
       <c r="D2" s="136" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E2" s="537" t="inlineStr">
+      <c r="E2" s="538" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="F2" s="537" t="inlineStr">
+      <c r="F2" s="538" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="G2" s="537" t="inlineStr">
+      <c r="G2" s="538" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="H2" s="537" t="inlineStr">
+      <c r="H2" s="538" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="I2" s="537" t="inlineStr">
+      <c r="I2" s="538" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
@@ -4981,7 +4915,7 @@
       <c r="U3" s="220" t="n"/>
       <c r="V3" s="219" t="n"/>
     </row>
-    <row r="4" outlineLevel="1" s="594">
+    <row r="4" outlineLevel="1" s="592">
       <c r="A4" s="199" t="n"/>
       <c r="B4" s="118" t="inlineStr">
         <is>
@@ -5037,7 +4971,7 @@
       <c r="U4" s="226" t="n"/>
       <c r="V4" s="225" t="n"/>
     </row>
-    <row r="5" outlineLevel="2" s="594">
+    <row r="5" outlineLevel="2" s="592">
       <c r="A5" s="109" t="n"/>
       <c r="B5" s="110" t="inlineStr">
         <is>
@@ -5098,7 +5032,7 @@
       <c r="U5" s="233" t="n"/>
       <c r="V5" s="232" t="n"/>
     </row>
-    <row r="6" outlineLevel="2" s="594">
+    <row r="6" outlineLevel="2" s="592">
       <c r="A6" s="109" t="n"/>
       <c r="B6" s="110" t="inlineStr">
         <is>
@@ -5159,7 +5093,7 @@
       <c r="U6" s="233" t="n"/>
       <c r="V6" s="232" t="n"/>
     </row>
-    <row r="7" outlineLevel="2" s="594">
+    <row r="7" outlineLevel="2" s="592">
       <c r="A7" s="109" t="n"/>
       <c r="B7" s="110" t="inlineStr">
         <is>
@@ -5179,7 +5113,7 @@
       <c r="U7" s="233" t="n"/>
       <c r="V7" s="232" t="n"/>
     </row>
-    <row r="8" outlineLevel="1" s="594">
+    <row r="8" outlineLevel="1" s="592">
       <c r="A8" s="199" t="n"/>
       <c r="B8" s="118" t="inlineStr">
         <is>
@@ -5235,7 +5169,7 @@
       <c r="U8" s="226" t="n"/>
       <c r="V8" s="225" t="n"/>
     </row>
-    <row r="9" outlineLevel="2" s="594">
+    <row r="9" outlineLevel="2" s="592">
       <c r="A9" s="109" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -5305,7 +5239,7 @@
       <c r="U10" s="240" t="n"/>
       <c r="V10" s="241" t="n"/>
     </row>
-    <row r="11" outlineLevel="2" s="594">
+    <row r="11" outlineLevel="2" s="592">
       <c r="A11" s="109" t="n"/>
       <c r="B11" s="202" t="inlineStr">
         <is>
@@ -5392,7 +5326,7 @@
       <c r="U12" s="220" t="n"/>
       <c r="V12" s="219" t="n"/>
     </row>
-    <row r="13" outlineLevel="1" s="594">
+    <row r="13" outlineLevel="1" s="592">
       <c r="A13" s="199" t="n"/>
       <c r="B13" s="118" t="inlineStr">
         <is>
@@ -5448,7 +5382,7 @@
       <c r="U13" s="226" t="n"/>
       <c r="V13" s="225" t="n"/>
     </row>
-    <row r="14" outlineLevel="2" s="594">
+    <row r="14" outlineLevel="2" s="592">
       <c r="A14" s="109" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -5501,7 +5435,7 @@
       <c r="U14" s="233" t="n"/>
       <c r="V14" s="232" t="n"/>
     </row>
-    <row r="15" outlineLevel="2" s="594">
+    <row r="15" outlineLevel="2" s="592">
       <c r="A15" s="109" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -5554,7 +5488,7 @@
       <c r="U15" s="233" t="n"/>
       <c r="V15" s="232" t="n"/>
     </row>
-    <row r="16" outlineLevel="2" s="594">
+    <row r="16" outlineLevel="2" s="592">
       <c r="A16" s="109" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -5607,7 +5541,7 @@
       <c r="U16" s="233" t="n"/>
       <c r="V16" s="232" t="n"/>
     </row>
-    <row r="17" outlineLevel="2" s="594">
+    <row r="17" outlineLevel="2" s="592">
       <c r="A17" s="109" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -5655,7 +5589,7 @@
       <c r="U17" s="233" t="n"/>
       <c r="V17" s="232" t="n"/>
     </row>
-    <row r="18" outlineLevel="2" s="594">
+    <row r="18" outlineLevel="2" s="592">
       <c r="A18" s="109" t="n"/>
       <c r="B18" s="128" t="inlineStr">
         <is>
@@ -5694,7 +5628,7 @@
       <c r="U18" s="233" t="n"/>
       <c r="V18" s="232" t="n"/>
     </row>
-    <row r="19" outlineLevel="2" s="594">
+    <row r="19" outlineLevel="2" s="592">
       <c r="A19" s="109" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -5742,7 +5676,7 @@
       <c r="U19" s="233" t="n"/>
       <c r="V19" s="232" t="n"/>
     </row>
-    <row r="20" outlineLevel="2" s="594">
+    <row r="20" outlineLevel="2" s="592">
       <c r="A20" s="109" t="n"/>
       <c r="B20" s="128" t="inlineStr">
         <is>
@@ -5781,7 +5715,7 @@
       <c r="U20" s="233" t="n"/>
       <c r="V20" s="232" t="n"/>
     </row>
-    <row r="21" outlineLevel="2" s="594">
+    <row r="21" outlineLevel="2" s="592">
       <c r="A21" s="109" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -5834,7 +5768,7 @@
       <c r="U21" s="233" t="n"/>
       <c r="V21" s="232" t="n"/>
     </row>
-    <row r="22" outlineLevel="2" s="594">
+    <row r="22" outlineLevel="2" s="592">
       <c r="A22" s="109" t="n"/>
       <c r="B22" s="110" t="inlineStr">
         <is>
@@ -5887,7 +5821,7 @@
       <c r="U22" s="233" t="n"/>
       <c r="V22" s="232" t="n"/>
     </row>
-    <row r="23" outlineLevel="2" s="594">
+    <row r="23" outlineLevel="2" s="592">
       <c r="A23" s="109" t="n"/>
       <c r="B23" s="110" t="inlineStr">
         <is>
@@ -5940,7 +5874,7 @@
       <c r="U23" s="233" t="n"/>
       <c r="V23" s="232" t="n"/>
     </row>
-    <row r="24" outlineLevel="2" s="594">
+    <row r="24" outlineLevel="2" s="592">
       <c r="A24" s="109" t="n"/>
       <c r="B24" s="110" t="inlineStr">
         <is>
@@ -5993,7 +5927,7 @@
       <c r="U24" s="233" t="n"/>
       <c r="V24" s="232" t="n"/>
     </row>
-    <row r="25" outlineLevel="2" s="594">
+    <row r="25" outlineLevel="2" s="592">
       <c r="A25" s="109" t="n"/>
       <c r="B25" s="202" t="inlineStr">
         <is>
@@ -6038,7 +5972,7 @@
       <c r="U25" s="233" t="n"/>
       <c r="V25" s="232" t="n"/>
     </row>
-    <row r="26" outlineLevel="2" s="594">
+    <row r="26" outlineLevel="2" s="592">
       <c r="A26" s="109" t="n"/>
       <c r="B26" s="202" t="inlineStr">
         <is>
@@ -6071,7 +6005,7 @@
       <c r="U26" s="233" t="n"/>
       <c r="V26" s="232" t="n"/>
     </row>
-    <row r="27" outlineLevel="2" s="594">
+    <row r="27" outlineLevel="2" s="592">
       <c r="A27" s="109" t="n"/>
       <c r="B27" s="202" t="inlineStr">
         <is>
@@ -6104,7 +6038,7 @@
       <c r="U27" s="233" t="n"/>
       <c r="V27" s="232" t="n"/>
     </row>
-    <row r="28" outlineLevel="2" s="594">
+    <row r="28" outlineLevel="2" s="592">
       <c r="A28" s="109" t="n"/>
       <c r="B28" s="202" t="inlineStr">
         <is>
@@ -6137,7 +6071,7 @@
       <c r="U28" s="233" t="n"/>
       <c r="V28" s="232" t="n"/>
     </row>
-    <row r="29" outlineLevel="2" s="594">
+    <row r="29" outlineLevel="2" s="592">
       <c r="A29" s="109" t="n"/>
       <c r="B29" s="202" t="inlineStr">
         <is>
@@ -6170,7 +6104,7 @@
       <c r="U29" s="233" t="n"/>
       <c r="V29" s="232" t="n"/>
     </row>
-    <row r="30" outlineLevel="2" s="594">
+    <row r="30" outlineLevel="2" s="592">
       <c r="A30" s="109" t="n"/>
       <c r="B30" s="202" t="inlineStr">
         <is>
@@ -6203,7 +6137,7 @@
       <c r="U30" s="233" t="n"/>
       <c r="V30" s="232" t="n"/>
     </row>
-    <row r="31" outlineLevel="2" s="594">
+    <row r="31" outlineLevel="2" s="592">
       <c r="A31" s="109" t="n"/>
       <c r="B31" s="202" t="inlineStr">
         <is>
@@ -6246,7 +6180,7 @@
       <c r="U31" s="233" t="n"/>
       <c r="V31" s="232" t="n"/>
     </row>
-    <row r="32" outlineLevel="2" s="594">
+    <row r="32" outlineLevel="2" s="592">
       <c r="A32" s="109" t="n"/>
       <c r="B32" s="202" t="inlineStr">
         <is>
@@ -6279,7 +6213,7 @@
       <c r="U32" s="233" t="n"/>
       <c r="V32" s="232" t="n"/>
     </row>
-    <row r="33" outlineLevel="2" s="594">
+    <row r="33" outlineLevel="2" s="592">
       <c r="A33" s="109" t="n"/>
       <c r="B33" s="202" t="inlineStr">
         <is>
@@ -6312,7 +6246,7 @@
       <c r="U33" s="233" t="n"/>
       <c r="V33" s="232" t="n"/>
     </row>
-    <row r="34" outlineLevel="2" s="594">
+    <row r="34" outlineLevel="2" s="592">
       <c r="A34" s="109" t="n"/>
       <c r="B34" s="202" t="inlineStr">
         <is>
@@ -6345,7 +6279,7 @@
       <c r="U34" s="233" t="n"/>
       <c r="V34" s="232" t="n"/>
     </row>
-    <row r="35" outlineLevel="2" ht="30" customHeight="1" s="594">
+    <row r="35" outlineLevel="2" ht="30" customHeight="1" s="592">
       <c r="A35" s="109" t="n"/>
       <c r="B35" s="202" t="inlineStr">
         <is>
@@ -6378,7 +6312,7 @@
       <c r="U35" s="233" t="n"/>
       <c r="V35" s="232" t="n"/>
     </row>
-    <row r="36" outlineLevel="2" s="594">
+    <row r="36" outlineLevel="2" s="592">
       <c r="A36" s="109" t="n"/>
       <c r="B36" s="202" t="inlineStr">
         <is>
@@ -6411,7 +6345,7 @@
       <c r="U36" s="233" t="n"/>
       <c r="V36" s="232" t="n"/>
     </row>
-    <row r="37" outlineLevel="1" s="594">
+    <row r="37" outlineLevel="1" s="592">
       <c r="A37" s="199" t="n"/>
       <c r="B37" s="118" t="inlineStr">
         <is>
@@ -6467,7 +6401,7 @@
       <c r="U37" s="226" t="n"/>
       <c r="V37" s="225" t="n"/>
     </row>
-    <row r="38" outlineLevel="2" s="594">
+    <row r="38" outlineLevel="2" s="592">
       <c r="A38" s="109" t="n"/>
       <c r="B38" s="126" t="inlineStr">
         <is>
@@ -6515,7 +6449,7 @@
       <c r="U38" s="233" t="n"/>
       <c r="V38" s="232" t="n"/>
     </row>
-    <row r="39" outlineLevel="2" s="594">
+    <row r="39" outlineLevel="2" s="592">
       <c r="A39" s="109" t="n"/>
       <c r="B39" s="128" t="inlineStr">
         <is>
@@ -6553,7 +6487,7 @@
       <c r="U39" s="233" t="n"/>
       <c r="V39" s="232" t="n"/>
     </row>
-    <row r="40" outlineLevel="2" s="594">
+    <row r="40" outlineLevel="2" s="592">
       <c r="A40" s="109" t="n"/>
       <c r="B40" s="126" t="inlineStr">
         <is>
@@ -6595,7 +6529,7 @@
       <c r="U40" s="233" t="n"/>
       <c r="V40" s="232" t="n"/>
     </row>
-    <row r="41" outlineLevel="2" s="594">
+    <row r="41" outlineLevel="2" s="592">
       <c r="A41" s="109" t="n"/>
       <c r="B41" s="202" t="inlineStr">
         <is>
@@ -6639,7 +6573,7 @@
       <c r="U41" s="233" t="n"/>
       <c r="V41" s="232" t="n"/>
     </row>
-    <row r="42" outlineLevel="1" s="594">
+    <row r="42" outlineLevel="1" s="592">
       <c r="A42" s="199" t="n"/>
       <c r="B42" s="118" t="inlineStr">
         <is>
@@ -6695,7 +6629,7 @@
       <c r="U42" s="226" t="n"/>
       <c r="V42" s="225" t="n"/>
     </row>
-    <row r="43" outlineLevel="2" s="594">
+    <row r="43" outlineLevel="2" s="592">
       <c r="A43" s="109" t="n"/>
       <c r="B43" s="110" t="inlineStr">
         <is>
@@ -6743,7 +6677,7 @@
       <c r="U43" s="233" t="n"/>
       <c r="V43" s="232" t="n"/>
     </row>
-    <row r="44" outlineLevel="2" s="594">
+    <row r="44" outlineLevel="2" s="592">
       <c r="A44" s="109" t="n"/>
       <c r="B44" s="128" t="inlineStr">
         <is>
@@ -6781,7 +6715,7 @@
       <c r="U44" s="233" t="n"/>
       <c r="V44" s="232" t="n"/>
     </row>
-    <row r="45" outlineLevel="2" s="594">
+    <row r="45" outlineLevel="2" s="592">
       <c r="A45" s="109" t="n"/>
       <c r="B45" s="110" t="inlineStr">
         <is>
@@ -6834,7 +6768,7 @@
       <c r="U45" s="233" t="n"/>
       <c r="V45" s="232" t="n"/>
     </row>
-    <row r="46" outlineLevel="2" s="594">
+    <row r="46" outlineLevel="2" s="592">
       <c r="A46" s="109" t="n"/>
       <c r="B46" s="126" t="inlineStr">
         <is>
@@ -6882,7 +6816,7 @@
       <c r="U46" s="233" t="n"/>
       <c r="V46" s="232" t="n"/>
     </row>
-    <row r="47" outlineLevel="2" s="594">
+    <row r="47" outlineLevel="2" s="592">
       <c r="A47" s="109" t="n"/>
       <c r="B47" s="128" t="inlineStr">
         <is>
@@ -6920,7 +6854,7 @@
       <c r="U47" s="233" t="n"/>
       <c r="V47" s="232" t="n"/>
     </row>
-    <row r="48" outlineLevel="2" s="594">
+    <row r="48" outlineLevel="2" s="592">
       <c r="A48" s="109" t="n"/>
       <c r="B48" s="126" t="inlineStr">
         <is>
@@ -6968,7 +6902,7 @@
       <c r="U48" s="233" t="n"/>
       <c r="V48" s="232" t="n"/>
     </row>
-    <row r="49" outlineLevel="2" s="594">
+    <row r="49" outlineLevel="2" s="592">
       <c r="A49" s="109" t="n"/>
       <c r="B49" s="124" t="inlineStr">
         <is>
@@ -7006,7 +6940,7 @@
       <c r="U49" s="233" t="n"/>
       <c r="V49" s="232" t="n"/>
     </row>
-    <row r="50" outlineLevel="2" s="594">
+    <row r="50" outlineLevel="2" s="592">
       <c r="A50" s="109" t="n"/>
       <c r="B50" s="126" t="inlineStr">
         <is>
@@ -7054,7 +6988,7 @@
       <c r="U50" s="233" t="n"/>
       <c r="V50" s="232" t="n"/>
     </row>
-    <row r="51" outlineLevel="2" s="594">
+    <row r="51" outlineLevel="2" s="592">
       <c r="A51" s="109" t="n"/>
       <c r="B51" s="128" t="inlineStr">
         <is>
@@ -7092,7 +7026,7 @@
       <c r="U51" s="233" t="n"/>
       <c r="V51" s="232" t="n"/>
     </row>
-    <row r="52" outlineLevel="2" s="594">
+    <row r="52" outlineLevel="2" s="592">
       <c r="A52" s="109" t="n"/>
       <c r="B52" s="128" t="inlineStr">
         <is>
@@ -7130,7 +7064,7 @@
       <c r="U52" s="233" t="n"/>
       <c r="V52" s="232" t="n"/>
     </row>
-    <row r="53" outlineLevel="2" s="594">
+    <row r="53" outlineLevel="2" s="592">
       <c r="A53" s="109" t="n"/>
       <c r="B53" s="110" t="inlineStr">
         <is>
@@ -7183,7 +7117,7 @@
       <c r="U53" s="233" t="n"/>
       <c r="V53" s="232" t="n"/>
     </row>
-    <row r="54" outlineLevel="2" ht="30" customHeight="1" s="594">
+    <row r="54" outlineLevel="2" ht="30" customHeight="1" s="592">
       <c r="A54" s="109" t="n"/>
       <c r="B54" s="202" t="inlineStr">
         <is>
@@ -7216,7 +7150,7 @@
       <c r="U54" s="233" t="n"/>
       <c r="V54" s="232" t="n"/>
     </row>
-    <row r="55" outlineLevel="2" ht="30" customHeight="1" s="594">
+    <row r="55" outlineLevel="2" ht="30" customHeight="1" s="592">
       <c r="A55" s="109" t="n"/>
       <c r="B55" s="202" t="inlineStr">
         <is>
@@ -7305,7 +7239,7 @@
       <c r="U56" s="220" t="n"/>
       <c r="V56" s="219" t="n"/>
     </row>
-    <row r="57" outlineLevel="1" s="594">
+    <row r="57" outlineLevel="1" s="592">
       <c r="A57" s="117" t="n"/>
       <c r="B57" s="118" t="inlineStr">
         <is>
@@ -7361,7 +7295,7 @@
       <c r="U57" s="251" t="n"/>
       <c r="V57" s="250" t="n"/>
     </row>
-    <row r="58" outlineLevel="2" ht="30" customHeight="1" s="594">
+    <row r="58" outlineLevel="2" ht="30" customHeight="1" s="592">
       <c r="A58" s="109" t="n"/>
       <c r="B58" s="110" t="inlineStr">
         <is>
@@ -7394,7 +7328,7 @@
       <c r="U58" s="233" t="n"/>
       <c r="V58" s="232" t="n"/>
     </row>
-    <row r="59" outlineLevel="3" ht="30" customHeight="1" s="594">
+    <row r="59" outlineLevel="3" ht="30" customHeight="1" s="592">
       <c r="A59" s="109" t="n"/>
       <c r="B59" s="110" t="inlineStr">
         <is>
@@ -7427,7 +7361,7 @@
       <c r="U59" s="233" t="n"/>
       <c r="V59" s="232" t="n"/>
     </row>
-    <row r="60" outlineLevel="3" ht="30" customHeight="1" s="594">
+    <row r="60" outlineLevel="3" ht="30" customHeight="1" s="592">
       <c r="A60" s="109" t="n"/>
       <c r="B60" s="110" t="inlineStr">
         <is>
@@ -7460,7 +7394,7 @@
       <c r="U60" s="233" t="n"/>
       <c r="V60" s="232" t="n"/>
     </row>
-    <row r="61" outlineLevel="2" s="594">
+    <row r="61" outlineLevel="2" s="592">
       <c r="A61" s="109" t="n"/>
       <c r="B61" s="202" t="inlineStr">
         <is>
@@ -7497,7 +7431,7 @@
       <c r="U61" s="233" t="n"/>
       <c r="V61" s="232" t="n"/>
     </row>
-    <row r="62" outlineLevel="3" s="594">
+    <row r="62" outlineLevel="3" s="592">
       <c r="A62" s="109" t="n"/>
       <c r="B62" s="202" t="inlineStr">
         <is>
@@ -7533,7 +7467,7 @@
       <c r="U62" s="233" t="n"/>
       <c r="V62" s="232" t="n"/>
     </row>
-    <row r="63" outlineLevel="3" collapsed="1" s="594">
+    <row r="63" outlineLevel="3" collapsed="1" s="592">
       <c r="A63" s="109" t="n"/>
       <c r="B63" s="202" t="inlineStr">
         <is>
@@ -7569,7 +7503,7 @@
       <c r="U63" s="233" t="n"/>
       <c r="V63" s="232" t="n"/>
     </row>
-    <row r="64" outlineLevel="1" s="594">
+    <row r="64" outlineLevel="1" s="592">
       <c r="A64" s="117" t="n"/>
       <c r="B64" s="118" t="inlineStr">
         <is>
@@ -7625,7 +7559,7 @@
       <c r="U64" s="251" t="n"/>
       <c r="V64" s="250" t="n"/>
     </row>
-    <row r="65" outlineLevel="2" ht="30" customHeight="1" s="594">
+    <row r="65" outlineLevel="2" ht="30" customHeight="1" s="592">
       <c r="A65" s="109" t="n"/>
       <c r="B65" s="110" t="inlineStr">
         <is>
@@ -7657,7 +7591,7 @@
       <c r="U65" s="233" t="n"/>
       <c r="V65" s="232" t="n"/>
     </row>
-    <row r="66" outlineLevel="3" ht="30" customHeight="1" s="594">
+    <row r="66" outlineLevel="3" ht="30" customHeight="1" s="592">
       <c r="A66" s="109" t="n"/>
       <c r="B66" s="110" t="inlineStr">
         <is>
@@ -7690,7 +7624,7 @@
       <c r="U66" s="233" t="n"/>
       <c r="V66" s="232" t="n"/>
     </row>
-    <row r="67" outlineLevel="3" ht="30" customHeight="1" s="594">
+    <row r="67" outlineLevel="3" ht="30" customHeight="1" s="592">
       <c r="A67" s="109" t="n"/>
       <c r="B67" s="110" t="inlineStr">
         <is>
@@ -7723,7 +7657,7 @@
       <c r="U67" s="233" t="n"/>
       <c r="V67" s="232" t="n"/>
     </row>
-    <row r="68" outlineLevel="2" s="594">
+    <row r="68" outlineLevel="2" s="592">
       <c r="A68" s="109" t="n"/>
       <c r="B68" s="202" t="inlineStr">
         <is>
@@ -7759,7 +7693,7 @@
       <c r="U68" s="233" t="n"/>
       <c r="V68" s="232" t="n"/>
     </row>
-    <row r="69" outlineLevel="3" s="594">
+    <row r="69" outlineLevel="3" s="592">
       <c r="A69" s="109" t="n"/>
       <c r="B69" s="123" t="inlineStr">
         <is>
@@ -7795,7 +7729,7 @@
       <c r="U69" s="233" t="n"/>
       <c r="V69" s="232" t="n"/>
     </row>
-    <row r="70" outlineLevel="3" collapsed="1" s="594">
+    <row r="70" outlineLevel="3" collapsed="1" s="592">
       <c r="A70" s="109" t="n"/>
       <c r="B70" s="202" t="inlineStr">
         <is>
@@ -7831,7 +7765,7 @@
       <c r="U70" s="233" t="n"/>
       <c r="V70" s="232" t="n"/>
     </row>
-    <row r="71" outlineLevel="1" s="594">
+    <row r="71" outlineLevel="1" s="592">
       <c r="A71" s="117" t="n"/>
       <c r="B71" s="118" t="inlineStr">
         <is>
@@ -7887,7 +7821,7 @@
       <c r="U71" s="251" t="n"/>
       <c r="V71" s="250" t="n"/>
     </row>
-    <row r="72" outlineLevel="2" ht="30" customHeight="1" s="594">
+    <row r="72" outlineLevel="2" ht="30" customHeight="1" s="592">
       <c r="A72" s="109" t="n"/>
       <c r="B72" s="110" t="inlineStr">
         <is>
@@ -7919,7 +7853,7 @@
       <c r="U72" s="233" t="n"/>
       <c r="V72" s="232" t="n"/>
     </row>
-    <row r="73" outlineLevel="3" ht="30" customHeight="1" s="594">
+    <row r="73" outlineLevel="3" ht="30" customHeight="1" s="592">
       <c r="A73" s="109" t="n"/>
       <c r="B73" s="110" t="inlineStr">
         <is>
@@ -7952,7 +7886,7 @@
       <c r="U73" s="233" t="n"/>
       <c r="V73" s="232" t="n"/>
     </row>
-    <row r="74" outlineLevel="3" ht="30" customHeight="1" s="594">
+    <row r="74" outlineLevel="3" ht="30" customHeight="1" s="592">
       <c r="A74" s="109" t="n"/>
       <c r="B74" s="110" t="inlineStr">
         <is>
@@ -7985,7 +7919,7 @@
       <c r="U74" s="233" t="n"/>
       <c r="V74" s="232" t="n"/>
     </row>
-    <row r="75" outlineLevel="2" s="594">
+    <row r="75" outlineLevel="2" s="592">
       <c r="A75" s="109" t="n"/>
       <c r="B75" s="202" t="inlineStr">
         <is>
@@ -8021,7 +7955,7 @@
       <c r="U75" s="233" t="n"/>
       <c r="V75" s="232" t="n"/>
     </row>
-    <row r="76" outlineLevel="3" s="594">
+    <row r="76" outlineLevel="3" s="592">
       <c r="A76" s="109" t="n"/>
       <c r="B76" s="202" t="inlineStr">
         <is>
@@ -8057,7 +7991,7 @@
       <c r="U76" s="233" t="n"/>
       <c r="V76" s="232" t="n"/>
     </row>
-    <row r="77" outlineLevel="3" collapsed="1" s="594">
+    <row r="77" outlineLevel="3" collapsed="1" s="592">
       <c r="A77" s="109" t="n"/>
       <c r="B77" s="202" t="inlineStr">
         <is>
@@ -8093,7 +8027,7 @@
       <c r="U77" s="233" t="n"/>
       <c r="V77" s="232" t="n"/>
     </row>
-    <row r="78" outlineLevel="1" s="594">
+    <row r="78" outlineLevel="1" s="592">
       <c r="A78" s="117" t="n"/>
       <c r="B78" s="118" t="inlineStr">
         <is>
@@ -8149,7 +8083,7 @@
       <c r="U78" s="251" t="n"/>
       <c r="V78" s="250" t="n"/>
     </row>
-    <row r="79" outlineLevel="2" ht="30" customHeight="1" s="594">
+    <row r="79" outlineLevel="2" ht="30" customHeight="1" s="592">
       <c r="A79" s="109" t="n"/>
       <c r="B79" s="110" t="inlineStr">
         <is>
@@ -8191,7 +8125,7 @@
       <c r="U79" s="233" t="n"/>
       <c r="V79" s="232" t="n"/>
     </row>
-    <row r="80" outlineLevel="1" s="594">
+    <row r="80" outlineLevel="1" s="592">
       <c r="A80" s="117" t="n"/>
       <c r="B80" s="118" t="inlineStr">
         <is>
@@ -8247,7 +8181,7 @@
       <c r="U80" s="251" t="n"/>
       <c r="V80" s="250" t="n"/>
     </row>
-    <row r="81" outlineLevel="2" ht="30" customHeight="1" s="594">
+    <row r="81" outlineLevel="2" ht="30" customHeight="1" s="592">
       <c r="A81" s="109" t="n"/>
       <c r="B81" s="110" t="inlineStr">
         <is>
@@ -8279,7 +8213,7 @@
       <c r="U81" s="233" t="n"/>
       <c r="V81" s="232" t="n"/>
     </row>
-    <row r="82" outlineLevel="3" ht="30" customHeight="1" s="594">
+    <row r="82" outlineLevel="3" ht="30" customHeight="1" s="592">
       <c r="A82" s="109" t="n"/>
       <c r="B82" s="110" t="inlineStr">
         <is>
@@ -8311,7 +8245,7 @@
       <c r="U82" s="233" t="n"/>
       <c r="V82" s="232" t="n"/>
     </row>
-    <row r="83" outlineLevel="3" ht="30" customHeight="1" s="594">
+    <row r="83" outlineLevel="3" ht="30" customHeight="1" s="592">
       <c r="A83" s="109" t="n"/>
       <c r="B83" s="110" t="inlineStr">
         <is>
@@ -8343,7 +8277,7 @@
       <c r="U83" s="233" t="n"/>
       <c r="V83" s="232" t="n"/>
     </row>
-    <row r="84" outlineLevel="2" s="594">
+    <row r="84" outlineLevel="2" s="592">
       <c r="A84" s="109" t="n"/>
       <c r="B84" s="202" t="inlineStr">
         <is>
@@ -8379,7 +8313,7 @@
       <c r="U84" s="233" t="n"/>
       <c r="V84" s="232" t="n"/>
     </row>
-    <row r="85" outlineLevel="3" s="594">
+    <row r="85" outlineLevel="3" s="592">
       <c r="A85" s="109" t="n"/>
       <c r="B85" s="123" t="inlineStr">
         <is>
@@ -8415,7 +8349,7 @@
       <c r="U85" s="233" t="n"/>
       <c r="V85" s="232" t="n"/>
     </row>
-    <row r="86" outlineLevel="3" collapsed="1" s="594">
+    <row r="86" outlineLevel="3" collapsed="1" s="592">
       <c r="A86" s="109" t="n"/>
       <c r="B86" s="123" t="inlineStr">
         <is>
@@ -8557,7 +8491,7 @@
       <c r="U92" s="233" t="n"/>
       <c r="V92" s="232" t="n"/>
     </row>
-    <row r="93" ht="30" customHeight="1" s="594">
+    <row r="93" ht="30" customHeight="1" s="592">
       <c r="A93" s="109" t="n"/>
       <c r="B93" s="110" t="inlineStr">
         <is>
@@ -8649,7 +8583,7 @@
       <c r="U96" s="233" t="n"/>
       <c r="V96" s="232" t="n"/>
     </row>
-    <row r="97" ht="30" customHeight="1" s="594">
+    <row r="97" ht="30" customHeight="1" s="592">
       <c r="A97" s="109" t="n"/>
       <c r="B97" s="110" t="inlineStr">
         <is>
@@ -8744,9 +8678,9 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="K1:M1"/>
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
@@ -8762,89 +8696,89 @@
   <dimension ref="A1:Z50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17.85546875" customWidth="1" style="594" min="1" max="1"/>
-    <col width="14.42578125" customWidth="1" style="594" min="2" max="2"/>
-    <col width="18.42578125" customWidth="1" style="594" min="3" max="3"/>
-    <col width="15.85546875" customWidth="1" style="594" min="4" max="4"/>
-    <col width="19.42578125" customWidth="1" style="594" min="5" max="6"/>
-    <col width="14.42578125" customWidth="1" style="594" min="7" max="7"/>
-    <col width="16.42578125" customWidth="1" style="594" min="8" max="8"/>
-    <col width="23.85546875" customWidth="1" style="594" min="9" max="9"/>
-    <col width="21.85546875" customWidth="1" style="594" min="10" max="10"/>
-    <col width="11.42578125" customWidth="1" style="594" min="11" max="11"/>
-    <col width="15.5703125" customWidth="1" style="594" min="12" max="12"/>
-    <col width="19.85546875" customWidth="1" style="594" min="13" max="13"/>
-    <col width="21.5703125" customWidth="1" style="594" min="14" max="14"/>
-    <col width="12.140625" customWidth="1" style="594" min="15" max="15"/>
-    <col width="15.5703125" customWidth="1" style="594" min="16" max="16"/>
-    <col width="24.5703125" customWidth="1" style="594" min="17" max="17"/>
-    <col width="26.85546875" customWidth="1" style="594" min="18" max="18"/>
-    <col width="15.140625" customWidth="1" style="594" min="20" max="20"/>
-    <col width="25.140625" customWidth="1" style="594" min="21" max="21"/>
-    <col width="20.140625" customWidth="1" style="594" min="22" max="22"/>
-    <col width="10" bestFit="1" customWidth="1" style="594" min="23" max="23"/>
-    <col width="15.42578125" customWidth="1" style="594" min="24" max="24"/>
-    <col width="20.42578125" customWidth="1" style="594" min="25" max="25"/>
-    <col width="25.85546875" customWidth="1" style="594" min="26" max="26"/>
+    <col width="17.85546875" customWidth="1" style="592" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" style="592" min="2" max="2"/>
+    <col width="18.42578125" customWidth="1" style="592" min="3" max="3"/>
+    <col width="15.85546875" customWidth="1" style="592" min="4" max="4"/>
+    <col width="19.42578125" customWidth="1" style="592" min="5" max="6"/>
+    <col width="14.42578125" customWidth="1" style="592" min="7" max="7"/>
+    <col width="16.42578125" customWidth="1" style="592" min="8" max="8"/>
+    <col width="23.85546875" customWidth="1" style="592" min="9" max="9"/>
+    <col width="21.85546875" customWidth="1" style="592" min="10" max="10"/>
+    <col width="11.42578125" customWidth="1" style="592" min="11" max="11"/>
+    <col width="15.5703125" customWidth="1" style="592" min="12" max="12"/>
+    <col width="19.85546875" customWidth="1" style="592" min="13" max="13"/>
+    <col width="21.5703125" customWidth="1" style="592" min="14" max="14"/>
+    <col width="12.140625" customWidth="1" style="592" min="15" max="15"/>
+    <col width="15.5703125" customWidth="1" style="592" min="16" max="16"/>
+    <col width="24.5703125" customWidth="1" style="592" min="17" max="17"/>
+    <col width="26.85546875" customWidth="1" style="592" min="18" max="18"/>
+    <col width="15.140625" customWidth="1" style="592" min="20" max="20"/>
+    <col width="25.140625" customWidth="1" style="592" min="21" max="21"/>
+    <col width="20.140625" customWidth="1" style="592" min="22" max="22"/>
+    <col width="10" bestFit="1" customWidth="1" style="592" min="23" max="23"/>
+    <col width="15.42578125" customWidth="1" style="592" min="24" max="24"/>
+    <col width="20.42578125" customWidth="1" style="592" min="25" max="25"/>
+    <col width="25.85546875" customWidth="1" style="592" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="C1" s="600" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="C1" s="582" t="inlineStr">
         <is>
           <t>IT 50 treni (flotta base)</t>
         </is>
       </c>
-      <c r="D1" s="601" t="n"/>
-      <c r="E1" s="601" t="n"/>
-      <c r="F1" s="602" t="n"/>
-      <c r="G1" s="600" t="inlineStr">
+      <c r="D1" s="583" t="n"/>
+      <c r="E1" s="583" t="n"/>
+      <c r="F1" s="584" t="n"/>
+      <c r="G1" s="582" t="inlineStr">
         <is>
           <t>IT 8 treni (51-58)</t>
         </is>
       </c>
-      <c r="H1" s="601" t="n"/>
-      <c r="I1" s="601" t="n"/>
-      <c r="J1" s="602" t="n"/>
-      <c r="K1" s="600" t="inlineStr">
+      <c r="H1" s="583" t="n"/>
+      <c r="I1" s="583" t="n"/>
+      <c r="J1" s="584" t="n"/>
+      <c r="K1" s="582" t="inlineStr">
         <is>
           <t>IT 6+30 treni (101-136)</t>
         </is>
       </c>
-      <c r="L1" s="601" t="n"/>
-      <c r="M1" s="601" t="n"/>
-      <c r="N1" s="602" t="n"/>
-      <c r="O1" s="600" t="inlineStr">
+      <c r="L1" s="583" t="n"/>
+      <c r="M1" s="583" t="n"/>
+      <c r="N1" s="584" t="n"/>
+      <c r="O1" s="582" t="inlineStr">
         <is>
           <t>I-FR 9 treni</t>
         </is>
       </c>
-      <c r="P1" s="601" t="n"/>
-      <c r="Q1" s="601" t="n"/>
-      <c r="R1" s="602" t="n"/>
-      <c r="S1" s="600" t="inlineStr">
+      <c r="P1" s="583" t="n"/>
+      <c r="Q1" s="583" t="n"/>
+      <c r="R1" s="584" t="n"/>
+      <c r="S1" s="582" t="inlineStr">
         <is>
           <t>DAI 9 treni</t>
         </is>
       </c>
-      <c r="T1" s="601" t="n"/>
-      <c r="U1" s="601" t="n"/>
-      <c r="V1" s="602" t="n"/>
-      <c r="W1" s="600" t="inlineStr">
+      <c r="T1" s="583" t="n"/>
+      <c r="U1" s="583" t="n"/>
+      <c r="V1" s="584" t="n"/>
+      <c r="W1" s="582" t="inlineStr">
         <is>
           <t>ES 20 treni</t>
         </is>
       </c>
-      <c r="X1" s="601" t="n"/>
-      <c r="Y1" s="601" t="n"/>
-      <c r="Z1" s="602" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="A2" s="578" t="inlineStr">
+      <c r="X1" s="583" t="n"/>
+      <c r="Y1" s="583" t="n"/>
+      <c r="Z1" s="584" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="A2" s="569" t="inlineStr">
         <is>
           <t>Sottosistema</t>
         </is>
       </c>
-      <c r="B2" s="579" t="n"/>
+      <c r="B2" s="570" t="n"/>
       <c r="C2" s="17" t="inlineStr">
         <is>
           <t>P/N</t>
@@ -8966,18 +8900,18 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="286.5" customHeight="1" s="594">
-      <c r="A3" s="604" t="inlineStr">
+    <row r="3" ht="286.5" customHeight="1" s="592">
+      <c r="A3" s="586" t="inlineStr">
         <is>
           <t>Carrelli</t>
         </is>
       </c>
-      <c r="B3" s="629" t="inlineStr">
+      <c r="B3" s="624" t="inlineStr">
         <is>
           <t>Motori</t>
         </is>
       </c>
-      <c r="C3" s="586" t="inlineStr">
+      <c r="C3" s="577" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -9002,7 +8936,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="G3" s="586" t="inlineStr">
+      <c r="G3" s="577" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -9027,7 +8961,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="K3" s="625" t="inlineStr">
+      <c r="K3" s="618" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -9052,7 +8986,7 @@
           <t>Sensoristica ERTMS-SCMT carrelli DM</t>
         </is>
       </c>
-      <c r="O3" s="586" t="inlineStr">
+      <c r="O3" s="577" t="inlineStr">
         <is>
           <t>100329688
 100329689
@@ -9065,7 +8999,7 @@
           <t>Sala Montata</t>
         </is>
       </c>
-      <c r="Q3" s="527" t="n"/>
+      <c r="Q3" s="528" t="n"/>
       <c r="R3" s="28" t="inlineStr">
         <is>
           <t>Sensoristica ERTMS-SCMT, Memor brush, ETCS antenna su carrelli ant. DM1/8
@@ -9074,7 +9008,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="S3" s="628" t="n"/>
+      <c r="S3" s="622" t="n"/>
       <c r="T3" s="29" t="inlineStr">
         <is>
           <t>Sala Montata</t>
@@ -9086,7 +9020,7 @@
           <t>tbd sensori boccola DM</t>
         </is>
       </c>
-      <c r="W3" s="586" t="inlineStr">
+      <c r="W3" s="577" t="inlineStr">
         <is>
           <t>DM: 100437987
 100470644</t>
@@ -9097,7 +9031,7 @@
           <t>Sala Montata</t>
         </is>
       </c>
-      <c r="Y3" s="527" t="n"/>
+      <c r="Y3" s="528" t="n"/>
       <c r="Z3" s="23" t="inlineStr">
         <is>
           <t>Sensoristica ETCS-ASFA-LZB carrelli DM</t>
@@ -9105,8 +9039,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="605" t="n"/>
-      <c r="C4" s="576" t="n"/>
+      <c r="A4" s="587" t="n"/>
+      <c r="C4" s="567" t="n"/>
       <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9116,7 +9050,7 @@
         <v>13900244911</v>
       </c>
       <c r="F4" s="35" t="n"/>
-      <c r="G4" s="576" t="n"/>
+      <c r="G4" s="567" t="n"/>
       <c r="H4" s="33" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9126,7 +9060,7 @@
         <v>13900244911</v>
       </c>
       <c r="J4" s="35" t="n"/>
-      <c r="K4" s="576" t="n"/>
+      <c r="K4" s="567" t="n"/>
       <c r="L4" s="36" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9136,7 +9070,7 @@
         <v>13900244911</v>
       </c>
       <c r="N4" s="38" t="n"/>
-      <c r="O4" s="576" t="n"/>
+      <c r="O4" s="567" t="n"/>
       <c r="P4" s="33" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9146,7 +9080,7 @@
         <v>13900244911</v>
       </c>
       <c r="R4" s="35" t="n"/>
-      <c r="S4" s="576" t="n"/>
+      <c r="S4" s="567" t="n"/>
       <c r="T4" s="40" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9156,7 +9090,7 @@
         <v>13900244911</v>
       </c>
       <c r="V4" s="42" t="n"/>
-      <c r="W4" s="576" t="n"/>
+      <c r="W4" s="567" t="n"/>
       <c r="X4" s="33" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9166,8 +9100,8 @@
       <c r="Z4" s="35" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="605" t="n"/>
-      <c r="C5" s="576" t="n"/>
+      <c r="A5" s="587" t="n"/>
+      <c r="C5" s="567" t="n"/>
       <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9179,7 +9113,7 @@
         </is>
       </c>
       <c r="F5" s="35" t="n"/>
-      <c r="G5" s="576" t="n"/>
+      <c r="G5" s="567" t="n"/>
       <c r="H5" s="33" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9191,7 +9125,7 @@
         </is>
       </c>
       <c r="J5" s="35" t="n"/>
-      <c r="K5" s="576" t="n"/>
+      <c r="K5" s="567" t="n"/>
       <c r="L5" s="36" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9203,7 +9137,7 @@
         </is>
       </c>
       <c r="N5" s="38" t="n"/>
-      <c r="O5" s="576" t="n"/>
+      <c r="O5" s="567" t="n"/>
       <c r="P5" s="33" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9215,7 +9149,7 @@
         </is>
       </c>
       <c r="R5" s="35" t="n"/>
-      <c r="S5" s="576" t="n"/>
+      <c r="S5" s="567" t="n"/>
       <c r="T5" s="40" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9227,7 +9161,7 @@
         </is>
       </c>
       <c r="V5" s="42" t="n"/>
-      <c r="W5" s="576" t="n"/>
+      <c r="W5" s="567" t="n"/>
       <c r="X5" s="33" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9236,9 +9170,9 @@
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="35" t="n"/>
     </row>
-    <row r="6" ht="87" customHeight="1" s="594">
-      <c r="A6" s="605" t="n"/>
-      <c r="C6" s="576" t="n"/>
+    <row r="6" ht="87" customHeight="1" s="592">
+      <c r="A6" s="587" t="n"/>
+      <c r="C6" s="567" t="n"/>
       <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9252,7 +9186,7 @@
         </is>
       </c>
       <c r="F6" s="35" t="n"/>
-      <c r="G6" s="576" t="n"/>
+      <c r="G6" s="567" t="n"/>
       <c r="H6" s="33" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9266,7 +9200,7 @@
         </is>
       </c>
       <c r="J6" s="35" t="n"/>
-      <c r="K6" s="576" t="n"/>
+      <c r="K6" s="567" t="n"/>
       <c r="L6" s="36" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9280,7 +9214,7 @@
         </is>
       </c>
       <c r="N6" s="38" t="n"/>
-      <c r="O6" s="576" t="n"/>
+      <c r="O6" s="567" t="n"/>
       <c r="P6" s="33" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9294,7 +9228,7 @@
         </is>
       </c>
       <c r="R6" s="35" t="n"/>
-      <c r="S6" s="576" t="n"/>
+      <c r="S6" s="567" t="n"/>
       <c r="T6" s="40" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9308,7 +9242,7 @@
         </is>
       </c>
       <c r="V6" s="42" t="n"/>
-      <c r="W6" s="576" t="n"/>
+      <c r="W6" s="567" t="n"/>
       <c r="X6" s="33" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9324,8 +9258,8 @@
       <c r="Z6" s="35" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="605" t="n"/>
-      <c r="C7" s="576" t="n"/>
+      <c r="A7" s="587" t="n"/>
+      <c r="C7" s="567" t="n"/>
       <c r="D7" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9337,7 +9271,7 @@
         </is>
       </c>
       <c r="F7" s="35" t="n"/>
-      <c r="G7" s="576" t="n"/>
+      <c r="G7" s="567" t="n"/>
       <c r="H7" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9349,7 +9283,7 @@
         </is>
       </c>
       <c r="J7" s="35" t="n"/>
-      <c r="K7" s="576" t="n"/>
+      <c r="K7" s="567" t="n"/>
       <c r="L7" s="36" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9361,7 +9295,7 @@
         </is>
       </c>
       <c r="N7" s="38" t="n"/>
-      <c r="O7" s="576" t="n"/>
+      <c r="O7" s="567" t="n"/>
       <c r="P7" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9373,7 +9307,7 @@
         </is>
       </c>
       <c r="R7" s="35" t="n"/>
-      <c r="S7" s="576" t="n"/>
+      <c r="S7" s="567" t="n"/>
       <c r="T7" s="40" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9385,7 +9319,7 @@
         </is>
       </c>
       <c r="V7" s="42" t="n"/>
-      <c r="W7" s="576" t="n"/>
+      <c r="W7" s="567" t="n"/>
       <c r="X7" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9395,9 +9329,9 @@
       <c r="Z7" s="35" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="605" t="n"/>
-      <c r="B8" s="538" t="n"/>
-      <c r="C8" s="587" t="n"/>
+      <c r="A8" s="587" t="n"/>
+      <c r="B8" s="539" t="n"/>
+      <c r="C8" s="578" t="n"/>
       <c r="D8" s="33" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9409,7 +9343,7 @@
           <t>Ephimess fase 2</t>
         </is>
       </c>
-      <c r="G8" s="587" t="n"/>
+      <c r="G8" s="578" t="n"/>
       <c r="H8" s="33" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9421,7 +9355,7 @@
           <t>Ephimess fase 2</t>
         </is>
       </c>
-      <c r="K8" s="587" t="n"/>
+      <c r="K8" s="578" t="n"/>
       <c r="L8" s="36" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9429,7 +9363,7 @@
       </c>
       <c r="M8" s="43" t="n"/>
       <c r="N8" s="38" t="n"/>
-      <c r="O8" s="587" t="n"/>
+      <c r="O8" s="578" t="n"/>
       <c r="P8" s="33" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9437,7 +9371,7 @@
       </c>
       <c r="Q8" s="44" t="n"/>
       <c r="R8" s="35" t="n"/>
-      <c r="S8" s="587" t="n"/>
+      <c r="S8" s="578" t="n"/>
       <c r="T8" s="40" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9445,7 +9379,7 @@
       </c>
       <c r="U8" s="45" t="n"/>
       <c r="V8" s="42" t="n"/>
-      <c r="W8" s="587" t="n"/>
+      <c r="W8" s="578" t="n"/>
       <c r="X8" s="33" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9454,14 +9388,14 @@
       <c r="Y8" s="1" t="n"/>
       <c r="Z8" s="35" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="594">
-      <c r="A9" s="605" t="n"/>
-      <c r="B9" s="611" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="592">
+      <c r="A9" s="587" t="n"/>
+      <c r="B9" s="602" t="inlineStr">
         <is>
           <t>Portanti</t>
         </is>
       </c>
-      <c r="C9" s="623" t="inlineStr">
+      <c r="C9" s="616" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -9480,7 +9414,7 @@
         </is>
       </c>
       <c r="F9" s="35" t="n"/>
-      <c r="G9" s="623" t="inlineStr">
+      <c r="G9" s="616" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -9499,7 +9433,7 @@
         </is>
       </c>
       <c r="J9" s="35" t="n"/>
-      <c r="K9" s="624" t="inlineStr">
+      <c r="K9" s="617" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -9519,7 +9453,7 @@
         </is>
       </c>
       <c r="N9" s="38" t="n"/>
-      <c r="O9" s="623" t="inlineStr">
+      <c r="O9" s="616" t="inlineStr">
         <is>
           <t>100360311
 100329690
@@ -9538,7 +9472,7 @@
         </is>
       </c>
       <c r="R9" s="35" t="n"/>
-      <c r="S9" s="585" t="n"/>
+      <c r="S9" s="576" t="n"/>
       <c r="T9" s="40" t="inlineStr">
         <is>
           <t>Sala</t>
@@ -9546,7 +9480,7 @@
       </c>
       <c r="U9" s="45" t="n"/>
       <c r="V9" s="42" t="n"/>
-      <c r="W9" s="599" t="n"/>
+      <c r="W9" s="600" t="n"/>
       <c r="X9" s="33" t="inlineStr">
         <is>
           <t>Sala</t>
@@ -9556,8 +9490,8 @@
       <c r="Z9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="605" t="n"/>
-      <c r="C10" s="576" t="n"/>
+      <c r="A10" s="587" t="n"/>
+      <c r="C10" s="567" t="n"/>
       <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9565,7 +9499,7 @@
       </c>
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="35" t="n"/>
-      <c r="G10" s="576" t="n"/>
+      <c r="G10" s="567" t="n"/>
       <c r="H10" s="33" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9573,7 +9507,7 @@
       </c>
       <c r="I10" s="1" t="n"/>
       <c r="J10" s="35" t="n"/>
-      <c r="K10" s="576" t="n"/>
+      <c r="K10" s="567" t="n"/>
       <c r="L10" s="36" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9581,7 +9515,7 @@
       </c>
       <c r="M10" s="43" t="n"/>
       <c r="N10" s="38" t="n"/>
-      <c r="O10" s="576" t="n"/>
+      <c r="O10" s="567" t="n"/>
       <c r="P10" s="33" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9589,7 +9523,7 @@
       </c>
       <c r="Q10" s="1" t="n"/>
       <c r="R10" s="35" t="n"/>
-      <c r="S10" s="576" t="n"/>
+      <c r="S10" s="567" t="n"/>
       <c r="T10" s="40" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9597,7 +9531,7 @@
       </c>
       <c r="U10" s="45" t="n"/>
       <c r="V10" s="42" t="n"/>
-      <c r="W10" s="576" t="n"/>
+      <c r="W10" s="567" t="n"/>
       <c r="X10" s="33" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9607,8 +9541,8 @@
       <c r="Z10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="605" t="n"/>
-      <c r="C11" s="576" t="n"/>
+      <c r="A11" s="587" t="n"/>
+      <c r="C11" s="567" t="n"/>
       <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9616,7 +9550,7 @@
       </c>
       <c r="E11" s="1" t="n"/>
       <c r="F11" s="35" t="n"/>
-      <c r="G11" s="576" t="n"/>
+      <c r="G11" s="567" t="n"/>
       <c r="H11" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9624,7 +9558,7 @@
       </c>
       <c r="I11" s="1" t="n"/>
       <c r="J11" s="35" t="n"/>
-      <c r="K11" s="576" t="n"/>
+      <c r="K11" s="567" t="n"/>
       <c r="L11" s="36" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9632,7 +9566,7 @@
       </c>
       <c r="M11" s="43" t="n"/>
       <c r="N11" s="38" t="n"/>
-      <c r="O11" s="576" t="n"/>
+      <c r="O11" s="567" t="n"/>
       <c r="P11" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9640,7 +9574,7 @@
       </c>
       <c r="Q11" s="1" t="n"/>
       <c r="R11" s="35" t="n"/>
-      <c r="S11" s="576" t="n"/>
+      <c r="S11" s="567" t="n"/>
       <c r="T11" s="40" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9648,7 +9582,7 @@
       </c>
       <c r="U11" s="45" t="n"/>
       <c r="V11" s="42" t="n"/>
-      <c r="W11" s="576" t="n"/>
+      <c r="W11" s="567" t="n"/>
       <c r="X11" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9657,10 +9591,10 @@
       <c r="Y11" s="1" t="n"/>
       <c r="Z11" s="35" t="n"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="A12" s="606" t="n"/>
-      <c r="B12" s="538" t="n"/>
-      <c r="C12" s="577" t="n"/>
+    <row r="12" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="A12" s="588" t="n"/>
+      <c r="B12" s="539" t="n"/>
+      <c r="C12" s="568" t="n"/>
       <c r="D12" s="52" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9668,7 +9602,7 @@
       </c>
       <c r="E12" s="53" t="n"/>
       <c r="F12" s="54" t="n"/>
-      <c r="G12" s="577" t="n"/>
+      <c r="G12" s="568" t="n"/>
       <c r="H12" s="52" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9676,7 +9610,7 @@
       </c>
       <c r="I12" s="53" t="n"/>
       <c r="J12" s="54" t="n"/>
-      <c r="K12" s="577" t="n"/>
+      <c r="K12" s="568" t="n"/>
       <c r="L12" s="55" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9684,7 +9618,7 @@
       </c>
       <c r="M12" s="56" t="n"/>
       <c r="N12" s="57" t="n"/>
-      <c r="O12" s="577" t="n"/>
+      <c r="O12" s="568" t="n"/>
       <c r="P12" s="52" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9692,7 +9626,7 @@
       </c>
       <c r="Q12" s="53" t="n"/>
       <c r="R12" s="54" t="n"/>
-      <c r="S12" s="577" t="n"/>
+      <c r="S12" s="568" t="n"/>
       <c r="T12" s="58" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9700,7 +9634,7 @@
       </c>
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60" t="n"/>
-      <c r="W12" s="577" t="n"/>
+      <c r="W12" s="568" t="n"/>
       <c r="X12" s="52" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9710,17 +9644,17 @@
       <c r="Z12" s="54" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="578" t="inlineStr">
+      <c r="A13" s="569" t="inlineStr">
         <is>
           <t>Pantografi</t>
         </is>
       </c>
-      <c r="B13" s="615" t="inlineStr">
+      <c r="B13" s="608" t="inlineStr">
         <is>
           <t>3 kV</t>
         </is>
       </c>
-      <c r="C13" s="590" t="n">
+      <c r="C13" s="581" t="n">
         <v>100170460</v>
       </c>
       <c r="D13" s="61" t="inlineStr">
@@ -9732,7 +9666,7 @@
         <v>10573076</v>
       </c>
       <c r="F13" s="63" t="n"/>
-      <c r="G13" s="589" t="n">
+      <c r="G13" s="580" t="n">
         <v>10949272</v>
       </c>
       <c r="H13" s="61" t="inlineStr">
@@ -9744,7 +9678,7 @@
         <v>10573076</v>
       </c>
       <c r="J13" s="63" t="n"/>
-      <c r="K13" s="589" t="n">
+      <c r="K13" s="580" t="n">
         <v>10949272</v>
       </c>
       <c r="L13" s="61" t="inlineStr">
@@ -9756,7 +9690,7 @@
         <v>10573076</v>
       </c>
       <c r="N13" s="63" t="n"/>
-      <c r="O13" s="590" t="n">
+      <c r="O13" s="581" t="n">
         <v>100170460</v>
       </c>
       <c r="P13" s="61" t="inlineStr">
@@ -9768,7 +9702,7 @@
         <v>10573076</v>
       </c>
       <c r="R13" s="63" t="n"/>
-      <c r="S13" s="617" t="n"/>
+      <c r="S13" s="613" t="n"/>
       <c r="T13" s="64" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9776,7 +9710,7 @@
       </c>
       <c r="U13" s="64" t="n"/>
       <c r="V13" s="65" t="n"/>
-      <c r="W13" s="590" t="n"/>
+      <c r="W13" s="581" t="n"/>
       <c r="X13" s="61" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9786,8 +9720,8 @@
       <c r="Z13" s="63" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="605" t="n"/>
-      <c r="C14" s="576" t="n"/>
+      <c r="A14" s="587" t="n"/>
+      <c r="C14" s="567" t="n"/>
       <c r="D14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9797,7 +9731,7 @@
         <v>10561136</v>
       </c>
       <c r="F14" s="35" t="n"/>
-      <c r="G14" s="576" t="n"/>
+      <c r="G14" s="567" t="n"/>
       <c r="H14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9807,7 +9741,7 @@
         <v>10561136</v>
       </c>
       <c r="J14" s="35" t="n"/>
-      <c r="K14" s="576" t="n"/>
+      <c r="K14" s="567" t="n"/>
       <c r="L14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9817,7 +9751,7 @@
         <v>10561136</v>
       </c>
       <c r="N14" s="35" t="n"/>
-      <c r="O14" s="576" t="n"/>
+      <c r="O14" s="567" t="n"/>
       <c r="P14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9827,7 +9761,7 @@
         <v>10561136</v>
       </c>
       <c r="R14" s="35" t="n"/>
-      <c r="S14" s="576" t="n"/>
+      <c r="S14" s="567" t="n"/>
       <c r="T14" s="45" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9835,7 +9769,7 @@
       </c>
       <c r="U14" s="45" t="n"/>
       <c r="V14" s="42" t="n"/>
-      <c r="W14" s="576" t="n"/>
+      <c r="W14" s="567" t="n"/>
       <c r="X14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9849,8 +9783,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="605" t="n"/>
-      <c r="C15" s="576" t="n"/>
+      <c r="A15" s="587" t="n"/>
+      <c r="C15" s="567" t="n"/>
       <c r="D15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9862,7 +9796,7 @@
         </is>
       </c>
       <c r="F15" s="35" t="n"/>
-      <c r="G15" s="576" t="n"/>
+      <c r="G15" s="567" t="n"/>
       <c r="H15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9874,7 +9808,7 @@
         </is>
       </c>
       <c r="J15" s="35" t="n"/>
-      <c r="K15" s="576" t="n"/>
+      <c r="K15" s="567" t="n"/>
       <c r="L15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9886,7 +9820,7 @@
         </is>
       </c>
       <c r="N15" s="35" t="n"/>
-      <c r="O15" s="576" t="n"/>
+      <c r="O15" s="567" t="n"/>
       <c r="P15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9898,7 +9832,7 @@
         </is>
       </c>
       <c r="R15" s="35" t="n"/>
-      <c r="S15" s="576" t="n"/>
+      <c r="S15" s="567" t="n"/>
       <c r="T15" s="45" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9906,7 +9840,7 @@
       </c>
       <c r="U15" s="45" t="n"/>
       <c r="V15" s="42" t="n"/>
-      <c r="W15" s="576" t="n"/>
+      <c r="W15" s="567" t="n"/>
       <c r="X15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9916,9 +9850,9 @@
       <c r="Z15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="605" t="n"/>
-      <c r="B16" s="538" t="n"/>
-      <c r="C16" s="587" t="n"/>
+      <c r="A16" s="587" t="n"/>
+      <c r="B16" s="539" t="n"/>
+      <c r="C16" s="578" t="n"/>
       <c r="D16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9928,7 +9862,7 @@
         <v>102895</v>
       </c>
       <c r="F16" s="35" t="n"/>
-      <c r="G16" s="587" t="n"/>
+      <c r="G16" s="578" t="n"/>
       <c r="H16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9944,7 +9878,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="K16" s="587" t="n"/>
+      <c r="K16" s="578" t="n"/>
       <c r="L16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9960,7 +9894,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="O16" s="587" t="n"/>
+      <c r="O16" s="578" t="n"/>
       <c r="P16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9976,7 +9910,7 @@
           <t>PPU DC Modificata per agg.panto 1.5</t>
         </is>
       </c>
-      <c r="S16" s="587" t="n"/>
+      <c r="S16" s="578" t="n"/>
       <c r="T16" s="45" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9984,7 +9918,7 @@
       </c>
       <c r="U16" s="45" t="n"/>
       <c r="V16" s="42" t="n"/>
-      <c r="W16" s="587" t="n"/>
+      <c r="W16" s="578" t="n"/>
       <c r="X16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9998,13 +9932,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="605" t="n"/>
-      <c r="B17" s="611" t="inlineStr">
+      <c r="A17" s="587" t="n"/>
+      <c r="B17" s="602" t="inlineStr">
         <is>
           <t>25 kV</t>
         </is>
       </c>
-      <c r="C17" s="588" t="n">
+      <c r="C17" s="579" t="n">
         <v>100170464</v>
       </c>
       <c r="D17" s="33" t="inlineStr">
@@ -10016,7 +9950,7 @@
         <v>10573076</v>
       </c>
       <c r="F17" s="35" t="n"/>
-      <c r="G17" s="610" t="n">
+      <c r="G17" s="601" t="n">
         <v>10949356</v>
       </c>
       <c r="H17" s="1" t="inlineStr">
@@ -10028,7 +9962,7 @@
         <v>10573076</v>
       </c>
       <c r="J17" s="35" t="n"/>
-      <c r="K17" s="610" t="n">
+      <c r="K17" s="601" t="n">
         <v>10949356</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -10040,7 +9974,7 @@
         <v>10573076</v>
       </c>
       <c r="N17" s="35" t="n"/>
-      <c r="O17" s="588" t="n">
+      <c r="O17" s="579" t="n">
         <v>100170464</v>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -10052,7 +9986,7 @@
         <v>10573076</v>
       </c>
       <c r="R17" s="35" t="n"/>
-      <c r="S17" s="603" t="n"/>
+      <c r="S17" s="585" t="n"/>
       <c r="T17" s="45" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10060,7 +9994,7 @@
       </c>
       <c r="U17" s="45" t="n"/>
       <c r="V17" s="42" t="n"/>
-      <c r="W17" s="588" t="n"/>
+      <c r="W17" s="579" t="n"/>
       <c r="X17" s="1" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10070,8 +10004,8 @@
       <c r="Z17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="605" t="n"/>
-      <c r="C18" s="576" t="n"/>
+      <c r="A18" s="587" t="n"/>
+      <c r="C18" s="567" t="n"/>
       <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10081,7 +10015,7 @@
         <v>10572700</v>
       </c>
       <c r="F18" s="35" t="n"/>
-      <c r="G18" s="576" t="n"/>
+      <c r="G18" s="567" t="n"/>
       <c r="H18" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10091,7 +10025,7 @@
         <v>10572700</v>
       </c>
       <c r="J18" s="35" t="n"/>
-      <c r="K18" s="576" t="n"/>
+      <c r="K18" s="567" t="n"/>
       <c r="L18" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10101,7 +10035,7 @@
         <v>10572700</v>
       </c>
       <c r="N18" s="35" t="n"/>
-      <c r="O18" s="576" t="n"/>
+      <c r="O18" s="567" t="n"/>
       <c r="P18" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10115,7 +10049,7 @@
           <t>Vedi strisciante</t>
         </is>
       </c>
-      <c r="S18" s="576" t="n"/>
+      <c r="S18" s="567" t="n"/>
       <c r="T18" s="45" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10123,7 +10057,7 @@
       </c>
       <c r="U18" s="45" t="n"/>
       <c r="V18" s="42" t="n"/>
-      <c r="W18" s="576" t="n"/>
+      <c r="W18" s="567" t="n"/>
       <c r="X18" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10133,8 +10067,8 @@
       <c r="Z18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="605" t="n"/>
-      <c r="C19" s="576" t="n"/>
+      <c r="A19" s="587" t="n"/>
+      <c r="C19" s="567" t="n"/>
       <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10146,7 +10080,7 @@
         </is>
       </c>
       <c r="F19" s="35" t="n"/>
-      <c r="G19" s="576" t="n"/>
+      <c r="G19" s="567" t="n"/>
       <c r="H19" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10158,7 +10092,7 @@
         </is>
       </c>
       <c r="J19" s="35" t="n"/>
-      <c r="K19" s="576" t="n"/>
+      <c r="K19" s="567" t="n"/>
       <c r="L19" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10170,7 +10104,7 @@
         </is>
       </c>
       <c r="N19" s="35" t="n"/>
-      <c r="O19" s="576" t="n"/>
+      <c r="O19" s="567" t="n"/>
       <c r="P19" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10186,7 +10120,7 @@
           <t>Conforme a norma FR SAM E903</t>
         </is>
       </c>
-      <c r="S19" s="576" t="n"/>
+      <c r="S19" s="567" t="n"/>
       <c r="T19" s="45" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10198,7 +10132,7 @@
         </is>
       </c>
       <c r="V19" s="42" t="n"/>
-      <c r="W19" s="576" t="n"/>
+      <c r="W19" s="567" t="n"/>
       <c r="X19" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10212,9 +10146,9 @@
       <c r="Z19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="605" t="n"/>
-      <c r="B20" s="538" t="n"/>
-      <c r="C20" s="587" t="n"/>
+      <c r="A20" s="587" t="n"/>
+      <c r="B20" s="539" t="n"/>
+      <c r="C20" s="578" t="n"/>
       <c r="D20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10224,7 +10158,7 @@
         <v>102895</v>
       </c>
       <c r="F20" s="35" t="n"/>
-      <c r="G20" s="587" t="n"/>
+      <c r="G20" s="578" t="n"/>
       <c r="H20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10240,7 +10174,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="K20" s="587" t="n"/>
+      <c r="K20" s="578" t="n"/>
       <c r="L20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10256,7 +10190,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="O20" s="587" t="n"/>
+      <c r="O20" s="578" t="n"/>
       <c r="P20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10266,7 +10200,7 @@
         <v>102895</v>
       </c>
       <c r="R20" s="35" t="n"/>
-      <c r="S20" s="587" t="n"/>
+      <c r="S20" s="578" t="n"/>
       <c r="T20" s="45" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10274,7 +10208,7 @@
       </c>
       <c r="U20" s="45" t="n"/>
       <c r="V20" s="42" t="n"/>
-      <c r="W20" s="587" t="n"/>
+      <c r="W20" s="578" t="n"/>
       <c r="X20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10288,13 +10222,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="605" t="n"/>
-      <c r="B21" s="611" t="inlineStr">
+      <c r="A21" s="587" t="n"/>
+      <c r="B21" s="602" t="inlineStr">
         <is>
           <t>1,5 kV</t>
         </is>
       </c>
-      <c r="C21" s="588" t="inlineStr">
+      <c r="C21" s="579" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10306,7 +10240,7 @@
       </c>
       <c r="E21" s="43" t="n"/>
       <c r="F21" s="38" t="n"/>
-      <c r="G21" s="588" t="inlineStr">
+      <c r="G21" s="579" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10318,7 +10252,7 @@
       </c>
       <c r="I21" s="43" t="n"/>
       <c r="J21" s="38" t="n"/>
-      <c r="K21" s="588" t="inlineStr">
+      <c r="K21" s="579" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10330,7 +10264,7 @@
       </c>
       <c r="M21" s="43" t="n"/>
       <c r="N21" s="38" t="n"/>
-      <c r="O21" s="610" t="n">
+      <c r="O21" s="601" t="n">
         <v>10851208</v>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -10342,7 +10276,7 @@
         <v>10573076</v>
       </c>
       <c r="R21" s="35" t="n"/>
-      <c r="S21" s="603" t="n"/>
+      <c r="S21" s="585" t="n"/>
       <c r="T21" s="45" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10350,7 +10284,7 @@
       </c>
       <c r="U21" s="45" t="n"/>
       <c r="V21" s="42" t="n"/>
-      <c r="W21" s="588" t="n"/>
+      <c r="W21" s="579" t="n"/>
       <c r="X21" s="1" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10360,8 +10294,8 @@
       <c r="Z21" s="38" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="605" t="n"/>
-      <c r="C22" s="576" t="n"/>
+      <c r="A22" s="587" t="n"/>
+      <c r="C22" s="567" t="n"/>
       <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10369,7 +10303,7 @@
       </c>
       <c r="E22" s="43" t="n"/>
       <c r="F22" s="38" t="n"/>
-      <c r="G22" s="576" t="n"/>
+      <c r="G22" s="567" t="n"/>
       <c r="H22" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10377,7 +10311,7 @@
       </c>
       <c r="I22" s="43" t="n"/>
       <c r="J22" s="38" t="n"/>
-      <c r="K22" s="576" t="n"/>
+      <c r="K22" s="567" t="n"/>
       <c r="L22" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10385,7 +10319,7 @@
       </c>
       <c r="M22" s="43" t="n"/>
       <c r="N22" s="38" t="n"/>
-      <c r="O22" s="576" t="n"/>
+      <c r="O22" s="567" t="n"/>
       <c r="P22" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10399,7 +10333,7 @@
           <t>Larghezza 1.950 mm</t>
         </is>
       </c>
-      <c r="S22" s="576" t="n"/>
+      <c r="S22" s="567" t="n"/>
       <c r="T22" s="45" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10407,7 +10341,7 @@
       </c>
       <c r="U22" s="45" t="n"/>
       <c r="V22" s="42" t="n"/>
-      <c r="W22" s="576" t="n"/>
+      <c r="W22" s="567" t="n"/>
       <c r="X22" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10417,8 +10351,8 @@
       <c r="Z22" s="38" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="605" t="n"/>
-      <c r="C23" s="576" t="n"/>
+      <c r="A23" s="587" t="n"/>
+      <c r="C23" s="567" t="n"/>
       <c r="D23" s="33" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10426,7 +10360,7 @@
       </c>
       <c r="E23" s="43" t="n"/>
       <c r="F23" s="38" t="n"/>
-      <c r="G23" s="576" t="n"/>
+      <c r="G23" s="567" t="n"/>
       <c r="H23" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10434,7 +10368,7 @@
       </c>
       <c r="I23" s="43" t="n"/>
       <c r="J23" s="38" t="n"/>
-      <c r="K23" s="576" t="n"/>
+      <c r="K23" s="567" t="n"/>
       <c r="L23" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10442,7 +10376,7 @@
       </c>
       <c r="M23" s="43" t="n"/>
       <c r="N23" s="38" t="n"/>
-      <c r="O23" s="576" t="n"/>
+      <c r="O23" s="567" t="n"/>
       <c r="P23" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10454,7 +10388,7 @@
         </is>
       </c>
       <c r="R23" s="35" t="n"/>
-      <c r="S23" s="576" t="n"/>
+      <c r="S23" s="567" t="n"/>
       <c r="T23" s="45" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10462,7 +10396,7 @@
       </c>
       <c r="U23" s="45" t="n"/>
       <c r="V23" s="42" t="n"/>
-      <c r="W23" s="576" t="n"/>
+      <c r="W23" s="567" t="n"/>
       <c r="X23" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10472,9 +10406,9 @@
       <c r="Z23" s="38" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="605" t="n"/>
-      <c r="B24" s="538" t="n"/>
-      <c r="C24" s="587" t="n"/>
+      <c r="A24" s="587" t="n"/>
+      <c r="B24" s="539" t="n"/>
+      <c r="C24" s="578" t="n"/>
       <c r="D24" s="33" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10482,7 +10416,7 @@
       </c>
       <c r="E24" s="43" t="n"/>
       <c r="F24" s="38" t="n"/>
-      <c r="G24" s="587" t="n"/>
+      <c r="G24" s="578" t="n"/>
       <c r="H24" s="1" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10490,7 +10424,7 @@
       </c>
       <c r="I24" s="43" t="n"/>
       <c r="J24" s="38" t="n"/>
-      <c r="K24" s="587" t="n"/>
+      <c r="K24" s="578" t="n"/>
       <c r="L24" s="1" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10498,7 +10432,7 @@
       </c>
       <c r="M24" s="43" t="n"/>
       <c r="N24" s="38" t="n"/>
-      <c r="O24" s="587" t="n"/>
+      <c r="O24" s="578" t="n"/>
       <c r="P24" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10514,7 +10448,7 @@
           <t>PPU Modificata per agg.panto 1.5</t>
         </is>
       </c>
-      <c r="S24" s="587" t="n"/>
+      <c r="S24" s="578" t="n"/>
       <c r="T24" s="45" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10522,7 +10456,7 @@
       </c>
       <c r="U24" s="45" t="n"/>
       <c r="V24" s="42" t="n"/>
-      <c r="W24" s="587" t="n"/>
+      <c r="W24" s="578" t="n"/>
       <c r="X24" s="1" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10532,13 +10466,13 @@
       <c r="Z24" s="38" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="605" t="n"/>
-      <c r="B25" s="611" t="inlineStr">
+      <c r="A25" s="587" t="n"/>
+      <c r="B25" s="602" t="inlineStr">
         <is>
           <t>15 kV</t>
         </is>
       </c>
-      <c r="C25" s="588" t="inlineStr">
+      <c r="C25" s="579" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10550,7 +10484,7 @@
       </c>
       <c r="E25" s="43" t="n"/>
       <c r="F25" s="38" t="n"/>
-      <c r="G25" s="588" t="inlineStr">
+      <c r="G25" s="579" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10562,7 +10496,7 @@
       </c>
       <c r="I25" s="43" t="n"/>
       <c r="J25" s="38" t="n"/>
-      <c r="K25" s="588" t="inlineStr">
+      <c r="K25" s="579" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10574,7 +10508,7 @@
       </c>
       <c r="M25" s="43" t="n"/>
       <c r="N25" s="38" t="n"/>
-      <c r="O25" s="575" t="n"/>
+      <c r="O25" s="566" t="n"/>
       <c r="P25" s="43" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10582,7 +10516,7 @@
       </c>
       <c r="Q25" s="43" t="n"/>
       <c r="R25" s="38" t="n"/>
-      <c r="S25" s="618" t="n"/>
+      <c r="S25" s="604" t="n"/>
       <c r="T25" s="45" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10590,7 +10524,7 @@
       </c>
       <c r="U25" s="45" t="n"/>
       <c r="V25" s="42" t="n"/>
-      <c r="W25" s="627" t="n"/>
+      <c r="W25" s="621" t="n"/>
       <c r="X25" s="1" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10600,8 +10534,8 @@
       <c r="Z25" s="38" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="605" t="n"/>
-      <c r="C26" s="576" t="n"/>
+      <c r="A26" s="587" t="n"/>
+      <c r="C26" s="567" t="n"/>
       <c r="D26" s="33" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10609,7 +10543,7 @@
       </c>
       <c r="E26" s="43" t="n"/>
       <c r="F26" s="38" t="n"/>
-      <c r="G26" s="576" t="n"/>
+      <c r="G26" s="567" t="n"/>
       <c r="H26" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10617,7 +10551,7 @@
       </c>
       <c r="I26" s="43" t="n"/>
       <c r="J26" s="38" t="n"/>
-      <c r="K26" s="576" t="n"/>
+      <c r="K26" s="567" t="n"/>
       <c r="L26" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10625,7 +10559,7 @@
       </c>
       <c r="M26" s="43" t="n"/>
       <c r="N26" s="38" t="n"/>
-      <c r="O26" s="576" t="n"/>
+      <c r="O26" s="567" t="n"/>
       <c r="P26" s="43" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10633,7 +10567,7 @@
       </c>
       <c r="Q26" s="43" t="n"/>
       <c r="R26" s="38" t="n"/>
-      <c r="S26" s="576" t="n"/>
+      <c r="S26" s="567" t="n"/>
       <c r="T26" s="45" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10641,7 +10575,7 @@
       </c>
       <c r="U26" s="45" t="n"/>
       <c r="V26" s="42" t="n"/>
-      <c r="W26" s="576" t="n"/>
+      <c r="W26" s="567" t="n"/>
       <c r="X26" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10651,8 +10585,8 @@
       <c r="Z26" s="38" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="605" t="n"/>
-      <c r="C27" s="576" t="n"/>
+      <c r="A27" s="587" t="n"/>
+      <c r="C27" s="567" t="n"/>
       <c r="D27" s="33" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10660,7 +10594,7 @@
       </c>
       <c r="E27" s="43" t="n"/>
       <c r="F27" s="38" t="n"/>
-      <c r="G27" s="576" t="n"/>
+      <c r="G27" s="567" t="n"/>
       <c r="H27" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10668,7 +10602,7 @@
       </c>
       <c r="I27" s="43" t="n"/>
       <c r="J27" s="38" t="n"/>
-      <c r="K27" s="576" t="n"/>
+      <c r="K27" s="567" t="n"/>
       <c r="L27" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10676,7 +10610,7 @@
       </c>
       <c r="M27" s="43" t="n"/>
       <c r="N27" s="38" t="n"/>
-      <c r="O27" s="576" t="n"/>
+      <c r="O27" s="567" t="n"/>
       <c r="P27" s="43" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10684,7 +10618,7 @@
       </c>
       <c r="Q27" s="43" t="n"/>
       <c r="R27" s="38" t="n"/>
-      <c r="S27" s="576" t="n"/>
+      <c r="S27" s="567" t="n"/>
       <c r="T27" s="45" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10692,7 +10626,7 @@
       </c>
       <c r="U27" s="45" t="n"/>
       <c r="V27" s="42" t="n"/>
-      <c r="W27" s="576" t="n"/>
+      <c r="W27" s="567" t="n"/>
       <c r="X27" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10701,10 +10635,10 @@
       <c r="Y27" s="43" t="n"/>
       <c r="Z27" s="38" t="n"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="A28" s="612" t="n"/>
-      <c r="B28" s="538" t="n"/>
-      <c r="C28" s="587" t="n"/>
+    <row r="28" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="A28" s="603" t="n"/>
+      <c r="B28" s="539" t="n"/>
+      <c r="C28" s="578" t="n"/>
       <c r="D28" s="52" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10712,7 +10646,7 @@
       </c>
       <c r="E28" s="56" t="n"/>
       <c r="F28" s="57" t="n"/>
-      <c r="G28" s="587" t="n"/>
+      <c r="G28" s="578" t="n"/>
       <c r="H28" s="53" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10720,7 +10654,7 @@
       </c>
       <c r="I28" s="56" t="n"/>
       <c r="J28" s="57" t="n"/>
-      <c r="K28" s="587" t="n"/>
+      <c r="K28" s="578" t="n"/>
       <c r="L28" s="53" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10728,7 +10662,7 @@
       </c>
       <c r="M28" s="56" t="n"/>
       <c r="N28" s="57" t="n"/>
-      <c r="O28" s="577" t="n"/>
+      <c r="O28" s="568" t="n"/>
       <c r="P28" s="56" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10736,7 +10670,7 @@
       </c>
       <c r="Q28" s="56" t="n"/>
       <c r="R28" s="57" t="n"/>
-      <c r="S28" s="577" t="n"/>
+      <c r="S28" s="568" t="n"/>
       <c r="T28" s="59" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10744,7 +10678,7 @@
       </c>
       <c r="U28" s="59" t="n"/>
       <c r="V28" s="60" t="n"/>
-      <c r="W28" s="577" t="n"/>
+      <c r="W28" s="568" t="n"/>
       <c r="X28" s="53" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10753,13 +10687,13 @@
       <c r="Y28" s="56" t="n"/>
       <c r="Z28" s="57" t="n"/>
     </row>
-    <row r="29" ht="101.45" customHeight="1" s="594">
-      <c r="A29" s="604" t="inlineStr">
+    <row r="29" ht="101.45" customHeight="1" s="592">
+      <c r="A29" s="586" t="inlineStr">
         <is>
           <t>TCMS Hardware</t>
         </is>
       </c>
-      <c r="B29" s="604" t="inlineStr">
+      <c r="B29" s="586" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
@@ -10794,12 +10728,12 @@
           <t>CCU-O</t>
         </is>
       </c>
-      <c r="M29" s="620" t="inlineStr">
+      <c r="M29" s="610" t="inlineStr">
         <is>
           <t>Nuova architettura Full Ethernet</t>
         </is>
       </c>
-      <c r="N29" s="582" t="n"/>
+      <c r="N29" s="573" t="n"/>
       <c r="O29" s="76" t="n"/>
       <c r="P29" s="77" t="inlineStr">
         <is>
@@ -10824,7 +10758,7 @@
         </is>
       </c>
       <c r="V29" s="63" t="n"/>
-      <c r="W29" s="78" t="n"/>
+      <c r="W29" s="550" t="n"/>
       <c r="X29" s="77" t="inlineStr">
         <is>
           <t>CCU-O</t>
@@ -10842,8 +10776,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="605" t="n"/>
-      <c r="B30" s="605" t="n"/>
+      <c r="A30" s="587" t="n"/>
+      <c r="B30" s="587" t="n"/>
       <c r="C30" s="80" t="n"/>
       <c r="D30" s="81" t="inlineStr">
         <is>
@@ -10874,8 +10808,8 @@
           <t>CCU-S</t>
         </is>
       </c>
-      <c r="M30" s="621" t="n"/>
-      <c r="N30" s="595" t="n"/>
+      <c r="M30" s="611" t="n"/>
+      <c r="N30" s="593" t="n"/>
       <c r="O30" s="80" t="n"/>
       <c r="P30" s="81" t="inlineStr">
         <is>
@@ -10900,7 +10834,7 @@
         </is>
       </c>
       <c r="V30" s="35" t="n"/>
-      <c r="W30" s="530" t="n"/>
+      <c r="W30" s="531" t="n"/>
       <c r="X30" s="81" t="inlineStr">
         <is>
           <t>CCU-S</t>
@@ -10913,9 +10847,9 @@
       </c>
       <c r="Z30" s="35" t="n"/>
     </row>
-    <row r="31" ht="144.6" customHeight="1" s="594">
-      <c r="A31" s="605" t="n"/>
-      <c r="B31" s="606" t="n"/>
+    <row r="31" ht="144.6" customHeight="1" s="592">
+      <c r="A31" s="587" t="n"/>
+      <c r="B31" s="588" t="n"/>
       <c r="C31" s="80" t="n"/>
       <c r="D31" s="82" t="inlineStr">
         <is>
@@ -10954,8 +10888,8 @@
           <t>MIO-S</t>
         </is>
       </c>
-      <c r="M31" s="621" t="n"/>
-      <c r="N31" s="595" t="n"/>
+      <c r="M31" s="611" t="n"/>
+      <c r="N31" s="593" t="n"/>
       <c r="O31" s="80" t="n"/>
       <c r="P31" s="82" t="inlineStr">
         <is>
@@ -10984,7 +10918,7 @@
         </is>
       </c>
       <c r="V31" s="35" t="n"/>
-      <c r="W31" s="530" t="n"/>
+      <c r="W31" s="531" t="n"/>
       <c r="X31" s="82" t="inlineStr">
         <is>
           <t>MIO-S</t>
@@ -11003,9 +10937,9 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="29.1" customHeight="1" s="594">
-      <c r="A32" s="605" t="n"/>
-      <c r="B32" s="629" t="inlineStr">
+    <row r="32" ht="29.1" customHeight="1" s="592">
+      <c r="A32" s="587" t="n"/>
+      <c r="B32" s="624" t="inlineStr">
         <is>
           <t>Teledia</t>
         </is>
@@ -11044,8 +10978,8 @@
           <t>MCG</t>
         </is>
       </c>
-      <c r="M32" s="621" t="n"/>
-      <c r="N32" s="595" t="n"/>
+      <c r="M32" s="611" t="n"/>
+      <c r="N32" s="593" t="n"/>
       <c r="O32" s="80" t="n"/>
       <c r="P32" s="82" t="inlineStr">
         <is>
@@ -11070,7 +11004,7 @@
         </is>
       </c>
       <c r="V32" s="35" t="n"/>
-      <c r="W32" s="530" t="n"/>
+      <c r="W32" s="531" t="n"/>
       <c r="X32" s="82" t="inlineStr">
         <is>
           <t>MCG</t>
@@ -11088,8 +11022,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="605" t="n"/>
-      <c r="B33" s="611" t="inlineStr">
+      <c r="A33" s="587" t="n"/>
+      <c r="B33" s="602" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
@@ -11124,8 +11058,8 @@
           <t>IDU/TOD</t>
         </is>
       </c>
-      <c r="M33" s="621" t="n"/>
-      <c r="N33" s="595" t="n"/>
+      <c r="M33" s="611" t="n"/>
+      <c r="N33" s="593" t="n"/>
       <c r="O33" s="80" t="n"/>
       <c r="P33" s="81" t="inlineStr">
         <is>
@@ -11150,7 +11084,7 @@
         </is>
       </c>
       <c r="V33" s="35" t="n"/>
-      <c r="W33" s="530" t="n"/>
+      <c r="W33" s="531" t="n"/>
       <c r="X33" s="81" t="inlineStr">
         <is>
           <t>IDU</t>
@@ -11163,9 +11097,9 @@
       </c>
       <c r="Z33" s="35" t="n"/>
     </row>
-    <row r="34" ht="14.45" customHeight="1" s="594">
-      <c r="A34" s="605" t="n"/>
-      <c r="B34" s="626" t="inlineStr">
+    <row r="34" ht="14.45" customHeight="1" s="592">
+      <c r="A34" s="587" t="n"/>
+      <c r="B34" s="620" t="inlineStr">
         <is>
           <t>Bus</t>
         </is>
@@ -11193,7 +11127,7 @@
           <t>3EST000236-6770</t>
         </is>
       </c>
-      <c r="J34" s="630" t="inlineStr">
+      <c r="J34" s="614" t="inlineStr">
         <is>
           <t>Sell no more supported for new projects due to internal component out of production (legacy only)</t>
         </is>
@@ -11204,8 +11138,8 @@
           <t>T Repeater</t>
         </is>
       </c>
-      <c r="M34" s="621" t="n"/>
-      <c r="N34" s="595" t="n"/>
+      <c r="M34" s="611" t="n"/>
+      <c r="N34" s="593" t="n"/>
       <c r="O34" s="80" t="n"/>
       <c r="P34" s="81" t="inlineStr">
         <is>
@@ -11230,7 +11164,7 @@
         </is>
       </c>
       <c r="V34" s="35" t="n"/>
-      <c r="W34" s="530" t="n"/>
+      <c r="W34" s="531" t="n"/>
       <c r="X34" s="81" t="inlineStr">
         <is>
           <t>T Repeater</t>
@@ -11241,15 +11175,15 @@
           <t>3EST000236-6770</t>
         </is>
       </c>
-      <c r="Z34" s="630" t="inlineStr">
+      <c r="Z34" s="614" t="inlineStr">
         <is>
           <t>Sell no more supported for new projects due to internal component out of production (legacy only)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="605" t="n"/>
-      <c r="B35" s="605" t="n"/>
+      <c r="A35" s="587" t="n"/>
+      <c r="B35" s="587" t="n"/>
       <c r="C35" s="80" t="n"/>
       <c r="D35" s="81" t="inlineStr">
         <is>
@@ -11273,15 +11207,15 @@
           <t>3EST000236-6769</t>
         </is>
       </c>
-      <c r="J35" s="631" t="n"/>
+      <c r="J35" s="615" t="n"/>
       <c r="K35" s="80" t="n"/>
       <c r="L35" s="81" t="inlineStr">
         <is>
           <t>T Switch</t>
         </is>
       </c>
-      <c r="M35" s="621" t="n"/>
-      <c r="N35" s="595" t="n"/>
+      <c r="M35" s="611" t="n"/>
+      <c r="N35" s="593" t="n"/>
       <c r="O35" s="80" t="n"/>
       <c r="P35" s="81" t="inlineStr">
         <is>
@@ -11306,7 +11240,7 @@
         </is>
       </c>
       <c r="V35" s="35" t="n"/>
-      <c r="W35" s="530" t="n"/>
+      <c r="W35" s="531" t="n"/>
       <c r="X35" s="81" t="inlineStr">
         <is>
           <t>T Switch</t>
@@ -11317,11 +11251,11 @@
           <t>3EST000236-6769</t>
         </is>
       </c>
-      <c r="Z35" s="631" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="A36" s="606" t="n"/>
-      <c r="B36" s="605" t="n"/>
+      <c r="Z35" s="615" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="A36" s="588" t="n"/>
+      <c r="B36" s="587" t="n"/>
       <c r="C36" s="89" t="n"/>
       <c r="D36" s="90" t="inlineStr">
         <is>
@@ -11345,15 +11279,15 @@
           <t>3EST000234-7837</t>
         </is>
       </c>
-      <c r="J36" s="631" t="n"/>
+      <c r="J36" s="615" t="n"/>
       <c r="K36" s="89" t="n"/>
       <c r="L36" s="90" t="inlineStr">
         <is>
           <t>R Switch</t>
         </is>
       </c>
-      <c r="M36" s="622" t="n"/>
-      <c r="N36" s="598" t="n"/>
+      <c r="M36" s="612" t="n"/>
+      <c r="N36" s="596" t="n"/>
       <c r="O36" s="89" t="n"/>
       <c r="P36" s="90" t="inlineStr">
         <is>
@@ -11378,7 +11312,7 @@
         </is>
       </c>
       <c r="V36" s="92" t="n"/>
-      <c r="W36" s="565" t="n"/>
+      <c r="W36" s="558" t="n"/>
       <c r="X36" s="90" t="inlineStr">
         <is>
           <t>R Switch</t>
@@ -11389,9 +11323,9 @@
           <t>3EST000234-7837</t>
         </is>
       </c>
-      <c r="Z36" s="631" t="n"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" s="594" thickBot="1">
+      <c r="Z36" s="615" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="A37" s="66" t="inlineStr">
         <is>
           <t>Energy Meter</t>
@@ -11402,62 +11336,62 @@
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C37" s="614" t="inlineStr">
+      <c r="C37" s="607" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D37" s="601" t="n"/>
-      <c r="E37" s="601" t="n"/>
-      <c r="F37" s="579" t="n"/>
-      <c r="G37" s="614" t="inlineStr">
+      <c r="D37" s="583" t="n"/>
+      <c r="E37" s="583" t="n"/>
+      <c r="F37" s="570" t="n"/>
+      <c r="G37" s="607" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H37" s="601" t="n"/>
-      <c r="I37" s="601" t="n"/>
-      <c r="J37" s="579" t="n"/>
-      <c r="K37" s="607" t="inlineStr">
+      <c r="H37" s="583" t="n"/>
+      <c r="I37" s="583" t="n"/>
+      <c r="J37" s="570" t="n"/>
+      <c r="K37" s="597" t="inlineStr">
         <is>
           <t>EMS Microelettrica  integrato con TCMS</t>
         </is>
       </c>
-      <c r="L37" s="601" t="n"/>
-      <c r="M37" s="601" t="n"/>
-      <c r="N37" s="579" t="n"/>
-      <c r="O37" s="607" t="inlineStr">
+      <c r="L37" s="583" t="n"/>
+      <c r="M37" s="583" t="n"/>
+      <c r="N37" s="570" t="n"/>
+      <c r="O37" s="597" t="inlineStr">
         <is>
           <t>EMS Microelettrica non integrato con TCMS</t>
         </is>
       </c>
-      <c r="P37" s="601" t="n"/>
-      <c r="Q37" s="601" t="n"/>
-      <c r="R37" s="579" t="n"/>
-      <c r="S37" s="607" t="inlineStr">
+      <c r="P37" s="583" t="n"/>
+      <c r="Q37" s="583" t="n"/>
+      <c r="R37" s="570" t="n"/>
+      <c r="S37" s="597" t="inlineStr">
         <is>
           <t>EMS Alstom  integrato con TCMS</t>
         </is>
       </c>
-      <c r="T37" s="601" t="n"/>
-      <c r="U37" s="601" t="n"/>
-      <c r="V37" s="579" t="n"/>
-      <c r="W37" s="607" t="inlineStr">
+      <c r="T37" s="583" t="n"/>
+      <c r="U37" s="583" t="n"/>
+      <c r="V37" s="570" t="n"/>
+      <c r="W37" s="597" t="inlineStr">
         <is>
           <t>EMS Alstom  integrato con TCMS</t>
         </is>
       </c>
-      <c r="X37" s="601" t="n"/>
-      <c r="Y37" s="601" t="n"/>
-      <c r="Z37" s="579" t="n"/>
-    </row>
-    <row r="38" ht="87" customHeight="1" s="594">
-      <c r="A38" s="604" t="inlineStr">
+      <c r="X37" s="583" t="n"/>
+      <c r="Y37" s="583" t="n"/>
+      <c r="Z37" s="570" t="n"/>
+    </row>
+    <row r="38" ht="87" customHeight="1" s="592">
+      <c r="A38" s="586" t="inlineStr">
         <is>
           <t>Freno</t>
         </is>
       </c>
-      <c r="B38" s="615" t="inlineStr">
+      <c r="B38" s="608" t="inlineStr">
         <is>
           <t>Centraline</t>
         </is>
@@ -11531,9 +11465,9 @@
       <c r="Y38" s="61" t="n"/>
       <c r="Z38" s="63" t="n"/>
     </row>
-    <row r="39" ht="101.45" customHeight="1" s="594">
-      <c r="A39" s="605" t="n"/>
-      <c r="B39" s="538" t="n"/>
+    <row r="39" ht="101.45" customHeight="1" s="592">
+      <c r="A39" s="587" t="n"/>
+      <c r="B39" s="539" t="n"/>
       <c r="C39" s="80" t="n"/>
       <c r="D39" s="33" t="inlineStr">
         <is>
@@ -11608,8 +11542,8 @@
       <c r="Z39" s="35" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="605" t="n"/>
-      <c r="B40" s="619" t="inlineStr">
+      <c r="A40" s="587" t="n"/>
+      <c r="B40" s="605" t="inlineStr">
         <is>
           <t>Pneumatica</t>
         </is>
@@ -11680,8 +11614,8 @@
       <c r="Z40" s="35" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="605" t="n"/>
-      <c r="B41" s="593" t="n"/>
+      <c r="A41" s="587" t="n"/>
+      <c r="B41" s="591" t="n"/>
       <c r="C41" s="80" t="n"/>
       <c r="D41" s="33" t="inlineStr">
         <is>
@@ -11747,9 +11681,9 @@
       <c r="Y41" s="1" t="n"/>
       <c r="Z41" s="35" t="n"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="A42" s="606" t="n"/>
-      <c r="B42" s="596" t="n"/>
+    <row r="42" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="A42" s="588" t="n"/>
+      <c r="B42" s="594" t="n"/>
       <c r="C42" s="89" t="n"/>
       <c r="D42" s="98" t="inlineStr">
         <is>
@@ -11848,194 +11782,194 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="604" t="inlineStr">
+      <c r="A43" s="586" t="inlineStr">
         <is>
           <t>PRM</t>
         </is>
       </c>
-      <c r="B43" s="615" t="inlineStr">
+      <c r="B43" s="608" t="inlineStr">
         <is>
           <t>Toilet</t>
         </is>
       </c>
-      <c r="C43" s="580" t="inlineStr">
+      <c r="C43" s="571" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="D43" s="581" t="n"/>
-      <c r="E43" s="581" t="n"/>
-      <c r="F43" s="582" t="n"/>
-      <c r="G43" s="580" t="inlineStr">
+      <c r="D43" s="572" t="n"/>
+      <c r="E43" s="572" t="n"/>
+      <c r="F43" s="573" t="n"/>
+      <c r="G43" s="571" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="H43" s="581" t="n"/>
-      <c r="I43" s="581" t="n"/>
-      <c r="J43" s="582" t="n"/>
-      <c r="K43" s="580" t="inlineStr">
+      <c r="H43" s="572" t="n"/>
+      <c r="I43" s="572" t="n"/>
+      <c r="J43" s="573" t="n"/>
+      <c r="K43" s="571" t="inlineStr">
         <is>
           <t>Toilet Production HK - conf. NRD Spagna + STI PRM 2019</t>
         </is>
       </c>
-      <c r="L43" s="581" t="n"/>
-      <c r="M43" s="581" t="n"/>
-      <c r="N43" s="582" t="n"/>
-      <c r="O43" s="580" t="inlineStr">
+      <c r="L43" s="572" t="n"/>
+      <c r="M43" s="572" t="n"/>
+      <c r="N43" s="573" t="n"/>
+      <c r="O43" s="571" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="P43" s="581" t="n"/>
-      <c r="Q43" s="581" t="n"/>
-      <c r="R43" s="582" t="n"/>
-      <c r="S43" s="580" t="inlineStr">
+      <c r="P43" s="572" t="n"/>
+      <c r="Q43" s="572" t="n"/>
+      <c r="R43" s="573" t="n"/>
+      <c r="S43" s="571" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="T43" s="581" t="n"/>
-      <c r="U43" s="581" t="n"/>
-      <c r="V43" s="582" t="n"/>
-      <c r="W43" s="580" t="inlineStr">
+      <c r="T43" s="572" t="n"/>
+      <c r="U43" s="572" t="n"/>
+      <c r="V43" s="573" t="n"/>
+      <c r="W43" s="571" t="inlineStr">
         <is>
           <t>Toilet Production HK - conf. NRD Spagna + STI PRM 2019</t>
         </is>
       </c>
-      <c r="X43" s="581" t="n"/>
-      <c r="Y43" s="581" t="n"/>
-      <c r="Z43" s="582" t="n"/>
+      <c r="X43" s="572" t="n"/>
+      <c r="Y43" s="572" t="n"/>
+      <c r="Z43" s="573" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="605" t="n"/>
-      <c r="B44" s="538" t="n"/>
-      <c r="C44" s="583" t="n"/>
-      <c r="D44" s="538" t="n"/>
-      <c r="E44" s="538" t="n"/>
-      <c r="F44" s="584" t="n"/>
-      <c r="G44" s="583" t="n"/>
-      <c r="H44" s="538" t="n"/>
-      <c r="I44" s="538" t="n"/>
-      <c r="J44" s="584" t="n"/>
-      <c r="K44" s="583" t="n"/>
-      <c r="L44" s="538" t="n"/>
-      <c r="M44" s="538" t="n"/>
-      <c r="N44" s="584" t="n"/>
-      <c r="O44" s="583" t="n"/>
-      <c r="P44" s="538" t="n"/>
-      <c r="Q44" s="538" t="n"/>
-      <c r="R44" s="584" t="n"/>
-      <c r="S44" s="583" t="n"/>
-      <c r="T44" s="538" t="n"/>
-      <c r="U44" s="538" t="n"/>
-      <c r="V44" s="584" t="n"/>
-      <c r="W44" s="583" t="n"/>
-      <c r="X44" s="538" t="n"/>
-      <c r="Y44" s="538" t="n"/>
-      <c r="Z44" s="584" t="n"/>
+      <c r="A44" s="587" t="n"/>
+      <c r="B44" s="539" t="n"/>
+      <c r="C44" s="574" t="n"/>
+      <c r="D44" s="539" t="n"/>
+      <c r="E44" s="539" t="n"/>
+      <c r="F44" s="575" t="n"/>
+      <c r="G44" s="574" t="n"/>
+      <c r="H44" s="539" t="n"/>
+      <c r="I44" s="539" t="n"/>
+      <c r="J44" s="575" t="n"/>
+      <c r="K44" s="574" t="n"/>
+      <c r="L44" s="539" t="n"/>
+      <c r="M44" s="539" t="n"/>
+      <c r="N44" s="575" t="n"/>
+      <c r="O44" s="574" t="n"/>
+      <c r="P44" s="539" t="n"/>
+      <c r="Q44" s="539" t="n"/>
+      <c r="R44" s="575" t="n"/>
+      <c r="S44" s="574" t="n"/>
+      <c r="T44" s="539" t="n"/>
+      <c r="U44" s="539" t="n"/>
+      <c r="V44" s="575" t="n"/>
+      <c r="W44" s="574" t="n"/>
+      <c r="X44" s="539" t="n"/>
+      <c r="Y44" s="539" t="n"/>
+      <c r="Z44" s="575" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="605" t="n"/>
-      <c r="B45" s="619" t="inlineStr">
+      <c r="A45" s="587" t="n"/>
+      <c r="B45" s="605" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="C45" s="609" t="inlineStr">
+      <c r="C45" s="599" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="D45" s="570" t="n"/>
-      <c r="E45" s="570" t="n"/>
-      <c r="F45" s="592" t="n"/>
-      <c r="G45" s="609" t="inlineStr">
+      <c r="D45" s="557" t="n"/>
+      <c r="E45" s="557" t="n"/>
+      <c r="F45" s="590" t="n"/>
+      <c r="G45" s="599" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="H45" s="570" t="n"/>
-      <c r="I45" s="570" t="n"/>
-      <c r="J45" s="592" t="n"/>
-      <c r="K45" s="591" t="inlineStr">
+      <c r="H45" s="557" t="n"/>
+      <c r="I45" s="557" t="n"/>
+      <c r="J45" s="590" t="n"/>
+      <c r="K45" s="589" t="inlineStr">
         <is>
           <t>Lift HK STI PRM 2019 (pedana più grande, azionamento elettrico)</t>
         </is>
       </c>
-      <c r="L45" s="570" t="n"/>
-      <c r="M45" s="570" t="n"/>
-      <c r="N45" s="592" t="n"/>
-      <c r="O45" s="609" t="inlineStr">
+      <c r="L45" s="557" t="n"/>
+      <c r="M45" s="557" t="n"/>
+      <c r="N45" s="590" t="n"/>
+      <c r="O45" s="599" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="P45" s="570" t="n"/>
-      <c r="Q45" s="570" t="n"/>
-      <c r="R45" s="592" t="n"/>
-      <c r="S45" s="609" t="inlineStr">
+      <c r="P45" s="557" t="n"/>
+      <c r="Q45" s="557" t="n"/>
+      <c r="R45" s="590" t="n"/>
+      <c r="S45" s="599" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="T45" s="570" t="n"/>
-      <c r="U45" s="570" t="n"/>
-      <c r="V45" s="592" t="n"/>
-      <c r="W45" s="591" t="inlineStr">
+      <c r="T45" s="557" t="n"/>
+      <c r="U45" s="557" t="n"/>
+      <c r="V45" s="590" t="n"/>
+      <c r="W45" s="589" t="inlineStr">
         <is>
           <t>Lift HK STI PRM 2019 (pedana più grande) azionamento idraulico</t>
         </is>
       </c>
-      <c r="X45" s="570" t="n"/>
-      <c r="Y45" s="570" t="n"/>
-      <c r="Z45" s="592" t="n"/>
+      <c r="X45" s="557" t="n"/>
+      <c r="Y45" s="557" t="n"/>
+      <c r="Z45" s="590" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="605" t="n"/>
-      <c r="B46" s="593" t="n"/>
-      <c r="C46" s="593" t="n"/>
-      <c r="F46" s="595" t="n"/>
-      <c r="G46" s="593" t="n"/>
-      <c r="J46" s="595" t="n"/>
-      <c r="K46" s="593" t="n"/>
-      <c r="N46" s="595" t="n"/>
-      <c r="O46" s="593" t="n"/>
-      <c r="R46" s="595" t="n"/>
-      <c r="S46" s="593" t="n"/>
-      <c r="V46" s="595" t="n"/>
-      <c r="W46" s="593" t="n"/>
-      <c r="Z46" s="595" t="n"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="A47" s="606" t="n"/>
-      <c r="B47" s="596" t="n"/>
-      <c r="C47" s="596" t="n"/>
-      <c r="D47" s="597" t="n"/>
-      <c r="E47" s="597" t="n"/>
-      <c r="F47" s="598" t="n"/>
-      <c r="G47" s="596" t="n"/>
-      <c r="H47" s="597" t="n"/>
-      <c r="I47" s="597" t="n"/>
-      <c r="J47" s="598" t="n"/>
-      <c r="K47" s="596" t="n"/>
-      <c r="L47" s="597" t="n"/>
-      <c r="M47" s="597" t="n"/>
-      <c r="N47" s="598" t="n"/>
-      <c r="O47" s="596" t="n"/>
-      <c r="P47" s="597" t="n"/>
-      <c r="Q47" s="597" t="n"/>
-      <c r="R47" s="598" t="n"/>
-      <c r="S47" s="596" t="n"/>
-      <c r="T47" s="597" t="n"/>
-      <c r="U47" s="597" t="n"/>
-      <c r="V47" s="598" t="n"/>
-      <c r="W47" s="596" t="n"/>
-      <c r="X47" s="597" t="n"/>
-      <c r="Y47" s="597" t="n"/>
-      <c r="Z47" s="598" t="n"/>
-    </row>
-    <row r="48" ht="29.45" customHeight="1" s="594" thickBot="1">
+      <c r="A46" s="587" t="n"/>
+      <c r="B46" s="591" t="n"/>
+      <c r="C46" s="591" t="n"/>
+      <c r="F46" s="593" t="n"/>
+      <c r="G46" s="591" t="n"/>
+      <c r="J46" s="593" t="n"/>
+      <c r="K46" s="591" t="n"/>
+      <c r="N46" s="593" t="n"/>
+      <c r="O46" s="591" t="n"/>
+      <c r="R46" s="593" t="n"/>
+      <c r="S46" s="591" t="n"/>
+      <c r="V46" s="593" t="n"/>
+      <c r="W46" s="591" t="n"/>
+      <c r="Z46" s="593" t="n"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="A47" s="588" t="n"/>
+      <c r="B47" s="594" t="n"/>
+      <c r="C47" s="594" t="n"/>
+      <c r="D47" s="595" t="n"/>
+      <c r="E47" s="595" t="n"/>
+      <c r="F47" s="596" t="n"/>
+      <c r="G47" s="594" t="n"/>
+      <c r="H47" s="595" t="n"/>
+      <c r="I47" s="595" t="n"/>
+      <c r="J47" s="596" t="n"/>
+      <c r="K47" s="594" t="n"/>
+      <c r="L47" s="595" t="n"/>
+      <c r="M47" s="595" t="n"/>
+      <c r="N47" s="596" t="n"/>
+      <c r="O47" s="594" t="n"/>
+      <c r="P47" s="595" t="n"/>
+      <c r="Q47" s="595" t="n"/>
+      <c r="R47" s="596" t="n"/>
+      <c r="S47" s="594" t="n"/>
+      <c r="T47" s="595" t="n"/>
+      <c r="U47" s="595" t="n"/>
+      <c r="V47" s="596" t="n"/>
+      <c r="W47" s="594" t="n"/>
+      <c r="X47" s="595" t="n"/>
+      <c r="Y47" s="595" t="n"/>
+      <c r="Z47" s="596" t="n"/>
+    </row>
+    <row r="48" ht="29.45" customHeight="1" s="592" thickBot="1">
       <c r="A48" s="100" t="inlineStr">
         <is>
           <t>Porte Esterne</t>
@@ -12046,58 +11980,58 @@
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C48" s="608" t="inlineStr">
+      <c r="C48" s="598" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="D48" s="601" t="n"/>
-      <c r="E48" s="601" t="n"/>
-      <c r="F48" s="579" t="n"/>
-      <c r="G48" s="608" t="inlineStr">
+      <c r="D48" s="583" t="n"/>
+      <c r="E48" s="583" t="n"/>
+      <c r="F48" s="570" t="n"/>
+      <c r="G48" s="598" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="H48" s="601" t="n"/>
-      <c r="I48" s="601" t="n"/>
-      <c r="J48" s="579" t="n"/>
-      <c r="K48" s="633" t="inlineStr">
+      <c r="H48" s="583" t="n"/>
+      <c r="I48" s="583" t="n"/>
+      <c r="J48" s="570" t="n"/>
+      <c r="K48" s="619" t="inlineStr">
         <is>
           <t>Porte esterne IFE TSI 2019
 Centralina Ethernet</t>
         </is>
       </c>
-      <c r="L48" s="601" t="n"/>
-      <c r="M48" s="601" t="n"/>
-      <c r="N48" s="579" t="n"/>
-      <c r="O48" s="608" t="inlineStr">
+      <c r="L48" s="583" t="n"/>
+      <c r="M48" s="583" t="n"/>
+      <c r="N48" s="570" t="n"/>
+      <c r="O48" s="598" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="P48" s="601" t="n"/>
-      <c r="Q48" s="601" t="n"/>
-      <c r="R48" s="579" t="n"/>
-      <c r="S48" s="608" t="inlineStr">
+      <c r="P48" s="583" t="n"/>
+      <c r="Q48" s="583" t="n"/>
+      <c r="R48" s="570" t="n"/>
+      <c r="S48" s="598" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="T48" s="601" t="n"/>
-      <c r="U48" s="601" t="n"/>
-      <c r="V48" s="579" t="n"/>
-      <c r="W48" s="632" t="inlineStr">
+      <c r="T48" s="583" t="n"/>
+      <c r="U48" s="583" t="n"/>
+      <c r="V48" s="570" t="n"/>
+      <c r="W48" s="623" t="inlineStr">
         <is>
           <t>Porte esterne IFE (TSI 2019)</t>
         </is>
       </c>
-      <c r="X48" s="601" t="n"/>
-      <c r="Y48" s="601" t="n"/>
-      <c r="Z48" s="579" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" s="594">
-      <c r="A49" s="578" t="inlineStr">
+      <c r="X48" s="583" t="n"/>
+      <c r="Y48" s="583" t="n"/>
+      <c r="Z48" s="570" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1" s="592">
+      <c r="A49" s="569" t="inlineStr">
         <is>
           <t>Antincendio</t>
         </is>
@@ -12108,110 +12042,110 @@
 Elettronica</t>
         </is>
       </c>
-      <c r="C49" s="580" t="inlineStr">
+      <c r="C49" s="571" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
-      <c r="D49" s="573" t="n"/>
-      <c r="E49" s="573" t="n"/>
-      <c r="F49" s="574" t="n"/>
-      <c r="G49" s="572" t="inlineStr">
+      <c r="D49" s="549" t="n"/>
+      <c r="E49" s="549" t="n"/>
+      <c r="F49" s="565" t="n"/>
+      <c r="G49" s="564" t="inlineStr">
         <is>
           <t>FDU-1000 (fornitura ISE)</t>
         </is>
       </c>
-      <c r="H49" s="573" t="n"/>
-      <c r="I49" s="573" t="n"/>
-      <c r="J49" s="574" t="n"/>
-      <c r="K49" s="572" t="inlineStr">
+      <c r="H49" s="549" t="n"/>
+      <c r="I49" s="549" t="n"/>
+      <c r="J49" s="565" t="n"/>
+      <c r="K49" s="564" t="inlineStr">
         <is>
           <t>FDU ISE</t>
         </is>
       </c>
-      <c r="L49" s="573" t="n"/>
-      <c r="M49" s="573" t="n"/>
-      <c r="N49" s="574" t="n"/>
-      <c r="O49" s="580" t="inlineStr">
+      <c r="L49" s="549" t="n"/>
+      <c r="M49" s="549" t="n"/>
+      <c r="N49" s="565" t="n"/>
+      <c r="O49" s="571" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
-      <c r="P49" s="573" t="n"/>
-      <c r="Q49" s="573" t="n"/>
-      <c r="R49" s="574" t="n"/>
-      <c r="S49" s="580" t="inlineStr">
+      <c r="P49" s="549" t="n"/>
+      <c r="Q49" s="549" t="n"/>
+      <c r="R49" s="565" t="n"/>
+      <c r="S49" s="571" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
-      <c r="T49" s="573" t="n"/>
-      <c r="U49" s="573" t="n"/>
-      <c r="V49" s="574" t="n"/>
-      <c r="W49" s="572" t="inlineStr">
+      <c r="T49" s="549" t="n"/>
+      <c r="U49" s="549" t="n"/>
+      <c r="V49" s="565" t="n"/>
+      <c r="W49" s="564" t="inlineStr">
         <is>
           <t>FDU-1000 (fornitura ISE)</t>
         </is>
       </c>
-      <c r="X49" s="573" t="n"/>
-      <c r="Y49" s="573" t="n"/>
-      <c r="Z49" s="574" t="n"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="A50" s="612" t="n"/>
+      <c r="X49" s="549" t="n"/>
+      <c r="Y49" s="549" t="n"/>
+      <c r="Z49" s="565" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="A50" s="603" t="n"/>
       <c r="B50" s="75" t="inlineStr">
         <is>
           <t>Estinzione</t>
         </is>
       </c>
-      <c r="C50" s="613" t="inlineStr">
+      <c r="C50" s="606" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="D50" s="597" t="n"/>
-      <c r="E50" s="597" t="n"/>
-      <c r="F50" s="598" t="n"/>
-      <c r="G50" s="616" t="inlineStr">
+      <c r="D50" s="595" t="n"/>
+      <c r="E50" s="595" t="n"/>
+      <c r="F50" s="596" t="n"/>
+      <c r="G50" s="609" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="H50" s="597" t="n"/>
-      <c r="I50" s="597" t="n"/>
-      <c r="J50" s="598" t="n"/>
-      <c r="K50" s="616" t="inlineStr">
+      <c r="H50" s="595" t="n"/>
+      <c r="I50" s="595" t="n"/>
+      <c r="J50" s="596" t="n"/>
+      <c r="K50" s="609" t="inlineStr">
         <is>
           <t>WaterMist Acquasys - 1 gruppo MAU (DM1)</t>
         </is>
       </c>
-      <c r="L50" s="597" t="n"/>
-      <c r="M50" s="597" t="n"/>
-      <c r="N50" s="598" t="n"/>
-      <c r="O50" s="613" t="inlineStr">
+      <c r="L50" s="595" t="n"/>
+      <c r="M50" s="595" t="n"/>
+      <c r="N50" s="596" t="n"/>
+      <c r="O50" s="606" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="P50" s="597" t="n"/>
-      <c r="Q50" s="597" t="n"/>
-      <c r="R50" s="598" t="n"/>
-      <c r="S50" s="613" t="inlineStr">
+      <c r="P50" s="595" t="n"/>
+      <c r="Q50" s="595" t="n"/>
+      <c r="R50" s="596" t="n"/>
+      <c r="S50" s="606" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="T50" s="597" t="n"/>
-      <c r="U50" s="597" t="n"/>
-      <c r="V50" s="598" t="n"/>
-      <c r="W50" s="613" t="inlineStr">
+      <c r="T50" s="595" t="n"/>
+      <c r="U50" s="595" t="n"/>
+      <c r="V50" s="596" t="n"/>
+      <c r="W50" s="606" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="X50" s="597" t="n"/>
-      <c r="Y50" s="597" t="n"/>
-      <c r="Z50" s="598" t="n"/>
+      <c r="X50" s="595" t="n"/>
+      <c r="Y50" s="595" t="n"/>
+      <c r="Z50" s="596" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="100">
@@ -12257,9 +12191,9 @@
     <mergeCell ref="Z34:Z36"/>
     <mergeCell ref="S13:S16"/>
     <mergeCell ref="C21:C24"/>
+    <mergeCell ref="K45:N47"/>
+    <mergeCell ref="B9:B12"/>
     <mergeCell ref="G48:J48"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="K45:N47"/>
     <mergeCell ref="C45:F47"/>
     <mergeCell ref="S48:V48"/>
     <mergeCell ref="J34:J36"/>
@@ -12335,11 +12269,11 @@
     <col width="28.42578125" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
     <col width="21.42578125" customWidth="1" style="13" min="5" max="5"/>
     <col width="35.5703125" customWidth="1" style="13" min="6" max="7"/>
-    <col width="8.7109375" customWidth="1" style="13" min="8" max="13"/>
-    <col width="8.7109375" customWidth="1" style="13" min="14" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="8" max="14"/>
+    <col width="8.7109375" customWidth="1" style="13" min="15" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="594">
+    <row r="1" ht="30" customHeight="1" s="592">
       <c r="A1" s="156" t="inlineStr">
         <is>
           <t>FUNC ID</t>
@@ -12350,18 +12284,18 @@
           <t>DESCRIZIONE FUNZIONE</t>
         </is>
       </c>
-      <c r="C1" s="525" t="inlineStr">
+      <c r="C1" s="526" t="inlineStr">
         <is>
           <t>DOC
 CARTELLA</t>
         </is>
       </c>
-      <c r="D1" s="525" t="inlineStr">
+      <c r="D1" s="526" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="E1" s="525" t="inlineStr">
+      <c r="E1" s="526" t="inlineStr">
         <is>
           <t>Info DOC</t>
         </is>
@@ -12418,7 +12352,7 @@
       </c>
       <c r="G3" s="314" t="n"/>
     </row>
-    <row r="4" ht="45" customHeight="1" s="594">
+    <row r="4" ht="45" customHeight="1" s="592">
       <c r="A4" s="103" t="inlineStr">
         <is>
           <t>Nel foglio indicato in Cx nella colonna B, cerca la riga corrispondente al DOC ID indicato in Dx</t>
@@ -12447,7 +12381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="594">
+    <row r="5" ht="45" customHeight="1" s="592">
       <c r="A5" s="103" t="inlineStr">
         <is>
           <t>Nel foglio CONFIG riga 1, cerca la colonna corrispondente alla flotta indicata da F1</t>
@@ -12473,7 +12407,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="594">
+    <row r="6" ht="45" customHeight="1" s="592">
       <c r="A6" s="103" t="inlineStr">
         <is>
           <t>Restituisci la posizione della cella corrispondente a riga/colonna sopra identificati</t>
@@ -12499,7 +12433,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="594">
+    <row r="7" ht="30" customHeight="1" s="592">
       <c r="A7" s="103" t="inlineStr">
         <is>
           <t>Alla posizione della cella, concatena il nome del foglio recuperato in Cx</t>
@@ -12525,7 +12459,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="594">
+    <row r="8" ht="60" customHeight="1" s="592">
       <c r="A8" s="103" t="inlineStr">
         <is>
           <t>Recupera il contenuto del foglio/cella indicato nell'indirizzo sopra, il quale corrisponde al nome del file archiviato</t>
@@ -12551,7 +12485,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="594">
+    <row r="9" ht="60" customHeight="1" s="592">
       <c r="A9" s="103" t="inlineStr">
         <is>
           <t>Recupera il prefisso del DOC ID posto prima del carattere "_", al quale corrisponde la sottocartella di archiviazione</t>
@@ -12577,7 +12511,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="165" customHeight="1" s="594">
+    <row r="10" ht="165" customHeight="1" s="592">
       <c r="A10" s="103" t="inlineStr">
         <is>
           <t>crea l'indirizzo completo per la costruzione del link, concatenando:
@@ -12615,7 +12549,7 @@
       <c r="D11" s="434" t="n"/>
       <c r="E11" s="435" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1" s="594">
+    <row r="12" ht="45" customHeight="1" s="592">
       <c r="A12" s="103" t="inlineStr">
         <is>
           <t>recupero del formato del file dal foglio indicato in Cx, alla riga indicata del DOC ID e colonna 3</t>
@@ -12645,7 +12579,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="594">
+    <row r="13" ht="60" customHeight="1" s="592">
       <c r="A13" s="103" t="inlineStr">
         <is>
           <t>crea l'indirizzo come sopra, inserendo anche la parte di recupero di estensione del file</t>
@@ -12659,7 +12593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="594">
+    <row r="14" ht="30" customHeight="1" s="592">
       <c r="A14" s="436" t="inlineStr">
         <is>
           <t>prova link con DOC Type &lt;&gt; pdf</t>
@@ -12691,7 +12625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="594">
+    <row r="17" ht="30" customHeight="1" s="592">
       <c r="A17" s="436" t="inlineStr">
         <is>
           <t>prova link con DOC Type &lt;&gt; pdf</t>
@@ -12740,7 +12674,7 @@
       <c r="F19" s="161" t="n"/>
       <c r="G19" s="161" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="594">
+    <row r="20" ht="30" customHeight="1" s="592">
       <c r="A20" s="106" t="inlineStr">
         <is>
           <t>parte iniziale - posizione cella foglio/flotta</t>
@@ -12940,12 +12874,12 @@
   <dimension ref="B2:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41.85546875" customWidth="1" style="594" min="2" max="2"/>
-    <col width="6.140625" bestFit="1" customWidth="1" style="594" min="7" max="7"/>
+    <col width="41.85546875" customWidth="1" style="592" min="2" max="2"/>
+    <col width="6.140625" bestFit="1" customWidth="1" style="592" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="594" thickBot="1"/>
-    <row r="2" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="592" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>VZI-50</t>
@@ -12976,13 +12910,13 @@
           <t>VZ-ES</t>
         </is>
       </c>
-      <c r="I2" s="579" t="inlineStr">
+      <c r="I2" s="570" t="inlineStr">
         <is>
           <t>VZ-DAI</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IPA (Indicazione Porte Aperte) </t>
@@ -13016,7 +12950,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30.75" customHeight="1" s="594" thickBot="1">
+    <row r="4" ht="30.75" customHeight="1" s="592" thickBot="1">
       <c r="B4" s="4" t="inlineStr">
         <is>
           <t>BY-PASS ALLARME APPLICAZIONE PARKING
@@ -13051,7 +12985,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>RIDONDANZA LOOP DNRA-BMS</t>
@@ -13085,7 +13019,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>INTERRUTTORI 220V SPOSTATI INTERNO CASSA</t>
@@ -13119,7 +13053,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>COMPRESSORE ARIA (?)</t>
@@ -13133,7 +13067,7 @@
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>BY-PASS ADD PER MARCIA SOCCORSO</t>
@@ -13167,7 +13101,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>ARREDI TOILET BAR BISTROT</t>
@@ -13181,7 +13115,7 @@
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="45.75" customHeight="1" s="594" thickBot="1">
+    <row r="10" ht="45.75" customHeight="1" s="592" thickBot="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>COMANDO DISACCOPPIAMENTO AUTOMATICO 
@@ -13216,7 +13150,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>PANTOGRAFI</t>
@@ -13230,13 +13164,13 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>PIANO DI MANUTENZIONE</t>
         </is>
       </c>
-      <c r="C12" s="530" t="n"/>
+      <c r="C12" s="531" t="n"/>
       <c r="D12" s="1" t="n"/>
       <c r="E12" s="1" t="n"/>
       <c r="F12" s="1" t="n"/>
@@ -13244,13 +13178,13 @@
       <c r="H12" s="1" t="n"/>
       <c r="I12" s="1" t="n"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="13" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>BL SSB</t>
         </is>
       </c>
-      <c r="C13" s="530" t="n"/>
+      <c r="C13" s="531" t="n"/>
       <c r="D13" s="1" t="n"/>
       <c r="E13" s="1" t="n"/>
       <c r="F13" s="1" t="n"/>
@@ -13258,13 +13192,13 @@
       <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="594" thickBot="1">
-      <c r="B14" s="612" t="inlineStr">
+    <row r="14" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="B14" s="603" t="inlineStr">
         <is>
           <t>BL DIS</t>
         </is>
       </c>
-      <c r="C14" s="530" t="n"/>
+      <c r="C14" s="531" t="n"/>
       <c r="D14" s="1" t="n"/>
       <c r="E14" s="1" t="n"/>
       <c r="F14" s="1" t="n"/>
@@ -13272,13 +13206,13 @@
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>ETCS HD (HW)</t>
         </is>
       </c>
-      <c r="C15" s="530" t="n"/>
+      <c r="C15" s="531" t="n"/>
       <c r="D15" s="1" t="n"/>
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="1" t="n"/>
@@ -13286,13 +13220,13 @@
       <c r="H15" s="1" t="n"/>
       <c r="I15" s="1" t="n"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANTINCENDIO </t>
         </is>
       </c>
-      <c r="C16" s="530" t="n"/>
+      <c r="C16" s="531" t="n"/>
       <c r="D16" s="1" t="n"/>
       <c r="E16" s="1" t="n"/>
       <c r="F16" s="1" t="n"/>
@@ -13300,7 +13234,7 @@
       <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="594" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="592" thickBot="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">LAYOUT INTERNO </t>
@@ -13341,8 +13275,8 @@
     <col width="8.7109375" customWidth="1" style="14" min="3" max="3"/>
     <col width="120.7109375" customWidth="1" style="103" min="4" max="4"/>
     <col width="60.140625" customWidth="1" style="103" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="13" min="6" max="11"/>
-    <col width="8.7109375" customWidth="1" style="13" min="12" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="6" max="12"/>
+    <col width="8.7109375" customWidth="1" style="13" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.45" customFormat="1" customHeight="1" s="192">
@@ -13372,7 +13306,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="594">
+    <row r="2" ht="30" customHeight="1" s="592">
       <c r="A2" s="308" t="n">
         <v>46190</v>
       </c>
@@ -13447,7 +13381,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="594">
+    <row r="5" ht="45" customHeight="1" s="592">
       <c r="A5" s="308" t="n">
         <v>46190</v>
       </c>
@@ -13497,7 +13431,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="594">
+    <row r="7" ht="45" customHeight="1" s="592">
       <c r="A7" s="308" t="n">
         <v>46189</v>
       </c>
@@ -13599,7 +13533,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="594">
+    <row r="11" ht="60" customHeight="1" s="592">
       <c r="A11" s="308" t="n">
         <v>46196</v>
       </c>
@@ -13625,7 +13559,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="105" customHeight="1" s="594">
+    <row r="12" ht="105" customHeight="1" s="592">
       <c r="A12" s="308" t="n">
         <v>46196</v>
       </c>
@@ -13650,7 +13584,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="594">
+    <row r="13" ht="30" customHeight="1" s="592">
       <c r="A13" s="308" t="n">
         <v>46197</v>
       </c>
@@ -13694,11 +13628,11 @@
     <col width="6.5703125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
     <col width="139.42578125" bestFit="1" customWidth="1" style="104" min="4" max="4"/>
     <col width="8.7109375" customWidth="1" style="14" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="13" min="6" max="11"/>
-    <col width="8.7109375" customWidth="1" style="13" min="12" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="6" max="12"/>
+    <col width="8.7109375" customWidth="1" style="13" min="13" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.6" customHeight="1" s="594">
+    <row r="1" ht="21.6" customHeight="1" s="592">
       <c r="A1" s="171" t="inlineStr">
         <is>
           <t>DESCRIZIONE</t>
@@ -13725,7 +13659,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="21.6" customHeight="1" s="594">
+    <row r="2" ht="21.6" customHeight="1" s="592">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Root Sharepoint</t>
@@ -13749,7 +13683,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="21.6" customHeight="1" s="594">
+    <row r="3" ht="21.6" customHeight="1" s="592">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Cartella Documenti Ingegneria</t>
@@ -13772,7 +13706,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="21.6" customHeight="1" s="594">
+    <row r="4" ht="21.6" customHeight="1" s="592">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Cartella Archiviazione doc ETR1000</t>
@@ -13795,7 +13729,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="21.6" customHeight="1" s="594">
+    <row r="5" ht="21.6" customHeight="1" s="592">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Documenti di configurazione</t>
@@ -13818,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="21.6" customHeight="1" s="594">
+    <row r="6" ht="21.6" customHeight="1" s="592">
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Raccolta documentazione Funzioni</t>
@@ -13841,17 +13775,17 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="21.95" customHeight="1" s="594"/>
-    <row r="8" ht="21.95" customHeight="1" s="594"/>
-    <row r="9" ht="21.95" customHeight="1" s="594"/>
-    <row r="10" ht="21.95" customHeight="1" s="594">
+    <row r="7" ht="21.95" customHeight="1" s="592"/>
+    <row r="8" ht="21.95" customHeight="1" s="592"/>
+    <row r="9" ht="21.95" customHeight="1" s="592"/>
+    <row r="10" ht="21.95" customHeight="1" s="592">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>VINCOLI</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="21.95" customHeight="1" s="594">
+    <row r="11" ht="21.95" customHeight="1" s="592">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Id Flotta</t>
@@ -13863,7 +13797,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="21.95" customHeight="1" s="594">
+    <row r="12" ht="21.95" customHeight="1" s="592">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>DOC ID</t>
@@ -13906,10 +13840,10 @@
   <dimension ref="A1:BW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.42578125" bestFit="1" customWidth="1" style="594" min="1" max="1"/>
-    <col width="17.5703125" customWidth="1" style="594" min="2" max="3"/>
-    <col width="15.42578125" customWidth="1" style="594" min="4" max="4"/>
-    <col width="15.140625" customWidth="1" style="594" min="5" max="5"/>
+    <col width="19.42578125" bestFit="1" customWidth="1" style="592" min="1" max="1"/>
+    <col width="17.5703125" customWidth="1" style="592" min="2" max="3"/>
+    <col width="15.42578125" customWidth="1" style="592" min="4" max="4"/>
+    <col width="15.140625" customWidth="1" style="592" min="5" max="5"/>
     <col width="11" customWidth="1" style="12" min="6" max="6"/>
     <col width="3.85546875" bestFit="1" customWidth="1" style="12" min="7" max="52"/>
     <col width="2.85546875" bestFit="1" customWidth="1" style="12" min="53" max="69"/>
@@ -15001,7 +14935,7 @@
       </c>
       <c r="D9" s="302" t="n"/>
       <c r="E9" s="303" t="n"/>
-      <c r="F9" s="609">
+      <c r="F9" s="599">
         <f>COUNTIF(G9:BW9,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -15119,145 +15053,145 @@
     <col width="6.5703125" customWidth="1" style="15" min="21" max="21"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="15" min="22" max="22"/>
     <col width="6.5703125" customWidth="1" style="15" min="23" max="23"/>
-    <col width="8.7109375" customWidth="1" style="103" min="24" max="29"/>
-    <col width="8.7109375" customWidth="1" style="103" min="30" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="24" max="30"/>
+    <col width="8.7109375" customWidth="1" style="103" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="105">
-      <c r="A1" s="525" t="inlineStr">
+      <c r="A1" s="526" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="533" t="inlineStr">
+      <c r="B1" s="534" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="525" t="inlineStr">
+      <c r="C1" s="526" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="531" t="inlineStr">
+      <c r="D1" s="532" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="529" t="n"/>
-      <c r="F1" s="530" t="n"/>
-      <c r="G1" s="540" t="inlineStr">
+      <c r="E1" s="530" t="n"/>
+      <c r="F1" s="531" t="n"/>
+      <c r="G1" s="541" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="H1" s="529" t="n"/>
-      <c r="I1" s="529" t="n"/>
-      <c r="J1" s="531" t="inlineStr">
+      <c r="H1" s="530" t="n"/>
+      <c r="I1" s="530" t="n"/>
+      <c r="J1" s="532" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="K1" s="529" t="n"/>
-      <c r="L1" s="530" t="n"/>
-      <c r="M1" s="537" t="inlineStr">
+      <c r="K1" s="530" t="n"/>
+      <c r="L1" s="531" t="n"/>
+      <c r="M1" s="538" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="N1" s="538" t="n"/>
-      <c r="O1" s="538" t="n"/>
-      <c r="P1" s="531" t="inlineStr">
+      <c r="N1" s="539" t="n"/>
+      <c r="O1" s="539" t="n"/>
+      <c r="P1" s="532" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="Q1" s="530" t="n"/>
-      <c r="R1" s="531" t="inlineStr">
+      <c r="Q1" s="531" t="n"/>
+      <c r="R1" s="532" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="S1" s="530" t="n"/>
-      <c r="T1" s="531" t="inlineStr">
+      <c r="S1" s="531" t="n"/>
+      <c r="T1" s="532" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="U1" s="530" t="n"/>
-      <c r="V1" s="531" t="inlineStr">
+      <c r="U1" s="531" t="n"/>
+      <c r="V1" s="532" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
         </is>
       </c>
-      <c r="W1" s="530" t="n"/>
+      <c r="W1" s="531" t="n"/>
     </row>
     <row r="2" ht="41.1" customFormat="1" customHeight="1" s="105">
-      <c r="A2" s="526" t="n"/>
-      <c r="B2" s="534" t="n"/>
-      <c r="C2" s="526" t="n"/>
-      <c r="D2" s="528" t="inlineStr">
+      <c r="A2" s="527" t="n"/>
+      <c r="B2" s="535" t="n"/>
+      <c r="C2" s="527" t="n"/>
+      <c r="D2" s="529" t="inlineStr">
         <is>
           <t>Doc BD130033980 - BL 6.0</t>
         </is>
       </c>
-      <c r="E2" s="529" t="n"/>
-      <c r="F2" s="530" t="n"/>
-      <c r="G2" s="532" t="inlineStr">
+      <c r="E2" s="530" t="n"/>
+      <c r="F2" s="531" t="n"/>
+      <c r="G2" s="533" t="inlineStr">
         <is>
           <t>BD140036813 - BL 4.2</t>
         </is>
       </c>
-      <c r="H2" s="529" t="n"/>
-      <c r="I2" s="529" t="n"/>
-      <c r="J2" s="528" t="inlineStr">
+      <c r="H2" s="530" t="n"/>
+      <c r="I2" s="530" t="n"/>
+      <c r="J2" s="529" t="inlineStr">
         <is>
           <t>3ECP414415-0001 - BL 4.0</t>
         </is>
       </c>
-      <c r="K2" s="529" t="n"/>
-      <c r="L2" s="530" t="n"/>
-      <c r="M2" s="539" t="inlineStr">
+      <c r="K2" s="530" t="n"/>
+      <c r="L2" s="531" t="n"/>
+      <c r="M2" s="540" t="inlineStr">
         <is>
           <t>VZ-ES Spagna
 BL 2.4</t>
         </is>
       </c>
-      <c r="N2" s="538" t="n"/>
-      <c r="O2" s="538" t="n"/>
-      <c r="P2" s="528" t="inlineStr">
+      <c r="N2" s="539" t="n"/>
+      <c r="O2" s="539" t="n"/>
+      <c r="P2" s="529" t="inlineStr">
         <is>
           <t>VZI-6_IT [R1]
 BL 4.0</t>
         </is>
       </c>
-      <c r="Q2" s="530" t="n"/>
-      <c r="R2" s="536" t="inlineStr">
+      <c r="Q2" s="531" t="n"/>
+      <c r="R2" s="537" t="inlineStr">
         <is>
           <t>VZI-4_IT [R1]
 BL 1.0</t>
         </is>
       </c>
-      <c r="S2" s="530" t="n"/>
-      <c r="T2" s="528" t="inlineStr">
+      <c r="S2" s="531" t="n"/>
+      <c r="T2" s="529" t="inlineStr">
         <is>
           <t>VZ-DAI
 BL xxx</t>
         </is>
       </c>
-      <c r="U2" s="530" t="n"/>
-      <c r="V2" s="528" t="inlineStr">
+      <c r="U2" s="531" t="n"/>
+      <c r="V2" s="529" t="inlineStr">
         <is>
           <t>VZ_ES Full HRI
 BL xxx</t>
         </is>
       </c>
-      <c r="W2" s="530" t="n"/>
+      <c r="W2" s="531" t="n"/>
     </row>
     <row r="3" ht="30" customFormat="1" customHeight="1" s="105">
-      <c r="A3" s="527" t="n"/>
-      <c r="B3" s="535" t="n"/>
-      <c r="C3" s="527" t="n"/>
+      <c r="A3" s="528" t="n"/>
+      <c r="B3" s="536" t="n"/>
+      <c r="C3" s="528" t="n"/>
       <c r="D3" s="152" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -15303,7 +15237,7 @@
           <t>Codice Config</t>
         </is>
       </c>
-      <c r="M3" s="532" t="inlineStr">
+      <c r="M3" s="533" t="inlineStr">
         <is>
           <t>File/Codice</t>
         </is>
@@ -15388,7 +15322,7 @@
       <c r="V4" s="443" t="n"/>
       <c r="W4" s="444" t="n"/>
     </row>
-    <row r="5" outlineLevel="1" s="594">
+    <row r="5" outlineLevel="1" s="592">
       <c r="A5" s="114" t="inlineStr">
         <is>
           <t>SW Config. Matrix</t>
@@ -15502,7 +15436,7 @@
       <c r="V6" s="446" t="n"/>
       <c r="W6" s="118" t="n"/>
     </row>
-    <row r="7" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="7" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Drive Control</t>
@@ -15585,7 +15519,7 @@
       <c r="U7" s="110" t="n"/>
       <c r="W7" s="110" t="n"/>
     </row>
-    <row r="8" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="8" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A8" s="114" t="inlineStr">
         <is>
           <t>Conventional Train Control</t>
@@ -15668,7 +15602,7 @@
       <c r="U8" s="110" t="n"/>
       <c r="W8" s="110" t="n"/>
     </row>
-    <row r="9" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="9" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A9" s="114" t="inlineStr">
         <is>
           <t>Train Protection - ATP</t>
@@ -15751,7 +15685,7 @@
       <c r="U9" s="110" t="n"/>
       <c r="W9" s="110" t="n"/>
     </row>
-    <row r="10" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="10" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A10" s="114" t="inlineStr">
         <is>
           <t>TCMS Architecture</t>
@@ -15834,7 +15768,7 @@
       <c r="U10" s="110" t="n"/>
       <c r="W10" s="110" t="n"/>
     </row>
-    <row r="11" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="11" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A11" s="114" t="inlineStr">
         <is>
           <t>Propulsion and Auxiliary</t>
@@ -15908,7 +15842,7 @@
       <c r="U11" s="110" t="n"/>
       <c r="W11" s="110" t="n"/>
     </row>
-    <row r="12" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="12" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A12" s="114" t="inlineStr">
         <is>
           <t>Line Voltage</t>
@@ -15991,7 +15925,7 @@
       <c r="U12" s="110" t="n"/>
       <c r="W12" s="110" t="n"/>
     </row>
-    <row r="13" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="13" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A13" s="114" t="inlineStr">
         <is>
           <t>Auxiliary Electrical Supply</t>
@@ -16074,7 +16008,7 @@
       <c r="U13" s="110" t="n"/>
       <c r="W13" s="110" t="n"/>
     </row>
-    <row r="14" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="14" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A14" s="114" t="inlineStr">
         <is>
           <t>Battery</t>
@@ -16157,7 +16091,7 @@
       <c r="U14" s="110" t="n"/>
       <c r="W14" s="110" t="n"/>
     </row>
-    <row r="15" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="15" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A15" s="114" t="inlineStr">
         <is>
           <t>Air Supply</t>
@@ -16240,7 +16174,7 @@
       <c r="U15" s="110" t="n"/>
       <c r="W15" s="110" t="n"/>
     </row>
-    <row r="16" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="16" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A16" s="114" t="inlineStr">
         <is>
           <t>Brake Control</t>
@@ -16323,7 +16257,7 @@
       <c r="U16" s="110" t="n"/>
       <c r="W16" s="110" t="n"/>
     </row>
-    <row r="17" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="17" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A17" s="114" t="inlineStr">
         <is>
           <t>Bogie</t>
@@ -16406,7 +16340,7 @@
       <c r="U17" s="110" t="n"/>
       <c r="W17" s="110" t="n"/>
     </row>
-    <row r="18" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="18" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A18" s="114" t="inlineStr">
         <is>
           <t>Wash Wiper</t>
@@ -16489,7 +16423,7 @@
       <c r="U18" s="110" t="n"/>
       <c r="W18" s="110" t="n"/>
     </row>
-    <row r="19" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="19" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A19" s="114" t="inlineStr">
         <is>
           <t>Windscreen heater</t>
@@ -16572,7 +16506,7 @@
       <c r="U19" s="110" t="n"/>
       <c r="W19" s="110" t="n"/>
     </row>
-    <row r="20" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="20" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A20" s="114" t="inlineStr">
         <is>
           <t>Automatic Coupler</t>
@@ -16655,7 +16589,7 @@
       <c r="U20" s="110" t="n"/>
       <c r="W20" s="110" t="n"/>
     </row>
-    <row r="21" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="21" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A21" s="114" t="inlineStr">
         <is>
           <t>Horn</t>
@@ -16738,7 +16672,7 @@
       <c r="U21" s="110" t="n"/>
       <c r="W21" s="110" t="n"/>
     </row>
-    <row r="22" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="22" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A22" s="114" t="inlineStr">
         <is>
           <t>Exterior and Interior Doors</t>
@@ -16821,7 +16755,7 @@
       <c r="U22" s="110" t="n"/>
       <c r="W22" s="110" t="n"/>
     </row>
-    <row r="23" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="23" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A23" s="114" t="inlineStr">
         <is>
           <t>Cab HVAC</t>
@@ -16904,7 +16838,7 @@
       <c r="U23" s="110" t="n"/>
       <c r="W23" s="110" t="n"/>
     </row>
-    <row r="24" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="24" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A24" s="114" t="inlineStr">
         <is>
           <t>Saloon HVAC</t>
@@ -16987,7 +16921,7 @@
       <c r="U24" s="110" t="n"/>
       <c r="W24" s="110" t="n"/>
     </row>
-    <row r="25" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="25" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A25" s="114" t="inlineStr">
         <is>
           <t>Fire Protection and Extinguishing</t>
@@ -17070,7 +17004,7 @@
       <c r="U25" s="110" t="n"/>
       <c r="W25" s="110" t="n"/>
     </row>
-    <row r="26" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="26" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A26" s="114" t="inlineStr">
         <is>
           <t>Toilet</t>
@@ -17153,7 +17087,7 @@
       <c r="U26" s="110" t="n"/>
       <c r="W26" s="110" t="n"/>
     </row>
-    <row r="27" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="27" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A27" s="114" t="inlineStr">
         <is>
           <t>Catering</t>
@@ -17236,7 +17170,7 @@
       <c r="U27" s="110" t="n"/>
       <c r="W27" s="110" t="n"/>
     </row>
-    <row r="28" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="28" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A28" s="114" t="inlineStr">
         <is>
           <t>PIS CCTV</t>
@@ -17319,7 +17253,7 @@
       <c r="U28" s="110" t="n"/>
       <c r="W28" s="110" t="n"/>
     </row>
-    <row r="29" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="29" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A29" s="114" t="inlineStr">
         <is>
           <t>Exterior Lighting</t>
@@ -17402,7 +17336,7 @@
       <c r="U29" s="110" t="n"/>
       <c r="W29" s="110" t="n"/>
     </row>
-    <row r="30" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="30" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A30" s="114" t="inlineStr">
         <is>
           <t>Interior Lighting</t>
@@ -17485,7 +17419,7 @@
       <c r="U30" s="110" t="n"/>
       <c r="W30" s="110" t="n"/>
     </row>
-    <row r="31" outlineLevel="1" s="594">
+    <row r="31" outlineLevel="1" s="592">
       <c r="A31" s="114" t="inlineStr">
         <is>
           <t>Train Control Design System</t>
@@ -17539,7 +17473,7 @@
       <c r="U31" s="110" t="n"/>
       <c r="W31" s="110" t="n"/>
     </row>
-    <row r="32" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="32" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A32" s="114" t="inlineStr">
         <is>
           <t>Schematic diagram for French ATP MU</t>
@@ -17584,7 +17518,7 @@
       <c r="U32" s="110" t="n"/>
       <c r="W32" s="110" t="n"/>
     </row>
-    <row r="33" outlineLevel="1" s="594">
+    <row r="33" outlineLevel="1" s="592">
       <c r="A33" s="438" t="inlineStr">
         <is>
           <t>Energy Meter System</t>
@@ -17625,7 +17559,7 @@
       <c r="U33" s="110" t="n"/>
       <c r="W33" s="110" t="n"/>
     </row>
-    <row r="34" ht="30" customHeight="1" s="594">
+    <row r="34" ht="30" customHeight="1" s="592">
       <c r="A34" s="445" t="inlineStr">
         <is>
           <t>Functional Requirement Specification (FRS)</t>
@@ -17654,7 +17588,7 @@
       <c r="V34" s="446" t="n"/>
       <c r="W34" s="118" t="n"/>
     </row>
-    <row r="35" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="35" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A35" s="114" t="inlineStr">
         <is>
           <t>Functional Vehicle Requirement Specification</t>
@@ -17723,7 +17657,7 @@
       <c r="U35" s="110" t="n"/>
       <c r="W35" s="110" t="n"/>
     </row>
-    <row r="36" outlineLevel="1" ht="60" customHeight="1" s="594">
+    <row r="36" outlineLevel="1" ht="60" customHeight="1" s="592">
       <c r="A36" s="114" t="inlineStr">
         <is>
           <t>Drive Control</t>
@@ -17816,7 +17750,7 @@
       <c r="U36" s="110" t="n"/>
       <c r="W36" s="110" t="n"/>
     </row>
-    <row r="37" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="37" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A37" s="114" t="inlineStr">
         <is>
           <t>Conventional Train Control</t>
@@ -17915,7 +17849,7 @@
       <c r="U37" s="110" t="n"/>
       <c r="W37" s="110" t="n"/>
     </row>
-    <row r="38" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="38" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A38" s="114" t="inlineStr">
         <is>
           <t>Train Protection - ATP</t>
@@ -18016,7 +17950,7 @@
       <c r="U38" s="110" t="n"/>
       <c r="W38" s="110" t="n"/>
     </row>
-    <row r="39" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="39" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A39" s="114" t="inlineStr">
         <is>
           <t>Diagnostics</t>
@@ -18115,7 +18049,7 @@
       <c r="U39" s="110" t="n"/>
       <c r="W39" s="110" t="n"/>
     </row>
-    <row r="40" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="40" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A40" s="114" t="inlineStr">
         <is>
           <t>Visualisation - MMI</t>
@@ -18214,7 +18148,7 @@
       <c r="U40" s="110" t="n"/>
       <c r="W40" s="110" t="n"/>
     </row>
-    <row r="41" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="41" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A41" s="114" t="inlineStr">
         <is>
           <t>TCMS - Operational</t>
@@ -18313,7 +18247,7 @@
       <c r="U41" s="110" t="n"/>
       <c r="W41" s="110" t="n"/>
     </row>
-    <row r="42" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="42" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A42" s="114" t="inlineStr">
         <is>
           <t>Train to Wayside Communication (Teledia)</t>
@@ -18412,7 +18346,7 @@
       <c r="U42" s="110" t="n"/>
       <c r="W42" s="110" t="n"/>
     </row>
-    <row r="43" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="43" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A43" s="114" t="inlineStr">
         <is>
           <t>Line Voltage</t>
@@ -18507,7 +18441,7 @@
       <c r="U43" s="110" t="n"/>
       <c r="W43" s="110" t="n"/>
     </row>
-    <row r="44" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="44" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A44" s="114" t="inlineStr">
         <is>
           <t>Aux Electrical Supply</t>
@@ -18602,7 +18536,7 @@
       <c r="U44" s="110" t="n"/>
       <c r="W44" s="110" t="n"/>
     </row>
-    <row r="45" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="45" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A45" s="114" t="inlineStr">
         <is>
           <t>Battery</t>
@@ -18701,7 +18635,7 @@
       <c r="U45" s="110" t="n"/>
       <c r="W45" s="110" t="n"/>
     </row>
-    <row r="46" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="46" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A46" s="114" t="inlineStr">
         <is>
           <t>Air Supply</t>
@@ -18800,7 +18734,7 @@
       <c r="U46" s="110" t="n"/>
       <c r="W46" s="110" t="n"/>
     </row>
-    <row r="47" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="47" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A47" s="114" t="inlineStr">
         <is>
           <t>Brake Control</t>
@@ -18895,7 +18829,7 @@
       <c r="U47" s="110" t="n"/>
       <c r="W47" s="110" t="n"/>
     </row>
-    <row r="48" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="48" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A48" s="114" t="inlineStr">
         <is>
           <t>Bogies</t>
@@ -18994,7 +18928,7 @@
       <c r="U48" s="110" t="n"/>
       <c r="W48" s="110" t="n"/>
     </row>
-    <row r="49" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="49" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A49" s="114" t="inlineStr">
         <is>
           <t>Wash Wiper</t>
@@ -19093,7 +19027,7 @@
       <c r="U49" s="110" t="n"/>
       <c r="W49" s="110" t="n"/>
     </row>
-    <row r="50" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="50" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A50" s="114" t="inlineStr">
         <is>
           <t>Windscreen</t>
@@ -19192,7 +19126,7 @@
       <c r="U50" s="110" t="n"/>
       <c r="W50" s="110" t="n"/>
     </row>
-    <row r="51" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="51" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A51" s="114" t="inlineStr">
         <is>
           <t>Coupler</t>
@@ -19291,7 +19225,7 @@
       <c r="U51" s="110" t="n"/>
       <c r="W51" s="110" t="n"/>
     </row>
-    <row r="52" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="52" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A52" s="114" t="inlineStr">
         <is>
           <t>Horn</t>
@@ -19390,7 +19324,7 @@
       <c r="U52" s="110" t="n"/>
       <c r="W52" s="110" t="n"/>
     </row>
-    <row r="53" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="53" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A53" s="114" t="inlineStr">
         <is>
           <t>Wheelchair Lifts</t>
@@ -19489,7 +19423,7 @@
       <c r="U53" s="110" t="n"/>
       <c r="W53" s="110" t="n"/>
     </row>
-    <row r="54" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="54" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A54" s="114" t="inlineStr">
         <is>
           <t>Exterior Door and Step Systems</t>
@@ -19588,7 +19522,7 @@
       <c r="U54" s="110" t="n"/>
       <c r="W54" s="110" t="n"/>
     </row>
-    <row r="55" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="55" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A55" s="114" t="inlineStr">
         <is>
           <t>Interior Doors</t>
@@ -19687,7 +19621,7 @@
       <c r="U55" s="110" t="n"/>
       <c r="W55" s="110" t="n"/>
     </row>
-    <row r="56" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="56" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A56" s="114" t="inlineStr">
         <is>
           <t>Cab HVAC</t>
@@ -19786,7 +19720,7 @@
       <c r="U56" s="110" t="n"/>
       <c r="W56" s="110" t="n"/>
     </row>
-    <row r="57" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="57" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A57" s="114" t="inlineStr">
         <is>
           <t>Saloon HVAC</t>
@@ -19885,7 +19819,7 @@
       <c r="U57" s="110" t="n"/>
       <c r="W57" s="110" t="n"/>
     </row>
-    <row r="58" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="58" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A58" s="114" t="inlineStr">
         <is>
           <t>Fire Protection and Extinction</t>
@@ -19984,7 +19918,7 @@
       <c r="U58" s="110" t="n"/>
       <c r="W58" s="110" t="n"/>
     </row>
-    <row r="59" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="59" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A59" s="114" t="inlineStr">
         <is>
           <t>Toilet</t>
@@ -20083,7 +20017,7 @@
       <c r="U59" s="110" t="n"/>
       <c r="W59" s="110" t="n"/>
     </row>
-    <row r="60" outlineLevel="1" s="594">
+    <row r="60" outlineLevel="1" s="592">
       <c r="A60" s="114" t="inlineStr">
         <is>
           <t>Catering - Bistrot</t>
@@ -20182,7 +20116,7 @@
       <c r="U60" s="110" t="n"/>
       <c r="W60" s="110" t="n"/>
     </row>
-    <row r="61" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="61" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A61" s="114" t="inlineStr">
         <is>
           <t>PIES</t>
@@ -20281,7 +20215,7 @@
       <c r="U61" s="110" t="n"/>
       <c r="W61" s="110" t="n"/>
     </row>
-    <row r="62" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="62" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A62" s="114" t="inlineStr">
         <is>
           <t>PIS 2.0</t>
@@ -20367,7 +20301,7 @@
       <c r="U62" s="110" t="n"/>
       <c r="W62" s="110" t="n"/>
     </row>
-    <row r="63" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="63" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A63" s="114" t="inlineStr">
         <is>
           <t>CCTV</t>
@@ -20462,7 +20396,7 @@
       <c r="U63" s="110" t="n"/>
       <c r="W63" s="110" t="n"/>
     </row>
-    <row r="64" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="64" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A64" s="114" t="inlineStr">
         <is>
           <t>Exterior Lighting</t>
@@ -20557,7 +20491,7 @@
       <c r="U64" s="110" t="n"/>
       <c r="W64" s="110" t="n"/>
     </row>
-    <row r="65" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="65" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A65" s="114" t="inlineStr">
         <is>
           <t>Interior Lighting</t>
@@ -20652,7 +20586,7 @@
       <c r="U65" s="110" t="n"/>
       <c r="W65" s="110" t="n"/>
     </row>
-    <row r="66" outlineLevel="1" s="594">
+    <row r="66" outlineLevel="1" s="592">
       <c r="A66" s="114" t="inlineStr">
         <is>
           <t>Train Protection - ATP (France)</t>
@@ -20693,7 +20627,7 @@
       <c r="U66" s="110" t="n"/>
       <c r="W66" s="110" t="n"/>
     </row>
-    <row r="67" outlineLevel="1" s="594">
+    <row r="67" outlineLevel="1" s="592">
       <c r="A67" s="438" t="inlineStr">
         <is>
           <t>Energy Meter System</t>
@@ -20776,7 +20710,7 @@
       <c r="V68" s="446" t="n"/>
       <c r="W68" s="118" t="n"/>
     </row>
-    <row r="69" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="69" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A69" s="114" t="inlineStr">
         <is>
           <t>Functional schematics DM1</t>
@@ -20859,7 +20793,7 @@
       <c r="U69" s="110" t="n"/>
       <c r="W69" s="110" t="n"/>
     </row>
-    <row r="70" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="70" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A70" s="114" t="inlineStr">
         <is>
           <t>Functional schematics TT2</t>
@@ -20942,7 +20876,7 @@
       <c r="U70" s="110" t="n"/>
       <c r="W70" s="110" t="n"/>
     </row>
-    <row r="71" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="71" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A71" s="114" t="inlineStr">
         <is>
           <t>Functional schematics M3</t>
@@ -21025,7 +20959,7 @@
       <c r="U71" s="110" t="n"/>
       <c r="W71" s="110" t="n"/>
     </row>
-    <row r="72" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="72" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A72" s="114" t="inlineStr">
         <is>
           <t>Functional schematics T4</t>
@@ -21108,7 +21042,7 @@
       <c r="U72" s="110" t="n"/>
       <c r="W72" s="110" t="n"/>
     </row>
-    <row r="73" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="73" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A73" s="114" t="inlineStr">
         <is>
           <t>Functional schematics T5</t>
@@ -21191,7 +21125,7 @@
       <c r="U73" s="110" t="n"/>
       <c r="W73" s="110" t="n"/>
     </row>
-    <row r="74" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="74" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A74" s="114" t="inlineStr">
         <is>
           <t>Functional schematics M6</t>
@@ -21274,7 +21208,7 @@
       <c r="U74" s="110" t="n"/>
       <c r="W74" s="110" t="n"/>
     </row>
-    <row r="75" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="75" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A75" s="114" t="inlineStr">
         <is>
           <t>Functional schematics TT7</t>
@@ -21357,7 +21291,7 @@
       <c r="U75" s="110" t="n"/>
       <c r="W75" s="110" t="n"/>
     </row>
-    <row r="76" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="76" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A76" s="114" t="inlineStr">
         <is>
           <t>Functional schematics DM8</t>
@@ -21440,7 +21374,7 @@
       <c r="U76" s="110" t="n"/>
       <c r="W76" s="110" t="n"/>
     </row>
-    <row r="77" ht="30" customHeight="1" s="594">
+    <row r="77" ht="30" customHeight="1" s="592">
       <c r="A77" s="445" t="inlineStr">
         <is>
           <t>Wiring table</t>
@@ -21485,7 +21419,7 @@
       <c r="V77" s="446" t="n"/>
       <c r="W77" s="118" t="n"/>
     </row>
-    <row r="78" outlineLevel="1" s="594">
+    <row r="78" outlineLevel="1" s="592">
       <c r="A78" s="114" t="inlineStr">
         <is>
           <t>Wiring table DM1</t>
@@ -21550,7 +21484,7 @@
       <c r="U78" s="110" t="n"/>
       <c r="W78" s="110" t="n"/>
     </row>
-    <row r="79" outlineLevel="1" s="594">
+    <row r="79" outlineLevel="1" s="592">
       <c r="A79" s="114" t="inlineStr">
         <is>
           <t>Wiring table TT2</t>
@@ -21615,7 +21549,7 @@
       <c r="U79" s="110" t="n"/>
       <c r="W79" s="110" t="n"/>
     </row>
-    <row r="80" outlineLevel="1" s="594">
+    <row r="80" outlineLevel="1" s="592">
       <c r="A80" s="114" t="inlineStr">
         <is>
           <t>Wiring table M3</t>
@@ -21680,7 +21614,7 @@
       <c r="U80" s="110" t="n"/>
       <c r="W80" s="110" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" s="594">
+    <row r="81" outlineLevel="1" s="592">
       <c r="A81" s="114" t="inlineStr">
         <is>
           <t>Wiring table T4</t>
@@ -21745,7 +21679,7 @@
       <c r="U81" s="110" t="n"/>
       <c r="W81" s="110" t="n"/>
     </row>
-    <row r="82" outlineLevel="1" s="594">
+    <row r="82" outlineLevel="1" s="592">
       <c r="A82" s="114" t="inlineStr">
         <is>
           <t>Wiring table T5</t>
@@ -21810,7 +21744,7 @@
       <c r="U82" s="110" t="n"/>
       <c r="W82" s="110" t="n"/>
     </row>
-    <row r="83" outlineLevel="1" s="594">
+    <row r="83" outlineLevel="1" s="592">
       <c r="A83" s="114" t="inlineStr">
         <is>
           <t>Wiring table M6</t>
@@ -21875,7 +21809,7 @@
       <c r="U83" s="110" t="n"/>
       <c r="W83" s="110" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" s="594">
+    <row r="84" outlineLevel="1" s="592">
       <c r="A84" s="114" t="inlineStr">
         <is>
           <t>Wiring table TT7</t>
@@ -21940,7 +21874,7 @@
       <c r="U84" s="110" t="n"/>
       <c r="W84" s="110" t="n"/>
     </row>
-    <row r="85" outlineLevel="1" s="594">
+    <row r="85" outlineLevel="1" s="592">
       <c r="A85" s="114" t="inlineStr">
         <is>
           <t>Wiring table DM8</t>
@@ -22034,7 +21968,7 @@
       <c r="V86" s="446" t="n"/>
       <c r="W86" s="118" t="n"/>
     </row>
-    <row r="87" outlineLevel="1" s="594">
+    <row r="87" outlineLevel="1" s="592">
       <c r="A87" s="114" t="inlineStr">
         <is>
           <t>Electric Part List DM1</t>
@@ -22099,7 +22033,7 @@
       <c r="U87" s="110" t="n"/>
       <c r="W87" s="110" t="n"/>
     </row>
-    <row r="88" outlineLevel="1" s="594">
+    <row r="88" outlineLevel="1" s="592">
       <c r="A88" s="114" t="inlineStr">
         <is>
           <t>Electric Part List TT2</t>
@@ -22164,7 +22098,7 @@
       <c r="U88" s="110" t="n"/>
       <c r="W88" s="110" t="n"/>
     </row>
-    <row r="89" outlineLevel="1" s="594">
+    <row r="89" outlineLevel="1" s="592">
       <c r="A89" s="114" t="inlineStr">
         <is>
           <t>Electric Part List M3</t>
@@ -22229,7 +22163,7 @@
       <c r="U89" s="110" t="n"/>
       <c r="W89" s="110" t="n"/>
     </row>
-    <row r="90" outlineLevel="1" s="594">
+    <row r="90" outlineLevel="1" s="592">
       <c r="A90" s="114" t="inlineStr">
         <is>
           <t>Electric Part List T4</t>
@@ -22294,7 +22228,7 @@
       <c r="U90" s="110" t="n"/>
       <c r="W90" s="110" t="n"/>
     </row>
-    <row r="91" outlineLevel="1" s="594">
+    <row r="91" outlineLevel="1" s="592">
       <c r="A91" s="114" t="inlineStr">
         <is>
           <t>Electric Part List T5</t>
@@ -22359,7 +22293,7 @@
       <c r="U91" s="110" t="n"/>
       <c r="W91" s="110" t="n"/>
     </row>
-    <row r="92" outlineLevel="1" s="594">
+    <row r="92" outlineLevel="1" s="592">
       <c r="A92" s="114" t="inlineStr">
         <is>
           <t>Electric Part List M6</t>
@@ -22424,7 +22358,7 @@
       <c r="U92" s="110" t="n"/>
       <c r="W92" s="110" t="n"/>
     </row>
-    <row r="93" outlineLevel="1" s="594">
+    <row r="93" outlineLevel="1" s="592">
       <c r="A93" s="114" t="inlineStr">
         <is>
           <t>Electric Part List TT7</t>
@@ -22489,7 +22423,7 @@
       <c r="U93" s="110" t="n"/>
       <c r="W93" s="110" t="n"/>
     </row>
-    <row r="94" outlineLevel="1" s="594">
+    <row r="94" outlineLevel="1" s="592">
       <c r="A94" s="114" t="inlineStr">
         <is>
           <t>Electric Part List DM8</t>
@@ -22587,7 +22521,7 @@
       <c r="V95" s="446" t="n"/>
       <c r="W95" s="118" t="n"/>
     </row>
-    <row r="96" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="96" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A96" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema TCMS</t>
@@ -22647,7 +22581,7 @@
       <c r="U96" s="110" t="n"/>
       <c r="W96" s="110" t="n"/>
     </row>
-    <row r="97" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="97" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A97" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema TCMS - Annex</t>
@@ -22698,7 +22632,7 @@
       <c r="U97" s="110" t="n"/>
       <c r="W97" s="110" t="n"/>
     </row>
-    <row r="98" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="98" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A98" s="114" t="inlineStr">
         <is>
           <t>ICD GTW IPTCOM-TRDP</t>
@@ -22753,7 +22687,7 @@
       <c r="U98" s="110" t="n"/>
       <c r="W98" s="110" t="n"/>
     </row>
-    <row r="99" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="99" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A99" s="114" t="inlineStr">
         <is>
           <t>ICD GTW IPTCOM-TRDP - Annex</t>
@@ -22804,7 +22738,7 @@
       <c r="U99" s="110" t="n"/>
       <c r="W99" s="110" t="n"/>
     </row>
-    <row r="100" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="100" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A100" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Propulsion TCU</t>
@@ -22864,7 +22798,7 @@
       <c r="U100" s="110" t="n"/>
       <c r="W100" s="110" t="n"/>
     </row>
-    <row r="101" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="101" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A101" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Propulsion TCU - Annex</t>
@@ -22915,7 +22849,7 @@
       <c r="U101" s="110" t="n"/>
       <c r="W101" s="110" t="n"/>
     </row>
-    <row r="102" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="102" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A102" s="114" t="inlineStr">
         <is>
           <t>ICD Pantografo</t>
@@ -22975,7 +22909,7 @@
       <c r="U102" s="110" t="n"/>
       <c r="W102" s="110" t="n"/>
     </row>
-    <row r="103" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="103" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A103" s="114" t="inlineStr">
         <is>
           <t>ICD Pantografo - Annex</t>
@@ -23026,7 +22960,7 @@
       <c r="U103" s="110" t="n"/>
       <c r="W103" s="110" t="n"/>
     </row>
-    <row r="104" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="104" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A104" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema BCU</t>
@@ -23086,7 +23020,7 @@
       <c r="U104" s="110" t="n"/>
       <c r="W104" s="110" t="n"/>
     </row>
-    <row r="105" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="105" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A105" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema BCU - Annex</t>
@@ -23141,7 +23075,7 @@
       <c r="U105" s="110" t="n"/>
       <c r="W105" s="110" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="106" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A106" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Segnalamento</t>
@@ -23196,7 +23130,7 @@
       <c r="U106" s="110" t="n"/>
       <c r="W106" s="110" t="n"/>
     </row>
-    <row r="107" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="107" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A107" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Segnalamento - Annex</t>
@@ -23247,7 +23181,7 @@
       <c r="U107" s="110" t="n"/>
       <c r="W107" s="110" t="n"/>
     </row>
-    <row r="108" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="108" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A108" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema PIS</t>
@@ -23307,7 +23241,7 @@
       <c r="U108" s="110" t="n"/>
       <c r="W108" s="110" t="n"/>
     </row>
-    <row r="109" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="109" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A109" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema PIS - Annex</t>
@@ -23358,7 +23292,7 @@
       <c r="U109" s="110" t="n"/>
       <c r="W109" s="110" t="n"/>
     </row>
-    <row r="110" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="110" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A110" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Toilette</t>
@@ -23418,7 +23352,7 @@
       <c r="U110" s="110" t="n"/>
       <c r="W110" s="110" t="n"/>
     </row>
-    <row r="111" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="111" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A111" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Toilette - Annex</t>
@@ -23469,7 +23403,7 @@
       <c r="U111" s="110" t="n"/>
       <c r="W111" s="110" t="n"/>
     </row>
-    <row r="112" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="112" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A112" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Anticendio</t>
@@ -23529,7 +23463,7 @@
       <c r="U112" s="110" t="n"/>
       <c r="W112" s="110" t="n"/>
     </row>
-    <row r="113" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="113" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A113" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Anticendio - Annex</t>
@@ -23580,7 +23514,7 @@
       <c r="U113" s="110" t="n"/>
       <c r="W113" s="110" t="n"/>
     </row>
-    <row r="114" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="114" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A114" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Porte</t>
@@ -23640,7 +23574,7 @@
       <c r="U114" s="110" t="n"/>
       <c r="W114" s="110" t="n"/>
     </row>
-    <row r="115" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="115" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A115" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Porte - Annex</t>
@@ -23691,7 +23625,7 @@
       <c r="U115" s="110" t="n"/>
       <c r="W115" s="110" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="116" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A116" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema HVSP</t>
@@ -23746,7 +23680,7 @@
       <c r="U116" s="110" t="n"/>
       <c r="W116" s="110" t="n"/>
     </row>
-    <row r="117" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="117" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A117" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema HVSP  - Annex</t>
@@ -23797,7 +23731,7 @@
       <c r="U117" s="110" t="n"/>
       <c r="W117" s="110" t="n"/>
     </row>
-    <row r="118" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="118" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A118" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Carica Batterie</t>
@@ -23857,7 +23791,7 @@
       <c r="U118" s="110" t="n"/>
       <c r="W118" s="110" t="n"/>
     </row>
-    <row r="119" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="119" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A119" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Carica Batterie - Annex</t>
@@ -23908,7 +23842,7 @@
       <c r="U119" s="110" t="n"/>
       <c r="W119" s="110" t="n"/>
     </row>
-    <row r="120" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="120" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A120" s="114" t="inlineStr">
         <is>
           <t>ICD HVAC</t>
@@ -23968,7 +23902,7 @@
       <c r="U120" s="110" t="n"/>
       <c r="W120" s="110" t="n"/>
     </row>
-    <row r="121" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="121" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A121" s="114" t="inlineStr">
         <is>
           <t>ICD HVAC - Annex</t>
@@ -24019,7 +23953,7 @@
       <c r="U121" s="110" t="n"/>
       <c r="W121" s="110" t="n"/>
     </row>
-    <row r="122" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="122" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A122" s="114" t="inlineStr">
         <is>
           <t>ICD Energy Measurement System</t>
@@ -24074,7 +24008,7 @@
       <c r="U122" s="110" t="n"/>
       <c r="W122" s="110" t="n"/>
     </row>
-    <row r="123" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="123" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A123" s="114" t="inlineStr">
         <is>
           <t>ICD Energy Measurement System - Annex</t>
@@ -24154,7 +24088,7 @@
       <c r="V124" s="446" t="n"/>
       <c r="W124" s="118" t="n"/>
     </row>
-    <row r="125" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="125" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A125" s="114" t="inlineStr">
         <is>
           <t>Train Performances</t>
@@ -24200,7 +24134,7 @@
       <c r="U125" s="110" t="n"/>
       <c r="W125" s="110" t="n"/>
     </row>
-    <row r="126" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="126" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A126" s="114" t="inlineStr">
         <is>
           <t>Train System Architecture</t>
@@ -24246,7 +24180,7 @@
       <c r="U126" s="110" t="n"/>
       <c r="W126" s="110" t="n"/>
     </row>
-    <row r="127" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="127" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A127" s="114" t="inlineStr">
         <is>
           <t>Train Running Simulations</t>
@@ -24292,7 +24226,7 @@
       <c r="U127" s="110" t="n"/>
       <c r="W127" s="110" t="n"/>
     </row>
-    <row r="128" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="128" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A128" s="114" t="inlineStr">
         <is>
           <t>SyFD Propulsion System</t>
@@ -24338,7 +24272,7 @@
       <c r="U128" s="110" t="n"/>
       <c r="W128" s="110" t="n"/>
     </row>
-    <row r="129" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="129" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A129" s="114" t="inlineStr">
         <is>
           <t>SyFD Train Control and Management System</t>
@@ -24384,7 +24318,7 @@
       <c r="U129" s="110" t="n"/>
       <c r="W129" s="110" t="n"/>
     </row>
-    <row r="130" outlineLevel="1" ht="30" customHeight="1" s="594">
+    <row r="130" outlineLevel="1" ht="30" customHeight="1" s="592">
       <c r="A130" s="115" t="inlineStr">
         <is>
           <t>SyFD Ethernet Train Communication Network</t>
@@ -24493,79 +24427,79 @@
     <col width="6.5703125" customWidth="1" style="15" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="15" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="15" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="103" min="20" max="25"/>
-    <col width="8.7109375" customWidth="1" style="103" min="26" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="20" max="26"/>
+    <col width="8.7109375" customWidth="1" style="103" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.45" customFormat="1" customHeight="1" s="105">
-      <c r="A1" s="525" t="inlineStr">
+      <c r="A1" s="526" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="541" t="inlineStr">
+      <c r="B1" s="542" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="533" t="inlineStr">
+      <c r="C1" s="534" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="545" t="inlineStr">
+      <c r="D1" s="546" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="546" t="n"/>
-      <c r="F1" s="543" t="inlineStr">
+      <c r="E1" s="547" t="n"/>
+      <c r="F1" s="544" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="G1" s="544" t="n"/>
-      <c r="H1" s="545" t="inlineStr">
+      <c r="G1" s="545" t="n"/>
+      <c r="H1" s="546" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="546" t="n"/>
-      <c r="J1" s="543" t="inlineStr">
+      <c r="I1" s="547" t="n"/>
+      <c r="J1" s="544" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="K1" s="544" t="n"/>
-      <c r="L1" s="545" t="inlineStr">
+      <c r="K1" s="545" t="n"/>
+      <c r="L1" s="546" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="M1" s="546" t="n"/>
-      <c r="N1" s="543" t="inlineStr">
+      <c r="M1" s="547" t="n"/>
+      <c r="N1" s="544" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="O1" s="544" t="n"/>
-      <c r="P1" s="545" t="inlineStr">
+      <c r="O1" s="545" t="n"/>
+      <c r="P1" s="546" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="Q1" s="546" t="n"/>
-      <c r="R1" s="543" t="inlineStr">
+      <c r="Q1" s="547" t="n"/>
+      <c r="R1" s="544" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
         </is>
       </c>
-      <c r="S1" s="544" t="n"/>
+      <c r="S1" s="545" t="n"/>
     </row>
     <row r="2" ht="26.45" customFormat="1" customHeight="1" s="105">
-      <c r="A2" s="527" t="n"/>
-      <c r="B2" s="542" t="n"/>
-      <c r="C2" s="535" t="n"/>
+      <c r="A2" s="528" t="n"/>
+      <c r="B2" s="543" t="n"/>
+      <c r="C2" s="536" t="n"/>
       <c r="D2" s="395" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -24606,12 +24540,12 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="L2" s="539" t="inlineStr">
+      <c r="L2" s="540" t="inlineStr">
         <is>
           <t>Codice</t>
         </is>
       </c>
-      <c r="M2" s="539" t="inlineStr">
+      <c r="M2" s="540" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
@@ -24672,7 +24606,7 @@
       <c r="R3" s="399" t="n"/>
       <c r="S3" s="400" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="594">
+    <row r="4" ht="30" customHeight="1" s="592">
       <c r="A4" s="106" t="inlineStr">
         <is>
           <t>Architettura di Controllo Treno ed Interfacce di Comando</t>
@@ -25146,7 +25080,7 @@
       <c r="R17" s="109" t="n"/>
       <c r="S17" s="110" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1" s="594">
+    <row r="18" ht="30" customHeight="1" s="592">
       <c r="A18" s="106" t="inlineStr">
         <is>
           <t>Auxiliary converter module, CM-C S 15/10 WA V02</t>
@@ -25181,7 +25115,7 @@
       <c r="R18" s="109" t="n"/>
       <c r="S18" s="110" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="594">
+    <row r="19" ht="30" customHeight="1" s="592">
       <c r="A19" s="106" t="inlineStr">
         <is>
           <t>Chopper converter module, CM-C L 30/07 WC V01</t>
@@ -25216,7 +25150,7 @@
       <c r="R19" s="109" t="n"/>
       <c r="S19" s="110" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="594">
+    <row r="20" ht="30" customHeight="1" s="592">
       <c r="A20" s="106" t="inlineStr">
         <is>
           <t>Line converter module, CM-C M 15/15 WL V06</t>
@@ -25251,7 +25185,7 @@
       <c r="R20" s="109" t="n"/>
       <c r="S20" s="110" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="594">
+    <row r="21" ht="30" customHeight="1" s="592">
       <c r="A21" s="106" t="inlineStr">
         <is>
           <t>Motor converter module, CM-C S 15/10 WM V02</t>
@@ -25427,7 +25361,7 @@
       <c r="R26" s="109" t="n"/>
       <c r="S26" s="110" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1" s="594">
+    <row r="27" ht="30" customHeight="1" s="592">
       <c r="A27" s="106" t="inlineStr">
         <is>
           <t>EPVE63 Test Intervento protezioni azionamento</t>
@@ -25465,7 +25399,7 @@
       <c r="S27" s="110" t="n"/>
       <c r="T27" s="425" t="n"/>
     </row>
-    <row r="28" ht="30" customHeight="1" s="594">
+    <row r="28" ht="30" customHeight="1" s="592">
       <c r="A28" s="106" t="inlineStr">
         <is>
           <t>EPVE63 Report Intervento protezioni
@@ -25618,7 +25552,7 @@
       <c r="S31" s="110" t="n"/>
       <c r="T31" s="425" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1" s="594">
+    <row r="32" ht="30" customHeight="1" s="592">
       <c r="A32" s="106" t="inlineStr">
         <is>
           <t>Test Intervento protezioni azionamento</t>
@@ -25855,92 +25789,93 @@
     <col width="26.42578125" bestFit="1" customWidth="1" style="14" min="27" max="27"/>
     <col width="4.42578125" bestFit="1" customWidth="1" style="14" min="28" max="28"/>
     <col width="8.85546875" bestFit="1" customWidth="1" style="524" min="29" max="29"/>
-    <col width="8.7109375" customWidth="1" style="13" min="30" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="30" max="30"/>
+    <col width="8.7109375" customWidth="1" style="13" min="31" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.45" customHeight="1" s="594">
-      <c r="A1" s="533" t="inlineStr">
+    <row r="1" ht="29.45" customHeight="1" s="592">
+      <c r="A1" s="534" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="541" t="inlineStr">
+      <c r="B1" s="542" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="541" t="inlineStr">
+      <c r="C1" s="542" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="554" t="inlineStr">
+      <c r="D1" s="553" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="E1" s="554" t="inlineStr">
+      <c r="E1" s="553" t="inlineStr">
         <is>
           <t>VOLUME
 SUBVOLUME
 _TOMO</t>
         </is>
       </c>
-      <c r="F1" s="634" t="inlineStr">
+      <c r="F1" s="551" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="G1" s="573" t="n"/>
-      <c r="H1" s="573" t="n"/>
-      <c r="I1" s="78" t="n"/>
-      <c r="J1" s="634" t="inlineStr">
+      <c r="G1" s="549" t="n"/>
+      <c r="H1" s="549" t="n"/>
+      <c r="I1" s="550" t="n"/>
+      <c r="J1" s="551" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="K1" s="573" t="n"/>
-      <c r="L1" s="573" t="n"/>
-      <c r="M1" s="78" t="n"/>
-      <c r="N1" s="635" t="inlineStr">
+      <c r="K1" s="549" t="n"/>
+      <c r="L1" s="549" t="n"/>
+      <c r="M1" s="550" t="n"/>
+      <c r="N1" s="552" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="O1" s="573" t="n"/>
-      <c r="P1" s="573" t="n"/>
-      <c r="Q1" s="78" t="n"/>
-      <c r="R1" s="635" t="inlineStr">
+      <c r="O1" s="549" t="n"/>
+      <c r="P1" s="549" t="n"/>
+      <c r="Q1" s="550" t="n"/>
+      <c r="R1" s="552" t="inlineStr">
         <is>
           <t>VZ-ES</t>
         </is>
       </c>
-      <c r="S1" s="573" t="n"/>
-      <c r="T1" s="573" t="n"/>
-      <c r="U1" s="78" t="n"/>
-      <c r="V1" s="636" t="inlineStr">
+      <c r="S1" s="549" t="n"/>
+      <c r="T1" s="549" t="n"/>
+      <c r="U1" s="550" t="n"/>
+      <c r="V1" s="548" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="W1" s="573" t="n"/>
-      <c r="X1" s="573" t="n"/>
-      <c r="Y1" s="78" t="n"/>
-      <c r="Z1" s="636" t="inlineStr">
+      <c r="W1" s="549" t="n"/>
+      <c r="X1" s="549" t="n"/>
+      <c r="Y1" s="550" t="n"/>
+      <c r="Z1" s="548" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="AA1" s="573" t="n"/>
-      <c r="AB1" s="573" t="n"/>
-      <c r="AC1" s="78" t="n"/>
-    </row>
-    <row r="2" ht="29.45" customHeight="1" s="594" thickBot="1">
-      <c r="A2" s="535" t="n"/>
-      <c r="B2" s="542" t="n"/>
-      <c r="C2" s="542" t="n"/>
-      <c r="D2" s="527" t="n"/>
-      <c r="E2" s="527" t="n"/>
+      <c r="AA1" s="549" t="n"/>
+      <c r="AB1" s="549" t="n"/>
+      <c r="AC1" s="550" t="n"/>
+    </row>
+    <row r="2" ht="29.45" customHeight="1" s="592" thickBot="1">
+      <c r="A2" s="536" t="n"/>
+      <c r="B2" s="543" t="n"/>
+      <c r="C2" s="543" t="n"/>
+      <c r="D2" s="528" t="n"/>
+      <c r="E2" s="528" t="n"/>
       <c r="F2" s="382" t="inlineStr">
         <is>
           <t>NOME FILE</t>
@@ -34361,79 +34296,79 @@
     <col width="6.5703125" customWidth="1" style="15" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="15" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="15" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="103" min="20" max="25"/>
-    <col width="8.7109375" customWidth="1" style="103" min="26" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="20" max="26"/>
+    <col width="8.7109375" customWidth="1" style="103" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.6" customFormat="1" customHeight="1" s="105">
-      <c r="A1" s="525" t="inlineStr">
+      <c r="A1" s="526" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="541" t="inlineStr">
+      <c r="B1" s="542" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="541" t="inlineStr">
+      <c r="C1" s="542" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="545" t="inlineStr">
+      <c r="D1" s="546" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="546" t="n"/>
-      <c r="F1" s="543" t="inlineStr">
+      <c r="E1" s="547" t="n"/>
+      <c r="F1" s="544" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="G1" s="544" t="n"/>
-      <c r="H1" s="545" t="inlineStr">
+      <c r="G1" s="545" t="n"/>
+      <c r="H1" s="546" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="546" t="n"/>
-      <c r="J1" s="543" t="inlineStr">
+      <c r="I1" s="547" t="n"/>
+      <c r="J1" s="544" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="K1" s="544" t="n"/>
-      <c r="L1" s="545" t="inlineStr">
+      <c r="K1" s="545" t="n"/>
+      <c r="L1" s="546" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="M1" s="546" t="n"/>
-      <c r="N1" s="543" t="inlineStr">
+      <c r="M1" s="547" t="n"/>
+      <c r="N1" s="544" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="O1" s="544" t="n"/>
-      <c r="P1" s="545" t="inlineStr">
+      <c r="O1" s="545" t="n"/>
+      <c r="P1" s="546" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="Q1" s="546" t="n"/>
-      <c r="R1" s="543" t="inlineStr">
+      <c r="Q1" s="547" t="n"/>
+      <c r="R1" s="544" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
         </is>
       </c>
-      <c r="S1" s="544" t="n"/>
+      <c r="S1" s="545" t="n"/>
     </row>
     <row r="2" ht="21.6" customFormat="1" customHeight="1" s="105">
-      <c r="A2" s="527" t="n"/>
-      <c r="B2" s="542" t="n"/>
-      <c r="C2" s="542" t="n"/>
+      <c r="A2" s="528" t="n"/>
+      <c r="B2" s="543" t="n"/>
+      <c r="C2" s="543" t="n"/>
       <c r="D2" s="395" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -34474,12 +34409,12 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="L2" s="539" t="inlineStr">
+      <c r="L2" s="540" t="inlineStr">
         <is>
           <t>Codice</t>
         </is>
       </c>
-      <c r="M2" s="539" t="inlineStr">
+      <c r="M2" s="540" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
@@ -34540,7 +34475,7 @@
       <c r="R3" s="399" t="n"/>
       <c r="S3" s="400" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="594">
+    <row r="4" ht="30" customHeight="1" s="592">
       <c r="A4" s="114" t="inlineStr">
         <is>
           <t>Sviluppo regole (Algoritmi Diagnostici)</t>
@@ -34704,7 +34639,7 @@
       <c r="R6" s="109" t="n"/>
       <c r="S6" s="110" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="594">
+    <row r="7" ht="30" customHeight="1" s="592">
       <c r="A7" s="114" t="inlineStr">
         <is>
           <t>PropulsionDiagnosticDataset</t>
@@ -34970,8 +34905,8 @@
     <col width="14.85546875" customWidth="1" style="15" min="11" max="12"/>
     <col width="8.7109375" customWidth="1" style="103" min="13" max="13"/>
     <col width="33.140625" customWidth="1" style="103" min="14" max="14"/>
-    <col width="8.7109375" customWidth="1" style="103" min="15" max="20"/>
-    <col width="8.7109375" customWidth="1" style="103" min="21" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="15" max="21"/>
+    <col width="8.7109375" customWidth="1" style="103" min="22" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customFormat="1" customHeight="1" s="105">
@@ -34985,18 +34920,18 @@
           <t>DESCRIZIONE FUNZIONE</t>
         </is>
       </c>
-      <c r="C1" s="525" t="inlineStr">
+      <c r="C1" s="526" t="inlineStr">
         <is>
           <t>DOC
 CARTELLA</t>
         </is>
       </c>
-      <c r="D1" s="525" t="inlineStr">
+      <c r="D1" s="526" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="E1" s="525" t="inlineStr">
+      <c r="E1" s="526" t="inlineStr">
         <is>
           <t>Info DOC</t>
         </is>
@@ -35011,22 +34946,22 @@
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="H1" s="537" t="inlineStr">
+      <c r="H1" s="538" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="537" t="inlineStr">
+      <c r="I1" s="538" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="J1" s="537" t="inlineStr">
+      <c r="J1" s="538" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="K1" s="537" t="inlineStr">
+      <c r="K1" s="538" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
@@ -35062,7 +34997,7 @@
       <c r="K2" s="161" t="n"/>
       <c r="L2" s="162" t="n"/>
     </row>
-    <row r="3" outlineLevel="1" s="594">
+    <row r="3" outlineLevel="1" s="592">
       <c r="B3" s="144" t="n"/>
       <c r="C3" s="158" t="inlineStr">
         <is>
@@ -35093,7 +35028,7 @@
       <c r="K3" s="157" t="n"/>
       <c r="L3" s="158" t="n"/>
     </row>
-    <row r="4" outlineLevel="2" s="594">
+    <row r="4" outlineLevel="2" s="592">
       <c r="B4" s="144" t="n"/>
       <c r="D4" s="358" t="n"/>
       <c r="E4" s="186" t="inlineStr">
@@ -35115,7 +35050,7 @@
       <c r="K4" s="85" t="n"/>
       <c r="L4" s="50" t="n"/>
     </row>
-    <row r="5" outlineLevel="2" ht="75" customHeight="1" s="594">
+    <row r="5" outlineLevel="2" ht="75" customHeight="1" s="592">
       <c r="B5" s="144" t="n"/>
       <c r="D5" s="107" t="n"/>
       <c r="E5" s="186" t="inlineStr">
@@ -35144,7 +35079,7 @@
       <c r="K5" s="159" t="n"/>
       <c r="L5" s="50" t="n"/>
     </row>
-    <row r="6" outlineLevel="2" ht="330" customHeight="1" s="594">
+    <row r="6" outlineLevel="2" ht="330" customHeight="1" s="592">
       <c r="B6" s="144" t="n"/>
       <c r="D6" s="108" t="n"/>
       <c r="E6" s="186" t="inlineStr">
@@ -35171,7 +35106,7 @@
       <c r="K6" s="50" t="n"/>
       <c r="L6" s="50" t="n"/>
     </row>
-    <row r="7" outlineLevel="1" s="594">
+    <row r="7" outlineLevel="1" s="592">
       <c r="B7" s="144" t="n"/>
       <c r="C7" s="158" t="inlineStr">
         <is>
@@ -35202,7 +35137,7 @@
       <c r="K7" s="157" t="n"/>
       <c r="L7" s="158" t="n"/>
     </row>
-    <row r="8" outlineLevel="2" s="594">
+    <row r="8" outlineLevel="2" s="592">
       <c r="B8" s="144" t="n"/>
       <c r="D8" s="358" t="n"/>
       <c r="E8" s="186" t="inlineStr">
@@ -35222,7 +35157,7 @@
       <c r="K8" s="85" t="n"/>
       <c r="L8" s="50" t="n"/>
     </row>
-    <row r="9" outlineLevel="2" ht="120" customHeight="1" s="594">
+    <row r="9" outlineLevel="2" ht="120" customHeight="1" s="592">
       <c r="B9" s="144" t="n"/>
       <c r="D9" s="107" t="n"/>
       <c r="E9" s="186" t="inlineStr">
@@ -35253,7 +35188,7 @@
       <c r="K9" s="159" t="n"/>
       <c r="L9" s="50" t="n"/>
     </row>
-    <row r="10" outlineLevel="2" ht="270" customHeight="1" s="594">
+    <row r="10" outlineLevel="2" ht="270" customHeight="1" s="592">
       <c r="B10" s="144" t="n"/>
       <c r="D10" s="108" t="n"/>
       <c r="E10" s="186" t="inlineStr">
@@ -35277,7 +35212,7 @@
       <c r="K10" s="50" t="n"/>
       <c r="L10" s="50" t="n"/>
     </row>
-    <row r="11" outlineLevel="1" s="594">
+    <row r="11" outlineLevel="1" s="592">
       <c r="B11" s="144" t="n"/>
       <c r="C11" s="158" t="inlineStr">
         <is>
@@ -35308,7 +35243,7 @@
       <c r="K11" s="158" t="n"/>
       <c r="L11" s="158" t="n"/>
     </row>
-    <row r="12" outlineLevel="2" s="594">
+    <row r="12" outlineLevel="2" s="592">
       <c r="B12" s="144" t="n"/>
       <c r="D12" s="358" t="n"/>
       <c r="E12" s="186" t="inlineStr">
@@ -35328,7 +35263,7 @@
       <c r="K12" s="50" t="n"/>
       <c r="L12" s="50" t="n"/>
     </row>
-    <row r="13" outlineLevel="2" ht="240" customHeight="1" s="594">
+    <row r="13" outlineLevel="2" ht="240" customHeight="1" s="592">
       <c r="B13" s="144" t="n"/>
       <c r="D13" s="108" t="n"/>
       <c r="E13" s="186" t="inlineStr">
@@ -35353,7 +35288,7 @@
       <c r="K13" s="50" t="n"/>
       <c r="L13" s="50" t="n"/>
     </row>
-    <row r="14" outlineLevel="1" s="594">
+    <row r="14" outlineLevel="1" s="592">
       <c r="B14" s="144" t="n"/>
       <c r="C14" s="158" t="inlineStr">
         <is>
@@ -35384,7 +35319,7 @@
       <c r="K14" s="158" t="n"/>
       <c r="L14" s="158" t="n"/>
     </row>
-    <row r="15" outlineLevel="2" s="594">
+    <row r="15" outlineLevel="2" s="592">
       <c r="A15" s="116" t="n"/>
       <c r="B15" s="144" t="n"/>
       <c r="D15" s="50" t="n"/>
@@ -35430,7 +35365,7 @@
       <c r="K16" s="161" t="n"/>
       <c r="L16" s="162" t="n"/>
     </row>
-    <row r="17" outlineLevel="1" s="594">
+    <row r="17" outlineLevel="1" s="592">
       <c r="A17" s="177" t="n"/>
       <c r="B17" s="385" t="n"/>
       <c r="C17" s="158" t="inlineStr">
@@ -35462,7 +35397,7 @@
       <c r="K17" s="157" t="n"/>
       <c r="L17" s="158" t="n"/>
     </row>
-    <row r="18" outlineLevel="2" s="594">
+    <row r="18" outlineLevel="2" s="592">
       <c r="A18" s="179" t="n"/>
       <c r="B18" s="386" t="n"/>
       <c r="C18" s="180" t="n"/>
@@ -35484,7 +35419,7 @@
       <c r="K18" s="85" t="n"/>
       <c r="L18" s="50" t="n"/>
     </row>
-    <row r="19" outlineLevel="2" ht="150" customHeight="1" s="594">
+    <row r="19" outlineLevel="2" ht="150" customHeight="1" s="592">
       <c r="A19" s="179" t="n"/>
       <c r="B19" s="386" t="n"/>
       <c r="C19" s="180" t="n"/>
@@ -35521,7 +35456,7 @@
       <c r="K19" s="85" t="n"/>
       <c r="L19" s="50" t="n"/>
     </row>
-    <row r="20" outlineLevel="2" ht="345" customHeight="1" s="594">
+    <row r="20" outlineLevel="2" ht="345" customHeight="1" s="592">
       <c r="A20" s="179" t="n"/>
       <c r="B20" s="386" t="n"/>
       <c r="C20" s="180" t="n"/>
@@ -35550,7 +35485,7 @@
       <c r="K20" s="85" t="n"/>
       <c r="L20" s="50" t="n"/>
     </row>
-    <row r="21" outlineLevel="1" s="594">
+    <row r="21" outlineLevel="1" s="592">
       <c r="A21" s="179" t="n"/>
       <c r="B21" s="386" t="n"/>
       <c r="C21" s="158" t="inlineStr">
@@ -35585,7 +35520,7 @@
       <c r="K21" s="158" t="n"/>
       <c r="L21" s="158" t="n"/>
     </row>
-    <row r="22" outlineLevel="2" s="594">
+    <row r="22" outlineLevel="2" s="592">
       <c r="A22" s="179" t="n"/>
       <c r="C22" s="180" t="n"/>
       <c r="D22" s="358" t="n"/>
@@ -35608,7 +35543,7 @@
       <c r="K22" s="50" t="n"/>
       <c r="L22" s="50" t="n"/>
     </row>
-    <row r="23" outlineLevel="2" ht="409.5" customHeight="1" s="594">
+    <row r="23" outlineLevel="2" ht="409.5" customHeight="1" s="592">
       <c r="A23" s="179" t="n"/>
       <c r="B23" s="386" t="n"/>
       <c r="C23" s="180" t="n"/>
@@ -35646,7 +35581,7 @@
       <c r="K23" s="50" t="n"/>
       <c r="L23" s="50" t="n"/>
     </row>
-    <row r="24" outlineLevel="1" s="594">
+    <row r="24" outlineLevel="1" s="592">
       <c r="A24" s="179" t="n"/>
       <c r="B24" s="386" t="n"/>
       <c r="C24" s="158" t="inlineStr">
@@ -35678,7 +35613,7 @@
       <c r="K24" s="158" t="n"/>
       <c r="L24" s="158" t="n"/>
     </row>
-    <row r="25" outlineLevel="2" s="594">
+    <row r="25" outlineLevel="2" s="592">
       <c r="A25" s="179" t="n"/>
       <c r="B25" s="180" t="n"/>
       <c r="C25" s="180" t="n"/>
@@ -35730,7 +35665,7 @@
       <c r="K26" s="429" t="n"/>
       <c r="L26" s="430" t="n"/>
     </row>
-    <row r="27" outlineLevel="1" s="594">
+    <row r="27" outlineLevel="1" s="592">
       <c r="A27" s="181" t="n"/>
       <c r="B27" s="182" t="n"/>
       <c r="C27" s="158" t="inlineStr">
@@ -35762,7 +35697,7 @@
       <c r="K27" s="157" t="n"/>
       <c r="L27" s="158" t="n"/>
     </row>
-    <row r="28" outlineLevel="2" s="594">
+    <row r="28" outlineLevel="2" s="592">
       <c r="A28" s="183" t="n"/>
       <c r="B28" s="184">
         <f t="array" ref="B28">INDIRECT("'" &amp; $C33 &amp; "'!B5")</f>
@@ -35787,7 +35722,7 @@
       <c r="K28" s="85" t="n"/>
       <c r="L28" s="50" t="n"/>
     </row>
-    <row r="29" outlineLevel="1" s="594">
+    <row r="29" outlineLevel="1" s="592">
       <c r="A29" s="183" t="n"/>
       <c r="B29" s="184" t="n"/>
       <c r="C29" s="158" t="inlineStr">
@@ -35819,7 +35754,7 @@
       <c r="K29" s="158" t="n"/>
       <c r="L29" s="158" t="n"/>
     </row>
-    <row r="30" outlineLevel="2" s="594">
+    <row r="30" outlineLevel="2" s="592">
       <c r="A30" s="183" t="n"/>
       <c r="B30" s="184" t="n"/>
       <c r="C30" s="178" t="n"/>
@@ -35841,7 +35776,7 @@
       <c r="K30" s="50" t="n"/>
       <c r="L30" s="50" t="n"/>
     </row>
-    <row r="31" outlineLevel="1" s="594">
+    <row r="31" outlineLevel="1" s="592">
       <c r="A31" s="183" t="n"/>
       <c r="B31" s="184" t="n"/>
       <c r="C31" s="158" t="inlineStr">
@@ -35873,7 +35808,7 @@
       <c r="K31" s="158" t="n"/>
       <c r="L31" s="158" t="n"/>
     </row>
-    <row r="32" outlineLevel="2" s="594">
+    <row r="32" outlineLevel="2" s="592">
       <c r="A32" s="183" t="n"/>
       <c r="B32" s="184" t="n"/>
       <c r="C32" s="184" t="n"/>
@@ -35895,7 +35830,7 @@
       <c r="K32" s="50" t="n"/>
       <c r="L32" s="50" t="n"/>
     </row>
-    <row r="33" outlineLevel="1" s="594">
+    <row r="33" outlineLevel="1" s="592">
       <c r="A33" s="116" t="n"/>
       <c r="B33" s="144" t="n"/>
       <c r="C33" s="158" t="inlineStr">
@@ -35927,7 +35862,7 @@
       <c r="K33" s="158" t="n"/>
       <c r="L33" s="158" t="n"/>
     </row>
-    <row r="34" outlineLevel="2" s="594">
+    <row r="34" outlineLevel="2" s="592">
       <c r="A34" s="116" t="n"/>
       <c r="B34" s="144" t="n"/>
       <c r="D34" s="358" t="n"/>
@@ -35948,7 +35883,7 @@
       <c r="K34" s="50" t="n"/>
       <c r="L34" s="50" t="n"/>
     </row>
-    <row r="35" outlineLevel="2" s="594">
+    <row r="35" outlineLevel="2" s="592">
       <c r="A35" s="116" t="n"/>
       <c r="B35" s="144" t="n"/>
       <c r="D35" s="108" t="n"/>
@@ -35965,7 +35900,7 @@
       <c r="K35" s="50" t="n"/>
       <c r="L35" s="50" t="n"/>
     </row>
-    <row r="36" outlineLevel="1" s="594">
+    <row r="36" outlineLevel="1" s="592">
       <c r="A36" s="116" t="n"/>
       <c r="B36" s="144" t="n"/>
       <c r="C36" s="158" t="inlineStr">
@@ -35994,7 +35929,7 @@
       <c r="K36" s="158" t="n"/>
       <c r="L36" s="158" t="n"/>
     </row>
-    <row r="37" outlineLevel="2" s="594">
+    <row r="37" outlineLevel="2" s="592">
       <c r="A37" s="116" t="n"/>
       <c r="B37" s="144" t="n"/>
       <c r="D37" s="358" t="n"/>
@@ -36013,7 +35948,7 @@
       <c r="K37" s="50" t="n"/>
       <c r="L37" s="50" t="n"/>
     </row>
-    <row r="38" outlineLevel="1" s="594">
+    <row r="38" outlineLevel="1" s="592">
       <c r="A38" s="116" t="n"/>
       <c r="B38" s="387" t="inlineStr">
         <is>
@@ -36046,7 +35981,7 @@
       <c r="K38" s="158" t="n"/>
       <c r="L38" s="158" t="n"/>
     </row>
-    <row r="39" outlineLevel="2" s="594">
+    <row r="39" outlineLevel="2" s="592">
       <c r="A39" s="116" t="n"/>
       <c r="B39" s="144" t="n"/>
       <c r="D39" s="358" t="n"/>
@@ -36065,7 +36000,7 @@
       <c r="K39" s="50" t="n"/>
       <c r="L39" s="50" t="n"/>
     </row>
-    <row r="40" ht="30" customHeight="1" s="594">
+    <row r="40" ht="30" customHeight="1" s="592">
       <c r="A40" s="176" t="inlineStr">
         <is>
           <t>LV_Country_code_selection</t>
@@ -36091,7 +36026,7 @@
       <c r="K40" s="161" t="n"/>
       <c r="L40" s="162" t="n"/>
     </row>
-    <row r="41" outlineLevel="1" s="594">
+    <row r="41" outlineLevel="1" s="592">
       <c r="A41" s="181" t="n"/>
       <c r="B41" s="182" t="n"/>
       <c r="C41" s="158" t="inlineStr">
@@ -36129,7 +36064,7 @@
       <c r="K41" s="157" t="n"/>
       <c r="L41" s="158" t="n"/>
     </row>
-    <row r="42" outlineLevel="2" s="594">
+    <row r="42" outlineLevel="2" s="592">
       <c r="A42" s="183" t="n"/>
       <c r="B42" s="184" t="n"/>
       <c r="C42" s="184" t="n"/>
@@ -36155,7 +36090,7 @@
       <c r="K42" s="85" t="n"/>
       <c r="L42" s="50" t="n"/>
     </row>
-    <row r="43" outlineLevel="2" s="594">
+    <row r="43" outlineLevel="2" s="592">
       <c r="A43" s="183" t="n"/>
       <c r="B43" s="184" t="n"/>
       <c r="C43" s="184" t="n"/>
@@ -36165,39 +36100,39 @@
           <t>Funzioni AI</t>
         </is>
       </c>
-      <c r="F43" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Country_code_selection è una selezione su IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema di controllo elettronico (IDU), la PCU (Power Control Unit) e il sistema di propulsione. La funzione viene attivata quando il driver seleziona un paese corrente dall'IDU, che viene poi inviato alle PCU per configurare i pantografi appropriati. In caso di fallimento, il sistema deve essere rilevato e corretto dal driver.
+      <c r="F43" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Country_code_selection è una selezione su IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema di controllo elettronico (IDU), il sistema di propulsione, i PCU della traine e il software di gestione del sistema. La funzione viene attivata quando il driver seleziona un paese corrente sul IDU, che viene poi inviato a tutti i PCU della traine. In caso di fallimento, il sistema deve essere riconosciuto e l'azione di ripristino prese.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 7 — Pagina finale: 17.</t>
+Pagina di riferimento: 7.</t>
         </is>
       </c>
       <c r="G43" s="456" t="n"/>
-      <c r="H43" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Country_code_selection è una selezione su IDU del paese corrente per informare la PCU sui pantografi selezionabili. È coinvolta nella gestione della configurazione elettrica del treno, specificamente per la scelta del paese di operazione che influenza la selezione dei pantografi adatto alla linea di corrente. La funzione è attivata quando il driver seleziona un paese dal IDU, e invia il codice di paese selezionato alle PCU del treno per configurare i pantografi in base al tipo di corrente utilizzata nella zona operativa.
+      <c r="H43" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Country_code_selection è una selezione su IDU del paese corrente per informare la PCU sui pantografi selezionabili. È coinvolta nella gestione elettrica del treno, specificamente nella configurazione della tensione di linea e dei pantografi adatti al paese di operazione. La funzione è attivata quando il driver seleziona un paese dall'IDU, che viene poi inviato alle PCU per configurare la tensione di linea e i pantografi appropriati. In caso di fallimento, la funzione supervisiona l'errore e fornisce feedback al driver. La funzione è progettata con una sicurezza di SIL 2 e richiede la conferma del driver prima dell'attivazione.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 7 — Pagina finale: 17.</t>
-        </is>
-      </c>
-      <c r="I43" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Country_code_selection seleziona l'IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema di gestione dell'IDU, la PCU e i componenti elettrici/meccanici del treno. La funzione è attivata quando si seleziona un paese diverso da quello previsto, con una logica di funzionamento che invia l'informazione al sistema di gestione dell'IDU e alla PCU. La funzione è progettata per garantire la sicurezza e la conformità alle normative, con requisiti di SIL 2 e ridondanze per evitare errori o fallimenti.
+Pagina di riferimento: 7.</t>
+        </is>
+      </c>
+      <c r="I43" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Country_code_selection seleziona l'IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema di gestione della velocità (TCMS), l'IDU e la PCU, con la logica di funzionamento basata sulla selezione di un codice di paese valido (1-8) che viene inviato alle PCU per configurare i pantografi. La funzione è progettata per garantire una sicurezza di livello SIL 2 e prevede la ridondanza nella comunicazione tra TCMS, IDU e PCU.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 7 — Pagina finale: 17.</t>
-        </is>
-      </c>
-      <c r="J43" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Country_code_selection è una selezione su IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema di gestione della velocità (TCMS), l'IDU (Interface Device Unit) e la PCU (Power Control Unit). La funzione è attivata quando si seleziona un paese non italiano, in cui caso viene visualizzato un messaggio all'operatore. La logica di funzionamento prevede la verifica della disponibilità del paese selezionato e l'invio di una notifica al driver se il paese è non disponibile.
+Pagina di riferimento: 7.</t>
+        </is>
+      </c>
+      <c r="J43" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Country_code_selection seleziona l'IDU del paese corrente per informare la PCU sui pantografi selezionabili, utilizzando il codice di paese Italy come riferimento operativo. La funzione è coinvoltiva del sistema IDU e della PCU, ed è caratterizzata da due condizioni di attivazione: se un codice non disponibile viene selezionato o se un codice non definito viene selezionato, il sistema invia una messaggio al conducente. La funzione è progettata per garantire la sicurezza e l'efficienza del sistema, con requisiti di sicurezza SIL 2.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 12 — Pagina finale: 22.</t>
+Pagina di riferimento: 12.</t>
         </is>
       </c>
       <c r="K43" s="455" t="n"/>
       <c r="L43" s="457" t="n"/>
     </row>
-    <row r="44" ht="30" customHeight="1" s="594">
+    <row r="44" ht="30" customHeight="1" s="592">
       <c r="A44" s="176" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lifting</t>
@@ -36223,7 +36158,7 @@
       <c r="K44" s="161" t="n"/>
       <c r="L44" s="162" t="n"/>
     </row>
-    <row r="45" outlineLevel="1" s="594">
+    <row r="45" outlineLevel="1" s="592">
       <c r="A45" s="181" t="n"/>
       <c r="B45" s="182" t="n"/>
       <c r="C45" s="158" t="inlineStr">
@@ -36261,7 +36196,7 @@
       <c r="K45" s="157" t="n"/>
       <c r="L45" s="158" t="n"/>
     </row>
-    <row r="46" outlineLevel="2" s="594">
+    <row r="46" outlineLevel="2" s="592">
       <c r="A46" s="183" t="n"/>
       <c r="B46" s="184" t="n"/>
       <c r="C46" s="184" t="n"/>
@@ -36287,7 +36222,7 @@
       <c r="K46" s="85" t="n"/>
       <c r="L46" s="50" t="n"/>
     </row>
-    <row r="47" outlineLevel="2" s="594">
+    <row r="47" outlineLevel="2" s="592">
       <c r="A47" s="183" t="n"/>
       <c r="B47" s="184" t="n"/>
       <c r="C47" s="184" t="n"/>
@@ -36297,39 +36232,39 @@
           <t>Funzioni AI</t>
         </is>
       </c>
-      <c r="F47" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che regola l'alzamento del pantografo 1 o 2 sulla base di tensione di linea e paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, il sistema di gestione della tensione di linea e il sistema di comunicazione tra il Control Center e la Unità di Comando (PCU). La funzione è attivata quando il driver seleziona una line voltage system e un paese, e viene disattivata se non si verifica l'alzamento del pantografo entro 35 secondi. In caso di fallimento, il sistema invia segnali di allarme e blocca il pantografo.
+      <c r="F47" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che controlla l'alzamento dei pantografi 1 e/o 2 in base alla tensione di linea (switch) e al paese (IDU) selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, il sistema di gestione della tensione di linea e il sistema di comunicazione TCMS-PCU. La funzione è attivata quando il driver seleziona la line voltage system e il paese corretto, e viene disattivata se non si verifica l'alzamento del pantografo entro 35 secondi o se si verificano condizioni di fallimento come mancato alzamento o uso di un tipo di pantografo sbagliato.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina iniziale: 8 — Pagina finale: 18.</t>
         </is>
       </c>
       <c r="G47" s="456" t="n"/>
-      <c r="H47" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che regola l'alzamento del pantografo 1 o 2 in base alla tensione di linea e al paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, il sistema di gestione della tensione di linea e il sistema di comunicazione tra il Control Center e il Pantografo. La funzione è attivata quando il driver seleziona una line voltage system e un paese, e viene disattivata se non si verifica l'alzamento del pantografo entro 35 secondi o se si verificano condizioni di fallimento come la mancata risposta del pantografo o la presenza di un sistema di gestione della tensione di linea invalido.
+      <c r="H47" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che regola l'alzamento del pantografo 1 o 2 in base alla tensione di linea e al paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, il sistema di gestione della tensione di linea e il sistema di comunicazione tra il Control Center e la Plataforma. La funzione è attivata quando il driver seleziona una line voltage system e un paese, e viene disattivata se non si verifica l'alzamento del pantografo entro 35 secondi o se si verificano condizioni di fallimento.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 8 — Pagina finale: 18.</t>
-        </is>
-      </c>
-      <c r="I47" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che controlla l'alzamento del pantografo 1 o 2 in base alla tensione di linea e al paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, la console di guida (PCU) e il sistema di gestione della tensione di linea (TCMS). La funzione è attivata quando il driver seleziona una line voltage system e un paese corretto, e viene eseguita automaticamente o manualmente. In caso di fallimento, la funzione verifica se il pantografo non si alza dopo 35 secondi e se la pressione del serbatoio è superiore a 750 kPa.
+Pagina iniziale: 8 — Pagina finale: 15.</t>
+        </is>
+      </c>
+      <c r="I47" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che controlla l'alzamento del pantografo 1 o 2 in base alla tensione di linea e al paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, la console del conducente (PCU) e il sistema di gestione della tensione di linea (TCMS). La funzione è attivata quando il conducente seleziona una line voltage system e un paese corretto, e viene eseguita automaticamente o manualmente. In caso di fallimento, la funzione verifica se il pantografo è stato alzato correttamente e se non ci sono errori di tipo hardware o software.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 8 — Pagina finale: 18.</t>
-        </is>
-      </c>
-      <c r="J47" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che controlla l'alzamento del pantografo 1 o 2 sulla base di tensione di linea (switch) e paese (IDU) selezionati, utilizzando il sistema TCMS. La logica di funzionamento attiva il comando in base alla validazione del paese selezionato e alla presenza di una corretta tensione di linea, mentre l'eventuale ridondanza è garantita dalla comunicazione con i PCU (Pantograph Control) e HVSP (High Voltage Switching Panel).
+Pagina iniziale: 8 — Pagina finale: 20.</t>
+        </is>
+      </c>
+      <c r="J47" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Pantograph_Lifting (Comando di alzamento pantografo 1 o 2 sulla base di tensione di linea e paese selezionati) è responsabile dell'alzamento del pantografo in base alle condizioni di linea e paese di operazione. I componenti principali coinvolti sono il sistema di controllo pantografico, il selector di tensione di linea e il software TCMS (Train Control and Management System). La funzione viene attivata quando il driver seleziona la tensione di linea e il paese di operazione, e in caso di emergenza, utilizza il paese più recentemente selezionato. La logica di funzionamento prevede l'invio di segnali al PCU (Pantograph Control Unit) e all'HVSP (High Voltage Switching Panel), con la possibilità di ridondanza per garantire la sicurezza.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 13 — Pagina finale: 23.</t>
+Pagina iniziale: 13 — Pagina finale: 21.</t>
         </is>
       </c>
       <c r="K47" s="455" t="n"/>
       <c r="L47" s="457" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1" s="594">
+    <row r="48" ht="30" customHeight="1" s="592">
       <c r="A48" s="176" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lowering</t>
@@ -36355,7 +36290,7 @@
       <c r="K48" s="161" t="n"/>
       <c r="L48" s="162" t="n"/>
     </row>
-    <row r="49" outlineLevel="1" s="594">
+    <row r="49" outlineLevel="1" s="592">
       <c r="A49" s="181" t="n"/>
       <c r="B49" s="182" t="n"/>
       <c r="C49" s="158" t="inlineStr">
@@ -36393,7 +36328,7 @@
       <c r="K49" s="157" t="n"/>
       <c r="L49" s="158" t="n"/>
     </row>
-    <row r="50" outlineLevel="2" s="594">
+    <row r="50" outlineLevel="2" s="592">
       <c r="A50" s="183" t="n"/>
       <c r="B50" s="184" t="n"/>
       <c r="C50" s="184" t="n"/>
@@ -36419,7 +36354,7 @@
       <c r="K50" s="85" t="n"/>
       <c r="L50" s="50" t="n"/>
     </row>
-    <row r="51" outlineLevel="2" s="594">
+    <row r="51" outlineLevel="2" s="592">
       <c r="A51" s="183" t="n"/>
       <c r="B51" s="184" t="n"/>
       <c r="C51" s="184" t="n"/>
@@ -36429,19 +36364,19 @@
           <t>Funzioni AI</t>
         </is>
       </c>
-      <c r="F51" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lowering (Comando di abbassamento pantografo) è finalizzata a ridurre il pantografo in modo sicuro e controllato quando si deattiva la linea elettrica. La funzione coinvolge il sistema elettrico, meccanico e software del treno, con l'uso di comandi manuali o automatici (come il pulsante di emergenza) per attivare la riduzione del pantografo. La logica di funzionamento prevede l'interruzione dei circuitti di corrente prima dell'abbassamento del pantografo, tranne in caso di emergenza. La funzione è progettata con un livello di sicurezza SIL 0 e prevede la bloccatura del pantografo in caso di fallimento per garantire la sicurezza del treno.
+      <c r="F51" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Pantograph_Lowering (Comando di abbassamento pantografo) è finalizzata a ridurre il pantografo in modo sicuro e controllato quando si deattiva la linea elettrica. La funzione coinvolge il sistema elettrico, il controllo del pantografo e il blocco della seconda pantografia in caso di interazione con la prima. La logica di funzionamento attiva il comando di abbassamento quando si verifica una delle seguenti condizioni: deattivazione della linea elettrica, pressione dell'Emergency push button o avvenuta una manovra di blocco del pantografo.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 14 — Pagina finale: 24.</t>
+Pagina iniziale: 14 — Pagina finale: 29.</t>
         </is>
       </c>
       <c r="G51" s="456" t="n"/>
-      <c r="H51" s="637" t="inlineStr">
-        <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lowering (Comando di abbassamento pantografo) è un comando manuale/automatico che attiva l'abbassamento del pantografo in caso di deattivazione della linea elettrica o di emergenza. I componenti principali coinvolti sono il sistema di controllo elettronico, il sistema di sicurezza e i comandi manuali (pantograph down, pulsante d'emergenza). La funzione è attivata quando la linea elettrica viene deattivata o in caso di emergenza, e il pantografo viene abbassato per evitare la scossa elettromagnetica. La funzione è progettata con un livello di sicurezza SIL 0 e prevede la presenza di comandi manuali per garantire la sicurezza in caso di fallimento del sistema.
+      <c r="H51" s="625" t="inlineStr">
+        <is>
+          <t>La funzione ferroviaria LV_Pantograph_Lowering (Comando di abbassamento pantografo) è un comando manuale/automatico che attiva l'abbassamento del pantografo in caso di deattivazione della linea elettrica o di emergenza. I componenti principali coinvolti sono il sistema di controllo del pantografo, i comandi di abbassamento (pantograph down) e l'impianto di sicurezza. La funzione viene attivata quando si verifica una delle seguenti condizioni: deattivazione della linea elettrica, pressione dell'emergenza o fallimento del sistema di controllo. In caso di fallimento, il pantografo viene bloccato per garantire la sicurezza.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 16 — Pagina finale: 26.</t>
+Pagina iniziale: 16 — Pagina finale: 20.</t>
         </is>
       </c>
       <c r="I51" s="465" t="n"/>
@@ -36514,7 +36449,7 @@
     </row>
     <row r="54" outlineLevel="2" customFormat="1" s="13">
       <c r="B54" s="103" t="n"/>
-      <c r="C54" s="542" t="n"/>
+      <c r="C54" s="543" t="n"/>
       <c r="D54" s="361" t="n"/>
       <c r="E54" s="321" t="inlineStr">
         <is>
@@ -36539,7 +36474,7 @@
     </row>
     <row r="55" outlineLevel="2" customFormat="1" s="13">
       <c r="B55" s="103" t="n"/>
-      <c r="C55" s="542" t="n"/>
+      <c r="C55" s="543" t="n"/>
       <c r="D55" s="458" t="n"/>
       <c r="E55" s="459" t="inlineStr">
         <is>
@@ -36619,7 +36554,7 @@
     </row>
     <row r="58" outlineLevel="2" customFormat="1" s="13">
       <c r="B58" s="103" t="n"/>
-      <c r="C58" s="542" t="n"/>
+      <c r="C58" s="543" t="n"/>
       <c r="D58" s="361" t="n"/>
       <c r="E58" s="321" t="inlineStr">
         <is>
@@ -36644,7 +36579,7 @@
     </row>
     <row r="59" outlineLevel="2" customFormat="1" s="13">
       <c r="B59" s="103" t="n"/>
-      <c r="C59" s="542" t="n"/>
+      <c r="C59" s="543" t="n"/>
       <c r="D59" s="458" t="n"/>
       <c r="E59" s="459" t="inlineStr">
         <is>
@@ -36724,7 +36659,7 @@
     </row>
     <row r="62" outlineLevel="2" customFormat="1" s="13">
       <c r="B62" s="103" t="n"/>
-      <c r="C62" s="542" t="n"/>
+      <c r="C62" s="543" t="n"/>
       <c r="D62" s="361" t="n"/>
       <c r="E62" s="321" t="inlineStr">
         <is>
@@ -36749,7 +36684,7 @@
     </row>
     <row r="63" outlineLevel="2" customFormat="1" s="13">
       <c r="B63" s="103" t="n"/>
-      <c r="C63" s="542" t="n"/>
+      <c r="C63" s="543" t="n"/>
       <c r="D63" s="458" t="n"/>
       <c r="E63" s="459" t="inlineStr">
         <is>
@@ -36829,7 +36764,7 @@
     </row>
     <row r="66" outlineLevel="2" customFormat="1" s="13">
       <c r="B66" s="103" t="n"/>
-      <c r="C66" s="542" t="n"/>
+      <c r="C66" s="543" t="n"/>
       <c r="D66" s="361" t="n"/>
       <c r="E66" s="321" t="inlineStr">
         <is>
@@ -36854,7 +36789,7 @@
     </row>
     <row r="67" outlineLevel="2" customFormat="1" s="13">
       <c r="B67" s="103" t="n"/>
-      <c r="C67" s="542" t="n"/>
+      <c r="C67" s="543" t="n"/>
       <c r="D67" s="458" t="n"/>
       <c r="E67" s="459" t="inlineStr">
         <is>
@@ -36934,7 +36869,7 @@
     </row>
     <row r="70" outlineLevel="2" customFormat="1" s="13">
       <c r="B70" s="103" t="n"/>
-      <c r="C70" s="542" t="n"/>
+      <c r="C70" s="543" t="n"/>
       <c r="D70" s="361" t="n"/>
       <c r="E70" s="321" t="inlineStr">
         <is>
@@ -36959,7 +36894,7 @@
     </row>
     <row r="71" outlineLevel="2" customFormat="1" s="13">
       <c r="B71" s="103" t="n"/>
-      <c r="C71" s="542" t="n"/>
+      <c r="C71" s="543" t="n"/>
       <c r="D71" s="458" t="n"/>
       <c r="E71" s="459" t="inlineStr">
         <is>
@@ -37039,7 +36974,7 @@
     </row>
     <row r="74" outlineLevel="2" customFormat="1" s="13">
       <c r="B74" s="103" t="n"/>
-      <c r="C74" s="542" t="n"/>
+      <c r="C74" s="543" t="n"/>
       <c r="D74" s="361" t="n"/>
       <c r="E74" s="321" t="inlineStr">
         <is>
@@ -37064,7 +36999,7 @@
     </row>
     <row r="75" outlineLevel="2" customFormat="1" s="13">
       <c r="B75" s="103" t="n"/>
-      <c r="C75" s="542" t="n"/>
+      <c r="C75" s="543" t="n"/>
       <c r="D75" s="458" t="n"/>
       <c r="E75" s="459" t="inlineStr">
         <is>
@@ -37144,7 +37079,7 @@
     </row>
     <row r="78" outlineLevel="2" customFormat="1" s="13">
       <c r="B78" s="103" t="n"/>
-      <c r="C78" s="542" t="n"/>
+      <c r="C78" s="543" t="n"/>
       <c r="D78" s="361" t="n"/>
       <c r="E78" s="321" t="inlineStr">
         <is>
@@ -37169,7 +37104,7 @@
     </row>
     <row r="79" outlineLevel="2" customFormat="1" s="13">
       <c r="B79" s="103" t="n"/>
-      <c r="C79" s="542" t="n"/>
+      <c r="C79" s="543" t="n"/>
       <c r="D79" s="458" t="n"/>
       <c r="E79" s="459" t="inlineStr">
         <is>
@@ -37249,7 +37184,7 @@
     </row>
     <row r="82" outlineLevel="2" customFormat="1" s="13">
       <c r="B82" s="103" t="n"/>
-      <c r="C82" s="542" t="n"/>
+      <c r="C82" s="543" t="n"/>
       <c r="D82" s="361" t="n"/>
       <c r="E82" s="321" t="inlineStr">
         <is>
@@ -37274,7 +37209,7 @@
     </row>
     <row r="83" outlineLevel="2" customFormat="1" s="13">
       <c r="B83" s="103" t="n"/>
-      <c r="C83" s="542" t="n"/>
+      <c r="C83" s="543" t="n"/>
       <c r="D83" s="458" t="n"/>
       <c r="E83" s="459" t="inlineStr">
         <is>
@@ -37356,7 +37291,7 @@
     </row>
     <row r="86" outlineLevel="2" customFormat="1" s="13">
       <c r="B86" s="103" t="n"/>
-      <c r="C86" s="542" t="n"/>
+      <c r="C86" s="543" t="n"/>
       <c r="D86" s="361" t="n"/>
       <c r="E86" s="321" t="inlineStr">
         <is>
@@ -37381,7 +37316,7 @@
     </row>
     <row r="87" outlineLevel="2" customFormat="1" s="13">
       <c r="B87" s="103" t="n"/>
-      <c r="C87" s="542" t="n"/>
+      <c r="C87" s="543" t="n"/>
       <c r="D87" s="458" t="n"/>
       <c r="E87" s="459" t="inlineStr">
         <is>
@@ -37461,7 +37396,7 @@
     </row>
     <row r="90" outlineLevel="2" customFormat="1" s="13">
       <c r="B90" s="103" t="n"/>
-      <c r="C90" s="542" t="n"/>
+      <c r="C90" s="543" t="n"/>
       <c r="D90" s="361" t="n"/>
       <c r="E90" s="321" t="inlineStr">
         <is>
@@ -37486,7 +37421,7 @@
     </row>
     <row r="91" outlineLevel="2" customFormat="1" s="13">
       <c r="B91" s="103" t="n"/>
-      <c r="C91" s="542" t="n"/>
+      <c r="C91" s="543" t="n"/>
       <c r="D91" s="458" t="n"/>
       <c r="E91" s="459" t="inlineStr">
         <is>
@@ -37566,7 +37501,7 @@
     </row>
     <row r="94" outlineLevel="2" customFormat="1" s="13">
       <c r="B94" s="103" t="n"/>
-      <c r="C94" s="542" t="n"/>
+      <c r="C94" s="543" t="n"/>
       <c r="D94" s="361" t="n"/>
       <c r="E94" s="321" t="inlineStr">
         <is>
@@ -37591,7 +37526,7 @@
     </row>
     <row r="95" outlineLevel="2" customFormat="1" s="13">
       <c r="B95" s="103" t="n"/>
-      <c r="C95" s="542" t="n"/>
+      <c r="C95" s="543" t="n"/>
       <c r="D95" s="458" t="n"/>
       <c r="E95" s="459" t="inlineStr">
         <is>
@@ -37671,7 +37606,7 @@
     </row>
     <row r="98" outlineLevel="2" customFormat="1" s="13">
       <c r="B98" s="103" t="n"/>
-      <c r="C98" s="542" t="n"/>
+      <c r="C98" s="543" t="n"/>
       <c r="D98" s="361" t="n"/>
       <c r="E98" s="321" t="inlineStr">
         <is>
@@ -37696,7 +37631,7 @@
     </row>
     <row r="99" outlineLevel="2" customFormat="1" s="13">
       <c r="B99" s="103" t="n"/>
-      <c r="C99" s="542" t="n"/>
+      <c r="C99" s="543" t="n"/>
       <c r="D99" s="458" t="n"/>
       <c r="E99" s="459" t="inlineStr">
         <is>
@@ -37776,7 +37711,7 @@
     </row>
     <row r="102" outlineLevel="2" customFormat="1" s="13">
       <c r="B102" s="103" t="n"/>
-      <c r="C102" s="542" t="n"/>
+      <c r="C102" s="543" t="n"/>
       <c r="D102" s="361" t="n"/>
       <c r="E102" s="321" t="inlineStr">
         <is>
@@ -37801,7 +37736,7 @@
     </row>
     <row r="103" outlineLevel="2" customFormat="1" s="13">
       <c r="B103" s="103" t="n"/>
-      <c r="C103" s="542" t="n"/>
+      <c r="C103" s="543" t="n"/>
       <c r="D103" s="458" t="n"/>
       <c r="E103" s="459" t="inlineStr">
         <is>
@@ -37872,7 +37807,7 @@
     </row>
     <row r="106" outlineLevel="2" customFormat="1" s="13">
       <c r="B106" s="103" t="n"/>
-      <c r="C106" s="542" t="n"/>
+      <c r="C106" s="543" t="n"/>
       <c r="D106" s="361" t="n"/>
       <c r="E106" s="321" t="inlineStr">
         <is>
@@ -37891,7 +37826,7 @@
     </row>
     <row r="107" outlineLevel="2" customFormat="1" s="13">
       <c r="B107" s="103" t="n"/>
-      <c r="C107" s="542" t="n"/>
+      <c r="C107" s="543" t="n"/>
       <c r="D107" s="458" t="n"/>
       <c r="E107" s="459" t="inlineStr">
         <is>
@@ -37962,7 +37897,7 @@
     </row>
     <row r="110" outlineLevel="2" customFormat="1" s="13">
       <c r="B110" s="103" t="n"/>
-      <c r="C110" s="542" t="n"/>
+      <c r="C110" s="543" t="n"/>
       <c r="D110" s="361" t="n"/>
       <c r="E110" s="321" t="inlineStr">
         <is>
@@ -37981,7 +37916,7 @@
     </row>
     <row r="111" outlineLevel="2" customFormat="1" s="13">
       <c r="B111" s="103" t="n"/>
-      <c r="C111" s="542" t="n"/>
+      <c r="C111" s="543" t="n"/>
       <c r="D111" s="458" t="n"/>
       <c r="E111" s="459" t="inlineStr">
         <is>
@@ -38058,7 +37993,7 @@
     </row>
     <row r="114" outlineLevel="2" customFormat="1" s="13">
       <c r="B114" s="103" t="n"/>
-      <c r="C114" s="542" t="n"/>
+      <c r="C114" s="543" t="n"/>
       <c r="D114" s="361" t="n"/>
       <c r="E114" s="321" t="inlineStr">
         <is>
@@ -38081,7 +38016,7 @@
     </row>
     <row r="115" outlineLevel="2" customFormat="1" s="13">
       <c r="B115" s="103" t="n"/>
-      <c r="C115" s="542" t="n"/>
+      <c r="C115" s="543" t="n"/>
       <c r="D115" s="458" t="n"/>
       <c r="E115" s="459" t="inlineStr">
         <is>
@@ -38161,7 +38096,7 @@
     </row>
     <row r="118" outlineLevel="2" customFormat="1" s="13">
       <c r="B118" s="103" t="n"/>
-      <c r="C118" s="542" t="n"/>
+      <c r="C118" s="543" t="n"/>
       <c r="D118" s="361" t="n"/>
       <c r="E118" s="321" t="inlineStr">
         <is>
@@ -38186,7 +38121,7 @@
     </row>
     <row r="119" outlineLevel="2" customFormat="1" s="13">
       <c r="B119" s="103" t="n"/>
-      <c r="C119" s="542" t="n"/>
+      <c r="C119" s="543" t="n"/>
       <c r="D119" s="458" t="n"/>
       <c r="E119" s="459" t="inlineStr">
         <is>
@@ -38266,7 +38201,7 @@
     </row>
     <row r="122" outlineLevel="2" customFormat="1" s="13">
       <c r="B122" s="103" t="n"/>
-      <c r="C122" s="542" t="n"/>
+      <c r="C122" s="543" t="n"/>
       <c r="D122" s="361" t="n"/>
       <c r="E122" s="321" t="inlineStr">
         <is>
@@ -38291,7 +38226,7 @@
     </row>
     <row r="123" outlineLevel="2" customFormat="1" s="13">
       <c r="B123" s="103" t="n"/>
-      <c r="C123" s="542" t="n"/>
+      <c r="C123" s="543" t="n"/>
       <c r="D123" s="458" t="n"/>
       <c r="E123" s="459" t="inlineStr">
         <is>
@@ -38371,7 +38306,7 @@
     </row>
     <row r="126" outlineLevel="2" customFormat="1" s="13">
       <c r="B126" s="103" t="n"/>
-      <c r="C126" s="542" t="n"/>
+      <c r="C126" s="543" t="n"/>
       <c r="D126" s="361" t="n"/>
       <c r="E126" s="321" t="inlineStr">
         <is>
@@ -38396,7 +38331,7 @@
     </row>
     <row r="127" outlineLevel="2" customFormat="1" s="13">
       <c r="B127" s="103" t="n"/>
-      <c r="C127" s="542" t="n"/>
+      <c r="C127" s="543" t="n"/>
       <c r="D127" s="458" t="n"/>
       <c r="E127" s="459" t="inlineStr">
         <is>
@@ -38476,7 +38411,7 @@
     </row>
     <row r="130" outlineLevel="2" customFormat="1" s="13">
       <c r="B130" s="103" t="n"/>
-      <c r="C130" s="542" t="n"/>
+      <c r="C130" s="543" t="n"/>
       <c r="D130" s="362" t="n"/>
       <c r="E130" s="324" t="inlineStr">
         <is>
@@ -38501,7 +38436,7 @@
     </row>
     <row r="131" outlineLevel="2" customFormat="1" s="13">
       <c r="B131" s="103" t="n"/>
-      <c r="C131" s="542" t="n"/>
+      <c r="C131" s="543" t="n"/>
       <c r="D131" s="458" t="n"/>
       <c r="E131" s="459" t="inlineStr">
         <is>
@@ -38577,7 +38512,7 @@
     </row>
     <row r="134" outlineLevel="2" customFormat="1" s="13">
       <c r="B134" s="103" t="n"/>
-      <c r="C134" s="621" t="n"/>
+      <c r="C134" s="611" t="n"/>
       <c r="D134" s="365" t="n"/>
       <c r="E134" s="331" t="inlineStr">
         <is>
@@ -38602,7 +38537,7 @@
     </row>
     <row r="135" outlineLevel="2" customFormat="1" s="13">
       <c r="B135" s="103" t="n"/>
-      <c r="C135" s="542" t="n"/>
+      <c r="C135" s="543" t="n"/>
       <c r="D135" s="458" t="n"/>
       <c r="E135" s="459" t="inlineStr">
         <is>
@@ -38678,7 +38613,7 @@
     </row>
     <row r="138" outlineLevel="2" customFormat="1" s="13">
       <c r="B138" s="103" t="n"/>
-      <c r="C138" s="621" t="n"/>
+      <c r="C138" s="611" t="n"/>
       <c r="D138" s="365" t="n"/>
       <c r="E138" s="331" t="inlineStr">
         <is>
@@ -38703,7 +38638,7 @@
     </row>
     <row r="139" outlineLevel="2" customFormat="1" s="13">
       <c r="B139" s="103" t="n"/>
-      <c r="C139" s="542" t="n"/>
+      <c r="C139" s="543" t="n"/>
       <c r="D139" s="458" t="n"/>
       <c r="E139" s="459" t="inlineStr">
         <is>
@@ -38779,7 +38714,7 @@
     </row>
     <row r="142" outlineLevel="2" customFormat="1" s="13">
       <c r="B142" s="103" t="n"/>
-      <c r="C142" s="621" t="n"/>
+      <c r="C142" s="611" t="n"/>
       <c r="D142" s="365" t="n"/>
       <c r="E142" s="331" t="inlineStr">
         <is>
@@ -38804,7 +38739,7 @@
     </row>
     <row r="143" outlineLevel="2" customFormat="1" s="13">
       <c r="B143" s="103" t="n"/>
-      <c r="C143" s="542" t="n"/>
+      <c r="C143" s="543" t="n"/>
       <c r="D143" s="458" t="n"/>
       <c r="E143" s="459" t="inlineStr">
         <is>
@@ -38880,7 +38815,7 @@
     </row>
     <row r="146" outlineLevel="2" customFormat="1" s="13">
       <c r="B146" s="103" t="n"/>
-      <c r="C146" s="621" t="n"/>
+      <c r="C146" s="611" t="n"/>
       <c r="D146" s="365" t="n"/>
       <c r="E146" s="331" t="inlineStr">
         <is>
@@ -38905,7 +38840,7 @@
     </row>
     <row r="147" outlineLevel="2" customFormat="1" s="13">
       <c r="B147" s="103" t="n"/>
-      <c r="C147" s="542" t="n"/>
+      <c r="C147" s="543" t="n"/>
       <c r="D147" s="458" t="n"/>
       <c r="E147" s="459" t="inlineStr">
         <is>
@@ -38981,7 +38916,7 @@
     </row>
     <row r="150" outlineLevel="2" customFormat="1" s="13">
       <c r="B150" s="103" t="n"/>
-      <c r="C150" s="621" t="n"/>
+      <c r="C150" s="611" t="n"/>
       <c r="D150" s="365" t="n"/>
       <c r="E150" s="331" t="inlineStr">
         <is>
@@ -39006,7 +38941,7 @@
     </row>
     <row r="151" outlineLevel="2" customFormat="1" s="13">
       <c r="B151" s="103" t="n"/>
-      <c r="C151" s="542" t="n"/>
+      <c r="C151" s="543" t="n"/>
       <c r="D151" s="458" t="n"/>
       <c r="E151" s="459" t="inlineStr">
         <is>
@@ -39082,7 +39017,7 @@
     </row>
     <row r="154" outlineLevel="2" customFormat="1" s="13">
       <c r="B154" s="103" t="n"/>
-      <c r="C154" s="621" t="n"/>
+      <c r="C154" s="611" t="n"/>
       <c r="D154" s="365" t="n"/>
       <c r="E154" s="331" t="inlineStr">
         <is>
@@ -39107,7 +39042,7 @@
     </row>
     <row r="155" outlineLevel="2" customFormat="1" s="13">
       <c r="B155" s="103" t="n"/>
-      <c r="C155" s="542" t="n"/>
+      <c r="C155" s="543" t="n"/>
       <c r="D155" s="458" t="n"/>
       <c r="E155" s="459" t="inlineStr">
         <is>
@@ -39183,7 +39118,7 @@
     </row>
     <row r="158" outlineLevel="2" customFormat="1" s="13">
       <c r="B158" s="103" t="n"/>
-      <c r="C158" s="621" t="n"/>
+      <c r="C158" s="611" t="n"/>
       <c r="D158" s="365" t="n"/>
       <c r="E158" s="331" t="inlineStr">
         <is>
@@ -39208,7 +39143,7 @@
     </row>
     <row r="159" outlineLevel="2" customFormat="1" s="13">
       <c r="B159" s="103" t="n"/>
-      <c r="C159" s="542" t="n"/>
+      <c r="C159" s="543" t="n"/>
       <c r="D159" s="458" t="n"/>
       <c r="E159" s="459" t="inlineStr">
         <is>
@@ -39284,7 +39219,7 @@
     </row>
     <row r="162" outlineLevel="2" customFormat="1" s="13">
       <c r="B162" s="103" t="n"/>
-      <c r="C162" s="542" t="n"/>
+      <c r="C162" s="543" t="n"/>
       <c r="D162" s="367" t="n"/>
       <c r="E162" s="337" t="inlineStr">
         <is>
@@ -39311,7 +39246,7 @@
     </row>
     <row r="163" outlineLevel="2" customFormat="1" s="13">
       <c r="B163" s="103" t="n"/>
-      <c r="C163" s="542" t="n"/>
+      <c r="C163" s="543" t="n"/>
       <c r="D163" s="458" t="n"/>
       <c r="E163" s="459" t="inlineStr">
         <is>
@@ -39348,7 +39283,7 @@
       <c r="K164" s="342" t="n"/>
       <c r="L164" s="343" t="n"/>
     </row>
-    <row r="165" outlineLevel="1" s="594">
+    <row r="165" outlineLevel="1" s="592">
       <c r="B165" s="376" t="n"/>
       <c r="C165" s="158" t="inlineStr">
         <is>
@@ -39379,7 +39314,7 @@
       <c r="K165" s="346" t="n"/>
       <c r="L165" s="346" t="n"/>
     </row>
-    <row r="166" outlineLevel="2" s="594">
+    <row r="166" outlineLevel="2" s="592">
       <c r="B166" s="376" t="n"/>
       <c r="D166" s="370" t="n"/>
       <c r="E166" s="348" t="inlineStr">
@@ -39407,7 +39342,7 @@
     </row>
     <row r="167" outlineLevel="2" customFormat="1" s="13">
       <c r="B167" s="103" t="n"/>
-      <c r="C167" s="542" t="n"/>
+      <c r="C167" s="543" t="n"/>
       <c r="D167" s="458" t="n"/>
       <c r="E167" s="459" t="inlineStr">
         <is>
@@ -39444,7 +39379,7 @@
       <c r="K168" s="352" t="n"/>
       <c r="L168" s="353" t="n"/>
     </row>
-    <row r="169" outlineLevel="1" s="594">
+    <row r="169" outlineLevel="1" s="592">
       <c r="B169" s="376" t="n"/>
       <c r="C169" s="158" t="inlineStr">
         <is>
@@ -39475,7 +39410,7 @@
       <c r="K169" s="346" t="n"/>
       <c r="L169" s="346" t="n"/>
     </row>
-    <row r="170" outlineLevel="2" s="594">
+    <row r="170" outlineLevel="2" s="592">
       <c r="B170" s="376" t="n"/>
       <c r="D170" s="370" t="n"/>
       <c r="E170" s="348" t="inlineStr">
@@ -39497,7 +39432,7 @@
     </row>
     <row r="171" outlineLevel="2" customFormat="1" s="13">
       <c r="B171" s="103" t="n"/>
-      <c r="C171" s="542" t="n"/>
+      <c r="C171" s="543" t="n"/>
       <c r="D171" s="458" t="n"/>
       <c r="E171" s="459" t="inlineStr">
         <is>
@@ -39534,7 +39469,7 @@
       <c r="K172" s="352" t="n"/>
       <c r="L172" s="353" t="n"/>
     </row>
-    <row r="173" outlineLevel="1" s="594">
+    <row r="173" outlineLevel="1" s="592">
       <c r="B173" s="376" t="n"/>
       <c r="C173" s="158" t="inlineStr">
         <is>
@@ -39565,7 +39500,7 @@
       <c r="K173" s="346" t="n"/>
       <c r="L173" s="346" t="n"/>
     </row>
-    <row r="174" outlineLevel="2" s="594">
+    <row r="174" outlineLevel="2" s="592">
       <c r="B174" s="376" t="n"/>
       <c r="D174" s="370" t="n"/>
       <c r="E174" s="348" t="inlineStr">
@@ -39587,7 +39522,7 @@
     </row>
     <row r="175" outlineLevel="2" customFormat="1" s="13">
       <c r="B175" s="103" t="n"/>
-      <c r="C175" s="542" t="n"/>
+      <c r="C175" s="543" t="n"/>
       <c r="D175" s="458" t="n"/>
       <c r="E175" s="459" t="inlineStr">
         <is>
@@ -39624,7 +39559,7 @@
       <c r="K176" s="352" t="n"/>
       <c r="L176" s="353" t="n"/>
     </row>
-    <row r="177" outlineLevel="1" s="594">
+    <row r="177" outlineLevel="1" s="592">
       <c r="B177" s="376" t="n"/>
       <c r="C177" s="158" t="inlineStr">
         <is>
@@ -39655,7 +39590,7 @@
       <c r="K177" s="346" t="n"/>
       <c r="L177" s="346" t="n"/>
     </row>
-    <row r="178" outlineLevel="2" s="594">
+    <row r="178" outlineLevel="2" s="592">
       <c r="B178" s="376" t="n"/>
       <c r="D178" s="370" t="n"/>
       <c r="E178" s="348" t="inlineStr">
@@ -39677,7 +39612,7 @@
     </row>
     <row r="179" outlineLevel="2" customFormat="1" s="13">
       <c r="B179" s="103" t="n"/>
-      <c r="C179" s="542" t="n"/>
+      <c r="C179" s="543" t="n"/>
       <c r="D179" s="458" t="n"/>
       <c r="E179" s="459" t="inlineStr">
         <is>
@@ -39714,7 +39649,7 @@
       <c r="K180" s="352" t="n"/>
       <c r="L180" s="353" t="n"/>
     </row>
-    <row r="181" outlineLevel="1" s="594">
+    <row r="181" outlineLevel="1" s="592">
       <c r="B181" s="376" t="n"/>
       <c r="C181" s="158" t="inlineStr">
         <is>
@@ -39745,7 +39680,7 @@
       <c r="K181" s="346" t="n"/>
       <c r="L181" s="346" t="n"/>
     </row>
-    <row r="182" outlineLevel="2" s="594">
+    <row r="182" outlineLevel="2" s="592">
       <c r="B182" s="376" t="n"/>
       <c r="D182" s="370" t="n"/>
       <c r="E182" s="348" t="inlineStr">
@@ -39767,7 +39702,7 @@
     </row>
     <row r="183" outlineLevel="2" customFormat="1" s="13">
       <c r="B183" s="103" t="n"/>
-      <c r="C183" s="542" t="n"/>
+      <c r="C183" s="543" t="n"/>
       <c r="D183" s="458" t="n"/>
       <c r="E183" s="459" t="inlineStr">
         <is>
@@ -39804,7 +39739,7 @@
       <c r="K184" s="352" t="n"/>
       <c r="L184" s="353" t="n"/>
     </row>
-    <row r="185" outlineLevel="1" s="594">
+    <row r="185" outlineLevel="1" s="592">
       <c r="B185" s="376" t="n"/>
       <c r="C185" s="158" t="inlineStr">
         <is>
@@ -39835,7 +39770,7 @@
       <c r="K185" s="346" t="n"/>
       <c r="L185" s="346" t="n"/>
     </row>
-    <row r="186" outlineLevel="2" s="594">
+    <row r="186" outlineLevel="2" s="592">
       <c r="B186" s="376" t="n"/>
       <c r="D186" s="372" t="n"/>
       <c r="E186" s="354" t="inlineStr">
@@ -39863,7 +39798,7 @@
     </row>
     <row r="187" outlineLevel="2" customFormat="1" s="13">
       <c r="B187" s="103" t="n"/>
-      <c r="C187" s="542" t="n"/>
+      <c r="C187" s="543" t="n"/>
       <c r="D187" s="458" t="n"/>
       <c r="E187" s="459" t="inlineStr">
         <is>
@@ -39900,7 +39835,7 @@
       <c r="K188" s="342" t="n"/>
       <c r="L188" s="343" t="n"/>
     </row>
-    <row r="189" outlineLevel="1" s="594">
+    <row r="189" outlineLevel="1" s="592">
       <c r="B189" s="376" t="n"/>
       <c r="C189" s="158" t="inlineStr">
         <is>
@@ -39934,7 +39869,7 @@
       <c r="K189" s="346" t="n"/>
       <c r="L189" s="346" t="n"/>
     </row>
-    <row r="190" outlineLevel="2" s="594">
+    <row r="190" outlineLevel="2" s="592">
       <c r="B190" s="376" t="n"/>
       <c r="D190" s="373" t="n"/>
       <c r="E190" s="356" t="inlineStr">
@@ -39962,7 +39897,7 @@
     </row>
     <row r="191" outlineLevel="2" customFormat="1" s="13">
       <c r="B191" s="103" t="n"/>
-      <c r="C191" s="542" t="n"/>
+      <c r="C191" s="543" t="n"/>
       <c r="D191" s="458" t="n"/>
       <c r="E191" s="459" t="inlineStr">
         <is>
@@ -39999,7 +39934,7 @@
       <c r="K192" s="352" t="n"/>
       <c r="L192" s="353" t="n"/>
     </row>
-    <row r="193" outlineLevel="1" s="594">
+    <row r="193" outlineLevel="1" s="592">
       <c r="B193" s="376" t="n"/>
       <c r="C193" s="158" t="inlineStr">
         <is>
@@ -40033,7 +39968,7 @@
       <c r="K193" s="346" t="n"/>
       <c r="L193" s="346" t="n"/>
     </row>
-    <row r="194" outlineLevel="2" s="594">
+    <row r="194" outlineLevel="2" s="592">
       <c r="B194" s="376" t="n"/>
       <c r="D194" s="373" t="n"/>
       <c r="E194" s="356" t="inlineStr">
@@ -40061,7 +39996,7 @@
     </row>
     <row r="195" outlineLevel="2" customFormat="1" s="13">
       <c r="B195" s="103" t="n"/>
-      <c r="C195" s="542" t="n"/>
+      <c r="C195" s="543" t="n"/>
       <c r="D195" s="458" t="n"/>
       <c r="E195" s="459" t="inlineStr">
         <is>
@@ -40098,7 +40033,7 @@
       <c r="K196" s="352" t="n"/>
       <c r="L196" s="353" t="n"/>
     </row>
-    <row r="197" outlineLevel="1" s="594">
+    <row r="197" outlineLevel="1" s="592">
       <c r="B197" s="376" t="n"/>
       <c r="C197" s="158" t="inlineStr">
         <is>
@@ -40132,7 +40067,7 @@
       <c r="K197" s="346" t="n"/>
       <c r="L197" s="346" t="n"/>
     </row>
-    <row r="198" outlineLevel="2" s="594">
+    <row r="198" outlineLevel="2" s="592">
       <c r="B198" s="376" t="n"/>
       <c r="D198" s="373" t="n"/>
       <c r="E198" s="356" t="inlineStr">
@@ -40160,7 +40095,7 @@
     </row>
     <row r="199" outlineLevel="2" customFormat="1" s="13">
       <c r="B199" s="103" t="n"/>
-      <c r="C199" s="542" t="n"/>
+      <c r="C199" s="543" t="n"/>
       <c r="D199" s="458" t="n"/>
       <c r="E199" s="459" t="inlineStr">
         <is>
@@ -40197,7 +40132,7 @@
       <c r="K200" s="352" t="n"/>
       <c r="L200" s="353" t="n"/>
     </row>
-    <row r="201" outlineLevel="1" s="594">
+    <row r="201" outlineLevel="1" s="592">
       <c r="B201" s="376" t="n"/>
       <c r="C201" s="158" t="inlineStr">
         <is>
@@ -40231,7 +40166,7 @@
       <c r="K201" s="346" t="n"/>
       <c r="L201" s="346" t="n"/>
     </row>
-    <row r="202" outlineLevel="2" s="594">
+    <row r="202" outlineLevel="2" s="592">
       <c r="B202" s="376" t="n"/>
       <c r="D202" s="373" t="n"/>
       <c r="E202" s="356" t="inlineStr">
@@ -40259,7 +40194,7 @@
     </row>
     <row r="203" outlineLevel="2" customFormat="1" s="13">
       <c r="B203" s="103" t="n"/>
-      <c r="C203" s="542" t="n"/>
+      <c r="C203" s="543" t="n"/>
       <c r="D203" s="458" t="n"/>
       <c r="E203" s="459" t="inlineStr">
         <is>
@@ -40296,7 +40231,7 @@
       <c r="K204" s="352" t="n"/>
       <c r="L204" s="353" t="n"/>
     </row>
-    <row r="205" outlineLevel="1" s="594">
+    <row r="205" outlineLevel="1" s="592">
       <c r="B205" s="376" t="n"/>
       <c r="C205" s="158" t="inlineStr">
         <is>
@@ -40330,7 +40265,7 @@
       <c r="K205" s="346" t="n"/>
       <c r="L205" s="346" t="n"/>
     </row>
-    <row r="206" outlineLevel="2" s="594">
+    <row r="206" outlineLevel="2" s="592">
       <c r="B206" s="376" t="n"/>
       <c r="D206" s="373" t="n"/>
       <c r="E206" s="356" t="inlineStr">
@@ -40358,7 +40293,7 @@
     </row>
     <row r="207" outlineLevel="2" customFormat="1" s="13">
       <c r="B207" s="103" t="n"/>
-      <c r="C207" s="542" t="n"/>
+      <c r="C207" s="543" t="n"/>
       <c r="D207" s="458" t="n"/>
       <c r="E207" s="459" t="inlineStr">
         <is>
@@ -40395,7 +40330,7 @@
       <c r="K208" s="352" t="n"/>
       <c r="L208" s="353" t="n"/>
     </row>
-    <row r="209" outlineLevel="1" s="594">
+    <row r="209" outlineLevel="1" s="592">
       <c r="B209" s="376" t="n"/>
       <c r="C209" s="158" t="inlineStr">
         <is>
@@ -40429,7 +40364,7 @@
       <c r="K209" s="346" t="n"/>
       <c r="L209" s="346" t="n"/>
     </row>
-    <row r="210" outlineLevel="2" s="594">
+    <row r="210" outlineLevel="2" s="592">
       <c r="B210" s="376" t="n"/>
       <c r="D210" s="373" t="n"/>
       <c r="E210" s="356" t="inlineStr">
@@ -40457,7 +40392,7 @@
     </row>
     <row r="211" outlineLevel="2" customFormat="1" s="13">
       <c r="B211" s="103" t="n"/>
-      <c r="C211" s="542" t="n"/>
+      <c r="C211" s="543" t="n"/>
       <c r="D211" s="458" t="n"/>
       <c r="E211" s="459" t="inlineStr">
         <is>
@@ -40494,7 +40429,7 @@
       <c r="K212" s="352" t="n"/>
       <c r="L212" s="353" t="n"/>
     </row>
-    <row r="213" outlineLevel="1" s="594">
+    <row r="213" outlineLevel="1" s="592">
       <c r="B213" s="376" t="n"/>
       <c r="C213" s="158" t="inlineStr">
         <is>
@@ -40528,7 +40463,7 @@
       <c r="K213" s="346" t="n"/>
       <c r="L213" s="346" t="n"/>
     </row>
-    <row r="214" outlineLevel="2" s="594">
+    <row r="214" outlineLevel="2" s="592">
       <c r="B214" s="376" t="n"/>
       <c r="D214" s="373" t="n"/>
       <c r="E214" s="356" t="inlineStr">
@@ -40556,7 +40491,7 @@
     </row>
     <row r="215" outlineLevel="2" customFormat="1" s="13">
       <c r="B215" s="103" t="n"/>
-      <c r="C215" s="542" t="n"/>
+      <c r="C215" s="543" t="n"/>
       <c r="D215" s="458" t="n"/>
       <c r="E215" s="459" t="inlineStr">
         <is>
@@ -40593,7 +40528,7 @@
       <c r="K216" s="352" t="n"/>
       <c r="L216" s="353" t="n"/>
     </row>
-    <row r="217" outlineLevel="1" s="594">
+    <row r="217" outlineLevel="1" s="592">
       <c r="B217" s="376" t="n"/>
       <c r="C217" s="158" t="inlineStr">
         <is>
@@ -40627,7 +40562,7 @@
       <c r="K217" s="346" t="n"/>
       <c r="L217" s="346" t="n"/>
     </row>
-    <row r="218" outlineLevel="2" s="594">
+    <row r="218" outlineLevel="2" s="592">
       <c r="B218" s="376" t="n"/>
       <c r="D218" s="372" t="n"/>
       <c r="E218" s="354" t="inlineStr">
@@ -40655,7 +40590,7 @@
     </row>
     <row r="219" outlineLevel="2" customFormat="1" s="13">
       <c r="B219" s="103" t="n"/>
-      <c r="C219" s="542" t="n"/>
+      <c r="C219" s="543" t="n"/>
       <c r="D219" s="458" t="n"/>
       <c r="E219" s="459" t="inlineStr">
         <is>
@@ -40692,7 +40627,7 @@
       <c r="K220" s="342" t="n"/>
       <c r="L220" s="343" t="n"/>
     </row>
-    <row r="221" outlineLevel="1" s="594">
+    <row r="221" outlineLevel="1" s="592">
       <c r="B221" s="376" t="n"/>
       <c r="C221" s="158" t="inlineStr">
         <is>
@@ -40729,7 +40664,7 @@
       <c r="K221" s="346" t="n"/>
       <c r="L221" s="346" t="n"/>
     </row>
-    <row r="222" outlineLevel="2" s="594">
+    <row r="222" outlineLevel="2" s="592">
       <c r="B222" s="376" t="n"/>
       <c r="D222" s="373" t="n"/>
       <c r="E222" s="356" t="inlineStr">
@@ -40755,7 +40690,7 @@
     </row>
     <row r="223" outlineLevel="2" customFormat="1" s="13">
       <c r="B223" s="103" t="n"/>
-      <c r="C223" s="542" t="n"/>
+      <c r="C223" s="543" t="n"/>
       <c r="D223" s="458" t="n"/>
       <c r="E223" s="459" t="inlineStr">
         <is>
@@ -40792,7 +40727,7 @@
       <c r="K224" s="352" t="n"/>
       <c r="L224" s="353" t="n"/>
     </row>
-    <row r="225" outlineLevel="1" s="594">
+    <row r="225" outlineLevel="1" s="592">
       <c r="B225" s="376" t="n"/>
       <c r="C225" s="158" t="inlineStr">
         <is>
@@ -40829,7 +40764,7 @@
       <c r="K225" s="346" t="n"/>
       <c r="L225" s="346" t="n"/>
     </row>
-    <row r="226" outlineLevel="2" s="594">
+    <row r="226" outlineLevel="2" s="592">
       <c r="B226" s="376" t="n"/>
       <c r="D226" s="373" t="n"/>
       <c r="E226" s="356" t="inlineStr">
@@ -40855,7 +40790,7 @@
     </row>
     <row r="227" outlineLevel="2" customFormat="1" s="13">
       <c r="B227" s="103" t="n"/>
-      <c r="C227" s="542" t="n"/>
+      <c r="C227" s="543" t="n"/>
       <c r="D227" s="458" t="n"/>
       <c r="E227" s="459" t="inlineStr">
         <is>
@@ -40892,7 +40827,7 @@
       <c r="K228" s="352" t="n"/>
       <c r="L228" s="353" t="n"/>
     </row>
-    <row r="229" outlineLevel="1" s="594">
+    <row r="229" outlineLevel="1" s="592">
       <c r="B229" s="376" t="n"/>
       <c r="C229" s="158" t="inlineStr">
         <is>
@@ -40929,7 +40864,7 @@
       <c r="K229" s="346" t="n"/>
       <c r="L229" s="346" t="n"/>
     </row>
-    <row r="230" outlineLevel="2" s="594">
+    <row r="230" outlineLevel="2" s="592">
       <c r="B230" s="376" t="n"/>
       <c r="D230" s="373" t="n"/>
       <c r="E230" s="356" t="inlineStr">
@@ -40955,7 +40890,7 @@
     </row>
     <row r="231" outlineLevel="2" customFormat="1" s="13">
       <c r="B231" s="103" t="n"/>
-      <c r="C231" s="542" t="n"/>
+      <c r="C231" s="543" t="n"/>
       <c r="D231" s="458" t="n"/>
       <c r="E231" s="459" t="inlineStr">
         <is>
@@ -40992,7 +40927,7 @@
       <c r="K232" s="352" t="n"/>
       <c r="L232" s="353" t="n"/>
     </row>
-    <row r="233" outlineLevel="1" s="594">
+    <row r="233" outlineLevel="1" s="592">
       <c r="B233" s="376" t="n"/>
       <c r="C233" s="158" t="inlineStr">
         <is>
@@ -41029,7 +40964,7 @@
       <c r="K233" s="346" t="n"/>
       <c r="L233" s="346" t="n"/>
     </row>
-    <row r="234" outlineLevel="2" s="594">
+    <row r="234" outlineLevel="2" s="592">
       <c r="B234" s="376" t="n"/>
       <c r="D234" s="373" t="n"/>
       <c r="E234" s="356" t="inlineStr">
@@ -41055,7 +40990,7 @@
     </row>
     <row r="235" outlineLevel="2" customFormat="1" s="13">
       <c r="B235" s="103" t="n"/>
-      <c r="C235" s="542" t="n"/>
+      <c r="C235" s="543" t="n"/>
       <c r="D235" s="458" t="n"/>
       <c r="E235" s="459" t="inlineStr">
         <is>
@@ -41092,7 +41027,7 @@
       <c r="K236" s="352" t="n"/>
       <c r="L236" s="353" t="n"/>
     </row>
-    <row r="237" outlineLevel="1" s="594">
+    <row r="237" outlineLevel="1" s="592">
       <c r="B237" s="376" t="n"/>
       <c r="C237" s="158" t="inlineStr">
         <is>
@@ -41129,7 +41064,7 @@
       <c r="K237" s="346" t="n"/>
       <c r="L237" s="346" t="n"/>
     </row>
-    <row r="238" outlineLevel="2" s="594">
+    <row r="238" outlineLevel="2" s="592">
       <c r="B238" s="376" t="n"/>
       <c r="D238" s="373" t="n"/>
       <c r="E238" s="356" t="inlineStr">
@@ -41153,7 +41088,7 @@
       <c r="K238" s="357" t="n"/>
       <c r="L238" s="357" t="n"/>
     </row>
-    <row r="239" outlineLevel="2" s="594">
+    <row r="239" outlineLevel="2" s="592">
       <c r="B239" s="376" t="n"/>
       <c r="D239" s="357" t="n"/>
       <c r="E239" s="459" t="inlineStr">
@@ -41191,7 +41126,7 @@
       <c r="K240" s="352" t="n"/>
       <c r="L240" s="353" t="n"/>
     </row>
-    <row r="241" outlineLevel="1" s="594">
+    <row r="241" outlineLevel="1" s="592">
       <c r="B241" s="376" t="n"/>
       <c r="C241" s="158" t="inlineStr">
         <is>
@@ -41228,7 +41163,7 @@
       <c r="K241" s="346" t="n"/>
       <c r="L241" s="346" t="n"/>
     </row>
-    <row r="242" outlineLevel="2" s="594">
+    <row r="242" outlineLevel="2" s="592">
       <c r="B242" s="376" t="n"/>
       <c r="D242" s="373" t="n"/>
       <c r="E242" s="356" t="inlineStr">
@@ -41252,7 +41187,7 @@
       <c r="K242" s="357" t="n"/>
       <c r="L242" s="357" t="n"/>
     </row>
-    <row r="243" outlineLevel="2" s="594">
+    <row r="243" outlineLevel="2" s="592">
       <c r="B243" s="376" t="n"/>
       <c r="D243" s="357" t="n"/>
       <c r="E243" s="459" t="inlineStr">
@@ -41290,7 +41225,7 @@
       <c r="K244" s="352" t="n"/>
       <c r="L244" s="353" t="n"/>
     </row>
-    <row r="245" outlineLevel="1" s="594">
+    <row r="245" outlineLevel="1" s="592">
       <c r="B245" s="376" t="n"/>
       <c r="C245" s="158" t="inlineStr">
         <is>
@@ -41327,7 +41262,7 @@
       <c r="K245" s="346" t="n"/>
       <c r="L245" s="346" t="n"/>
     </row>
-    <row r="246" outlineLevel="2" s="594">
+    <row r="246" outlineLevel="2" s="592">
       <c r="B246" s="376" t="n"/>
       <c r="D246" s="373" t="n"/>
       <c r="E246" s="356" t="inlineStr">
@@ -41351,7 +41286,7 @@
       <c r="K246" s="357" t="n"/>
       <c r="L246" s="357" t="n"/>
     </row>
-    <row r="247" outlineLevel="2" s="594">
+    <row r="247" outlineLevel="2" s="592">
       <c r="B247" s="376" t="n"/>
       <c r="D247" s="357" t="n"/>
       <c r="E247" s="459" t="inlineStr">
@@ -41389,7 +41324,7 @@
       <c r="K248" s="352" t="n"/>
       <c r="L248" s="353" t="n"/>
     </row>
-    <row r="249" outlineLevel="1" s="594">
+    <row r="249" outlineLevel="1" s="592">
       <c r="B249" s="376" t="n"/>
       <c r="C249" s="158" t="inlineStr">
         <is>
@@ -41426,7 +41361,7 @@
       <c r="K249" s="346" t="n"/>
       <c r="L249" s="346" t="n"/>
     </row>
-    <row r="250" outlineLevel="2" s="594">
+    <row r="250" outlineLevel="2" s="592">
       <c r="B250" s="376" t="n"/>
       <c r="D250" s="373" t="n"/>
       <c r="E250" s="356" t="inlineStr">
@@ -41450,7 +41385,7 @@
       <c r="K250" s="357" t="n"/>
       <c r="L250" s="357" t="n"/>
     </row>
-    <row r="251" outlineLevel="2" s="594">
+    <row r="251" outlineLevel="2" s="592">
       <c r="B251" s="376" t="n"/>
       <c r="D251" s="357" t="n"/>
       <c r="E251" s="459" t="inlineStr">
@@ -41488,7 +41423,7 @@
       <c r="K252" s="352" t="n"/>
       <c r="L252" s="353" t="n"/>
     </row>
-    <row r="253" outlineLevel="1" s="594">
+    <row r="253" outlineLevel="1" s="592">
       <c r="B253" s="376" t="n"/>
       <c r="C253" s="158" t="inlineStr">
         <is>
@@ -41525,7 +41460,7 @@
       <c r="K253" s="346" t="n"/>
       <c r="L253" s="346" t="n"/>
     </row>
-    <row r="254" outlineLevel="2" s="594">
+    <row r="254" outlineLevel="2" s="592">
       <c r="B254" s="376" t="n"/>
       <c r="D254" s="373" t="n"/>
       <c r="E254" s="356" t="inlineStr">
@@ -41549,7 +41484,7 @@
       <c r="K254" s="357" t="n"/>
       <c r="L254" s="357" t="n"/>
     </row>
-    <row r="255" outlineLevel="2" s="594">
+    <row r="255" outlineLevel="2" s="592">
       <c r="B255" s="376" t="n"/>
       <c r="D255" s="357" t="n"/>
       <c r="E255" s="459" t="inlineStr">
@@ -41587,7 +41522,7 @@
       <c r="K256" s="352" t="n"/>
       <c r="L256" s="353" t="n"/>
     </row>
-    <row r="257" outlineLevel="1" s="594">
+    <row r="257" outlineLevel="1" s="592">
       <c r="B257" s="376" t="n"/>
       <c r="C257" s="158" t="inlineStr">
         <is>
@@ -41624,7 +41559,7 @@
       <c r="K257" s="346" t="n"/>
       <c r="L257" s="346" t="n"/>
     </row>
-    <row r="258" outlineLevel="2" s="594">
+    <row r="258" outlineLevel="2" s="592">
       <c r="B258" s="376" t="n"/>
       <c r="D258" s="373" t="n"/>
       <c r="E258" s="356" t="inlineStr">
@@ -41648,7 +41583,7 @@
       <c r="K258" s="357" t="n"/>
       <c r="L258" s="357" t="n"/>
     </row>
-    <row r="259" outlineLevel="2" s="594">
+    <row r="259" outlineLevel="2" s="592">
       <c r="B259" s="376" t="n"/>
       <c r="D259" s="357" t="n"/>
       <c r="E259" s="459" t="inlineStr">
@@ -41686,7 +41621,7 @@
       <c r="K260" s="352" t="n"/>
       <c r="L260" s="353" t="n"/>
     </row>
-    <row r="261" outlineLevel="1" s="594">
+    <row r="261" outlineLevel="1" s="592">
       <c r="B261" s="376" t="n"/>
       <c r="C261" s="158" t="inlineStr">
         <is>
@@ -41723,7 +41658,7 @@
       <c r="K261" s="346" t="n"/>
       <c r="L261" s="346" t="n"/>
     </row>
-    <row r="262" outlineLevel="2" s="594">
+    <row r="262" outlineLevel="2" s="592">
       <c r="B262" s="376" t="n"/>
       <c r="D262" s="373" t="n"/>
       <c r="E262" s="356" t="inlineStr">
@@ -41747,7 +41682,7 @@
       <c r="K262" s="357" t="n"/>
       <c r="L262" s="357" t="n"/>
     </row>
-    <row r="263" outlineLevel="2" s="594">
+    <row r="263" outlineLevel="2" s="592">
       <c r="B263" s="376" t="n"/>
       <c r="D263" s="357" t="n"/>
       <c r="E263" s="459" t="inlineStr">
@@ -41785,7 +41720,7 @@
       <c r="K264" s="352" t="n"/>
       <c r="L264" s="353" t="n"/>
     </row>
-    <row r="265" outlineLevel="1" s="594">
+    <row r="265" outlineLevel="1" s="592">
       <c r="B265" s="376" t="n"/>
       <c r="C265" s="158" t="inlineStr">
         <is>
@@ -41822,7 +41757,7 @@
       <c r="K265" s="346" t="n"/>
       <c r="L265" s="346" t="n"/>
     </row>
-    <row r="266" outlineLevel="2" s="594">
+    <row r="266" outlineLevel="2" s="592">
       <c r="B266" s="376" t="n"/>
       <c r="D266" s="373" t="n"/>
       <c r="E266" s="356" t="inlineStr">
@@ -41846,7 +41781,7 @@
       <c r="K266" s="357" t="n"/>
       <c r="L266" s="357" t="n"/>
     </row>
-    <row r="267" outlineLevel="2" s="594">
+    <row r="267" outlineLevel="2" s="592">
       <c r="B267" s="376" t="n"/>
       <c r="D267" s="357" t="n"/>
       <c r="E267" s="459" t="inlineStr">
@@ -41884,7 +41819,7 @@
       <c r="K268" s="352" t="n"/>
       <c r="L268" s="353" t="n"/>
     </row>
-    <row r="269" outlineLevel="1" s="594">
+    <row r="269" outlineLevel="1" s="592">
       <c r="B269" s="376" t="n"/>
       <c r="C269" s="158" t="inlineStr">
         <is>
@@ -41921,7 +41856,7 @@
       <c r="K269" s="346" t="n"/>
       <c r="L269" s="346" t="n"/>
     </row>
-    <row r="270" outlineLevel="2" s="594">
+    <row r="270" outlineLevel="2" s="592">
       <c r="B270" s="376" t="n"/>
       <c r="D270" s="373" t="n"/>
       <c r="E270" s="356" t="inlineStr">
@@ -41945,7 +41880,7 @@
       <c r="K270" s="357" t="n"/>
       <c r="L270" s="357" t="n"/>
     </row>
-    <row r="271" outlineLevel="2" s="594">
+    <row r="271" outlineLevel="2" s="592">
       <c r="B271" s="376" t="n"/>
       <c r="D271" s="357" t="n"/>
       <c r="E271" s="459" t="inlineStr">
@@ -41983,7 +41918,7 @@
       <c r="K272" s="352" t="n"/>
       <c r="L272" s="353" t="n"/>
     </row>
-    <row r="273" outlineLevel="1" s="594">
+    <row r="273" outlineLevel="1" s="592">
       <c r="B273" s="376" t="n"/>
       <c r="C273" s="158" t="inlineStr">
         <is>
@@ -42020,7 +41955,7 @@
       <c r="K273" s="346" t="n"/>
       <c r="L273" s="346" t="n"/>
     </row>
-    <row r="274" outlineLevel="2" s="594">
+    <row r="274" outlineLevel="2" s="592">
       <c r="B274" s="376" t="n"/>
       <c r="D274" s="372" t="n"/>
       <c r="E274" s="354" t="inlineStr">
@@ -42040,7 +41975,7 @@
       <c r="K274" s="355" t="n"/>
       <c r="L274" s="355" t="n"/>
     </row>
-    <row r="275" outlineLevel="2" s="594">
+    <row r="275" outlineLevel="2" s="592">
       <c r="B275" s="376" t="n"/>
       <c r="D275" s="357" t="n"/>
       <c r="E275" s="459" t="inlineStr">
@@ -42078,7 +42013,7 @@
       <c r="K276" s="342" t="n"/>
       <c r="L276" s="343" t="n"/>
     </row>
-    <row r="277" outlineLevel="1" s="594">
+    <row r="277" outlineLevel="1" s="592">
       <c r="B277" s="376" t="n"/>
       <c r="C277" s="158" t="inlineStr">
         <is>
@@ -42112,7 +42047,7 @@
       <c r="K277" s="346" t="n"/>
       <c r="L277" s="346" t="n"/>
     </row>
-    <row r="278" outlineLevel="2" s="594">
+    <row r="278" outlineLevel="2" s="592">
       <c r="B278" s="376" t="n"/>
       <c r="D278" s="373" t="n"/>
       <c r="E278" s="356" t="inlineStr">
@@ -42134,7 +42069,7 @@
       <c r="K278" s="357" t="n"/>
       <c r="L278" s="357" t="n"/>
     </row>
-    <row r="279" outlineLevel="2" s="594">
+    <row r="279" outlineLevel="2" s="592">
       <c r="B279" s="376" t="n"/>
       <c r="D279" s="357" t="n"/>
       <c r="E279" s="459" t="inlineStr">
@@ -42172,7 +42107,7 @@
       <c r="K280" s="352" t="n"/>
       <c r="L280" s="353" t="n"/>
     </row>
-    <row r="281" outlineLevel="1" s="594">
+    <row r="281" outlineLevel="1" s="592">
       <c r="B281" s="376" t="n"/>
       <c r="C281" s="158" t="inlineStr">
         <is>
@@ -42206,7 +42141,7 @@
       <c r="K281" s="346" t="n"/>
       <c r="L281" s="346" t="n"/>
     </row>
-    <row r="282" outlineLevel="2" s="594">
+    <row r="282" outlineLevel="2" s="592">
       <c r="B282" s="376" t="n"/>
       <c r="D282" s="373" t="n"/>
       <c r="E282" s="356" t="inlineStr">
@@ -42228,7 +42163,7 @@
       <c r="K282" s="357" t="n"/>
       <c r="L282" s="357" t="n"/>
     </row>
-    <row r="283" outlineLevel="2" s="594">
+    <row r="283" outlineLevel="2" s="592">
       <c r="B283" s="376" t="n"/>
       <c r="D283" s="357" t="n"/>
       <c r="E283" s="459" t="inlineStr">
@@ -42266,7 +42201,7 @@
       <c r="K284" s="352" t="n"/>
       <c r="L284" s="353" t="n"/>
     </row>
-    <row r="285" outlineLevel="1" s="594">
+    <row r="285" outlineLevel="1" s="592">
       <c r="B285" s="376" t="n"/>
       <c r="C285" s="158" t="inlineStr">
         <is>
@@ -42300,7 +42235,7 @@
       <c r="K285" s="346" t="n"/>
       <c r="L285" s="346" t="n"/>
     </row>
-    <row r="286" outlineLevel="2" s="594">
+    <row r="286" outlineLevel="2" s="592">
       <c r="B286" s="376" t="n"/>
       <c r="D286" s="373" t="n"/>
       <c r="E286" s="356" t="inlineStr">
@@ -42322,7 +42257,7 @@
       <c r="K286" s="357" t="n"/>
       <c r="L286" s="357" t="n"/>
     </row>
-    <row r="287" outlineLevel="2" s="594">
+    <row r="287" outlineLevel="2" s="592">
       <c r="B287" s="376" t="n"/>
       <c r="D287" s="357" t="n"/>
       <c r="E287" s="459" t="inlineStr">
@@ -42360,7 +42295,7 @@
       <c r="K288" s="352" t="n"/>
       <c r="L288" s="353" t="n"/>
     </row>
-    <row r="289" outlineLevel="1" s="594">
+    <row r="289" outlineLevel="1" s="592">
       <c r="B289" s="376" t="n"/>
       <c r="C289" s="158" t="inlineStr">
         <is>
@@ -42394,7 +42329,7 @@
       <c r="K289" s="346" t="n"/>
       <c r="L289" s="346" t="n"/>
     </row>
-    <row r="290" outlineLevel="2" s="594">
+    <row r="290" outlineLevel="2" s="592">
       <c r="B290" s="376" t="n"/>
       <c r="D290" s="373" t="n"/>
       <c r="E290" s="356" t="inlineStr">
@@ -42416,7 +42351,7 @@
       <c r="K290" s="357" t="n"/>
       <c r="L290" s="357" t="n"/>
     </row>
-    <row r="291" outlineLevel="2" s="594">
+    <row r="291" outlineLevel="2" s="592">
       <c r="B291" s="376" t="n"/>
       <c r="D291" s="357" t="n"/>
       <c r="E291" s="459" t="inlineStr">
@@ -42454,7 +42389,7 @@
       <c r="K292" s="352" t="n"/>
       <c r="L292" s="353" t="n"/>
     </row>
-    <row r="293" outlineLevel="1" s="594">
+    <row r="293" outlineLevel="1" s="592">
       <c r="B293" s="376" t="n"/>
       <c r="C293" s="158" t="inlineStr">
         <is>
@@ -42488,7 +42423,7 @@
       <c r="K293" s="346" t="n"/>
       <c r="L293" s="346" t="n"/>
     </row>
-    <row r="294" outlineLevel="2" s="594">
+    <row r="294" outlineLevel="2" s="592">
       <c r="B294" s="376" t="n"/>
       <c r="D294" s="372" t="n"/>
       <c r="E294" s="354" t="inlineStr">
@@ -42512,7 +42447,7 @@
       <c r="K294" s="355" t="n"/>
       <c r="L294" s="355" t="n"/>
     </row>
-    <row r="295" outlineLevel="2" s="594">
+    <row r="295" outlineLevel="2" s="592">
       <c r="B295" s="376" t="n"/>
       <c r="D295" s="357" t="n"/>
       <c r="E295" s="459" t="inlineStr">

--- a/DB Flotte ETR1000 Ver_1.7_00.xlsx
+++ b/DB Flotte ETR1000 Ver_1.7_00.xlsx
@@ -3436,11 +3436,6 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3449,6 +3444,14 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3467,43 +3470,35 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="93" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="93" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3515,59 +3510,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3577,80 +3561,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="95" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4612,8 +4612,8 @@
   <cols>
     <col width="10.85546875" customWidth="1" style="13" min="1" max="2"/>
     <col width="59" customWidth="1" style="13" min="3" max="3"/>
-    <col width="8.7109375" customWidth="1" style="13" min="4" max="10"/>
-    <col width="8.7109375" customWidth="1" style="13" min="11" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="4" max="11"/>
+    <col width="8.7109375" customWidth="1" style="13" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="188">
@@ -4695,100 +4695,100 @@
     <col width="8.7109375" customWidth="1" style="260" min="20" max="20"/>
     <col width="6.7109375" customWidth="1" style="260" min="21" max="21"/>
     <col width="8.7109375" customWidth="1" style="260" min="22" max="22"/>
-    <col width="8.7109375" customWidth="1" style="103" min="23" max="29"/>
-    <col width="8.7109375" customWidth="1" style="103" min="30" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="23" max="30"/>
+    <col width="8.7109375" customWidth="1" style="103" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customFormat="1" customHeight="1" s="105">
-      <c r="A1" s="554" t="inlineStr">
+      <c r="A1" s="562" t="inlineStr">
         <is>
           <t>Impianto</t>
         </is>
       </c>
-      <c r="B1" s="561" t="inlineStr">
+      <c r="B1" s="558" t="inlineStr">
         <is>
           <t>Gruppo/Componente</t>
         </is>
       </c>
-      <c r="C1" s="560" t="inlineStr">
+      <c r="C1" s="557" t="inlineStr">
         <is>
           <t>P/N</t>
         </is>
       </c>
-      <c r="D1" s="563" t="inlineStr">
+      <c r="D1" s="561" t="inlineStr">
         <is>
           <t>Applicabilità flotte</t>
         </is>
       </c>
-      <c r="E1" s="557" t="n"/>
-      <c r="F1" s="557" t="n"/>
-      <c r="G1" s="557" t="n"/>
-      <c r="H1" s="557" t="n"/>
-      <c r="I1" s="557" t="n"/>
-      <c r="J1" s="558" t="n"/>
-      <c r="K1" s="556" t="inlineStr">
+      <c r="E1" s="560" t="n"/>
+      <c r="F1" s="560" t="n"/>
+      <c r="G1" s="560" t="n"/>
+      <c r="H1" s="560" t="n"/>
+      <c r="I1" s="560" t="n"/>
+      <c r="J1" s="555" t="n"/>
+      <c r="K1" s="554" t="inlineStr">
         <is>
           <t>Manuale</t>
         </is>
       </c>
-      <c r="L1" s="557" t="n"/>
-      <c r="M1" s="558" t="n"/>
-      <c r="N1" s="556" t="inlineStr">
+      <c r="L1" s="560" t="n"/>
+      <c r="M1" s="555" t="n"/>
+      <c r="N1" s="554" t="inlineStr">
         <is>
           <t>CPR</t>
         </is>
       </c>
-      <c r="O1" s="557" t="n"/>
-      <c r="P1" s="558" t="n"/>
-      <c r="Q1" s="556" t="inlineStr">
+      <c r="O1" s="560" t="n"/>
+      <c r="P1" s="555" t="n"/>
+      <c r="Q1" s="554" t="inlineStr">
         <is>
           <t>Raccolta doc</t>
         </is>
       </c>
-      <c r="R1" s="558" t="n"/>
-      <c r="S1" s="559" t="inlineStr">
+      <c r="R1" s="555" t="n"/>
+      <c r="S1" s="556" t="inlineStr">
         <is>
           <t>Schema elettrico</t>
         </is>
       </c>
-      <c r="T1" s="558" t="n"/>
-      <c r="U1" s="559" t="inlineStr">
+      <c r="T1" s="555" t="n"/>
+      <c r="U1" s="556" t="inlineStr">
         <is>
           <t>Schema Pneumatico</t>
         </is>
       </c>
-      <c r="V1" s="558" t="n"/>
+      <c r="V1" s="555" t="n"/>
     </row>
     <row r="2" ht="31.5" customFormat="1" customHeight="1" s="105">
-      <c r="A2" s="555" t="n"/>
-      <c r="B2" s="562" t="n"/>
-      <c r="C2" s="528" t="n"/>
+      <c r="A2" s="563" t="n"/>
+      <c r="B2" s="559" t="n"/>
+      <c r="C2" s="533" t="n"/>
       <c r="D2" s="136" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E2" s="538" t="inlineStr">
+      <c r="E2" s="539" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="F2" s="538" t="inlineStr">
+      <c r="F2" s="539" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="G2" s="538" t="inlineStr">
+      <c r="G2" s="539" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="H2" s="538" t="inlineStr">
+      <c r="H2" s="539" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="I2" s="538" t="inlineStr">
+      <c r="I2" s="539" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
@@ -4915,7 +4915,7 @@
       <c r="U3" s="220" t="n"/>
       <c r="V3" s="219" t="n"/>
     </row>
-    <row r="4" outlineLevel="1" s="592">
+    <row r="4" outlineLevel="1" s="582">
       <c r="A4" s="199" t="n"/>
       <c r="B4" s="118" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
       <c r="U4" s="226" t="n"/>
       <c r="V4" s="225" t="n"/>
     </row>
-    <row r="5" outlineLevel="2" s="592">
+    <row r="5" outlineLevel="2" s="582">
       <c r="A5" s="109" t="n"/>
       <c r="B5" s="110" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
       <c r="U5" s="233" t="n"/>
       <c r="V5" s="232" t="n"/>
     </row>
-    <row r="6" outlineLevel="2" s="592">
+    <row r="6" outlineLevel="2" s="582">
       <c r="A6" s="109" t="n"/>
       <c r="B6" s="110" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       <c r="U6" s="233" t="n"/>
       <c r="V6" s="232" t="n"/>
     </row>
-    <row r="7" outlineLevel="2" s="592">
+    <row r="7" outlineLevel="2" s="582">
       <c r="A7" s="109" t="n"/>
       <c r="B7" s="110" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
       <c r="U7" s="233" t="n"/>
       <c r="V7" s="232" t="n"/>
     </row>
-    <row r="8" outlineLevel="1" s="592">
+    <row r="8" outlineLevel="1" s="582">
       <c r="A8" s="199" t="n"/>
       <c r="B8" s="118" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
       <c r="U8" s="226" t="n"/>
       <c r="V8" s="225" t="n"/>
     </row>
-    <row r="9" outlineLevel="2" s="592">
+    <row r="9" outlineLevel="2" s="582">
       <c r="A9" s="109" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
       <c r="U10" s="240" t="n"/>
       <c r="V10" s="241" t="n"/>
     </row>
-    <row r="11" outlineLevel="2" s="592">
+    <row r="11" outlineLevel="2" s="582">
       <c r="A11" s="109" t="n"/>
       <c r="B11" s="202" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       <c r="U12" s="220" t="n"/>
       <c r="V12" s="219" t="n"/>
     </row>
-    <row r="13" outlineLevel="1" s="592">
+    <row r="13" outlineLevel="1" s="582">
       <c r="A13" s="199" t="n"/>
       <c r="B13" s="118" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
       <c r="U13" s="226" t="n"/>
       <c r="V13" s="225" t="n"/>
     </row>
-    <row r="14" outlineLevel="2" s="592">
+    <row r="14" outlineLevel="2" s="582">
       <c r="A14" s="109" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
       <c r="U14" s="233" t="n"/>
       <c r="V14" s="232" t="n"/>
     </row>
-    <row r="15" outlineLevel="2" s="592">
+    <row r="15" outlineLevel="2" s="582">
       <c r="A15" s="109" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       <c r="U15" s="233" t="n"/>
       <c r="V15" s="232" t="n"/>
     </row>
-    <row r="16" outlineLevel="2" s="592">
+    <row r="16" outlineLevel="2" s="582">
       <c r="A16" s="109" t="n"/>
       <c r="B16" s="126" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
       <c r="U16" s="233" t="n"/>
       <c r="V16" s="232" t="n"/>
     </row>
-    <row r="17" outlineLevel="2" s="592">
+    <row r="17" outlineLevel="2" s="582">
       <c r="A17" s="109" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
       <c r="U17" s="233" t="n"/>
       <c r="V17" s="232" t="n"/>
     </row>
-    <row r="18" outlineLevel="2" s="592">
+    <row r="18" outlineLevel="2" s="582">
       <c r="A18" s="109" t="n"/>
       <c r="B18" s="128" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       <c r="U18" s="233" t="n"/>
       <c r="V18" s="232" t="n"/>
     </row>
-    <row r="19" outlineLevel="2" s="592">
+    <row r="19" outlineLevel="2" s="582">
       <c r="A19" s="109" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
       <c r="U19" s="233" t="n"/>
       <c r="V19" s="232" t="n"/>
     </row>
-    <row r="20" outlineLevel="2" s="592">
+    <row r="20" outlineLevel="2" s="582">
       <c r="A20" s="109" t="n"/>
       <c r="B20" s="128" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
       <c r="U20" s="233" t="n"/>
       <c r="V20" s="232" t="n"/>
     </row>
-    <row r="21" outlineLevel="2" s="592">
+    <row r="21" outlineLevel="2" s="582">
       <c r="A21" s="109" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
       <c r="U21" s="233" t="n"/>
       <c r="V21" s="232" t="n"/>
     </row>
-    <row r="22" outlineLevel="2" s="592">
+    <row r="22" outlineLevel="2" s="582">
       <c r="A22" s="109" t="n"/>
       <c r="B22" s="110" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
       <c r="U22" s="233" t="n"/>
       <c r="V22" s="232" t="n"/>
     </row>
-    <row r="23" outlineLevel="2" s="592">
+    <row r="23" outlineLevel="2" s="582">
       <c r="A23" s="109" t="n"/>
       <c r="B23" s="110" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
       <c r="U23" s="233" t="n"/>
       <c r="V23" s="232" t="n"/>
     </row>
-    <row r="24" outlineLevel="2" s="592">
+    <row r="24" outlineLevel="2" s="582">
       <c r="A24" s="109" t="n"/>
       <c r="B24" s="110" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
       <c r="U24" s="233" t="n"/>
       <c r="V24" s="232" t="n"/>
     </row>
-    <row r="25" outlineLevel="2" s="592">
+    <row r="25" outlineLevel="2" s="582">
       <c r="A25" s="109" t="n"/>
       <c r="B25" s="202" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
       <c r="U25" s="233" t="n"/>
       <c r="V25" s="232" t="n"/>
     </row>
-    <row r="26" outlineLevel="2" s="592">
+    <row r="26" outlineLevel="2" s="582">
       <c r="A26" s="109" t="n"/>
       <c r="B26" s="202" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
       <c r="U26" s="233" t="n"/>
       <c r="V26" s="232" t="n"/>
     </row>
-    <row r="27" outlineLevel="2" s="592">
+    <row r="27" outlineLevel="2" s="582">
       <c r="A27" s="109" t="n"/>
       <c r="B27" s="202" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
       <c r="U27" s="233" t="n"/>
       <c r="V27" s="232" t="n"/>
     </row>
-    <row r="28" outlineLevel="2" s="592">
+    <row r="28" outlineLevel="2" s="582">
       <c r="A28" s="109" t="n"/>
       <c r="B28" s="202" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       <c r="U28" s="233" t="n"/>
       <c r="V28" s="232" t="n"/>
     </row>
-    <row r="29" outlineLevel="2" s="592">
+    <row r="29" outlineLevel="2" s="582">
       <c r="A29" s="109" t="n"/>
       <c r="B29" s="202" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
       <c r="U29" s="233" t="n"/>
       <c r="V29" s="232" t="n"/>
     </row>
-    <row r="30" outlineLevel="2" s="592">
+    <row r="30" outlineLevel="2" s="582">
       <c r="A30" s="109" t="n"/>
       <c r="B30" s="202" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       <c r="U30" s="233" t="n"/>
       <c r="V30" s="232" t="n"/>
     </row>
-    <row r="31" outlineLevel="2" s="592">
+    <row r="31" outlineLevel="2" s="582">
       <c r="A31" s="109" t="n"/>
       <c r="B31" s="202" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
       <c r="U31" s="233" t="n"/>
       <c r="V31" s="232" t="n"/>
     </row>
-    <row r="32" outlineLevel="2" s="592">
+    <row r="32" outlineLevel="2" s="582">
       <c r="A32" s="109" t="n"/>
       <c r="B32" s="202" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
       <c r="U32" s="233" t="n"/>
       <c r="V32" s="232" t="n"/>
     </row>
-    <row r="33" outlineLevel="2" s="592">
+    <row r="33" outlineLevel="2" s="582">
       <c r="A33" s="109" t="n"/>
       <c r="B33" s="202" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
       <c r="U33" s="233" t="n"/>
       <c r="V33" s="232" t="n"/>
     </row>
-    <row r="34" outlineLevel="2" s="592">
+    <row r="34" outlineLevel="2" s="582">
       <c r="A34" s="109" t="n"/>
       <c r="B34" s="202" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
       <c r="U34" s="233" t="n"/>
       <c r="V34" s="232" t="n"/>
     </row>
-    <row r="35" outlineLevel="2" ht="30" customHeight="1" s="592">
+    <row r="35" outlineLevel="2" ht="30" customHeight="1" s="582">
       <c r="A35" s="109" t="n"/>
       <c r="B35" s="202" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
       <c r="U35" s="233" t="n"/>
       <c r="V35" s="232" t="n"/>
     </row>
-    <row r="36" outlineLevel="2" s="592">
+    <row r="36" outlineLevel="2" s="582">
       <c r="A36" s="109" t="n"/>
       <c r="B36" s="202" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
       <c r="U36" s="233" t="n"/>
       <c r="V36" s="232" t="n"/>
     </row>
-    <row r="37" outlineLevel="1" s="592">
+    <row r="37" outlineLevel="1" s="582">
       <c r="A37" s="199" t="n"/>
       <c r="B37" s="118" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
       <c r="U37" s="226" t="n"/>
       <c r="V37" s="225" t="n"/>
     </row>
-    <row r="38" outlineLevel="2" s="592">
+    <row r="38" outlineLevel="2" s="582">
       <c r="A38" s="109" t="n"/>
       <c r="B38" s="126" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
       <c r="U38" s="233" t="n"/>
       <c r="V38" s="232" t="n"/>
     </row>
-    <row r="39" outlineLevel="2" s="592">
+    <row r="39" outlineLevel="2" s="582">
       <c r="A39" s="109" t="n"/>
       <c r="B39" s="128" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
       <c r="U39" s="233" t="n"/>
       <c r="V39" s="232" t="n"/>
     </row>
-    <row r="40" outlineLevel="2" s="592">
+    <row r="40" outlineLevel="2" s="582">
       <c r="A40" s="109" t="n"/>
       <c r="B40" s="126" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
       <c r="U40" s="233" t="n"/>
       <c r="V40" s="232" t="n"/>
     </row>
-    <row r="41" outlineLevel="2" s="592">
+    <row r="41" outlineLevel="2" s="582">
       <c r="A41" s="109" t="n"/>
       <c r="B41" s="202" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
       <c r="U41" s="233" t="n"/>
       <c r="V41" s="232" t="n"/>
     </row>
-    <row r="42" outlineLevel="1" s="592">
+    <row r="42" outlineLevel="1" s="582">
       <c r="A42" s="199" t="n"/>
       <c r="B42" s="118" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
       <c r="U42" s="226" t="n"/>
       <c r="V42" s="225" t="n"/>
     </row>
-    <row r="43" outlineLevel="2" s="592">
+    <row r="43" outlineLevel="2" s="582">
       <c r="A43" s="109" t="n"/>
       <c r="B43" s="110" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
       <c r="U43" s="233" t="n"/>
       <c r="V43" s="232" t="n"/>
     </row>
-    <row r="44" outlineLevel="2" s="592">
+    <row r="44" outlineLevel="2" s="582">
       <c r="A44" s="109" t="n"/>
       <c r="B44" s="128" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
       <c r="U44" s="233" t="n"/>
       <c r="V44" s="232" t="n"/>
     </row>
-    <row r="45" outlineLevel="2" s="592">
+    <row r="45" outlineLevel="2" s="582">
       <c r="A45" s="109" t="n"/>
       <c r="B45" s="110" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
       <c r="U45" s="233" t="n"/>
       <c r="V45" s="232" t="n"/>
     </row>
-    <row r="46" outlineLevel="2" s="592">
+    <row r="46" outlineLevel="2" s="582">
       <c r="A46" s="109" t="n"/>
       <c r="B46" s="126" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
       <c r="U46" s="233" t="n"/>
       <c r="V46" s="232" t="n"/>
     </row>
-    <row r="47" outlineLevel="2" s="592">
+    <row r="47" outlineLevel="2" s="582">
       <c r="A47" s="109" t="n"/>
       <c r="B47" s="128" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
       <c r="U47" s="233" t="n"/>
       <c r="V47" s="232" t="n"/>
     </row>
-    <row r="48" outlineLevel="2" s="592">
+    <row r="48" outlineLevel="2" s="582">
       <c r="A48" s="109" t="n"/>
       <c r="B48" s="126" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
       <c r="U48" s="233" t="n"/>
       <c r="V48" s="232" t="n"/>
     </row>
-    <row r="49" outlineLevel="2" s="592">
+    <row r="49" outlineLevel="2" s="582">
       <c r="A49" s="109" t="n"/>
       <c r="B49" s="124" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
       <c r="U49" s="233" t="n"/>
       <c r="V49" s="232" t="n"/>
     </row>
-    <row r="50" outlineLevel="2" s="592">
+    <row r="50" outlineLevel="2" s="582">
       <c r="A50" s="109" t="n"/>
       <c r="B50" s="126" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
       <c r="U50" s="233" t="n"/>
       <c r="V50" s="232" t="n"/>
     </row>
-    <row r="51" outlineLevel="2" s="592">
+    <row r="51" outlineLevel="2" s="582">
       <c r="A51" s="109" t="n"/>
       <c r="B51" s="128" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
       <c r="U51" s="233" t="n"/>
       <c r="V51" s="232" t="n"/>
     </row>
-    <row r="52" outlineLevel="2" s="592">
+    <row r="52" outlineLevel="2" s="582">
       <c r="A52" s="109" t="n"/>
       <c r="B52" s="128" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
       <c r="U52" s="233" t="n"/>
       <c r="V52" s="232" t="n"/>
     </row>
-    <row r="53" outlineLevel="2" s="592">
+    <row r="53" outlineLevel="2" s="582">
       <c r="A53" s="109" t="n"/>
       <c r="B53" s="110" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
       <c r="U53" s="233" t="n"/>
       <c r="V53" s="232" t="n"/>
     </row>
-    <row r="54" outlineLevel="2" ht="30" customHeight="1" s="592">
+    <row r="54" outlineLevel="2" ht="30" customHeight="1" s="582">
       <c r="A54" s="109" t="n"/>
       <c r="B54" s="202" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
       <c r="U54" s="233" t="n"/>
       <c r="V54" s="232" t="n"/>
     </row>
-    <row r="55" outlineLevel="2" ht="30" customHeight="1" s="592">
+    <row r="55" outlineLevel="2" ht="30" customHeight="1" s="582">
       <c r="A55" s="109" t="n"/>
       <c r="B55" s="202" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
       <c r="U56" s="220" t="n"/>
       <c r="V56" s="219" t="n"/>
     </row>
-    <row r="57" outlineLevel="1" s="592">
+    <row r="57" outlineLevel="1" s="582">
       <c r="A57" s="117" t="n"/>
       <c r="B57" s="118" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
       <c r="U57" s="251" t="n"/>
       <c r="V57" s="250" t="n"/>
     </row>
-    <row r="58" outlineLevel="2" ht="30" customHeight="1" s="592">
+    <row r="58" outlineLevel="2" ht="30" customHeight="1" s="582">
       <c r="A58" s="109" t="n"/>
       <c r="B58" s="110" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
       <c r="U58" s="233" t="n"/>
       <c r="V58" s="232" t="n"/>
     </row>
-    <row r="59" outlineLevel="3" ht="30" customHeight="1" s="592">
+    <row r="59" outlineLevel="3" ht="30" customHeight="1" s="582">
       <c r="A59" s="109" t="n"/>
       <c r="B59" s="110" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
       <c r="U59" s="233" t="n"/>
       <c r="V59" s="232" t="n"/>
     </row>
-    <row r="60" outlineLevel="3" ht="30" customHeight="1" s="592">
+    <row r="60" outlineLevel="3" ht="30" customHeight="1" s="582">
       <c r="A60" s="109" t="n"/>
       <c r="B60" s="110" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
       <c r="U60" s="233" t="n"/>
       <c r="V60" s="232" t="n"/>
     </row>
-    <row r="61" outlineLevel="2" s="592">
+    <row r="61" outlineLevel="2" s="582">
       <c r="A61" s="109" t="n"/>
       <c r="B61" s="202" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
       <c r="U61" s="233" t="n"/>
       <c r="V61" s="232" t="n"/>
     </row>
-    <row r="62" outlineLevel="3" s="592">
+    <row r="62" outlineLevel="3" s="582">
       <c r="A62" s="109" t="n"/>
       <c r="B62" s="202" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
       <c r="U62" s="233" t="n"/>
       <c r="V62" s="232" t="n"/>
     </row>
-    <row r="63" outlineLevel="3" collapsed="1" s="592">
+    <row r="63" outlineLevel="3" collapsed="1" s="582">
       <c r="A63" s="109" t="n"/>
       <c r="B63" s="202" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
       <c r="U63" s="233" t="n"/>
       <c r="V63" s="232" t="n"/>
     </row>
-    <row r="64" outlineLevel="1" s="592">
+    <row r="64" outlineLevel="1" s="582">
       <c r="A64" s="117" t="n"/>
       <c r="B64" s="118" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
       <c r="U64" s="251" t="n"/>
       <c r="V64" s="250" t="n"/>
     </row>
-    <row r="65" outlineLevel="2" ht="30" customHeight="1" s="592">
+    <row r="65" outlineLevel="2" ht="30" customHeight="1" s="582">
       <c r="A65" s="109" t="n"/>
       <c r="B65" s="110" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
       <c r="U65" s="233" t="n"/>
       <c r="V65" s="232" t="n"/>
     </row>
-    <row r="66" outlineLevel="3" ht="30" customHeight="1" s="592">
+    <row r="66" outlineLevel="3" ht="30" customHeight="1" s="582">
       <c r="A66" s="109" t="n"/>
       <c r="B66" s="110" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
       <c r="U66" s="233" t="n"/>
       <c r="V66" s="232" t="n"/>
     </row>
-    <row r="67" outlineLevel="3" ht="30" customHeight="1" s="592">
+    <row r="67" outlineLevel="3" ht="30" customHeight="1" s="582">
       <c r="A67" s="109" t="n"/>
       <c r="B67" s="110" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
       <c r="U67" s="233" t="n"/>
       <c r="V67" s="232" t="n"/>
     </row>
-    <row r="68" outlineLevel="2" s="592">
+    <row r="68" outlineLevel="2" s="582">
       <c r="A68" s="109" t="n"/>
       <c r="B68" s="202" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
       <c r="U68" s="233" t="n"/>
       <c r="V68" s="232" t="n"/>
     </row>
-    <row r="69" outlineLevel="3" s="592">
+    <row r="69" outlineLevel="3" s="582">
       <c r="A69" s="109" t="n"/>
       <c r="B69" s="123" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
       <c r="U69" s="233" t="n"/>
       <c r="V69" s="232" t="n"/>
     </row>
-    <row r="70" outlineLevel="3" collapsed="1" s="592">
+    <row r="70" outlineLevel="3" collapsed="1" s="582">
       <c r="A70" s="109" t="n"/>
       <c r="B70" s="202" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
       <c r="U70" s="233" t="n"/>
       <c r="V70" s="232" t="n"/>
     </row>
-    <row r="71" outlineLevel="1" s="592">
+    <row r="71" outlineLevel="1" s="582">
       <c r="A71" s="117" t="n"/>
       <c r="B71" s="118" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
       <c r="U71" s="251" t="n"/>
       <c r="V71" s="250" t="n"/>
     </row>
-    <row r="72" outlineLevel="2" ht="30" customHeight="1" s="592">
+    <row r="72" outlineLevel="2" ht="30" customHeight="1" s="582">
       <c r="A72" s="109" t="n"/>
       <c r="B72" s="110" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
       <c r="U72" s="233" t="n"/>
       <c r="V72" s="232" t="n"/>
     </row>
-    <row r="73" outlineLevel="3" ht="30" customHeight="1" s="592">
+    <row r="73" outlineLevel="3" ht="30" customHeight="1" s="582">
       <c r="A73" s="109" t="n"/>
       <c r="B73" s="110" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
       <c r="U73" s="233" t="n"/>
       <c r="V73" s="232" t="n"/>
     </row>
-    <row r="74" outlineLevel="3" ht="30" customHeight="1" s="592">
+    <row r="74" outlineLevel="3" ht="30" customHeight="1" s="582">
       <c r="A74" s="109" t="n"/>
       <c r="B74" s="110" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
       <c r="U74" s="233" t="n"/>
       <c r="V74" s="232" t="n"/>
     </row>
-    <row r="75" outlineLevel="2" s="592">
+    <row r="75" outlineLevel="2" s="582">
       <c r="A75" s="109" t="n"/>
       <c r="B75" s="202" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
       <c r="U75" s="233" t="n"/>
       <c r="V75" s="232" t="n"/>
     </row>
-    <row r="76" outlineLevel="3" s="592">
+    <row r="76" outlineLevel="3" s="582">
       <c r="A76" s="109" t="n"/>
       <c r="B76" s="202" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
       <c r="U76" s="233" t="n"/>
       <c r="V76" s="232" t="n"/>
     </row>
-    <row r="77" outlineLevel="3" collapsed="1" s="592">
+    <row r="77" outlineLevel="3" collapsed="1" s="582">
       <c r="A77" s="109" t="n"/>
       <c r="B77" s="202" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
       <c r="U77" s="233" t="n"/>
       <c r="V77" s="232" t="n"/>
     </row>
-    <row r="78" outlineLevel="1" s="592">
+    <row r="78" outlineLevel="1" s="582">
       <c r="A78" s="117" t="n"/>
       <c r="B78" s="118" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
       <c r="U78" s="251" t="n"/>
       <c r="V78" s="250" t="n"/>
     </row>
-    <row r="79" outlineLevel="2" ht="30" customHeight="1" s="592">
+    <row r="79" outlineLevel="2" ht="30" customHeight="1" s="582">
       <c r="A79" s="109" t="n"/>
       <c r="B79" s="110" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
       <c r="U79" s="233" t="n"/>
       <c r="V79" s="232" t="n"/>
     </row>
-    <row r="80" outlineLevel="1" s="592">
+    <row r="80" outlineLevel="1" s="582">
       <c r="A80" s="117" t="n"/>
       <c r="B80" s="118" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
       <c r="U80" s="251" t="n"/>
       <c r="V80" s="250" t="n"/>
     </row>
-    <row r="81" outlineLevel="2" ht="30" customHeight="1" s="592">
+    <row r="81" outlineLevel="2" ht="30" customHeight="1" s="582">
       <c r="A81" s="109" t="n"/>
       <c r="B81" s="110" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
       <c r="U81" s="233" t="n"/>
       <c r="V81" s="232" t="n"/>
     </row>
-    <row r="82" outlineLevel="3" ht="30" customHeight="1" s="592">
+    <row r="82" outlineLevel="3" ht="30" customHeight="1" s="582">
       <c r="A82" s="109" t="n"/>
       <c r="B82" s="110" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
       <c r="U82" s="233" t="n"/>
       <c r="V82" s="232" t="n"/>
     </row>
-    <row r="83" outlineLevel="3" ht="30" customHeight="1" s="592">
+    <row r="83" outlineLevel="3" ht="30" customHeight="1" s="582">
       <c r="A83" s="109" t="n"/>
       <c r="B83" s="110" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
       <c r="U83" s="233" t="n"/>
       <c r="V83" s="232" t="n"/>
     </row>
-    <row r="84" outlineLevel="2" s="592">
+    <row r="84" outlineLevel="2" s="582">
       <c r="A84" s="109" t="n"/>
       <c r="B84" s="202" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
       <c r="U84" s="233" t="n"/>
       <c r="V84" s="232" t="n"/>
     </row>
-    <row r="85" outlineLevel="3" s="592">
+    <row r="85" outlineLevel="3" s="582">
       <c r="A85" s="109" t="n"/>
       <c r="B85" s="123" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
       <c r="U85" s="233" t="n"/>
       <c r="V85" s="232" t="n"/>
     </row>
-    <row r="86" outlineLevel="3" collapsed="1" s="592">
+    <row r="86" outlineLevel="3" collapsed="1" s="582">
       <c r="A86" s="109" t="n"/>
       <c r="B86" s="123" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
       <c r="U92" s="233" t="n"/>
       <c r="V92" s="232" t="n"/>
     </row>
-    <row r="93" ht="30" customHeight="1" s="592">
+    <row r="93" ht="30" customHeight="1" s="582">
       <c r="A93" s="109" t="n"/>
       <c r="B93" s="110" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
       <c r="U96" s="233" t="n"/>
       <c r="V96" s="232" t="n"/>
     </row>
-    <row r="97" ht="30" customHeight="1" s="592">
+    <row r="97" ht="30" customHeight="1" s="582">
       <c r="A97" s="109" t="n"/>
       <c r="B97" s="110" t="inlineStr">
         <is>
@@ -8678,9 +8678,9 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="K1:M1"/>
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
@@ -8696,89 +8696,89 @@
   <dimension ref="A1:Z50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17.85546875" customWidth="1" style="592" min="1" max="1"/>
-    <col width="14.42578125" customWidth="1" style="592" min="2" max="2"/>
-    <col width="18.42578125" customWidth="1" style="592" min="3" max="3"/>
-    <col width="15.85546875" customWidth="1" style="592" min="4" max="4"/>
-    <col width="19.42578125" customWidth="1" style="592" min="5" max="6"/>
-    <col width="14.42578125" customWidth="1" style="592" min="7" max="7"/>
-    <col width="16.42578125" customWidth="1" style="592" min="8" max="8"/>
-    <col width="23.85546875" customWidth="1" style="592" min="9" max="9"/>
-    <col width="21.85546875" customWidth="1" style="592" min="10" max="10"/>
-    <col width="11.42578125" customWidth="1" style="592" min="11" max="11"/>
-    <col width="15.5703125" customWidth="1" style="592" min="12" max="12"/>
-    <col width="19.85546875" customWidth="1" style="592" min="13" max="13"/>
-    <col width="21.5703125" customWidth="1" style="592" min="14" max="14"/>
-    <col width="12.140625" customWidth="1" style="592" min="15" max="15"/>
-    <col width="15.5703125" customWidth="1" style="592" min="16" max="16"/>
-    <col width="24.5703125" customWidth="1" style="592" min="17" max="17"/>
-    <col width="26.85546875" customWidth="1" style="592" min="18" max="18"/>
-    <col width="15.140625" customWidth="1" style="592" min="20" max="20"/>
-    <col width="25.140625" customWidth="1" style="592" min="21" max="21"/>
-    <col width="20.140625" customWidth="1" style="592" min="22" max="22"/>
-    <col width="10" bestFit="1" customWidth="1" style="592" min="23" max="23"/>
-    <col width="15.42578125" customWidth="1" style="592" min="24" max="24"/>
-    <col width="20.42578125" customWidth="1" style="592" min="25" max="25"/>
-    <col width="25.85546875" customWidth="1" style="592" min="26" max="26"/>
+    <col width="17.85546875" customWidth="1" style="582" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" style="582" min="2" max="2"/>
+    <col width="18.42578125" customWidth="1" style="582" min="3" max="3"/>
+    <col width="15.85546875" customWidth="1" style="582" min="4" max="4"/>
+    <col width="19.42578125" customWidth="1" style="582" min="5" max="6"/>
+    <col width="14.42578125" customWidth="1" style="582" min="7" max="7"/>
+    <col width="16.42578125" customWidth="1" style="582" min="8" max="8"/>
+    <col width="23.85546875" customWidth="1" style="582" min="9" max="9"/>
+    <col width="21.85546875" customWidth="1" style="582" min="10" max="10"/>
+    <col width="11.42578125" customWidth="1" style="582" min="11" max="11"/>
+    <col width="15.5703125" customWidth="1" style="582" min="12" max="12"/>
+    <col width="19.85546875" customWidth="1" style="582" min="13" max="13"/>
+    <col width="21.5703125" customWidth="1" style="582" min="14" max="14"/>
+    <col width="12.140625" customWidth="1" style="582" min="15" max="15"/>
+    <col width="15.5703125" customWidth="1" style="582" min="16" max="16"/>
+    <col width="24.5703125" customWidth="1" style="582" min="17" max="17"/>
+    <col width="26.85546875" customWidth="1" style="582" min="18" max="18"/>
+    <col width="15.140625" customWidth="1" style="582" min="20" max="20"/>
+    <col width="25.140625" customWidth="1" style="582" min="21" max="21"/>
+    <col width="20.140625" customWidth="1" style="582" min="22" max="22"/>
+    <col width="10" bestFit="1" customWidth="1" style="582" min="23" max="23"/>
+    <col width="15.42578125" customWidth="1" style="582" min="24" max="24"/>
+    <col width="20.42578125" customWidth="1" style="582" min="25" max="25"/>
+    <col width="25.85546875" customWidth="1" style="582" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="C1" s="582" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="C1" s="595" t="inlineStr">
         <is>
           <t>IT 50 treni (flotta base)</t>
         </is>
       </c>
-      <c r="D1" s="583" t="n"/>
-      <c r="E1" s="583" t="n"/>
-      <c r="F1" s="584" t="n"/>
-      <c r="G1" s="582" t="inlineStr">
+      <c r="D1" s="566" t="n"/>
+      <c r="E1" s="566" t="n"/>
+      <c r="F1" s="596" t="n"/>
+      <c r="G1" s="595" t="inlineStr">
         <is>
           <t>IT 8 treni (51-58)</t>
         </is>
       </c>
-      <c r="H1" s="583" t="n"/>
-      <c r="I1" s="583" t="n"/>
-      <c r="J1" s="584" t="n"/>
-      <c r="K1" s="582" t="inlineStr">
+      <c r="H1" s="566" t="n"/>
+      <c r="I1" s="566" t="n"/>
+      <c r="J1" s="596" t="n"/>
+      <c r="K1" s="595" t="inlineStr">
         <is>
           <t>IT 6+30 treni (101-136)</t>
         </is>
       </c>
-      <c r="L1" s="583" t="n"/>
-      <c r="M1" s="583" t="n"/>
-      <c r="N1" s="584" t="n"/>
-      <c r="O1" s="582" t="inlineStr">
+      <c r="L1" s="566" t="n"/>
+      <c r="M1" s="566" t="n"/>
+      <c r="N1" s="596" t="n"/>
+      <c r="O1" s="595" t="inlineStr">
         <is>
           <t>I-FR 9 treni</t>
         </is>
       </c>
-      <c r="P1" s="583" t="n"/>
-      <c r="Q1" s="583" t="n"/>
-      <c r="R1" s="584" t="n"/>
-      <c r="S1" s="582" t="inlineStr">
+      <c r="P1" s="566" t="n"/>
+      <c r="Q1" s="566" t="n"/>
+      <c r="R1" s="596" t="n"/>
+      <c r="S1" s="595" t="inlineStr">
         <is>
           <t>DAI 9 treni</t>
         </is>
       </c>
-      <c r="T1" s="583" t="n"/>
-      <c r="U1" s="583" t="n"/>
-      <c r="V1" s="584" t="n"/>
-      <c r="W1" s="582" t="inlineStr">
+      <c r="T1" s="566" t="n"/>
+      <c r="U1" s="566" t="n"/>
+      <c r="V1" s="596" t="n"/>
+      <c r="W1" s="595" t="inlineStr">
         <is>
           <t>ES 20 treni</t>
         </is>
       </c>
-      <c r="X1" s="583" t="n"/>
-      <c r="Y1" s="583" t="n"/>
-      <c r="Z1" s="584" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="A2" s="569" t="inlineStr">
+      <c r="X1" s="566" t="n"/>
+      <c r="Y1" s="566" t="n"/>
+      <c r="Z1" s="596" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="A2" s="607" t="inlineStr">
         <is>
           <t>Sottosistema</t>
         </is>
       </c>
-      <c r="B2" s="570" t="n"/>
+      <c r="B2" s="567" t="n"/>
       <c r="C2" s="17" t="inlineStr">
         <is>
           <t>P/N</t>
@@ -8900,18 +8900,18 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="286.5" customHeight="1" s="592">
-      <c r="A3" s="586" t="inlineStr">
+    <row r="3" ht="286.5" customHeight="1" s="582">
+      <c r="A3" s="590" t="inlineStr">
         <is>
           <t>Carrelli</t>
         </is>
       </c>
-      <c r="B3" s="624" t="inlineStr">
+      <c r="B3" s="589" t="inlineStr">
         <is>
           <t>Motori</t>
         </is>
       </c>
-      <c r="C3" s="577" t="inlineStr">
+      <c r="C3" s="568" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -8936,7 +8936,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="G3" s="577" t="inlineStr">
+      <c r="G3" s="568" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -8961,7 +8961,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="K3" s="618" t="inlineStr">
+      <c r="K3" s="605" t="inlineStr">
         <is>
           <t>100360301
 100360302
@@ -8986,7 +8986,7 @@
           <t>Sensoristica ERTMS-SCMT carrelli DM</t>
         </is>
       </c>
-      <c r="O3" s="577" t="inlineStr">
+      <c r="O3" s="568" t="inlineStr">
         <is>
           <t>100329688
 100329689
@@ -8999,7 +8999,7 @@
           <t>Sala Montata</t>
         </is>
       </c>
-      <c r="Q3" s="528" t="n"/>
+      <c r="Q3" s="533" t="n"/>
       <c r="R3" s="28" t="inlineStr">
         <is>
           <t>Sensoristica ERTMS-SCMT, Memor brush, ETCS antenna su carrelli ant. DM1/8
@@ -9008,7 +9008,7 @@
 Sala senza boccole: 100360064</t>
         </is>
       </c>
-      <c r="S3" s="622" t="n"/>
+      <c r="S3" s="576" t="n"/>
       <c r="T3" s="29" t="inlineStr">
         <is>
           <t>Sala Montata</t>
@@ -9020,7 +9020,7 @@
           <t>tbd sensori boccola DM</t>
         </is>
       </c>
-      <c r="W3" s="577" t="inlineStr">
+      <c r="W3" s="568" t="inlineStr">
         <is>
           <t>DM: 100437987
 100470644</t>
@@ -9031,7 +9031,7 @@
           <t>Sala Montata</t>
         </is>
       </c>
-      <c r="Y3" s="528" t="n"/>
+      <c r="Y3" s="533" t="n"/>
       <c r="Z3" s="23" t="inlineStr">
         <is>
           <t>Sensoristica ETCS-ASFA-LZB carrelli DM</t>
@@ -9039,8 +9039,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="587" t="n"/>
-      <c r="C4" s="567" t="n"/>
+      <c r="A4" s="572" t="n"/>
+      <c r="C4" s="569" t="n"/>
       <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9050,7 +9050,7 @@
         <v>13900244911</v>
       </c>
       <c r="F4" s="35" t="n"/>
-      <c r="G4" s="567" t="n"/>
+      <c r="G4" s="569" t="n"/>
       <c r="H4" s="33" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9060,7 +9060,7 @@
         <v>13900244911</v>
       </c>
       <c r="J4" s="35" t="n"/>
-      <c r="K4" s="567" t="n"/>
+      <c r="K4" s="569" t="n"/>
       <c r="L4" s="36" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9070,7 +9070,7 @@
         <v>13900244911</v>
       </c>
       <c r="N4" s="38" t="n"/>
-      <c r="O4" s="567" t="n"/>
+      <c r="O4" s="569" t="n"/>
       <c r="P4" s="33" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9080,7 +9080,7 @@
         <v>13900244911</v>
       </c>
       <c r="R4" s="35" t="n"/>
-      <c r="S4" s="567" t="n"/>
+      <c r="S4" s="569" t="n"/>
       <c r="T4" s="40" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9090,7 +9090,7 @@
         <v>13900244911</v>
       </c>
       <c r="V4" s="42" t="n"/>
-      <c r="W4" s="567" t="n"/>
+      <c r="W4" s="569" t="n"/>
       <c r="X4" s="33" t="inlineStr">
         <is>
           <t>Riduttore</t>
@@ -9100,8 +9100,8 @@
       <c r="Z4" s="35" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="587" t="n"/>
-      <c r="C5" s="567" t="n"/>
+      <c r="A5" s="572" t="n"/>
+      <c r="C5" s="569" t="n"/>
       <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="F5" s="35" t="n"/>
-      <c r="G5" s="567" t="n"/>
+      <c r="G5" s="569" t="n"/>
       <c r="H5" s="33" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="J5" s="35" t="n"/>
-      <c r="K5" s="567" t="n"/>
+      <c r="K5" s="569" t="n"/>
       <c r="L5" s="36" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="N5" s="38" t="n"/>
-      <c r="O5" s="567" t="n"/>
+      <c r="O5" s="569" t="n"/>
       <c r="P5" s="33" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="R5" s="35" t="n"/>
-      <c r="S5" s="567" t="n"/>
+      <c r="S5" s="569" t="n"/>
       <c r="T5" s="40" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="V5" s="42" t="n"/>
-      <c r="W5" s="567" t="n"/>
+      <c r="W5" s="569" t="n"/>
       <c r="X5" s="33" t="inlineStr">
         <is>
           <t>Motore</t>
@@ -9170,9 +9170,9 @@
       <c r="Y5" s="1" t="n"/>
       <c r="Z5" s="35" t="n"/>
     </row>
-    <row r="6" ht="87" customHeight="1" s="592">
-      <c r="A6" s="587" t="n"/>
-      <c r="C6" s="567" t="n"/>
+    <row r="6" ht="87" customHeight="1" s="582">
+      <c r="A6" s="572" t="n"/>
+      <c r="C6" s="569" t="n"/>
       <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="F6" s="35" t="n"/>
-      <c r="G6" s="567" t="n"/>
+      <c r="G6" s="569" t="n"/>
       <c r="H6" s="33" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="J6" s="35" t="n"/>
-      <c r="K6" s="567" t="n"/>
+      <c r="K6" s="569" t="n"/>
       <c r="L6" s="36" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="N6" s="38" t="n"/>
-      <c r="O6" s="567" t="n"/>
+      <c r="O6" s="569" t="n"/>
       <c r="P6" s="33" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="R6" s="35" t="n"/>
-      <c r="S6" s="567" t="n"/>
+      <c r="S6" s="569" t="n"/>
       <c r="T6" s="40" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="V6" s="42" t="n"/>
-      <c r="W6" s="567" t="n"/>
+      <c r="W6" s="569" t="n"/>
       <c r="X6" s="33" t="inlineStr">
         <is>
           <t>Cil.Freno</t>
@@ -9258,8 +9258,8 @@
       <c r="Z6" s="35" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="587" t="n"/>
-      <c r="C7" s="567" t="n"/>
+      <c r="A7" s="572" t="n"/>
+      <c r="C7" s="569" t="n"/>
       <c r="D7" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="F7" s="35" t="n"/>
-      <c r="G7" s="567" t="n"/>
+      <c r="G7" s="569" t="n"/>
       <c r="H7" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="J7" s="35" t="n"/>
-      <c r="K7" s="567" t="n"/>
+      <c r="K7" s="569" t="n"/>
       <c r="L7" s="36" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="N7" s="38" t="n"/>
-      <c r="O7" s="567" t="n"/>
+      <c r="O7" s="569" t="n"/>
       <c r="P7" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="R7" s="35" t="n"/>
-      <c r="S7" s="567" t="n"/>
+      <c r="S7" s="569" t="n"/>
       <c r="T7" s="40" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="V7" s="42" t="n"/>
-      <c r="W7" s="567" t="n"/>
+      <c r="W7" s="569" t="n"/>
       <c r="X7" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9329,9 +9329,9 @@
       <c r="Z7" s="35" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="587" t="n"/>
-      <c r="B8" s="539" t="n"/>
-      <c r="C8" s="578" t="n"/>
+      <c r="A8" s="572" t="n"/>
+      <c r="B8" s="540" t="n"/>
+      <c r="C8" s="570" t="n"/>
       <c r="D8" s="33" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9343,7 +9343,7 @@
           <t>Ephimess fase 2</t>
         </is>
       </c>
-      <c r="G8" s="578" t="n"/>
+      <c r="G8" s="570" t="n"/>
       <c r="H8" s="33" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9355,7 +9355,7 @@
           <t>Ephimess fase 2</t>
         </is>
       </c>
-      <c r="K8" s="578" t="n"/>
+      <c r="K8" s="570" t="n"/>
       <c r="L8" s="36" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="M8" s="43" t="n"/>
       <c r="N8" s="38" t="n"/>
-      <c r="O8" s="578" t="n"/>
+      <c r="O8" s="570" t="n"/>
       <c r="P8" s="33" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="Q8" s="44" t="n"/>
       <c r="R8" s="35" t="n"/>
-      <c r="S8" s="578" t="n"/>
+      <c r="S8" s="570" t="n"/>
       <c r="T8" s="40" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="U8" s="45" t="n"/>
       <c r="V8" s="42" t="n"/>
-      <c r="W8" s="578" t="n"/>
+      <c r="W8" s="570" t="n"/>
       <c r="X8" s="33" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9388,14 +9388,14 @@
       <c r="Y8" s="1" t="n"/>
       <c r="Z8" s="35" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="592">
-      <c r="A9" s="587" t="n"/>
-      <c r="B9" s="602" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="582">
+      <c r="A9" s="572" t="n"/>
+      <c r="B9" s="610" t="inlineStr">
         <is>
           <t>Portanti</t>
         </is>
       </c>
-      <c r="C9" s="616" t="inlineStr">
+      <c r="C9" s="598" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="F9" s="35" t="n"/>
-      <c r="G9" s="616" t="inlineStr">
+      <c r="G9" s="598" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="J9" s="35" t="n"/>
-      <c r="K9" s="617" t="inlineStr">
+      <c r="K9" s="599" t="inlineStr">
         <is>
           <t>100360311
 100360312
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="N9" s="38" t="n"/>
-      <c r="O9" s="616" t="inlineStr">
+      <c r="O9" s="598" t="inlineStr">
         <is>
           <t>100360311
 100329690
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="R9" s="35" t="n"/>
-      <c r="S9" s="576" t="n"/>
+      <c r="S9" s="624" t="n"/>
       <c r="T9" s="40" t="inlineStr">
         <is>
           <t>Sala</t>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="U9" s="45" t="n"/>
       <c r="V9" s="42" t="n"/>
-      <c r="W9" s="600" t="n"/>
+      <c r="W9" s="621" t="n"/>
       <c r="X9" s="33" t="inlineStr">
         <is>
           <t>Sala</t>
@@ -9490,8 +9490,8 @@
       <c r="Z9" s="35" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="587" t="n"/>
-      <c r="C10" s="567" t="n"/>
+      <c r="A10" s="572" t="n"/>
+      <c r="C10" s="569" t="n"/>
       <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="35" t="n"/>
-      <c r="G10" s="567" t="n"/>
+      <c r="G10" s="569" t="n"/>
       <c r="H10" s="33" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="I10" s="1" t="n"/>
       <c r="J10" s="35" t="n"/>
-      <c r="K10" s="567" t="n"/>
+      <c r="K10" s="569" t="n"/>
       <c r="L10" s="36" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M10" s="43" t="n"/>
       <c r="N10" s="38" t="n"/>
-      <c r="O10" s="567" t="n"/>
+      <c r="O10" s="569" t="n"/>
       <c r="P10" s="33" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="Q10" s="1" t="n"/>
       <c r="R10" s="35" t="n"/>
-      <c r="S10" s="567" t="n"/>
+      <c r="S10" s="569" t="n"/>
       <c r="T10" s="40" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="U10" s="45" t="n"/>
       <c r="V10" s="42" t="n"/>
-      <c r="W10" s="567" t="n"/>
+      <c r="W10" s="569" t="n"/>
       <c r="X10" s="33" t="inlineStr">
         <is>
           <t>Freno</t>
@@ -9541,8 +9541,8 @@
       <c r="Z10" s="35" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="587" t="n"/>
-      <c r="C11" s="567" t="n"/>
+      <c r="A11" s="572" t="n"/>
+      <c r="C11" s="569" t="n"/>
       <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E11" s="1" t="n"/>
       <c r="F11" s="35" t="n"/>
-      <c r="G11" s="567" t="n"/>
+      <c r="G11" s="569" t="n"/>
       <c r="H11" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="I11" s="1" t="n"/>
       <c r="J11" s="35" t="n"/>
-      <c r="K11" s="567" t="n"/>
+      <c r="K11" s="569" t="n"/>
       <c r="L11" s="36" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="M11" s="43" t="n"/>
       <c r="N11" s="38" t="n"/>
-      <c r="O11" s="567" t="n"/>
+      <c r="O11" s="569" t="n"/>
       <c r="P11" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="Q11" s="1" t="n"/>
       <c r="R11" s="35" t="n"/>
-      <c r="S11" s="567" t="n"/>
+      <c r="S11" s="569" t="n"/>
       <c r="T11" s="40" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="U11" s="45" t="n"/>
       <c r="V11" s="42" t="n"/>
-      <c r="W11" s="567" t="n"/>
+      <c r="W11" s="569" t="n"/>
       <c r="X11" s="33" t="inlineStr">
         <is>
           <t>Als</t>
@@ -9591,10 +9591,10 @@
       <c r="Y11" s="1" t="n"/>
       <c r="Z11" s="35" t="n"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="A12" s="588" t="n"/>
-      <c r="B12" s="539" t="n"/>
-      <c r="C12" s="568" t="n"/>
+    <row r="12" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="A12" s="591" t="n"/>
+      <c r="B12" s="540" t="n"/>
+      <c r="C12" s="574" t="n"/>
       <c r="D12" s="52" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E12" s="53" t="n"/>
       <c r="F12" s="54" t="n"/>
-      <c r="G12" s="568" t="n"/>
+      <c r="G12" s="574" t="n"/>
       <c r="H12" s="52" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="I12" s="53" t="n"/>
       <c r="J12" s="54" t="n"/>
-      <c r="K12" s="568" t="n"/>
+      <c r="K12" s="574" t="n"/>
       <c r="L12" s="55" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="M12" s="56" t="n"/>
       <c r="N12" s="57" t="n"/>
-      <c r="O12" s="568" t="n"/>
+      <c r="O12" s="574" t="n"/>
       <c r="P12" s="52" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="Q12" s="53" t="n"/>
       <c r="R12" s="54" t="n"/>
-      <c r="S12" s="568" t="n"/>
+      <c r="S12" s="574" t="n"/>
       <c r="T12" s="58" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="U12" s="59" t="n"/>
       <c r="V12" s="60" t="n"/>
-      <c r="W12" s="568" t="n"/>
+      <c r="W12" s="574" t="n"/>
       <c r="X12" s="52" t="inlineStr">
         <is>
           <t>BMS</t>
@@ -9644,17 +9644,17 @@
       <c r="Z12" s="54" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="569" t="inlineStr">
+      <c r="A13" s="607" t="inlineStr">
         <is>
           <t>Pantografi</t>
         </is>
       </c>
-      <c r="B13" s="608" t="inlineStr">
+      <c r="B13" s="564" t="inlineStr">
         <is>
           <t>3 kV</t>
         </is>
       </c>
-      <c r="C13" s="581" t="n">
+      <c r="C13" s="622" t="n">
         <v>100170460</v>
       </c>
       <c r="D13" s="61" t="inlineStr">
@@ -9666,7 +9666,7 @@
         <v>10573076</v>
       </c>
       <c r="F13" s="63" t="n"/>
-      <c r="G13" s="580" t="n">
+      <c r="G13" s="609" t="n">
         <v>10949272</v>
       </c>
       <c r="H13" s="61" t="inlineStr">
@@ -9678,7 +9678,7 @@
         <v>10573076</v>
       </c>
       <c r="J13" s="63" t="n"/>
-      <c r="K13" s="580" t="n">
+      <c r="K13" s="609" t="n">
         <v>10949272</v>
       </c>
       <c r="L13" s="61" t="inlineStr">
@@ -9690,7 +9690,7 @@
         <v>10573076</v>
       </c>
       <c r="N13" s="63" t="n"/>
-      <c r="O13" s="581" t="n">
+      <c r="O13" s="622" t="n">
         <v>100170460</v>
       </c>
       <c r="P13" s="61" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="U13" s="64" t="n"/>
       <c r="V13" s="65" t="n"/>
-      <c r="W13" s="581" t="n"/>
+      <c r="W13" s="622" t="n"/>
       <c r="X13" s="61" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9720,8 +9720,8 @@
       <c r="Z13" s="63" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="587" t="n"/>
-      <c r="C14" s="567" t="n"/>
+      <c r="A14" s="572" t="n"/>
+      <c r="C14" s="569" t="n"/>
       <c r="D14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9731,7 +9731,7 @@
         <v>10561136</v>
       </c>
       <c r="F14" s="35" t="n"/>
-      <c r="G14" s="567" t="n"/>
+      <c r="G14" s="569" t="n"/>
       <c r="H14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9741,7 +9741,7 @@
         <v>10561136</v>
       </c>
       <c r="J14" s="35" t="n"/>
-      <c r="K14" s="567" t="n"/>
+      <c r="K14" s="569" t="n"/>
       <c r="L14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9751,7 +9751,7 @@
         <v>10561136</v>
       </c>
       <c r="N14" s="35" t="n"/>
-      <c r="O14" s="567" t="n"/>
+      <c r="O14" s="569" t="n"/>
       <c r="P14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9761,7 +9761,7 @@
         <v>10561136</v>
       </c>
       <c r="R14" s="35" t="n"/>
-      <c r="S14" s="567" t="n"/>
+      <c r="S14" s="569" t="n"/>
       <c r="T14" s="45" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="U14" s="45" t="n"/>
       <c r="V14" s="42" t="n"/>
-      <c r="W14" s="567" t="n"/>
+      <c r="W14" s="569" t="n"/>
       <c r="X14" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -9783,8 +9783,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="587" t="n"/>
-      <c r="C15" s="567" t="n"/>
+      <c r="A15" s="572" t="n"/>
+      <c r="C15" s="569" t="n"/>
       <c r="D15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9796,7 +9796,7 @@
         </is>
       </c>
       <c r="F15" s="35" t="n"/>
-      <c r="G15" s="567" t="n"/>
+      <c r="G15" s="569" t="n"/>
       <c r="H15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="J15" s="35" t="n"/>
-      <c r="K15" s="567" t="n"/>
+      <c r="K15" s="569" t="n"/>
       <c r="L15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9820,7 +9820,7 @@
         </is>
       </c>
       <c r="N15" s="35" t="n"/>
-      <c r="O15" s="567" t="n"/>
+      <c r="O15" s="569" t="n"/>
       <c r="P15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="R15" s="35" t="n"/>
-      <c r="S15" s="567" t="n"/>
+      <c r="S15" s="569" t="n"/>
       <c r="T15" s="45" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="U15" s="45" t="n"/>
       <c r="V15" s="42" t="n"/>
-      <c r="W15" s="567" t="n"/>
+      <c r="W15" s="569" t="n"/>
       <c r="X15" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -9850,9 +9850,9 @@
       <c r="Z15" s="35" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="587" t="n"/>
-      <c r="B16" s="539" t="n"/>
-      <c r="C16" s="578" t="n"/>
+      <c r="A16" s="572" t="n"/>
+      <c r="B16" s="540" t="n"/>
+      <c r="C16" s="570" t="n"/>
       <c r="D16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9862,7 +9862,7 @@
         <v>102895</v>
       </c>
       <c r="F16" s="35" t="n"/>
-      <c r="G16" s="578" t="n"/>
+      <c r="G16" s="570" t="n"/>
       <c r="H16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9878,7 +9878,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="K16" s="578" t="n"/>
+      <c r="K16" s="570" t="n"/>
       <c r="L16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9894,7 +9894,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="O16" s="578" t="n"/>
+      <c r="O16" s="570" t="n"/>
       <c r="P16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9910,7 +9910,7 @@
           <t>PPU DC Modificata per agg.panto 1.5</t>
         </is>
       </c>
-      <c r="S16" s="578" t="n"/>
+      <c r="S16" s="570" t="n"/>
       <c r="T16" s="45" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="U16" s="45" t="n"/>
       <c r="V16" s="42" t="n"/>
-      <c r="W16" s="578" t="n"/>
+      <c r="W16" s="570" t="n"/>
       <c r="X16" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -9932,13 +9932,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="587" t="n"/>
-      <c r="B17" s="602" t="inlineStr">
+      <c r="A17" s="572" t="n"/>
+      <c r="B17" s="610" t="inlineStr">
         <is>
           <t>25 kV</t>
         </is>
       </c>
-      <c r="C17" s="579" t="n">
+      <c r="C17" s="575" t="n">
         <v>100170464</v>
       </c>
       <c r="D17" s="33" t="inlineStr">
@@ -9950,7 +9950,7 @@
         <v>10573076</v>
       </c>
       <c r="F17" s="35" t="n"/>
-      <c r="G17" s="601" t="n">
+      <c r="G17" s="594" t="n">
         <v>10949356</v>
       </c>
       <c r="H17" s="1" t="inlineStr">
@@ -9962,7 +9962,7 @@
         <v>10573076</v>
       </c>
       <c r="J17" s="35" t="n"/>
-      <c r="K17" s="601" t="n">
+      <c r="K17" s="594" t="n">
         <v>10949356</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -9974,7 +9974,7 @@
         <v>10573076</v>
       </c>
       <c r="N17" s="35" t="n"/>
-      <c r="O17" s="579" t="n">
+      <c r="O17" s="575" t="n">
         <v>100170464</v>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -9986,7 +9986,7 @@
         <v>10573076</v>
       </c>
       <c r="R17" s="35" t="n"/>
-      <c r="S17" s="585" t="n"/>
+      <c r="S17" s="606" t="n"/>
       <c r="T17" s="45" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="U17" s="45" t="n"/>
       <c r="V17" s="42" t="n"/>
-      <c r="W17" s="579" t="n"/>
+      <c r="W17" s="575" t="n"/>
       <c r="X17" s="1" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10004,8 +10004,8 @@
       <c r="Z17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="587" t="n"/>
-      <c r="C18" s="567" t="n"/>
+      <c r="A18" s="572" t="n"/>
+      <c r="C18" s="569" t="n"/>
       <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10015,7 +10015,7 @@
         <v>10572700</v>
       </c>
       <c r="F18" s="35" t="n"/>
-      <c r="G18" s="567" t="n"/>
+      <c r="G18" s="569" t="n"/>
       <c r="H18" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10025,7 +10025,7 @@
         <v>10572700</v>
       </c>
       <c r="J18" s="35" t="n"/>
-      <c r="K18" s="567" t="n"/>
+      <c r="K18" s="569" t="n"/>
       <c r="L18" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10035,7 +10035,7 @@
         <v>10572700</v>
       </c>
       <c r="N18" s="35" t="n"/>
-      <c r="O18" s="567" t="n"/>
+      <c r="O18" s="569" t="n"/>
       <c r="P18" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10049,7 +10049,7 @@
           <t>Vedi strisciante</t>
         </is>
       </c>
-      <c r="S18" s="567" t="n"/>
+      <c r="S18" s="569" t="n"/>
       <c r="T18" s="45" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="U18" s="45" t="n"/>
       <c r="V18" s="42" t="n"/>
-      <c r="W18" s="567" t="n"/>
+      <c r="W18" s="569" t="n"/>
       <c r="X18" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10067,8 +10067,8 @@
       <c r="Z18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="587" t="n"/>
-      <c r="C19" s="567" t="n"/>
+      <c r="A19" s="572" t="n"/>
+      <c r="C19" s="569" t="n"/>
       <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="F19" s="35" t="n"/>
-      <c r="G19" s="567" t="n"/>
+      <c r="G19" s="569" t="n"/>
       <c r="H19" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="J19" s="35" t="n"/>
-      <c r="K19" s="567" t="n"/>
+      <c r="K19" s="569" t="n"/>
       <c r="L19" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="N19" s="35" t="n"/>
-      <c r="O19" s="567" t="n"/>
+      <c r="O19" s="569" t="n"/>
       <c r="P19" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10120,7 +10120,7 @@
           <t>Conforme a norma FR SAM E903</t>
         </is>
       </c>
-      <c r="S19" s="567" t="n"/>
+      <c r="S19" s="569" t="n"/>
       <c r="T19" s="45" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="V19" s="42" t="n"/>
-      <c r="W19" s="567" t="n"/>
+      <c r="W19" s="569" t="n"/>
       <c r="X19" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10146,9 +10146,9 @@
       <c r="Z19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="587" t="n"/>
-      <c r="B20" s="539" t="n"/>
-      <c r="C20" s="578" t="n"/>
+      <c r="A20" s="572" t="n"/>
+      <c r="B20" s="540" t="n"/>
+      <c r="C20" s="570" t="n"/>
       <c r="D20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10158,7 +10158,7 @@
         <v>102895</v>
       </c>
       <c r="F20" s="35" t="n"/>
-      <c r="G20" s="578" t="n"/>
+      <c r="G20" s="570" t="n"/>
       <c r="H20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10174,7 +10174,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="K20" s="578" t="n"/>
+      <c r="K20" s="570" t="n"/>
       <c r="L20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10190,7 +10190,7 @@
           <t>Con isolamento ADD</t>
         </is>
       </c>
-      <c r="O20" s="578" t="n"/>
+      <c r="O20" s="570" t="n"/>
       <c r="P20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10200,7 +10200,7 @@
         <v>102895</v>
       </c>
       <c r="R20" s="35" t="n"/>
-      <c r="S20" s="578" t="n"/>
+      <c r="S20" s="570" t="n"/>
       <c r="T20" s="45" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="U20" s="45" t="n"/>
       <c r="V20" s="42" t="n"/>
-      <c r="W20" s="578" t="n"/>
+      <c r="W20" s="570" t="n"/>
       <c r="X20" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10222,13 +10222,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="587" t="n"/>
-      <c r="B21" s="602" t="inlineStr">
+      <c r="A21" s="572" t="n"/>
+      <c r="B21" s="610" t="inlineStr">
         <is>
           <t>1,5 kV</t>
         </is>
       </c>
-      <c r="C21" s="579" t="inlineStr">
+      <c r="C21" s="575" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="E21" s="43" t="n"/>
       <c r="F21" s="38" t="n"/>
-      <c r="G21" s="579" t="inlineStr">
+      <c r="G21" s="575" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="I21" s="43" t="n"/>
       <c r="J21" s="38" t="n"/>
-      <c r="K21" s="579" t="inlineStr">
+      <c r="K21" s="575" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="M21" s="43" t="n"/>
       <c r="N21" s="38" t="n"/>
-      <c r="O21" s="601" t="n">
+      <c r="O21" s="594" t="n">
         <v>10851208</v>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -10276,7 +10276,7 @@
         <v>10573076</v>
       </c>
       <c r="R21" s="35" t="n"/>
-      <c r="S21" s="585" t="n"/>
+      <c r="S21" s="606" t="n"/>
       <c r="T21" s="45" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="U21" s="45" t="n"/>
       <c r="V21" s="42" t="n"/>
-      <c r="W21" s="579" t="n"/>
+      <c r="W21" s="575" t="n"/>
       <c r="X21" s="1" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10294,8 +10294,8 @@
       <c r="Z21" s="38" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="587" t="n"/>
-      <c r="C22" s="567" t="n"/>
+      <c r="A22" s="572" t="n"/>
+      <c r="C22" s="569" t="n"/>
       <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="E22" s="43" t="n"/>
       <c r="F22" s="38" t="n"/>
-      <c r="G22" s="567" t="n"/>
+      <c r="G22" s="569" t="n"/>
       <c r="H22" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="I22" s="43" t="n"/>
       <c r="J22" s="38" t="n"/>
-      <c r="K22" s="567" t="n"/>
+      <c r="K22" s="569" t="n"/>
       <c r="L22" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M22" s="43" t="n"/>
       <c r="N22" s="38" t="n"/>
-      <c r="O22" s="567" t="n"/>
+      <c r="O22" s="569" t="n"/>
       <c r="P22" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10333,7 +10333,7 @@
           <t>Larghezza 1.950 mm</t>
         </is>
       </c>
-      <c r="S22" s="567" t="n"/>
+      <c r="S22" s="569" t="n"/>
       <c r="T22" s="45" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="U22" s="45" t="n"/>
       <c r="V22" s="42" t="n"/>
-      <c r="W22" s="567" t="n"/>
+      <c r="W22" s="569" t="n"/>
       <c r="X22" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10351,8 +10351,8 @@
       <c r="Z22" s="38" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="587" t="n"/>
-      <c r="C23" s="567" t="n"/>
+      <c r="A23" s="572" t="n"/>
+      <c r="C23" s="569" t="n"/>
       <c r="D23" s="33" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="E23" s="43" t="n"/>
       <c r="F23" s="38" t="n"/>
-      <c r="G23" s="567" t="n"/>
+      <c r="G23" s="569" t="n"/>
       <c r="H23" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="I23" s="43" t="n"/>
       <c r="J23" s="38" t="n"/>
-      <c r="K23" s="567" t="n"/>
+      <c r="K23" s="569" t="n"/>
       <c r="L23" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="M23" s="43" t="n"/>
       <c r="N23" s="38" t="n"/>
-      <c r="O23" s="567" t="n"/>
+      <c r="O23" s="569" t="n"/>
       <c r="P23" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="R23" s="35" t="n"/>
-      <c r="S23" s="567" t="n"/>
+      <c r="S23" s="569" t="n"/>
       <c r="T23" s="45" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="U23" s="45" t="n"/>
       <c r="V23" s="42" t="n"/>
-      <c r="W23" s="567" t="n"/>
+      <c r="W23" s="569" t="n"/>
       <c r="X23" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10406,9 +10406,9 @@
       <c r="Z23" s="38" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="587" t="n"/>
-      <c r="B24" s="539" t="n"/>
-      <c r="C24" s="578" t="n"/>
+      <c r="A24" s="572" t="n"/>
+      <c r="B24" s="540" t="n"/>
+      <c r="C24" s="570" t="n"/>
       <c r="D24" s="33" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E24" s="43" t="n"/>
       <c r="F24" s="38" t="n"/>
-      <c r="G24" s="578" t="n"/>
+      <c r="G24" s="570" t="n"/>
       <c r="H24" s="1" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="I24" s="43" t="n"/>
       <c r="J24" s="38" t="n"/>
-      <c r="K24" s="578" t="n"/>
+      <c r="K24" s="570" t="n"/>
       <c r="L24" s="1" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="M24" s="43" t="n"/>
       <c r="N24" s="38" t="n"/>
-      <c r="O24" s="578" t="n"/>
+      <c r="O24" s="570" t="n"/>
       <c r="P24" s="1" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10448,7 +10448,7 @@
           <t>PPU Modificata per agg.panto 1.5</t>
         </is>
       </c>
-      <c r="S24" s="578" t="n"/>
+      <c r="S24" s="570" t="n"/>
       <c r="T24" s="45" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="U24" s="45" t="n"/>
       <c r="V24" s="42" t="n"/>
-      <c r="W24" s="578" t="n"/>
+      <c r="W24" s="570" t="n"/>
       <c r="X24" s="1" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10466,13 +10466,13 @@
       <c r="Z24" s="38" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="587" t="n"/>
-      <c r="B25" s="602" t="inlineStr">
+      <c r="A25" s="572" t="n"/>
+      <c r="B25" s="610" t="inlineStr">
         <is>
           <t>15 kV</t>
         </is>
       </c>
-      <c r="C25" s="579" t="inlineStr">
+      <c r="C25" s="575" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="E25" s="43" t="n"/>
       <c r="F25" s="38" t="n"/>
-      <c r="G25" s="579" t="inlineStr">
+      <c r="G25" s="575" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="I25" s="43" t="n"/>
       <c r="J25" s="38" t="n"/>
-      <c r="K25" s="579" t="inlineStr">
+      <c r="K25" s="575" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="M25" s="43" t="n"/>
       <c r="N25" s="38" t="n"/>
-      <c r="O25" s="566" t="n"/>
+      <c r="O25" s="623" t="n"/>
       <c r="P25" s="43" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="Q25" s="43" t="n"/>
       <c r="R25" s="38" t="n"/>
-      <c r="S25" s="604" t="n"/>
+      <c r="S25" s="620" t="n"/>
       <c r="T25" s="45" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10524,7 +10524,7 @@
       </c>
       <c r="U25" s="45" t="n"/>
       <c r="V25" s="42" t="n"/>
-      <c r="W25" s="621" t="n"/>
+      <c r="W25" s="573" t="n"/>
       <c r="X25" s="1" t="inlineStr">
         <is>
           <t>Struttura</t>
@@ -10534,8 +10534,8 @@
       <c r="Z25" s="38" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="587" t="n"/>
-      <c r="C26" s="567" t="n"/>
+      <c r="A26" s="572" t="n"/>
+      <c r="C26" s="569" t="n"/>
       <c r="D26" s="33" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="E26" s="43" t="n"/>
       <c r="F26" s="38" t="n"/>
-      <c r="G26" s="567" t="n"/>
+      <c r="G26" s="569" t="n"/>
       <c r="H26" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="I26" s="43" t="n"/>
       <c r="J26" s="38" t="n"/>
-      <c r="K26" s="567" t="n"/>
+      <c r="K26" s="569" t="n"/>
       <c r="L26" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="M26" s="43" t="n"/>
       <c r="N26" s="38" t="n"/>
-      <c r="O26" s="567" t="n"/>
+      <c r="O26" s="569" t="n"/>
       <c r="P26" s="43" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="Q26" s="43" t="n"/>
       <c r="R26" s="38" t="n"/>
-      <c r="S26" s="567" t="n"/>
+      <c r="S26" s="569" t="n"/>
       <c r="T26" s="45" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10575,7 +10575,7 @@
       </c>
       <c r="U26" s="45" t="n"/>
       <c r="V26" s="42" t="n"/>
-      <c r="W26" s="567" t="n"/>
+      <c r="W26" s="569" t="n"/>
       <c r="X26" s="1" t="inlineStr">
         <is>
           <t>Archetto</t>
@@ -10585,8 +10585,8 @@
       <c r="Z26" s="38" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="587" t="n"/>
-      <c r="C27" s="567" t="n"/>
+      <c r="A27" s="572" t="n"/>
+      <c r="C27" s="569" t="n"/>
       <c r="D27" s="33" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E27" s="43" t="n"/>
       <c r="F27" s="38" t="n"/>
-      <c r="G27" s="567" t="n"/>
+      <c r="G27" s="569" t="n"/>
       <c r="H27" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="I27" s="43" t="n"/>
       <c r="J27" s="38" t="n"/>
-      <c r="K27" s="567" t="n"/>
+      <c r="K27" s="569" t="n"/>
       <c r="L27" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="M27" s="43" t="n"/>
       <c r="N27" s="38" t="n"/>
-      <c r="O27" s="567" t="n"/>
+      <c r="O27" s="569" t="n"/>
       <c r="P27" s="43" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="Q27" s="43" t="n"/>
       <c r="R27" s="38" t="n"/>
-      <c r="S27" s="567" t="n"/>
+      <c r="S27" s="569" t="n"/>
       <c r="T27" s="45" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="U27" s="45" t="n"/>
       <c r="V27" s="42" t="n"/>
-      <c r="W27" s="567" t="n"/>
+      <c r="W27" s="569" t="n"/>
       <c r="X27" s="1" t="inlineStr">
         <is>
           <t>Strisciante</t>
@@ -10635,10 +10635,10 @@
       <c r="Y27" s="43" t="n"/>
       <c r="Z27" s="38" t="n"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="A28" s="603" t="n"/>
-      <c r="B28" s="539" t="n"/>
-      <c r="C28" s="578" t="n"/>
+    <row r="28" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="A28" s="608" t="n"/>
+      <c r="B28" s="540" t="n"/>
+      <c r="C28" s="570" t="n"/>
       <c r="D28" s="52" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="E28" s="56" t="n"/>
       <c r="F28" s="57" t="n"/>
-      <c r="G28" s="578" t="n"/>
+      <c r="G28" s="570" t="n"/>
       <c r="H28" s="53" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="I28" s="56" t="n"/>
       <c r="J28" s="57" t="n"/>
-      <c r="K28" s="578" t="n"/>
+      <c r="K28" s="570" t="n"/>
       <c r="L28" s="53" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="M28" s="56" t="n"/>
       <c r="N28" s="57" t="n"/>
-      <c r="O28" s="568" t="n"/>
+      <c r="O28" s="574" t="n"/>
       <c r="P28" s="56" t="inlineStr">
         <is>
           <t>PPU</t>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="Q28" s="56" t="n"/>
       <c r="R28" s="57" t="n"/>
-      <c r="S28" s="568" t="n"/>
+      <c r="S28" s="574" t="n"/>
       <c r="T28" s="59" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="U28" s="59" t="n"/>
       <c r="V28" s="60" t="n"/>
-      <c r="W28" s="568" t="n"/>
+      <c r="W28" s="574" t="n"/>
       <c r="X28" s="53" t="inlineStr">
         <is>
           <t>PCU</t>
@@ -10687,13 +10687,13 @@
       <c r="Y28" s="56" t="n"/>
       <c r="Z28" s="57" t="n"/>
     </row>
-    <row r="29" ht="101.45" customHeight="1" s="592">
-      <c r="A29" s="586" t="inlineStr">
+    <row r="29" ht="101.45" customHeight="1" s="582">
+      <c r="A29" s="590" t="inlineStr">
         <is>
           <t>TCMS Hardware</t>
         </is>
       </c>
-      <c r="B29" s="586" t="inlineStr">
+      <c r="B29" s="590" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
@@ -10728,12 +10728,12 @@
           <t>CCU-O</t>
         </is>
       </c>
-      <c r="M29" s="610" t="inlineStr">
+      <c r="M29" s="617" t="inlineStr">
         <is>
           <t>Nuova architettura Full Ethernet</t>
         </is>
       </c>
-      <c r="N29" s="573" t="n"/>
+      <c r="N29" s="602" t="n"/>
       <c r="O29" s="76" t="n"/>
       <c r="P29" s="77" t="inlineStr">
         <is>
@@ -10776,8 +10776,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="587" t="n"/>
-      <c r="B30" s="587" t="n"/>
+      <c r="A30" s="572" t="n"/>
+      <c r="B30" s="572" t="n"/>
       <c r="C30" s="80" t="n"/>
       <c r="D30" s="81" t="inlineStr">
         <is>
@@ -10808,8 +10808,8 @@
           <t>CCU-S</t>
         </is>
       </c>
-      <c r="M30" s="611" t="n"/>
-      <c r="N30" s="593" t="n"/>
+      <c r="M30" s="618" t="n"/>
+      <c r="N30" s="583" t="n"/>
       <c r="O30" s="80" t="n"/>
       <c r="P30" s="81" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="V30" s="35" t="n"/>
-      <c r="W30" s="531" t="n"/>
+      <c r="W30" s="528" t="n"/>
       <c r="X30" s="81" t="inlineStr">
         <is>
           <t>CCU-S</t>
@@ -10847,9 +10847,9 @@
       </c>
       <c r="Z30" s="35" t="n"/>
     </row>
-    <row r="31" ht="144.6" customHeight="1" s="592">
-      <c r="A31" s="587" t="n"/>
-      <c r="B31" s="588" t="n"/>
+    <row r="31" ht="144.6" customHeight="1" s="582">
+      <c r="A31" s="572" t="n"/>
+      <c r="B31" s="591" t="n"/>
       <c r="C31" s="80" t="n"/>
       <c r="D31" s="82" t="inlineStr">
         <is>
@@ -10888,8 +10888,8 @@
           <t>MIO-S</t>
         </is>
       </c>
-      <c r="M31" s="611" t="n"/>
-      <c r="N31" s="593" t="n"/>
+      <c r="M31" s="618" t="n"/>
+      <c r="N31" s="583" t="n"/>
       <c r="O31" s="80" t="n"/>
       <c r="P31" s="82" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="V31" s="35" t="n"/>
-      <c r="W31" s="531" t="n"/>
+      <c r="W31" s="528" t="n"/>
       <c r="X31" s="82" t="inlineStr">
         <is>
           <t>MIO-S</t>
@@ -10937,9 +10937,9 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="29.1" customHeight="1" s="592">
-      <c r="A32" s="587" t="n"/>
-      <c r="B32" s="624" t="inlineStr">
+    <row r="32" ht="29.1" customHeight="1" s="582">
+      <c r="A32" s="572" t="n"/>
+      <c r="B32" s="589" t="inlineStr">
         <is>
           <t>Teledia</t>
         </is>
@@ -10978,8 +10978,8 @@
           <t>MCG</t>
         </is>
       </c>
-      <c r="M32" s="611" t="n"/>
-      <c r="N32" s="593" t="n"/>
+      <c r="M32" s="618" t="n"/>
+      <c r="N32" s="583" t="n"/>
       <c r="O32" s="80" t="n"/>
       <c r="P32" s="82" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="V32" s="35" t="n"/>
-      <c r="W32" s="531" t="n"/>
+      <c r="W32" s="528" t="n"/>
       <c r="X32" s="82" t="inlineStr">
         <is>
           <t>MCG</t>
@@ -11022,8 +11022,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="587" t="n"/>
-      <c r="B33" s="602" t="inlineStr">
+      <c r="A33" s="572" t="n"/>
+      <c r="B33" s="610" t="inlineStr">
         <is>
           <t>Monitor</t>
         </is>
@@ -11058,8 +11058,8 @@
           <t>IDU/TOD</t>
         </is>
       </c>
-      <c r="M33" s="611" t="n"/>
-      <c r="N33" s="593" t="n"/>
+      <c r="M33" s="618" t="n"/>
+      <c r="N33" s="583" t="n"/>
       <c r="O33" s="80" t="n"/>
       <c r="P33" s="81" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="V33" s="35" t="n"/>
-      <c r="W33" s="531" t="n"/>
+      <c r="W33" s="528" t="n"/>
       <c r="X33" s="81" t="inlineStr">
         <is>
           <t>IDU</t>
@@ -11097,9 +11097,9 @@
       </c>
       <c r="Z33" s="35" t="n"/>
     </row>
-    <row r="34" ht="14.45" customHeight="1" s="592">
-      <c r="A34" s="587" t="n"/>
-      <c r="B34" s="620" t="inlineStr">
+    <row r="34" ht="14.45" customHeight="1" s="582">
+      <c r="A34" s="572" t="n"/>
+      <c r="B34" s="571" t="inlineStr">
         <is>
           <t>Bus</t>
         </is>
@@ -11127,7 +11127,7 @@
           <t>3EST000236-6770</t>
         </is>
       </c>
-      <c r="J34" s="614" t="inlineStr">
+      <c r="J34" s="611" t="inlineStr">
         <is>
           <t>Sell no more supported for new projects due to internal component out of production (legacy only)</t>
         </is>
@@ -11138,8 +11138,8 @@
           <t>T Repeater</t>
         </is>
       </c>
-      <c r="M34" s="611" t="n"/>
-      <c r="N34" s="593" t="n"/>
+      <c r="M34" s="618" t="n"/>
+      <c r="N34" s="583" t="n"/>
       <c r="O34" s="80" t="n"/>
       <c r="P34" s="81" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         </is>
       </c>
       <c r="V34" s="35" t="n"/>
-      <c r="W34" s="531" t="n"/>
+      <c r="W34" s="528" t="n"/>
       <c r="X34" s="81" t="inlineStr">
         <is>
           <t>T Repeater</t>
@@ -11175,15 +11175,15 @@
           <t>3EST000236-6770</t>
         </is>
       </c>
-      <c r="Z34" s="614" t="inlineStr">
+      <c r="Z34" s="611" t="inlineStr">
         <is>
           <t>Sell no more supported for new projects due to internal component out of production (legacy only)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="587" t="n"/>
-      <c r="B35" s="587" t="n"/>
+      <c r="A35" s="572" t="n"/>
+      <c r="B35" s="572" t="n"/>
       <c r="C35" s="80" t="n"/>
       <c r="D35" s="81" t="inlineStr">
         <is>
@@ -11207,15 +11207,15 @@
           <t>3EST000236-6769</t>
         </is>
       </c>
-      <c r="J35" s="615" t="n"/>
+      <c r="J35" s="612" t="n"/>
       <c r="K35" s="80" t="n"/>
       <c r="L35" s="81" t="inlineStr">
         <is>
           <t>T Switch</t>
         </is>
       </c>
-      <c r="M35" s="611" t="n"/>
-      <c r="N35" s="593" t="n"/>
+      <c r="M35" s="618" t="n"/>
+      <c r="N35" s="583" t="n"/>
       <c r="O35" s="80" t="n"/>
       <c r="P35" s="81" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="V35" s="35" t="n"/>
-      <c r="W35" s="531" t="n"/>
+      <c r="W35" s="528" t="n"/>
       <c r="X35" s="81" t="inlineStr">
         <is>
           <t>T Switch</t>
@@ -11251,11 +11251,11 @@
           <t>3EST000236-6769</t>
         </is>
       </c>
-      <c r="Z35" s="615" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="A36" s="588" t="n"/>
-      <c r="B36" s="587" t="n"/>
+      <c r="Z35" s="612" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="A36" s="591" t="n"/>
+      <c r="B36" s="572" t="n"/>
       <c r="C36" s="89" t="n"/>
       <c r="D36" s="90" t="inlineStr">
         <is>
@@ -11279,15 +11279,15 @@
           <t>3EST000234-7837</t>
         </is>
       </c>
-      <c r="J36" s="615" t="n"/>
+      <c r="J36" s="612" t="n"/>
       <c r="K36" s="89" t="n"/>
       <c r="L36" s="90" t="inlineStr">
         <is>
           <t>R Switch</t>
         </is>
       </c>
-      <c r="M36" s="612" t="n"/>
-      <c r="N36" s="596" t="n"/>
+      <c r="M36" s="619" t="n"/>
+      <c r="N36" s="586" t="n"/>
       <c r="O36" s="89" t="n"/>
       <c r="P36" s="90" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="V36" s="92" t="n"/>
-      <c r="W36" s="558" t="n"/>
+      <c r="W36" s="555" t="n"/>
       <c r="X36" s="90" t="inlineStr">
         <is>
           <t>R Switch</t>
@@ -11323,9 +11323,9 @@
           <t>3EST000234-7837</t>
         </is>
       </c>
-      <c r="Z36" s="615" t="n"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" s="592" thickBot="1">
+      <c r="Z36" s="612" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="A37" s="66" t="inlineStr">
         <is>
           <t>Energy Meter</t>
@@ -11336,62 +11336,62 @@
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C37" s="607" t="inlineStr">
+      <c r="C37" s="578" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D37" s="583" t="n"/>
-      <c r="E37" s="583" t="n"/>
-      <c r="F37" s="570" t="n"/>
-      <c r="G37" s="607" t="inlineStr">
+      <c r="D37" s="566" t="n"/>
+      <c r="E37" s="566" t="n"/>
+      <c r="F37" s="567" t="n"/>
+      <c r="G37" s="578" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H37" s="583" t="n"/>
-      <c r="I37" s="583" t="n"/>
-      <c r="J37" s="570" t="n"/>
-      <c r="K37" s="597" t="inlineStr">
+      <c r="H37" s="566" t="n"/>
+      <c r="I37" s="566" t="n"/>
+      <c r="J37" s="567" t="n"/>
+      <c r="K37" s="588" t="inlineStr">
         <is>
           <t>EMS Microelettrica  integrato con TCMS</t>
         </is>
       </c>
-      <c r="L37" s="583" t="n"/>
-      <c r="M37" s="583" t="n"/>
-      <c r="N37" s="570" t="n"/>
-      <c r="O37" s="597" t="inlineStr">
+      <c r="L37" s="566" t="n"/>
+      <c r="M37" s="566" t="n"/>
+      <c r="N37" s="567" t="n"/>
+      <c r="O37" s="588" t="inlineStr">
         <is>
           <t>EMS Microelettrica non integrato con TCMS</t>
         </is>
       </c>
-      <c r="P37" s="583" t="n"/>
-      <c r="Q37" s="583" t="n"/>
-      <c r="R37" s="570" t="n"/>
-      <c r="S37" s="597" t="inlineStr">
+      <c r="P37" s="566" t="n"/>
+      <c r="Q37" s="566" t="n"/>
+      <c r="R37" s="567" t="n"/>
+      <c r="S37" s="588" t="inlineStr">
         <is>
           <t>EMS Alstom  integrato con TCMS</t>
         </is>
       </c>
-      <c r="T37" s="583" t="n"/>
-      <c r="U37" s="583" t="n"/>
-      <c r="V37" s="570" t="n"/>
-      <c r="W37" s="597" t="inlineStr">
+      <c r="T37" s="566" t="n"/>
+      <c r="U37" s="566" t="n"/>
+      <c r="V37" s="567" t="n"/>
+      <c r="W37" s="588" t="inlineStr">
         <is>
           <t>EMS Alstom  integrato con TCMS</t>
         </is>
       </c>
-      <c r="X37" s="583" t="n"/>
-      <c r="Y37" s="583" t="n"/>
-      <c r="Z37" s="570" t="n"/>
-    </row>
-    <row r="38" ht="87" customHeight="1" s="592">
-      <c r="A38" s="586" t="inlineStr">
+      <c r="X37" s="566" t="n"/>
+      <c r="Y37" s="566" t="n"/>
+      <c r="Z37" s="567" t="n"/>
+    </row>
+    <row r="38" ht="87" customHeight="1" s="582">
+      <c r="A38" s="590" t="inlineStr">
         <is>
           <t>Freno</t>
         </is>
       </c>
-      <c r="B38" s="608" t="inlineStr">
+      <c r="B38" s="564" t="inlineStr">
         <is>
           <t>Centraline</t>
         </is>
@@ -11465,9 +11465,9 @@
       <c r="Y38" s="61" t="n"/>
       <c r="Z38" s="63" t="n"/>
     </row>
-    <row r="39" ht="101.45" customHeight="1" s="592">
-      <c r="A39" s="587" t="n"/>
-      <c r="B39" s="539" t="n"/>
+    <row r="39" ht="101.45" customHeight="1" s="582">
+      <c r="A39" s="572" t="n"/>
+      <c r="B39" s="540" t="n"/>
       <c r="C39" s="80" t="n"/>
       <c r="D39" s="33" t="inlineStr">
         <is>
@@ -11542,8 +11542,8 @@
       <c r="Z39" s="35" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="587" t="n"/>
-      <c r="B40" s="605" t="inlineStr">
+      <c r="A40" s="572" t="n"/>
+      <c r="B40" s="587" t="inlineStr">
         <is>
           <t>Pneumatica</t>
         </is>
@@ -11614,8 +11614,8 @@
       <c r="Z40" s="35" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="587" t="n"/>
-      <c r="B41" s="591" t="n"/>
+      <c r="A41" s="572" t="n"/>
+      <c r="B41" s="581" t="n"/>
       <c r="C41" s="80" t="n"/>
       <c r="D41" s="33" t="inlineStr">
         <is>
@@ -11681,9 +11681,9 @@
       <c r="Y41" s="1" t="n"/>
       <c r="Z41" s="35" t="n"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="A42" s="588" t="n"/>
-      <c r="B42" s="594" t="n"/>
+    <row r="42" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="A42" s="591" t="n"/>
+      <c r="B42" s="584" t="n"/>
       <c r="C42" s="89" t="n"/>
       <c r="D42" s="98" t="inlineStr">
         <is>
@@ -11782,194 +11782,194 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="586" t="inlineStr">
+      <c r="A43" s="590" t="inlineStr">
         <is>
           <t>PRM</t>
         </is>
       </c>
-      <c r="B43" s="608" t="inlineStr">
+      <c r="B43" s="564" t="inlineStr">
         <is>
           <t>Toilet</t>
         </is>
       </c>
-      <c r="C43" s="571" t="inlineStr">
+      <c r="C43" s="600" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="D43" s="572" t="n"/>
-      <c r="E43" s="572" t="n"/>
-      <c r="F43" s="573" t="n"/>
-      <c r="G43" s="571" t="inlineStr">
+      <c r="D43" s="601" t="n"/>
+      <c r="E43" s="601" t="n"/>
+      <c r="F43" s="602" t="n"/>
+      <c r="G43" s="600" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="H43" s="572" t="n"/>
-      <c r="I43" s="572" t="n"/>
-      <c r="J43" s="573" t="n"/>
-      <c r="K43" s="571" t="inlineStr">
+      <c r="H43" s="601" t="n"/>
+      <c r="I43" s="601" t="n"/>
+      <c r="J43" s="602" t="n"/>
+      <c r="K43" s="600" t="inlineStr">
         <is>
           <t>Toilet Production HK - conf. NRD Spagna + STI PRM 2019</t>
         </is>
       </c>
-      <c r="L43" s="572" t="n"/>
-      <c r="M43" s="572" t="n"/>
-      <c r="N43" s="573" t="n"/>
-      <c r="O43" s="571" t="inlineStr">
+      <c r="L43" s="601" t="n"/>
+      <c r="M43" s="601" t="n"/>
+      <c r="N43" s="602" t="n"/>
+      <c r="O43" s="600" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="P43" s="572" t="n"/>
-      <c r="Q43" s="572" t="n"/>
-      <c r="R43" s="573" t="n"/>
-      <c r="S43" s="571" t="inlineStr">
+      <c r="P43" s="601" t="n"/>
+      <c r="Q43" s="601" t="n"/>
+      <c r="R43" s="602" t="n"/>
+      <c r="S43" s="600" t="inlineStr">
         <is>
           <t>Toilet Production HK standard flotta base</t>
         </is>
       </c>
-      <c r="T43" s="572" t="n"/>
-      <c r="U43" s="572" t="n"/>
-      <c r="V43" s="573" t="n"/>
-      <c r="W43" s="571" t="inlineStr">
+      <c r="T43" s="601" t="n"/>
+      <c r="U43" s="601" t="n"/>
+      <c r="V43" s="602" t="n"/>
+      <c r="W43" s="600" t="inlineStr">
         <is>
           <t>Toilet Production HK - conf. NRD Spagna + STI PRM 2019</t>
         </is>
       </c>
-      <c r="X43" s="572" t="n"/>
-      <c r="Y43" s="572" t="n"/>
-      <c r="Z43" s="573" t="n"/>
+      <c r="X43" s="601" t="n"/>
+      <c r="Y43" s="601" t="n"/>
+      <c r="Z43" s="602" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="587" t="n"/>
-      <c r="B44" s="539" t="n"/>
-      <c r="C44" s="574" t="n"/>
-      <c r="D44" s="539" t="n"/>
-      <c r="E44" s="539" t="n"/>
-      <c r="F44" s="575" t="n"/>
-      <c r="G44" s="574" t="n"/>
-      <c r="H44" s="539" t="n"/>
-      <c r="I44" s="539" t="n"/>
-      <c r="J44" s="575" t="n"/>
-      <c r="K44" s="574" t="n"/>
-      <c r="L44" s="539" t="n"/>
-      <c r="M44" s="539" t="n"/>
-      <c r="N44" s="575" t="n"/>
-      <c r="O44" s="574" t="n"/>
-      <c r="P44" s="539" t="n"/>
-      <c r="Q44" s="539" t="n"/>
-      <c r="R44" s="575" t="n"/>
-      <c r="S44" s="574" t="n"/>
-      <c r="T44" s="539" t="n"/>
-      <c r="U44" s="539" t="n"/>
-      <c r="V44" s="575" t="n"/>
-      <c r="W44" s="574" t="n"/>
-      <c r="X44" s="539" t="n"/>
-      <c r="Y44" s="539" t="n"/>
-      <c r="Z44" s="575" t="n"/>
+      <c r="A44" s="572" t="n"/>
+      <c r="B44" s="540" t="n"/>
+      <c r="C44" s="603" t="n"/>
+      <c r="D44" s="540" t="n"/>
+      <c r="E44" s="540" t="n"/>
+      <c r="F44" s="604" t="n"/>
+      <c r="G44" s="603" t="n"/>
+      <c r="H44" s="540" t="n"/>
+      <c r="I44" s="540" t="n"/>
+      <c r="J44" s="604" t="n"/>
+      <c r="K44" s="603" t="n"/>
+      <c r="L44" s="540" t="n"/>
+      <c r="M44" s="540" t="n"/>
+      <c r="N44" s="604" t="n"/>
+      <c r="O44" s="603" t="n"/>
+      <c r="P44" s="540" t="n"/>
+      <c r="Q44" s="540" t="n"/>
+      <c r="R44" s="604" t="n"/>
+      <c r="S44" s="603" t="n"/>
+      <c r="T44" s="540" t="n"/>
+      <c r="U44" s="540" t="n"/>
+      <c r="V44" s="604" t="n"/>
+      <c r="W44" s="603" t="n"/>
+      <c r="X44" s="540" t="n"/>
+      <c r="Y44" s="540" t="n"/>
+      <c r="Z44" s="604" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="587" t="n"/>
-      <c r="B45" s="605" t="inlineStr">
+      <c r="A45" s="572" t="n"/>
+      <c r="B45" s="587" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="C45" s="599" t="inlineStr">
+      <c r="C45" s="579" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="D45" s="557" t="n"/>
-      <c r="E45" s="557" t="n"/>
-      <c r="F45" s="590" t="n"/>
-      <c r="G45" s="599" t="inlineStr">
+      <c r="D45" s="560" t="n"/>
+      <c r="E45" s="560" t="n"/>
+      <c r="F45" s="580" t="n"/>
+      <c r="G45" s="579" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="H45" s="557" t="n"/>
-      <c r="I45" s="557" t="n"/>
-      <c r="J45" s="590" t="n"/>
-      <c r="K45" s="589" t="inlineStr">
+      <c r="H45" s="560" t="n"/>
+      <c r="I45" s="560" t="n"/>
+      <c r="J45" s="580" t="n"/>
+      <c r="K45" s="614" t="inlineStr">
         <is>
           <t>Lift HK STI PRM 2019 (pedana più grande, azionamento elettrico)</t>
         </is>
       </c>
-      <c r="L45" s="557" t="n"/>
-      <c r="M45" s="557" t="n"/>
-      <c r="N45" s="590" t="n"/>
-      <c r="O45" s="599" t="inlineStr">
+      <c r="L45" s="560" t="n"/>
+      <c r="M45" s="560" t="n"/>
+      <c r="N45" s="580" t="n"/>
+      <c r="O45" s="579" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="P45" s="557" t="n"/>
-      <c r="Q45" s="557" t="n"/>
-      <c r="R45" s="590" t="n"/>
-      <c r="S45" s="599" t="inlineStr">
+      <c r="P45" s="560" t="n"/>
+      <c r="Q45" s="560" t="n"/>
+      <c r="R45" s="580" t="n"/>
+      <c r="S45" s="579" t="inlineStr">
         <is>
           <t>Lift HK standard flotta base azionamento idraulico</t>
         </is>
       </c>
-      <c r="T45" s="557" t="n"/>
-      <c r="U45" s="557" t="n"/>
-      <c r="V45" s="590" t="n"/>
-      <c r="W45" s="589" t="inlineStr">
+      <c r="T45" s="560" t="n"/>
+      <c r="U45" s="560" t="n"/>
+      <c r="V45" s="580" t="n"/>
+      <c r="W45" s="614" t="inlineStr">
         <is>
           <t>Lift HK STI PRM 2019 (pedana più grande) azionamento idraulico</t>
         </is>
       </c>
-      <c r="X45" s="557" t="n"/>
-      <c r="Y45" s="557" t="n"/>
-      <c r="Z45" s="590" t="n"/>
+      <c r="X45" s="560" t="n"/>
+      <c r="Y45" s="560" t="n"/>
+      <c r="Z45" s="580" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="587" t="n"/>
-      <c r="B46" s="591" t="n"/>
-      <c r="C46" s="591" t="n"/>
-      <c r="F46" s="593" t="n"/>
-      <c r="G46" s="591" t="n"/>
-      <c r="J46" s="593" t="n"/>
-      <c r="K46" s="591" t="n"/>
-      <c r="N46" s="593" t="n"/>
-      <c r="O46" s="591" t="n"/>
-      <c r="R46" s="593" t="n"/>
-      <c r="S46" s="591" t="n"/>
-      <c r="V46" s="593" t="n"/>
-      <c r="W46" s="591" t="n"/>
-      <c r="Z46" s="593" t="n"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="A47" s="588" t="n"/>
-      <c r="B47" s="594" t="n"/>
-      <c r="C47" s="594" t="n"/>
-      <c r="D47" s="595" t="n"/>
-      <c r="E47" s="595" t="n"/>
-      <c r="F47" s="596" t="n"/>
-      <c r="G47" s="594" t="n"/>
-      <c r="H47" s="595" t="n"/>
-      <c r="I47" s="595" t="n"/>
-      <c r="J47" s="596" t="n"/>
-      <c r="K47" s="594" t="n"/>
-      <c r="L47" s="595" t="n"/>
-      <c r="M47" s="595" t="n"/>
-      <c r="N47" s="596" t="n"/>
-      <c r="O47" s="594" t="n"/>
-      <c r="P47" s="595" t="n"/>
-      <c r="Q47" s="595" t="n"/>
-      <c r="R47" s="596" t="n"/>
-      <c r="S47" s="594" t="n"/>
-      <c r="T47" s="595" t="n"/>
-      <c r="U47" s="595" t="n"/>
-      <c r="V47" s="596" t="n"/>
-      <c r="W47" s="594" t="n"/>
-      <c r="X47" s="595" t="n"/>
-      <c r="Y47" s="595" t="n"/>
-      <c r="Z47" s="596" t="n"/>
-    </row>
-    <row r="48" ht="29.45" customHeight="1" s="592" thickBot="1">
+      <c r="A46" s="572" t="n"/>
+      <c r="B46" s="581" t="n"/>
+      <c r="C46" s="581" t="n"/>
+      <c r="F46" s="583" t="n"/>
+      <c r="G46" s="581" t="n"/>
+      <c r="J46" s="583" t="n"/>
+      <c r="K46" s="581" t="n"/>
+      <c r="N46" s="583" t="n"/>
+      <c r="O46" s="581" t="n"/>
+      <c r="R46" s="583" t="n"/>
+      <c r="S46" s="581" t="n"/>
+      <c r="V46" s="583" t="n"/>
+      <c r="W46" s="581" t="n"/>
+      <c r="Z46" s="583" t="n"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="A47" s="591" t="n"/>
+      <c r="B47" s="584" t="n"/>
+      <c r="C47" s="584" t="n"/>
+      <c r="D47" s="585" t="n"/>
+      <c r="E47" s="585" t="n"/>
+      <c r="F47" s="586" t="n"/>
+      <c r="G47" s="584" t="n"/>
+      <c r="H47" s="585" t="n"/>
+      <c r="I47" s="585" t="n"/>
+      <c r="J47" s="586" t="n"/>
+      <c r="K47" s="584" t="n"/>
+      <c r="L47" s="585" t="n"/>
+      <c r="M47" s="585" t="n"/>
+      <c r="N47" s="586" t="n"/>
+      <c r="O47" s="584" t="n"/>
+      <c r="P47" s="585" t="n"/>
+      <c r="Q47" s="585" t="n"/>
+      <c r="R47" s="586" t="n"/>
+      <c r="S47" s="584" t="n"/>
+      <c r="T47" s="585" t="n"/>
+      <c r="U47" s="585" t="n"/>
+      <c r="V47" s="586" t="n"/>
+      <c r="W47" s="584" t="n"/>
+      <c r="X47" s="585" t="n"/>
+      <c r="Y47" s="585" t="n"/>
+      <c r="Z47" s="586" t="n"/>
+    </row>
+    <row r="48" ht="29.45" customHeight="1" s="582" thickBot="1">
       <c r="A48" s="100" t="inlineStr">
         <is>
           <t>Porte Esterne</t>
@@ -11980,58 +11980,58 @@
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C48" s="598" t="inlineStr">
+      <c r="C48" s="615" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="D48" s="583" t="n"/>
-      <c r="E48" s="583" t="n"/>
-      <c r="F48" s="570" t="n"/>
-      <c r="G48" s="598" t="inlineStr">
+      <c r="D48" s="566" t="n"/>
+      <c r="E48" s="566" t="n"/>
+      <c r="F48" s="567" t="n"/>
+      <c r="G48" s="615" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="H48" s="583" t="n"/>
-      <c r="I48" s="583" t="n"/>
-      <c r="J48" s="570" t="n"/>
-      <c r="K48" s="619" t="inlineStr">
+      <c r="H48" s="566" t="n"/>
+      <c r="I48" s="566" t="n"/>
+      <c r="J48" s="567" t="n"/>
+      <c r="K48" s="565" t="inlineStr">
         <is>
           <t>Porte esterne IFE TSI 2019
 Centralina Ethernet</t>
         </is>
       </c>
-      <c r="L48" s="583" t="n"/>
-      <c r="M48" s="583" t="n"/>
-      <c r="N48" s="570" t="n"/>
-      <c r="O48" s="598" t="inlineStr">
+      <c r="L48" s="566" t="n"/>
+      <c r="M48" s="566" t="n"/>
+      <c r="N48" s="567" t="n"/>
+      <c r="O48" s="615" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="P48" s="583" t="n"/>
-      <c r="Q48" s="583" t="n"/>
-      <c r="R48" s="570" t="n"/>
-      <c r="S48" s="598" t="inlineStr">
+      <c r="P48" s="566" t="n"/>
+      <c r="Q48" s="566" t="n"/>
+      <c r="R48" s="567" t="n"/>
+      <c r="S48" s="615" t="inlineStr">
         <is>
           <t>Porte esterne IFE standard flotta base</t>
         </is>
       </c>
-      <c r="T48" s="583" t="n"/>
-      <c r="U48" s="583" t="n"/>
-      <c r="V48" s="570" t="n"/>
-      <c r="W48" s="623" t="inlineStr">
+      <c r="T48" s="566" t="n"/>
+      <c r="U48" s="566" t="n"/>
+      <c r="V48" s="567" t="n"/>
+      <c r="W48" s="577" t="inlineStr">
         <is>
           <t>Porte esterne IFE (TSI 2019)</t>
         </is>
       </c>
-      <c r="X48" s="583" t="n"/>
-      <c r="Y48" s="583" t="n"/>
-      <c r="Z48" s="570" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" s="592">
-      <c r="A49" s="569" t="inlineStr">
+      <c r="X48" s="566" t="n"/>
+      <c r="Y48" s="566" t="n"/>
+      <c r="Z48" s="567" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1" s="582">
+      <c r="A49" s="607" t="inlineStr">
         <is>
           <t>Antincendio</t>
         </is>
@@ -12042,110 +12042,110 @@
 Elettronica</t>
         </is>
       </c>
-      <c r="C49" s="571" t="inlineStr">
+      <c r="C49" s="600" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
       <c r="D49" s="549" t="n"/>
       <c r="E49" s="549" t="n"/>
-      <c r="F49" s="565" t="n"/>
-      <c r="G49" s="564" t="inlineStr">
+      <c r="F49" s="593" t="n"/>
+      <c r="G49" s="592" t="inlineStr">
         <is>
           <t>FDU-1000 (fornitura ISE)</t>
         </is>
       </c>
       <c r="H49" s="549" t="n"/>
       <c r="I49" s="549" t="n"/>
-      <c r="J49" s="565" t="n"/>
-      <c r="K49" s="564" t="inlineStr">
+      <c r="J49" s="593" t="n"/>
+      <c r="K49" s="592" t="inlineStr">
         <is>
           <t>FDU ISE</t>
         </is>
       </c>
       <c r="L49" s="549" t="n"/>
       <c r="M49" s="549" t="n"/>
-      <c r="N49" s="565" t="n"/>
-      <c r="O49" s="571" t="inlineStr">
+      <c r="N49" s="593" t="n"/>
+      <c r="O49" s="600" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
       <c r="P49" s="549" t="n"/>
       <c r="Q49" s="549" t="n"/>
-      <c r="R49" s="565" t="n"/>
-      <c r="S49" s="571" t="inlineStr">
+      <c r="R49" s="593" t="n"/>
+      <c r="S49" s="600" t="inlineStr">
         <is>
           <t>SCU Saira</t>
         </is>
       </c>
       <c r="T49" s="549" t="n"/>
       <c r="U49" s="549" t="n"/>
-      <c r="V49" s="565" t="n"/>
-      <c r="W49" s="564" t="inlineStr">
+      <c r="V49" s="593" t="n"/>
+      <c r="W49" s="592" t="inlineStr">
         <is>
           <t>FDU-1000 (fornitura ISE)</t>
         </is>
       </c>
       <c r="X49" s="549" t="n"/>
       <c r="Y49" s="549" t="n"/>
-      <c r="Z49" s="565" t="n"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="A50" s="603" t="n"/>
+      <c r="Z49" s="593" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="A50" s="608" t="n"/>
       <c r="B50" s="75" t="inlineStr">
         <is>
           <t>Estinzione</t>
         </is>
       </c>
-      <c r="C50" s="606" t="inlineStr">
+      <c r="C50" s="597" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="D50" s="595" t="n"/>
-      <c r="E50" s="595" t="n"/>
-      <c r="F50" s="596" t="n"/>
-      <c r="G50" s="609" t="inlineStr">
+      <c r="D50" s="585" t="n"/>
+      <c r="E50" s="585" t="n"/>
+      <c r="F50" s="586" t="n"/>
+      <c r="G50" s="616" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="H50" s="595" t="n"/>
-      <c r="I50" s="595" t="n"/>
-      <c r="J50" s="596" t="n"/>
-      <c r="K50" s="609" t="inlineStr">
+      <c r="H50" s="585" t="n"/>
+      <c r="I50" s="585" t="n"/>
+      <c r="J50" s="586" t="n"/>
+      <c r="K50" s="616" t="inlineStr">
         <is>
           <t>WaterMist Acquasys - 1 gruppo MAU (DM1)</t>
         </is>
       </c>
-      <c r="L50" s="595" t="n"/>
-      <c r="M50" s="595" t="n"/>
-      <c r="N50" s="596" t="n"/>
-      <c r="O50" s="606" t="inlineStr">
+      <c r="L50" s="585" t="n"/>
+      <c r="M50" s="585" t="n"/>
+      <c r="N50" s="586" t="n"/>
+      <c r="O50" s="597" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="P50" s="595" t="n"/>
-      <c r="Q50" s="595" t="n"/>
-      <c r="R50" s="596" t="n"/>
-      <c r="S50" s="606" t="inlineStr">
+      <c r="P50" s="585" t="n"/>
+      <c r="Q50" s="585" t="n"/>
+      <c r="R50" s="586" t="n"/>
+      <c r="S50" s="597" t="inlineStr">
         <is>
           <t>WaterMist Marioff - 2 gruppi MAU (DM1/8)</t>
         </is>
       </c>
-      <c r="T50" s="595" t="n"/>
-      <c r="U50" s="595" t="n"/>
-      <c r="V50" s="596" t="n"/>
-      <c r="W50" s="606" t="inlineStr">
+      <c r="T50" s="585" t="n"/>
+      <c r="U50" s="585" t="n"/>
+      <c r="V50" s="586" t="n"/>
+      <c r="W50" s="597" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="X50" s="595" t="n"/>
-      <c r="Y50" s="595" t="n"/>
-      <c r="Z50" s="596" t="n"/>
+      <c r="X50" s="585" t="n"/>
+      <c r="Y50" s="585" t="n"/>
+      <c r="Z50" s="586" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="100">
@@ -12186,8 +12186,8 @@
     <mergeCell ref="K37:N37"/>
     <mergeCell ref="A13:A28"/>
     <mergeCell ref="G13:G16"/>
+    <mergeCell ref="B17:B20"/>
     <mergeCell ref="W37:Z37"/>
-    <mergeCell ref="B17:B20"/>
     <mergeCell ref="Z34:Z36"/>
     <mergeCell ref="S13:S16"/>
     <mergeCell ref="C21:C24"/>
@@ -12238,8 +12238,8 @@
     <mergeCell ref="A43:A47"/>
     <mergeCell ref="W49:Z49"/>
     <mergeCell ref="O25:O28"/>
+    <mergeCell ref="K43:N44"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="K43:N44"/>
     <mergeCell ref="S9:S12"/>
     <mergeCell ref="G3:G8"/>
     <mergeCell ref="C17:C20"/>
@@ -12269,11 +12269,11 @@
     <col width="28.42578125" bestFit="1" customWidth="1" style="13" min="4" max="4"/>
     <col width="21.42578125" customWidth="1" style="13" min="5" max="5"/>
     <col width="35.5703125" customWidth="1" style="13" min="6" max="7"/>
-    <col width="8.7109375" customWidth="1" style="13" min="8" max="14"/>
-    <col width="8.7109375" customWidth="1" style="13" min="15" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="8" max="15"/>
+    <col width="8.7109375" customWidth="1" style="13" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="592">
+    <row r="1" ht="30" customHeight="1" s="582">
       <c r="A1" s="156" t="inlineStr">
         <is>
           <t>FUNC ID</t>
@@ -12284,18 +12284,18 @@
           <t>DESCRIZIONE FUNZIONE</t>
         </is>
       </c>
-      <c r="C1" s="526" t="inlineStr">
+      <c r="C1" s="531" t="inlineStr">
         <is>
           <t>DOC
 CARTELLA</t>
         </is>
       </c>
-      <c r="D1" s="526" t="inlineStr">
+      <c r="D1" s="531" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="E1" s="526" t="inlineStr">
+      <c r="E1" s="531" t="inlineStr">
         <is>
           <t>Info DOC</t>
         </is>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="G3" s="314" t="n"/>
     </row>
-    <row r="4" ht="45" customHeight="1" s="592">
+    <row r="4" ht="45" customHeight="1" s="582">
       <c r="A4" s="103" t="inlineStr">
         <is>
           <t>Nel foglio indicato in Cx nella colonna B, cerca la riga corrispondente al DOC ID indicato in Dx</t>
@@ -12381,7 +12381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="592">
+    <row r="5" ht="45" customHeight="1" s="582">
       <c r="A5" s="103" t="inlineStr">
         <is>
           <t>Nel foglio CONFIG riga 1, cerca la colonna corrispondente alla flotta indicata da F1</t>
@@ -12407,7 +12407,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="592">
+    <row r="6" ht="45" customHeight="1" s="582">
       <c r="A6" s="103" t="inlineStr">
         <is>
           <t>Restituisci la posizione della cella corrispondente a riga/colonna sopra identificati</t>
@@ -12433,7 +12433,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="592">
+    <row r="7" ht="30" customHeight="1" s="582">
       <c r="A7" s="103" t="inlineStr">
         <is>
           <t>Alla posizione della cella, concatena il nome del foglio recuperato in Cx</t>
@@ -12459,7 +12459,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="592">
+    <row r="8" ht="60" customHeight="1" s="582">
       <c r="A8" s="103" t="inlineStr">
         <is>
           <t>Recupera il contenuto del foglio/cella indicato nell'indirizzo sopra, il quale corrisponde al nome del file archiviato</t>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="592">
+    <row r="9" ht="60" customHeight="1" s="582">
       <c r="A9" s="103" t="inlineStr">
         <is>
           <t>Recupera il prefisso del DOC ID posto prima del carattere "_", al quale corrisponde la sottocartella di archiviazione</t>
@@ -12511,7 +12511,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="165" customHeight="1" s="592">
+    <row r="10" ht="165" customHeight="1" s="582">
       <c r="A10" s="103" t="inlineStr">
         <is>
           <t>crea l'indirizzo completo per la costruzione del link, concatenando:
@@ -12549,7 +12549,7 @@
       <c r="D11" s="434" t="n"/>
       <c r="E11" s="435" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1" s="592">
+    <row r="12" ht="45" customHeight="1" s="582">
       <c r="A12" s="103" t="inlineStr">
         <is>
           <t>recupero del formato del file dal foglio indicato in Cx, alla riga indicata del DOC ID e colonna 3</t>
@@ -12579,7 +12579,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="592">
+    <row r="13" ht="60" customHeight="1" s="582">
       <c r="A13" s="103" t="inlineStr">
         <is>
           <t>crea l'indirizzo come sopra, inserendo anche la parte di recupero di estensione del file</t>
@@ -12593,7 +12593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="592">
+    <row r="14" ht="30" customHeight="1" s="582">
       <c r="A14" s="436" t="inlineStr">
         <is>
           <t>prova link con DOC Type &lt;&gt; pdf</t>
@@ -12625,7 +12625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="592">
+    <row r="17" ht="30" customHeight="1" s="582">
       <c r="A17" s="436" t="inlineStr">
         <is>
           <t>prova link con DOC Type &lt;&gt; pdf</t>
@@ -12674,7 +12674,7 @@
       <c r="F19" s="161" t="n"/>
       <c r="G19" s="161" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="592">
+    <row r="20" ht="30" customHeight="1" s="582">
       <c r="A20" s="106" t="inlineStr">
         <is>
           <t>parte iniziale - posizione cella foglio/flotta</t>
@@ -12874,12 +12874,12 @@
   <dimension ref="B2:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41.85546875" customWidth="1" style="592" min="2" max="2"/>
-    <col width="6.140625" bestFit="1" customWidth="1" style="592" min="7" max="7"/>
+    <col width="41.85546875" customWidth="1" style="582" min="2" max="2"/>
+    <col width="6.140625" bestFit="1" customWidth="1" style="582" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="592" thickBot="1"/>
-    <row r="2" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="582" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>VZI-50</t>
@@ -12910,13 +12910,13 @@
           <t>VZ-ES</t>
         </is>
       </c>
-      <c r="I2" s="570" t="inlineStr">
+      <c r="I2" s="567" t="inlineStr">
         <is>
           <t>VZ-DAI</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">IPA (Indicazione Porte Aperte) </t>
@@ -12950,7 +12950,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30.75" customHeight="1" s="592" thickBot="1">
+    <row r="4" ht="30.75" customHeight="1" s="582" thickBot="1">
       <c r="B4" s="4" t="inlineStr">
         <is>
           <t>BY-PASS ALLARME APPLICAZIONE PARKING
@@ -12985,7 +12985,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>RIDONDANZA LOOP DNRA-BMS</t>
@@ -13019,7 +13019,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>INTERRUTTORI 220V SPOSTATI INTERNO CASSA</t>
@@ -13053,7 +13053,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>COMPRESSORE ARIA (?)</t>
@@ -13067,7 +13067,7 @@
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>BY-PASS ADD PER MARCIA SOCCORSO</t>
@@ -13101,7 +13101,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>ARREDI TOILET BAR BISTROT</t>
@@ -13115,7 +13115,7 @@
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
     </row>
-    <row r="10" ht="45.75" customHeight="1" s="592" thickBot="1">
+    <row r="10" ht="45.75" customHeight="1" s="582" thickBot="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>COMANDO DISACCOPPIAMENTO AUTOMATICO 
@@ -13150,7 +13150,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>PANTOGRAFI</t>
@@ -13164,13 +13164,13 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>PIANO DI MANUTENZIONE</t>
         </is>
       </c>
-      <c r="C12" s="531" t="n"/>
+      <c r="C12" s="528" t="n"/>
       <c r="D12" s="1" t="n"/>
       <c r="E12" s="1" t="n"/>
       <c r="F12" s="1" t="n"/>
@@ -13178,13 +13178,13 @@
       <c r="H12" s="1" t="n"/>
       <c r="I12" s="1" t="n"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="13" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>BL SSB</t>
         </is>
       </c>
-      <c r="C13" s="531" t="n"/>
+      <c r="C13" s="528" t="n"/>
       <c r="D13" s="1" t="n"/>
       <c r="E13" s="1" t="n"/>
       <c r="F13" s="1" t="n"/>
@@ -13192,13 +13192,13 @@
       <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="592" thickBot="1">
-      <c r="B14" s="603" t="inlineStr">
+    <row r="14" ht="15.75" customHeight="1" s="582" thickBot="1">
+      <c r="B14" s="608" t="inlineStr">
         <is>
           <t>BL DIS</t>
         </is>
       </c>
-      <c r="C14" s="531" t="n"/>
+      <c r="C14" s="528" t="n"/>
       <c r="D14" s="1" t="n"/>
       <c r="E14" s="1" t="n"/>
       <c r="F14" s="1" t="n"/>
@@ -13206,13 +13206,13 @@
       <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>ETCS HD (HW)</t>
         </is>
       </c>
-      <c r="C15" s="531" t="n"/>
+      <c r="C15" s="528" t="n"/>
       <c r="D15" s="1" t="n"/>
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="1" t="n"/>
@@ -13220,13 +13220,13 @@
       <c r="H15" s="1" t="n"/>
       <c r="I15" s="1" t="n"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANTINCENDIO </t>
         </is>
       </c>
-      <c r="C16" s="531" t="n"/>
+      <c r="C16" s="528" t="n"/>
       <c r="D16" s="1" t="n"/>
       <c r="E16" s="1" t="n"/>
       <c r="F16" s="1" t="n"/>
@@ -13234,7 +13234,7 @@
       <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="592" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="582" thickBot="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">LAYOUT INTERNO </t>
@@ -13275,8 +13275,8 @@
     <col width="8.7109375" customWidth="1" style="14" min="3" max="3"/>
     <col width="120.7109375" customWidth="1" style="103" min="4" max="4"/>
     <col width="60.140625" customWidth="1" style="103" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="13" min="6" max="12"/>
-    <col width="8.7109375" customWidth="1" style="13" min="13" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="6" max="13"/>
+    <col width="8.7109375" customWidth="1" style="13" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.45" customFormat="1" customHeight="1" s="192">
@@ -13306,7 +13306,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="592">
+    <row r="2" ht="30" customHeight="1" s="582">
       <c r="A2" s="308" t="n">
         <v>46190</v>
       </c>
@@ -13381,7 +13381,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="592">
+    <row r="5" ht="45" customHeight="1" s="582">
       <c r="A5" s="308" t="n">
         <v>46190</v>
       </c>
@@ -13431,7 +13431,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="592">
+    <row r="7" ht="45" customHeight="1" s="582">
       <c r="A7" s="308" t="n">
         <v>46189</v>
       </c>
@@ -13533,7 +13533,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="592">
+    <row r="11" ht="60" customHeight="1" s="582">
       <c r="A11" s="308" t="n">
         <v>46196</v>
       </c>
@@ -13559,7 +13559,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="105" customHeight="1" s="592">
+    <row r="12" ht="105" customHeight="1" s="582">
       <c r="A12" s="308" t="n">
         <v>46196</v>
       </c>
@@ -13584,7 +13584,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="592">
+    <row r="13" ht="30" customHeight="1" s="582">
       <c r="A13" s="308" t="n">
         <v>46197</v>
       </c>
@@ -13628,11 +13628,11 @@
     <col width="6.5703125" bestFit="1" customWidth="1" style="13" min="3" max="3"/>
     <col width="139.42578125" bestFit="1" customWidth="1" style="104" min="4" max="4"/>
     <col width="8.7109375" customWidth="1" style="14" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" style="13" min="6" max="12"/>
-    <col width="8.7109375" customWidth="1" style="13" min="13" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="6" max="13"/>
+    <col width="8.7109375" customWidth="1" style="13" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.6" customHeight="1" s="592">
+    <row r="1" ht="21.6" customHeight="1" s="582">
       <c r="A1" s="171" t="inlineStr">
         <is>
           <t>DESCRIZIONE</t>
@@ -13659,7 +13659,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="21.6" customHeight="1" s="592">
+    <row r="2" ht="21.6" customHeight="1" s="582">
       <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Root Sharepoint</t>
@@ -13683,7 +13683,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" ht="21.6" customHeight="1" s="592">
+    <row r="3" ht="21.6" customHeight="1" s="582">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Cartella Documenti Ingegneria</t>
@@ -13706,7 +13706,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="21.6" customHeight="1" s="592">
+    <row r="4" ht="21.6" customHeight="1" s="582">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Cartella Archiviazione doc ETR1000</t>
@@ -13729,7 +13729,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="21.6" customHeight="1" s="592">
+    <row r="5" ht="21.6" customHeight="1" s="582">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Documenti di configurazione</t>
@@ -13752,7 +13752,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="21.6" customHeight="1" s="592">
+    <row r="6" ht="21.6" customHeight="1" s="582">
       <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Raccolta documentazione Funzioni</t>
@@ -13775,17 +13775,17 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="21.95" customHeight="1" s="592"/>
-    <row r="8" ht="21.95" customHeight="1" s="592"/>
-    <row r="9" ht="21.95" customHeight="1" s="592"/>
-    <row r="10" ht="21.95" customHeight="1" s="592">
+    <row r="7" ht="21.95" customHeight="1" s="582"/>
+    <row r="8" ht="21.95" customHeight="1" s="582"/>
+    <row r="9" ht="21.95" customHeight="1" s="582"/>
+    <row r="10" ht="21.95" customHeight="1" s="582">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>VINCOLI</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="21.95" customHeight="1" s="592">
+    <row r="11" ht="21.95" customHeight="1" s="582">
       <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Id Flotta</t>
@@ -13797,7 +13797,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="21.95" customHeight="1" s="592">
+    <row r="12" ht="21.95" customHeight="1" s="582">
       <c r="A12" s="13" t="inlineStr">
         <is>
           <t>DOC ID</t>
@@ -13840,10 +13840,10 @@
   <dimension ref="A1:BW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.42578125" bestFit="1" customWidth="1" style="592" min="1" max="1"/>
-    <col width="17.5703125" customWidth="1" style="592" min="2" max="3"/>
-    <col width="15.42578125" customWidth="1" style="592" min="4" max="4"/>
-    <col width="15.140625" customWidth="1" style="592" min="5" max="5"/>
+    <col width="19.42578125" bestFit="1" customWidth="1" style="582" min="1" max="1"/>
+    <col width="17.5703125" customWidth="1" style="582" min="2" max="3"/>
+    <col width="15.42578125" customWidth="1" style="582" min="4" max="4"/>
+    <col width="15.140625" customWidth="1" style="582" min="5" max="5"/>
     <col width="11" customWidth="1" style="12" min="6" max="6"/>
     <col width="3.85546875" bestFit="1" customWidth="1" style="12" min="7" max="52"/>
     <col width="2.85546875" bestFit="1" customWidth="1" style="12" min="53" max="69"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="D9" s="302" t="n"/>
       <c r="E9" s="303" t="n"/>
-      <c r="F9" s="599">
+      <c r="F9" s="579">
         <f>COUNTIF(G9:BW9,"&lt;&gt;")</f>
         <v/>
       </c>
@@ -15053,145 +15053,145 @@
     <col width="6.5703125" customWidth="1" style="15" min="21" max="21"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="15" min="22" max="22"/>
     <col width="6.5703125" customWidth="1" style="15" min="23" max="23"/>
-    <col width="8.7109375" customWidth="1" style="103" min="24" max="30"/>
-    <col width="8.7109375" customWidth="1" style="103" min="31" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="24" max="31"/>
+    <col width="8.7109375" customWidth="1" style="103" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="105">
-      <c r="A1" s="526" t="inlineStr">
+      <c r="A1" s="531" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="534" t="inlineStr">
+      <c r="B1" s="535" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="526" t="inlineStr">
+      <c r="C1" s="531" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="532" t="inlineStr">
+      <c r="D1" s="529" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="530" t="n"/>
-      <c r="F1" s="531" t="n"/>
-      <c r="G1" s="541" t="inlineStr">
+      <c r="E1" s="527" t="n"/>
+      <c r="F1" s="528" t="n"/>
+      <c r="G1" s="530" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="H1" s="530" t="n"/>
-      <c r="I1" s="530" t="n"/>
-      <c r="J1" s="532" t="inlineStr">
+      <c r="H1" s="527" t="n"/>
+      <c r="I1" s="527" t="n"/>
+      <c r="J1" s="529" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="K1" s="530" t="n"/>
-      <c r="L1" s="531" t="n"/>
-      <c r="M1" s="538" t="inlineStr">
+      <c r="K1" s="527" t="n"/>
+      <c r="L1" s="528" t="n"/>
+      <c r="M1" s="539" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="N1" s="539" t="n"/>
-      <c r="O1" s="539" t="n"/>
-      <c r="P1" s="532" t="inlineStr">
+      <c r="N1" s="540" t="n"/>
+      <c r="O1" s="540" t="n"/>
+      <c r="P1" s="529" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="Q1" s="531" t="n"/>
-      <c r="R1" s="532" t="inlineStr">
+      <c r="Q1" s="528" t="n"/>
+      <c r="R1" s="529" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
-      <c r="S1" s="531" t="n"/>
-      <c r="T1" s="532" t="inlineStr">
+      <c r="S1" s="528" t="n"/>
+      <c r="T1" s="529" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="U1" s="531" t="n"/>
-      <c r="V1" s="532" t="inlineStr">
+      <c r="U1" s="528" t="n"/>
+      <c r="V1" s="529" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
         </is>
       </c>
-      <c r="W1" s="531" t="n"/>
+      <c r="W1" s="528" t="n"/>
     </row>
     <row r="2" ht="41.1" customFormat="1" customHeight="1" s="105">
-      <c r="A2" s="527" t="n"/>
-      <c r="B2" s="535" t="n"/>
-      <c r="C2" s="527" t="n"/>
-      <c r="D2" s="529" t="inlineStr">
+      <c r="A2" s="532" t="n"/>
+      <c r="B2" s="536" t="n"/>
+      <c r="C2" s="532" t="n"/>
+      <c r="D2" s="526" t="inlineStr">
         <is>
           <t>Doc BD130033980 - BL 6.0</t>
         </is>
       </c>
-      <c r="E2" s="530" t="n"/>
-      <c r="F2" s="531" t="n"/>
-      <c r="G2" s="533" t="inlineStr">
+      <c r="E2" s="527" t="n"/>
+      <c r="F2" s="528" t="n"/>
+      <c r="G2" s="534" t="inlineStr">
         <is>
           <t>BD140036813 - BL 4.2</t>
         </is>
       </c>
-      <c r="H2" s="530" t="n"/>
-      <c r="I2" s="530" t="n"/>
-      <c r="J2" s="529" t="inlineStr">
+      <c r="H2" s="527" t="n"/>
+      <c r="I2" s="527" t="n"/>
+      <c r="J2" s="526" t="inlineStr">
         <is>
           <t>3ECP414415-0001 - BL 4.0</t>
         </is>
       </c>
-      <c r="K2" s="530" t="n"/>
-      <c r="L2" s="531" t="n"/>
-      <c r="M2" s="540" t="inlineStr">
+      <c r="K2" s="527" t="n"/>
+      <c r="L2" s="528" t="n"/>
+      <c r="M2" s="541" t="inlineStr">
         <is>
           <t>VZ-ES Spagna
 BL 2.4</t>
         </is>
       </c>
-      <c r="N2" s="539" t="n"/>
-      <c r="O2" s="539" t="n"/>
-      <c r="P2" s="529" t="inlineStr">
+      <c r="N2" s="540" t="n"/>
+      <c r="O2" s="540" t="n"/>
+      <c r="P2" s="526" t="inlineStr">
         <is>
           <t>VZI-6_IT [R1]
 BL 4.0</t>
         </is>
       </c>
-      <c r="Q2" s="531" t="n"/>
-      <c r="R2" s="537" t="inlineStr">
+      <c r="Q2" s="528" t="n"/>
+      <c r="R2" s="538" t="inlineStr">
         <is>
           <t>VZI-4_IT [R1]
 BL 1.0</t>
         </is>
       </c>
-      <c r="S2" s="531" t="n"/>
-      <c r="T2" s="529" t="inlineStr">
+      <c r="S2" s="528" t="n"/>
+      <c r="T2" s="526" t="inlineStr">
         <is>
           <t>VZ-DAI
 BL xxx</t>
         </is>
       </c>
-      <c r="U2" s="531" t="n"/>
-      <c r="V2" s="529" t="inlineStr">
+      <c r="U2" s="528" t="n"/>
+      <c r="V2" s="526" t="inlineStr">
         <is>
           <t>VZ_ES Full HRI
 BL xxx</t>
         </is>
       </c>
-      <c r="W2" s="531" t="n"/>
+      <c r="W2" s="528" t="n"/>
     </row>
     <row r="3" ht="30" customFormat="1" customHeight="1" s="105">
-      <c r="A3" s="528" t="n"/>
-      <c r="B3" s="536" t="n"/>
-      <c r="C3" s="528" t="n"/>
+      <c r="A3" s="533" t="n"/>
+      <c r="B3" s="537" t="n"/>
+      <c r="C3" s="533" t="n"/>
       <c r="D3" s="152" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -15237,7 +15237,7 @@
           <t>Codice Config</t>
         </is>
       </c>
-      <c r="M3" s="533" t="inlineStr">
+      <c r="M3" s="534" t="inlineStr">
         <is>
           <t>File/Codice</t>
         </is>
@@ -15322,7 +15322,7 @@
       <c r="V4" s="443" t="n"/>
       <c r="W4" s="444" t="n"/>
     </row>
-    <row r="5" outlineLevel="1" s="592">
+    <row r="5" outlineLevel="1" s="582">
       <c r="A5" s="114" t="inlineStr">
         <is>
           <t>SW Config. Matrix</t>
@@ -15436,7 +15436,7 @@
       <c r="V6" s="446" t="n"/>
       <c r="W6" s="118" t="n"/>
     </row>
-    <row r="7" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="7" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Drive Control</t>
@@ -15519,7 +15519,7 @@
       <c r="U7" s="110" t="n"/>
       <c r="W7" s="110" t="n"/>
     </row>
-    <row r="8" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="8" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A8" s="114" t="inlineStr">
         <is>
           <t>Conventional Train Control</t>
@@ -15602,7 +15602,7 @@
       <c r="U8" s="110" t="n"/>
       <c r="W8" s="110" t="n"/>
     </row>
-    <row r="9" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="9" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A9" s="114" t="inlineStr">
         <is>
           <t>Train Protection - ATP</t>
@@ -15685,7 +15685,7 @@
       <c r="U9" s="110" t="n"/>
       <c r="W9" s="110" t="n"/>
     </row>
-    <row r="10" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="10" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A10" s="114" t="inlineStr">
         <is>
           <t>TCMS Architecture</t>
@@ -15768,7 +15768,7 @@
       <c r="U10" s="110" t="n"/>
       <c r="W10" s="110" t="n"/>
     </row>
-    <row r="11" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="11" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A11" s="114" t="inlineStr">
         <is>
           <t>Propulsion and Auxiliary</t>
@@ -15842,7 +15842,7 @@
       <c r="U11" s="110" t="n"/>
       <c r="W11" s="110" t="n"/>
     </row>
-    <row r="12" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="12" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A12" s="114" t="inlineStr">
         <is>
           <t>Line Voltage</t>
@@ -15925,7 +15925,7 @@
       <c r="U12" s="110" t="n"/>
       <c r="W12" s="110" t="n"/>
     </row>
-    <row r="13" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="13" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A13" s="114" t="inlineStr">
         <is>
           <t>Auxiliary Electrical Supply</t>
@@ -16008,7 +16008,7 @@
       <c r="U13" s="110" t="n"/>
       <c r="W13" s="110" t="n"/>
     </row>
-    <row r="14" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="14" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A14" s="114" t="inlineStr">
         <is>
           <t>Battery</t>
@@ -16091,7 +16091,7 @@
       <c r="U14" s="110" t="n"/>
       <c r="W14" s="110" t="n"/>
     </row>
-    <row r="15" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="15" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A15" s="114" t="inlineStr">
         <is>
           <t>Air Supply</t>
@@ -16174,7 +16174,7 @@
       <c r="U15" s="110" t="n"/>
       <c r="W15" s="110" t="n"/>
     </row>
-    <row r="16" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="16" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A16" s="114" t="inlineStr">
         <is>
           <t>Brake Control</t>
@@ -16257,7 +16257,7 @@
       <c r="U16" s="110" t="n"/>
       <c r="W16" s="110" t="n"/>
     </row>
-    <row r="17" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="17" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A17" s="114" t="inlineStr">
         <is>
           <t>Bogie</t>
@@ -16340,7 +16340,7 @@
       <c r="U17" s="110" t="n"/>
       <c r="W17" s="110" t="n"/>
     </row>
-    <row r="18" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="18" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A18" s="114" t="inlineStr">
         <is>
           <t>Wash Wiper</t>
@@ -16423,7 +16423,7 @@
       <c r="U18" s="110" t="n"/>
       <c r="W18" s="110" t="n"/>
     </row>
-    <row r="19" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="19" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A19" s="114" t="inlineStr">
         <is>
           <t>Windscreen heater</t>
@@ -16506,7 +16506,7 @@
       <c r="U19" s="110" t="n"/>
       <c r="W19" s="110" t="n"/>
     </row>
-    <row r="20" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="20" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A20" s="114" t="inlineStr">
         <is>
           <t>Automatic Coupler</t>
@@ -16589,7 +16589,7 @@
       <c r="U20" s="110" t="n"/>
       <c r="W20" s="110" t="n"/>
     </row>
-    <row r="21" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="21" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A21" s="114" t="inlineStr">
         <is>
           <t>Horn</t>
@@ -16672,7 +16672,7 @@
       <c r="U21" s="110" t="n"/>
       <c r="W21" s="110" t="n"/>
     </row>
-    <row r="22" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="22" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A22" s="114" t="inlineStr">
         <is>
           <t>Exterior and Interior Doors</t>
@@ -16755,7 +16755,7 @@
       <c r="U22" s="110" t="n"/>
       <c r="W22" s="110" t="n"/>
     </row>
-    <row r="23" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="23" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A23" s="114" t="inlineStr">
         <is>
           <t>Cab HVAC</t>
@@ -16838,7 +16838,7 @@
       <c r="U23" s="110" t="n"/>
       <c r="W23" s="110" t="n"/>
     </row>
-    <row r="24" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="24" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A24" s="114" t="inlineStr">
         <is>
           <t>Saloon HVAC</t>
@@ -16921,7 +16921,7 @@
       <c r="U24" s="110" t="n"/>
       <c r="W24" s="110" t="n"/>
     </row>
-    <row r="25" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="25" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A25" s="114" t="inlineStr">
         <is>
           <t>Fire Protection and Extinguishing</t>
@@ -17004,7 +17004,7 @@
       <c r="U25" s="110" t="n"/>
       <c r="W25" s="110" t="n"/>
     </row>
-    <row r="26" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="26" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A26" s="114" t="inlineStr">
         <is>
           <t>Toilet</t>
@@ -17087,7 +17087,7 @@
       <c r="U26" s="110" t="n"/>
       <c r="W26" s="110" t="n"/>
     </row>
-    <row r="27" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="27" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A27" s="114" t="inlineStr">
         <is>
           <t>Catering</t>
@@ -17170,7 +17170,7 @@
       <c r="U27" s="110" t="n"/>
       <c r="W27" s="110" t="n"/>
     </row>
-    <row r="28" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="28" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A28" s="114" t="inlineStr">
         <is>
           <t>PIS CCTV</t>
@@ -17253,7 +17253,7 @@
       <c r="U28" s="110" t="n"/>
       <c r="W28" s="110" t="n"/>
     </row>
-    <row r="29" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="29" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A29" s="114" t="inlineStr">
         <is>
           <t>Exterior Lighting</t>
@@ -17336,7 +17336,7 @@
       <c r="U29" s="110" t="n"/>
       <c r="W29" s="110" t="n"/>
     </row>
-    <row r="30" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="30" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A30" s="114" t="inlineStr">
         <is>
           <t>Interior Lighting</t>
@@ -17419,7 +17419,7 @@
       <c r="U30" s="110" t="n"/>
       <c r="W30" s="110" t="n"/>
     </row>
-    <row r="31" outlineLevel="1" s="592">
+    <row r="31" outlineLevel="1" s="582">
       <c r="A31" s="114" t="inlineStr">
         <is>
           <t>Train Control Design System</t>
@@ -17473,7 +17473,7 @@
       <c r="U31" s="110" t="n"/>
       <c r="W31" s="110" t="n"/>
     </row>
-    <row r="32" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="32" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A32" s="114" t="inlineStr">
         <is>
           <t>Schematic diagram for French ATP MU</t>
@@ -17518,7 +17518,7 @@
       <c r="U32" s="110" t="n"/>
       <c r="W32" s="110" t="n"/>
     </row>
-    <row r="33" outlineLevel="1" s="592">
+    <row r="33" outlineLevel="1" s="582">
       <c r="A33" s="438" t="inlineStr">
         <is>
           <t>Energy Meter System</t>
@@ -17559,7 +17559,7 @@
       <c r="U33" s="110" t="n"/>
       <c r="W33" s="110" t="n"/>
     </row>
-    <row r="34" ht="30" customHeight="1" s="592">
+    <row r="34" ht="30" customHeight="1" s="582">
       <c r="A34" s="445" t="inlineStr">
         <is>
           <t>Functional Requirement Specification (FRS)</t>
@@ -17588,7 +17588,7 @@
       <c r="V34" s="446" t="n"/>
       <c r="W34" s="118" t="n"/>
     </row>
-    <row r="35" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="35" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A35" s="114" t="inlineStr">
         <is>
           <t>Functional Vehicle Requirement Specification</t>
@@ -17657,7 +17657,7 @@
       <c r="U35" s="110" t="n"/>
       <c r="W35" s="110" t="n"/>
     </row>
-    <row r="36" outlineLevel="1" ht="60" customHeight="1" s="592">
+    <row r="36" outlineLevel="1" ht="60" customHeight="1" s="582">
       <c r="A36" s="114" t="inlineStr">
         <is>
           <t>Drive Control</t>
@@ -17750,7 +17750,7 @@
       <c r="U36" s="110" t="n"/>
       <c r="W36" s="110" t="n"/>
     </row>
-    <row r="37" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="37" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A37" s="114" t="inlineStr">
         <is>
           <t>Conventional Train Control</t>
@@ -17849,7 +17849,7 @@
       <c r="U37" s="110" t="n"/>
       <c r="W37" s="110" t="n"/>
     </row>
-    <row r="38" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="38" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A38" s="114" t="inlineStr">
         <is>
           <t>Train Protection - ATP</t>
@@ -17950,7 +17950,7 @@
       <c r="U38" s="110" t="n"/>
       <c r="W38" s="110" t="n"/>
     </row>
-    <row r="39" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="39" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A39" s="114" t="inlineStr">
         <is>
           <t>Diagnostics</t>
@@ -18049,7 +18049,7 @@
       <c r="U39" s="110" t="n"/>
       <c r="W39" s="110" t="n"/>
     </row>
-    <row r="40" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="40" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A40" s="114" t="inlineStr">
         <is>
           <t>Visualisation - MMI</t>
@@ -18148,7 +18148,7 @@
       <c r="U40" s="110" t="n"/>
       <c r="W40" s="110" t="n"/>
     </row>
-    <row r="41" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="41" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A41" s="114" t="inlineStr">
         <is>
           <t>TCMS - Operational</t>
@@ -18247,7 +18247,7 @@
       <c r="U41" s="110" t="n"/>
       <c r="W41" s="110" t="n"/>
     </row>
-    <row r="42" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="42" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A42" s="114" t="inlineStr">
         <is>
           <t>Train to Wayside Communication (Teledia)</t>
@@ -18346,7 +18346,7 @@
       <c r="U42" s="110" t="n"/>
       <c r="W42" s="110" t="n"/>
     </row>
-    <row r="43" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="43" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A43" s="114" t="inlineStr">
         <is>
           <t>Line Voltage</t>
@@ -18441,7 +18441,7 @@
       <c r="U43" s="110" t="n"/>
       <c r="W43" s="110" t="n"/>
     </row>
-    <row r="44" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="44" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A44" s="114" t="inlineStr">
         <is>
           <t>Aux Electrical Supply</t>
@@ -18536,7 +18536,7 @@
       <c r="U44" s="110" t="n"/>
       <c r="W44" s="110" t="n"/>
     </row>
-    <row r="45" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="45" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A45" s="114" t="inlineStr">
         <is>
           <t>Battery</t>
@@ -18635,7 +18635,7 @@
       <c r="U45" s="110" t="n"/>
       <c r="W45" s="110" t="n"/>
     </row>
-    <row r="46" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="46" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A46" s="114" t="inlineStr">
         <is>
           <t>Air Supply</t>
@@ -18734,7 +18734,7 @@
       <c r="U46" s="110" t="n"/>
       <c r="W46" s="110" t="n"/>
     </row>
-    <row r="47" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="47" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A47" s="114" t="inlineStr">
         <is>
           <t>Brake Control</t>
@@ -18829,7 +18829,7 @@
       <c r="U47" s="110" t="n"/>
       <c r="W47" s="110" t="n"/>
     </row>
-    <row r="48" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="48" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A48" s="114" t="inlineStr">
         <is>
           <t>Bogies</t>
@@ -18928,7 +18928,7 @@
       <c r="U48" s="110" t="n"/>
       <c r="W48" s="110" t="n"/>
     </row>
-    <row r="49" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="49" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A49" s="114" t="inlineStr">
         <is>
           <t>Wash Wiper</t>
@@ -19027,7 +19027,7 @@
       <c r="U49" s="110" t="n"/>
       <c r="W49" s="110" t="n"/>
     </row>
-    <row r="50" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="50" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A50" s="114" t="inlineStr">
         <is>
           <t>Windscreen</t>
@@ -19126,7 +19126,7 @@
       <c r="U50" s="110" t="n"/>
       <c r="W50" s="110" t="n"/>
     </row>
-    <row r="51" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="51" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A51" s="114" t="inlineStr">
         <is>
           <t>Coupler</t>
@@ -19225,7 +19225,7 @@
       <c r="U51" s="110" t="n"/>
       <c r="W51" s="110" t="n"/>
     </row>
-    <row r="52" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="52" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A52" s="114" t="inlineStr">
         <is>
           <t>Horn</t>
@@ -19324,7 +19324,7 @@
       <c r="U52" s="110" t="n"/>
       <c r="W52" s="110" t="n"/>
     </row>
-    <row r="53" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="53" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A53" s="114" t="inlineStr">
         <is>
           <t>Wheelchair Lifts</t>
@@ -19423,7 +19423,7 @@
       <c r="U53" s="110" t="n"/>
       <c r="W53" s="110" t="n"/>
     </row>
-    <row r="54" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="54" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A54" s="114" t="inlineStr">
         <is>
           <t>Exterior Door and Step Systems</t>
@@ -19522,7 +19522,7 @@
       <c r="U54" s="110" t="n"/>
       <c r="W54" s="110" t="n"/>
     </row>
-    <row r="55" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="55" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A55" s="114" t="inlineStr">
         <is>
           <t>Interior Doors</t>
@@ -19621,7 +19621,7 @@
       <c r="U55" s="110" t="n"/>
       <c r="W55" s="110" t="n"/>
     </row>
-    <row r="56" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="56" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A56" s="114" t="inlineStr">
         <is>
           <t>Cab HVAC</t>
@@ -19720,7 +19720,7 @@
       <c r="U56" s="110" t="n"/>
       <c r="W56" s="110" t="n"/>
     </row>
-    <row r="57" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="57" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A57" s="114" t="inlineStr">
         <is>
           <t>Saloon HVAC</t>
@@ -19819,7 +19819,7 @@
       <c r="U57" s="110" t="n"/>
       <c r="W57" s="110" t="n"/>
     </row>
-    <row r="58" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="58" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A58" s="114" t="inlineStr">
         <is>
           <t>Fire Protection and Extinction</t>
@@ -19918,7 +19918,7 @@
       <c r="U58" s="110" t="n"/>
       <c r="W58" s="110" t="n"/>
     </row>
-    <row r="59" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="59" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A59" s="114" t="inlineStr">
         <is>
           <t>Toilet</t>
@@ -20017,7 +20017,7 @@
       <c r="U59" s="110" t="n"/>
       <c r="W59" s="110" t="n"/>
     </row>
-    <row r="60" outlineLevel="1" s="592">
+    <row r="60" outlineLevel="1" s="582">
       <c r="A60" s="114" t="inlineStr">
         <is>
           <t>Catering - Bistrot</t>
@@ -20116,7 +20116,7 @@
       <c r="U60" s="110" t="n"/>
       <c r="W60" s="110" t="n"/>
     </row>
-    <row r="61" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="61" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A61" s="114" t="inlineStr">
         <is>
           <t>PIES</t>
@@ -20215,7 +20215,7 @@
       <c r="U61" s="110" t="n"/>
       <c r="W61" s="110" t="n"/>
     </row>
-    <row r="62" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="62" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A62" s="114" t="inlineStr">
         <is>
           <t>PIS 2.0</t>
@@ -20301,7 +20301,7 @@
       <c r="U62" s="110" t="n"/>
       <c r="W62" s="110" t="n"/>
     </row>
-    <row r="63" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="63" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A63" s="114" t="inlineStr">
         <is>
           <t>CCTV</t>
@@ -20396,7 +20396,7 @@
       <c r="U63" s="110" t="n"/>
       <c r="W63" s="110" t="n"/>
     </row>
-    <row r="64" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="64" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A64" s="114" t="inlineStr">
         <is>
           <t>Exterior Lighting</t>
@@ -20491,7 +20491,7 @@
       <c r="U64" s="110" t="n"/>
       <c r="W64" s="110" t="n"/>
     </row>
-    <row r="65" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="65" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A65" s="114" t="inlineStr">
         <is>
           <t>Interior Lighting</t>
@@ -20586,7 +20586,7 @@
       <c r="U65" s="110" t="n"/>
       <c r="W65" s="110" t="n"/>
     </row>
-    <row r="66" outlineLevel="1" s="592">
+    <row r="66" outlineLevel="1" s="582">
       <c r="A66" s="114" t="inlineStr">
         <is>
           <t>Train Protection - ATP (France)</t>
@@ -20627,7 +20627,7 @@
       <c r="U66" s="110" t="n"/>
       <c r="W66" s="110" t="n"/>
     </row>
-    <row r="67" outlineLevel="1" s="592">
+    <row r="67" outlineLevel="1" s="582">
       <c r="A67" s="438" t="inlineStr">
         <is>
           <t>Energy Meter System</t>
@@ -20710,7 +20710,7 @@
       <c r="V68" s="446" t="n"/>
       <c r="W68" s="118" t="n"/>
     </row>
-    <row r="69" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="69" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A69" s="114" t="inlineStr">
         <is>
           <t>Functional schematics DM1</t>
@@ -20793,7 +20793,7 @@
       <c r="U69" s="110" t="n"/>
       <c r="W69" s="110" t="n"/>
     </row>
-    <row r="70" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="70" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A70" s="114" t="inlineStr">
         <is>
           <t>Functional schematics TT2</t>
@@ -20876,7 +20876,7 @@
       <c r="U70" s="110" t="n"/>
       <c r="W70" s="110" t="n"/>
     </row>
-    <row r="71" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="71" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A71" s="114" t="inlineStr">
         <is>
           <t>Functional schematics M3</t>
@@ -20959,7 +20959,7 @@
       <c r="U71" s="110" t="n"/>
       <c r="W71" s="110" t="n"/>
     </row>
-    <row r="72" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="72" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A72" s="114" t="inlineStr">
         <is>
           <t>Functional schematics T4</t>
@@ -21042,7 +21042,7 @@
       <c r="U72" s="110" t="n"/>
       <c r="W72" s="110" t="n"/>
     </row>
-    <row r="73" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="73" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A73" s="114" t="inlineStr">
         <is>
           <t>Functional schematics T5</t>
@@ -21125,7 +21125,7 @@
       <c r="U73" s="110" t="n"/>
       <c r="W73" s="110" t="n"/>
     </row>
-    <row r="74" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="74" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A74" s="114" t="inlineStr">
         <is>
           <t>Functional schematics M6</t>
@@ -21208,7 +21208,7 @@
       <c r="U74" s="110" t="n"/>
       <c r="W74" s="110" t="n"/>
     </row>
-    <row r="75" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="75" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A75" s="114" t="inlineStr">
         <is>
           <t>Functional schematics TT7</t>
@@ -21291,7 +21291,7 @@
       <c r="U75" s="110" t="n"/>
       <c r="W75" s="110" t="n"/>
     </row>
-    <row r="76" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="76" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A76" s="114" t="inlineStr">
         <is>
           <t>Functional schematics DM8</t>
@@ -21374,7 +21374,7 @@
       <c r="U76" s="110" t="n"/>
       <c r="W76" s="110" t="n"/>
     </row>
-    <row r="77" ht="30" customHeight="1" s="592">
+    <row r="77" ht="30" customHeight="1" s="582">
       <c r="A77" s="445" t="inlineStr">
         <is>
           <t>Wiring table</t>
@@ -21419,7 +21419,7 @@
       <c r="V77" s="446" t="n"/>
       <c r="W77" s="118" t="n"/>
     </row>
-    <row r="78" outlineLevel="1" s="592">
+    <row r="78" outlineLevel="1" s="582">
       <c r="A78" s="114" t="inlineStr">
         <is>
           <t>Wiring table DM1</t>
@@ -21484,7 +21484,7 @@
       <c r="U78" s="110" t="n"/>
       <c r="W78" s="110" t="n"/>
     </row>
-    <row r="79" outlineLevel="1" s="592">
+    <row r="79" outlineLevel="1" s="582">
       <c r="A79" s="114" t="inlineStr">
         <is>
           <t>Wiring table TT2</t>
@@ -21549,7 +21549,7 @@
       <c r="U79" s="110" t="n"/>
       <c r="W79" s="110" t="n"/>
     </row>
-    <row r="80" outlineLevel="1" s="592">
+    <row r="80" outlineLevel="1" s="582">
       <c r="A80" s="114" t="inlineStr">
         <is>
           <t>Wiring table M3</t>
@@ -21614,7 +21614,7 @@
       <c r="U80" s="110" t="n"/>
       <c r="W80" s="110" t="n"/>
     </row>
-    <row r="81" outlineLevel="1" s="592">
+    <row r="81" outlineLevel="1" s="582">
       <c r="A81" s="114" t="inlineStr">
         <is>
           <t>Wiring table T4</t>
@@ -21679,7 +21679,7 @@
       <c r="U81" s="110" t="n"/>
       <c r="W81" s="110" t="n"/>
     </row>
-    <row r="82" outlineLevel="1" s="592">
+    <row r="82" outlineLevel="1" s="582">
       <c r="A82" s="114" t="inlineStr">
         <is>
           <t>Wiring table T5</t>
@@ -21744,7 +21744,7 @@
       <c r="U82" s="110" t="n"/>
       <c r="W82" s="110" t="n"/>
     </row>
-    <row r="83" outlineLevel="1" s="592">
+    <row r="83" outlineLevel="1" s="582">
       <c r="A83" s="114" t="inlineStr">
         <is>
           <t>Wiring table M6</t>
@@ -21809,7 +21809,7 @@
       <c r="U83" s="110" t="n"/>
       <c r="W83" s="110" t="n"/>
     </row>
-    <row r="84" outlineLevel="1" s="592">
+    <row r="84" outlineLevel="1" s="582">
       <c r="A84" s="114" t="inlineStr">
         <is>
           <t>Wiring table TT7</t>
@@ -21874,7 +21874,7 @@
       <c r="U84" s="110" t="n"/>
       <c r="W84" s="110" t="n"/>
     </row>
-    <row r="85" outlineLevel="1" s="592">
+    <row r="85" outlineLevel="1" s="582">
       <c r="A85" s="114" t="inlineStr">
         <is>
           <t>Wiring table DM8</t>
@@ -21968,7 +21968,7 @@
       <c r="V86" s="446" t="n"/>
       <c r="W86" s="118" t="n"/>
     </row>
-    <row r="87" outlineLevel="1" s="592">
+    <row r="87" outlineLevel="1" s="582">
       <c r="A87" s="114" t="inlineStr">
         <is>
           <t>Electric Part List DM1</t>
@@ -22033,7 +22033,7 @@
       <c r="U87" s="110" t="n"/>
       <c r="W87" s="110" t="n"/>
     </row>
-    <row r="88" outlineLevel="1" s="592">
+    <row r="88" outlineLevel="1" s="582">
       <c r="A88" s="114" t="inlineStr">
         <is>
           <t>Electric Part List TT2</t>
@@ -22098,7 +22098,7 @@
       <c r="U88" s="110" t="n"/>
       <c r="W88" s="110" t="n"/>
     </row>
-    <row r="89" outlineLevel="1" s="592">
+    <row r="89" outlineLevel="1" s="582">
       <c r="A89" s="114" t="inlineStr">
         <is>
           <t>Electric Part List M3</t>
@@ -22163,7 +22163,7 @@
       <c r="U89" s="110" t="n"/>
       <c r="W89" s="110" t="n"/>
     </row>
-    <row r="90" outlineLevel="1" s="592">
+    <row r="90" outlineLevel="1" s="582">
       <c r="A90" s="114" t="inlineStr">
         <is>
           <t>Electric Part List T4</t>
@@ -22228,7 +22228,7 @@
       <c r="U90" s="110" t="n"/>
       <c r="W90" s="110" t="n"/>
     </row>
-    <row r="91" outlineLevel="1" s="592">
+    <row r="91" outlineLevel="1" s="582">
       <c r="A91" s="114" t="inlineStr">
         <is>
           <t>Electric Part List T5</t>
@@ -22293,7 +22293,7 @@
       <c r="U91" s="110" t="n"/>
       <c r="W91" s="110" t="n"/>
     </row>
-    <row r="92" outlineLevel="1" s="592">
+    <row r="92" outlineLevel="1" s="582">
       <c r="A92" s="114" t="inlineStr">
         <is>
           <t>Electric Part List M6</t>
@@ -22358,7 +22358,7 @@
       <c r="U92" s="110" t="n"/>
       <c r="W92" s="110" t="n"/>
     </row>
-    <row r="93" outlineLevel="1" s="592">
+    <row r="93" outlineLevel="1" s="582">
       <c r="A93" s="114" t="inlineStr">
         <is>
           <t>Electric Part List TT7</t>
@@ -22423,7 +22423,7 @@
       <c r="U93" s="110" t="n"/>
       <c r="W93" s="110" t="n"/>
     </row>
-    <row r="94" outlineLevel="1" s="592">
+    <row r="94" outlineLevel="1" s="582">
       <c r="A94" s="114" t="inlineStr">
         <is>
           <t>Electric Part List DM8</t>
@@ -22521,7 +22521,7 @@
       <c r="V95" s="446" t="n"/>
       <c r="W95" s="118" t="n"/>
     </row>
-    <row r="96" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="96" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A96" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema TCMS</t>
@@ -22581,7 +22581,7 @@
       <c r="U96" s="110" t="n"/>
       <c r="W96" s="110" t="n"/>
     </row>
-    <row r="97" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="97" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A97" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema TCMS - Annex</t>
@@ -22632,7 +22632,7 @@
       <c r="U97" s="110" t="n"/>
       <c r="W97" s="110" t="n"/>
     </row>
-    <row r="98" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="98" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A98" s="114" t="inlineStr">
         <is>
           <t>ICD GTW IPTCOM-TRDP</t>
@@ -22687,7 +22687,7 @@
       <c r="U98" s="110" t="n"/>
       <c r="W98" s="110" t="n"/>
     </row>
-    <row r="99" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="99" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A99" s="114" t="inlineStr">
         <is>
           <t>ICD GTW IPTCOM-TRDP - Annex</t>
@@ -22738,7 +22738,7 @@
       <c r="U99" s="110" t="n"/>
       <c r="W99" s="110" t="n"/>
     </row>
-    <row r="100" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="100" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A100" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Propulsion TCU</t>
@@ -22798,7 +22798,7 @@
       <c r="U100" s="110" t="n"/>
       <c r="W100" s="110" t="n"/>
     </row>
-    <row r="101" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="101" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A101" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Propulsion TCU - Annex</t>
@@ -22849,7 +22849,7 @@
       <c r="U101" s="110" t="n"/>
       <c r="W101" s="110" t="n"/>
     </row>
-    <row r="102" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="102" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A102" s="114" t="inlineStr">
         <is>
           <t>ICD Pantografo</t>
@@ -22909,7 +22909,7 @@
       <c r="U102" s="110" t="n"/>
       <c r="W102" s="110" t="n"/>
     </row>
-    <row r="103" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="103" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A103" s="114" t="inlineStr">
         <is>
           <t>ICD Pantografo - Annex</t>
@@ -22960,7 +22960,7 @@
       <c r="U103" s="110" t="n"/>
       <c r="W103" s="110" t="n"/>
     </row>
-    <row r="104" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="104" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A104" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema BCU</t>
@@ -23020,7 +23020,7 @@
       <c r="U104" s="110" t="n"/>
       <c r="W104" s="110" t="n"/>
     </row>
-    <row r="105" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="105" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A105" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema BCU - Annex</t>
@@ -23075,7 +23075,7 @@
       <c r="U105" s="110" t="n"/>
       <c r="W105" s="110" t="n"/>
     </row>
-    <row r="106" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="106" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A106" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Segnalamento</t>
@@ -23130,7 +23130,7 @@
       <c r="U106" s="110" t="n"/>
       <c r="W106" s="110" t="n"/>
     </row>
-    <row r="107" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="107" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A107" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Segnalamento - Annex</t>
@@ -23181,7 +23181,7 @@
       <c r="U107" s="110" t="n"/>
       <c r="W107" s="110" t="n"/>
     </row>
-    <row r="108" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="108" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A108" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema PIS</t>
@@ -23241,7 +23241,7 @@
       <c r="U108" s="110" t="n"/>
       <c r="W108" s="110" t="n"/>
     </row>
-    <row r="109" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="109" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A109" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema PIS - Annex</t>
@@ -23292,7 +23292,7 @@
       <c r="U109" s="110" t="n"/>
       <c r="W109" s="110" t="n"/>
     </row>
-    <row r="110" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="110" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A110" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Toilette</t>
@@ -23352,7 +23352,7 @@
       <c r="U110" s="110" t="n"/>
       <c r="W110" s="110" t="n"/>
     </row>
-    <row r="111" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="111" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A111" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Toilette - Annex</t>
@@ -23403,7 +23403,7 @@
       <c r="U111" s="110" t="n"/>
       <c r="W111" s="110" t="n"/>
     </row>
-    <row r="112" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="112" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A112" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Anticendio</t>
@@ -23463,7 +23463,7 @@
       <c r="U112" s="110" t="n"/>
       <c r="W112" s="110" t="n"/>
     </row>
-    <row r="113" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="113" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A113" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Anticendio - Annex</t>
@@ -23514,7 +23514,7 @@
       <c r="U113" s="110" t="n"/>
       <c r="W113" s="110" t="n"/>
     </row>
-    <row r="114" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="114" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A114" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Porte</t>
@@ -23574,7 +23574,7 @@
       <c r="U114" s="110" t="n"/>
       <c r="W114" s="110" t="n"/>
     </row>
-    <row r="115" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="115" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A115" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Porte - Annex</t>
@@ -23625,7 +23625,7 @@
       <c r="U115" s="110" t="n"/>
       <c r="W115" s="110" t="n"/>
     </row>
-    <row r="116" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="116" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A116" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema HVSP</t>
@@ -23680,7 +23680,7 @@
       <c r="U116" s="110" t="n"/>
       <c r="W116" s="110" t="n"/>
     </row>
-    <row r="117" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="117" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A117" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema HVSP  - Annex</t>
@@ -23731,7 +23731,7 @@
       <c r="U117" s="110" t="n"/>
       <c r="W117" s="110" t="n"/>
     </row>
-    <row r="118" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="118" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A118" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Carica Batterie</t>
@@ -23791,7 +23791,7 @@
       <c r="U118" s="110" t="n"/>
       <c r="W118" s="110" t="n"/>
     </row>
-    <row r="119" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="119" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A119" s="114" t="inlineStr">
         <is>
           <t>ICD Sistema Carica Batterie - Annex</t>
@@ -23842,7 +23842,7 @@
       <c r="U119" s="110" t="n"/>
       <c r="W119" s="110" t="n"/>
     </row>
-    <row r="120" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="120" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A120" s="114" t="inlineStr">
         <is>
           <t>ICD HVAC</t>
@@ -23902,7 +23902,7 @@
       <c r="U120" s="110" t="n"/>
       <c r="W120" s="110" t="n"/>
     </row>
-    <row r="121" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="121" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A121" s="114" t="inlineStr">
         <is>
           <t>ICD HVAC - Annex</t>
@@ -23953,7 +23953,7 @@
       <c r="U121" s="110" t="n"/>
       <c r="W121" s="110" t="n"/>
     </row>
-    <row r="122" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="122" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A122" s="114" t="inlineStr">
         <is>
           <t>ICD Energy Measurement System</t>
@@ -24008,7 +24008,7 @@
       <c r="U122" s="110" t="n"/>
       <c r="W122" s="110" t="n"/>
     </row>
-    <row r="123" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="123" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A123" s="114" t="inlineStr">
         <is>
           <t>ICD Energy Measurement System - Annex</t>
@@ -24088,7 +24088,7 @@
       <c r="V124" s="446" t="n"/>
       <c r="W124" s="118" t="n"/>
     </row>
-    <row r="125" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="125" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A125" s="114" t="inlineStr">
         <is>
           <t>Train Performances</t>
@@ -24134,7 +24134,7 @@
       <c r="U125" s="110" t="n"/>
       <c r="W125" s="110" t="n"/>
     </row>
-    <row r="126" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="126" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A126" s="114" t="inlineStr">
         <is>
           <t>Train System Architecture</t>
@@ -24180,7 +24180,7 @@
       <c r="U126" s="110" t="n"/>
       <c r="W126" s="110" t="n"/>
     </row>
-    <row r="127" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="127" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A127" s="114" t="inlineStr">
         <is>
           <t>Train Running Simulations</t>
@@ -24226,7 +24226,7 @@
       <c r="U127" s="110" t="n"/>
       <c r="W127" s="110" t="n"/>
     </row>
-    <row r="128" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="128" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A128" s="114" t="inlineStr">
         <is>
           <t>SyFD Propulsion System</t>
@@ -24272,7 +24272,7 @@
       <c r="U128" s="110" t="n"/>
       <c r="W128" s="110" t="n"/>
     </row>
-    <row r="129" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="129" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A129" s="114" t="inlineStr">
         <is>
           <t>SyFD Train Control and Management System</t>
@@ -24318,7 +24318,7 @@
       <c r="U129" s="110" t="n"/>
       <c r="W129" s="110" t="n"/>
     </row>
-    <row r="130" outlineLevel="1" ht="30" customHeight="1" s="592">
+    <row r="130" outlineLevel="1" ht="30" customHeight="1" s="582">
       <c r="A130" s="115" t="inlineStr">
         <is>
           <t>SyFD Ethernet Train Communication Network</t>
@@ -24427,68 +24427,68 @@
     <col width="6.5703125" customWidth="1" style="15" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="15" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="15" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="103" min="20" max="26"/>
-    <col width="8.7109375" customWidth="1" style="103" min="27" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="20" max="27"/>
+    <col width="8.7109375" customWidth="1" style="103" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.45" customFormat="1" customHeight="1" s="105">
-      <c r="A1" s="526" t="inlineStr">
+      <c r="A1" s="531" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="542" t="inlineStr">
+      <c r="B1" s="546" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="534" t="inlineStr">
+      <c r="C1" s="535" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="546" t="inlineStr">
+      <c r="D1" s="542" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="547" t="n"/>
+      <c r="E1" s="543" t="n"/>
       <c r="F1" s="544" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
       <c r="G1" s="545" t="n"/>
-      <c r="H1" s="546" t="inlineStr">
+      <c r="H1" s="542" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="547" t="n"/>
+      <c r="I1" s="543" t="n"/>
       <c r="J1" s="544" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
       <c r="K1" s="545" t="n"/>
-      <c r="L1" s="546" t="inlineStr">
+      <c r="L1" s="542" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="M1" s="547" t="n"/>
+      <c r="M1" s="543" t="n"/>
       <c r="N1" s="544" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
       <c r="O1" s="545" t="n"/>
-      <c r="P1" s="546" t="inlineStr">
+      <c r="P1" s="542" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="Q1" s="547" t="n"/>
+      <c r="Q1" s="543" t="n"/>
       <c r="R1" s="544" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
@@ -24497,9 +24497,9 @@
       <c r="S1" s="545" t="n"/>
     </row>
     <row r="2" ht="26.45" customFormat="1" customHeight="1" s="105">
-      <c r="A2" s="528" t="n"/>
-      <c r="B2" s="543" t="n"/>
-      <c r="C2" s="536" t="n"/>
+      <c r="A2" s="533" t="n"/>
+      <c r="B2" s="547" t="n"/>
+      <c r="C2" s="537" t="n"/>
       <c r="D2" s="395" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -24540,12 +24540,12 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="L2" s="540" t="inlineStr">
+      <c r="L2" s="541" t="inlineStr">
         <is>
           <t>Codice</t>
         </is>
       </c>
-      <c r="M2" s="540" t="inlineStr">
+      <c r="M2" s="541" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
@@ -24606,7 +24606,7 @@
       <c r="R3" s="399" t="n"/>
       <c r="S3" s="400" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="592">
+    <row r="4" ht="30" customHeight="1" s="582">
       <c r="A4" s="106" t="inlineStr">
         <is>
           <t>Architettura di Controllo Treno ed Interfacce di Comando</t>
@@ -25080,7 +25080,7 @@
       <c r="R17" s="109" t="n"/>
       <c r="S17" s="110" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1" s="592">
+    <row r="18" ht="30" customHeight="1" s="582">
       <c r="A18" s="106" t="inlineStr">
         <is>
           <t>Auxiliary converter module, CM-C S 15/10 WA V02</t>
@@ -25115,7 +25115,7 @@
       <c r="R18" s="109" t="n"/>
       <c r="S18" s="110" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1" s="592">
+    <row r="19" ht="30" customHeight="1" s="582">
       <c r="A19" s="106" t="inlineStr">
         <is>
           <t>Chopper converter module, CM-C L 30/07 WC V01</t>
@@ -25150,7 +25150,7 @@
       <c r="R19" s="109" t="n"/>
       <c r="S19" s="110" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1" s="592">
+    <row r="20" ht="30" customHeight="1" s="582">
       <c r="A20" s="106" t="inlineStr">
         <is>
           <t>Line converter module, CM-C M 15/15 WL V06</t>
@@ -25185,7 +25185,7 @@
       <c r="R20" s="109" t="n"/>
       <c r="S20" s="110" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1" s="592">
+    <row r="21" ht="30" customHeight="1" s="582">
       <c r="A21" s="106" t="inlineStr">
         <is>
           <t>Motor converter module, CM-C S 15/10 WM V02</t>
@@ -25361,7 +25361,7 @@
       <c r="R26" s="109" t="n"/>
       <c r="S26" s="110" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1" s="592">
+    <row r="27" ht="30" customHeight="1" s="582">
       <c r="A27" s="106" t="inlineStr">
         <is>
           <t>EPVE63 Test Intervento protezioni azionamento</t>
@@ -25399,7 +25399,7 @@
       <c r="S27" s="110" t="n"/>
       <c r="T27" s="425" t="n"/>
     </row>
-    <row r="28" ht="30" customHeight="1" s="592">
+    <row r="28" ht="30" customHeight="1" s="582">
       <c r="A28" s="106" t="inlineStr">
         <is>
           <t>EPVE63 Report Intervento protezioni
@@ -25552,7 +25552,7 @@
       <c r="S31" s="110" t="n"/>
       <c r="T31" s="425" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1" s="592">
+    <row r="32" ht="30" customHeight="1" s="582">
       <c r="A32" s="106" t="inlineStr">
         <is>
           <t>Test Intervento protezioni azionamento</t>
@@ -25789,39 +25789,39 @@
     <col width="26.42578125" bestFit="1" customWidth="1" style="14" min="27" max="27"/>
     <col width="4.42578125" bestFit="1" customWidth="1" style="14" min="28" max="28"/>
     <col width="8.85546875" bestFit="1" customWidth="1" style="524" min="29" max="29"/>
-    <col width="8.7109375" customWidth="1" style="13" min="30" max="30"/>
-    <col width="8.7109375" customWidth="1" style="13" min="31" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="13" min="30" max="31"/>
+    <col width="8.7109375" customWidth="1" style="13" min="32" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.45" customHeight="1" s="592">
-      <c r="A1" s="534" t="inlineStr">
+    <row r="1" ht="29.45" customHeight="1" s="582">
+      <c r="A1" s="535" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="542" t="inlineStr">
+      <c r="B1" s="546" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="542" t="inlineStr">
+      <c r="C1" s="546" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="553" t="inlineStr">
+      <c r="D1" s="552" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="E1" s="553" t="inlineStr">
+      <c r="E1" s="552" t="inlineStr">
         <is>
           <t>VOLUME
 SUBVOLUME
 _TOMO</t>
         </is>
       </c>
-      <c r="F1" s="551" t="inlineStr">
+      <c r="F1" s="548" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
@@ -25829,7 +25829,7 @@
       <c r="G1" s="549" t="n"/>
       <c r="H1" s="549" t="n"/>
       <c r="I1" s="550" t="n"/>
-      <c r="J1" s="551" t="inlineStr">
+      <c r="J1" s="548" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
@@ -25837,7 +25837,7 @@
       <c r="K1" s="549" t="n"/>
       <c r="L1" s="549" t="n"/>
       <c r="M1" s="550" t="n"/>
-      <c r="N1" s="552" t="inlineStr">
+      <c r="N1" s="551" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
@@ -25845,7 +25845,7 @@
       <c r="O1" s="549" t="n"/>
       <c r="P1" s="549" t="n"/>
       <c r="Q1" s="550" t="n"/>
-      <c r="R1" s="552" t="inlineStr">
+      <c r="R1" s="551" t="inlineStr">
         <is>
           <t>VZ-ES</t>
         </is>
@@ -25853,7 +25853,7 @@
       <c r="S1" s="549" t="n"/>
       <c r="T1" s="549" t="n"/>
       <c r="U1" s="550" t="n"/>
-      <c r="V1" s="548" t="inlineStr">
+      <c r="V1" s="553" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
@@ -25861,7 +25861,7 @@
       <c r="W1" s="549" t="n"/>
       <c r="X1" s="549" t="n"/>
       <c r="Y1" s="550" t="n"/>
-      <c r="Z1" s="548" t="inlineStr">
+      <c r="Z1" s="553" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
@@ -25870,12 +25870,12 @@
       <c r="AB1" s="549" t="n"/>
       <c r="AC1" s="550" t="n"/>
     </row>
-    <row r="2" ht="29.45" customHeight="1" s="592" thickBot="1">
-      <c r="A2" s="536" t="n"/>
-      <c r="B2" s="543" t="n"/>
-      <c r="C2" s="543" t="n"/>
-      <c r="D2" s="528" t="n"/>
-      <c r="E2" s="528" t="n"/>
+    <row r="2" ht="29.45" customHeight="1" s="582" thickBot="1">
+      <c r="A2" s="537" t="n"/>
+      <c r="B2" s="547" t="n"/>
+      <c r="C2" s="547" t="n"/>
+      <c r="D2" s="533" t="n"/>
+      <c r="E2" s="533" t="n"/>
       <c r="F2" s="382" t="inlineStr">
         <is>
           <t>NOME FILE</t>
@@ -34296,68 +34296,68 @@
     <col width="6.5703125" customWidth="1" style="15" min="17" max="17"/>
     <col width="6.5703125" bestFit="1" customWidth="1" style="15" min="18" max="18"/>
     <col width="6.5703125" customWidth="1" style="15" min="19" max="19"/>
-    <col width="8.7109375" customWidth="1" style="103" min="20" max="26"/>
-    <col width="8.7109375" customWidth="1" style="103" min="27" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="20" max="27"/>
+    <col width="8.7109375" customWidth="1" style="103" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.6" customFormat="1" customHeight="1" s="105">
-      <c r="A1" s="526" t="inlineStr">
+      <c r="A1" s="531" t="inlineStr">
         <is>
           <t>DOC DESCRIPTION</t>
         </is>
       </c>
-      <c r="B1" s="542" t="inlineStr">
+      <c r="B1" s="546" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="C1" s="542" t="inlineStr">
+      <c r="C1" s="546" t="inlineStr">
         <is>
           <t>DOC EXT</t>
         </is>
       </c>
-      <c r="D1" s="546" t="inlineStr">
+      <c r="D1" s="542" t="inlineStr">
         <is>
           <t>VZI_Base</t>
         </is>
       </c>
-      <c r="E1" s="547" t="n"/>
+      <c r="E1" s="543" t="n"/>
       <c r="F1" s="544" t="inlineStr">
         <is>
           <t>VZI_New14</t>
         </is>
       </c>
       <c r="G1" s="545" t="n"/>
-      <c r="H1" s="546" t="inlineStr">
+      <c r="H1" s="542" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="547" t="n"/>
+      <c r="I1" s="543" t="n"/>
       <c r="J1" s="544" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
       <c r="K1" s="545" t="n"/>
-      <c r="L1" s="546" t="inlineStr">
+      <c r="L1" s="542" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="M1" s="547" t="n"/>
+      <c r="M1" s="543" t="n"/>
       <c r="N1" s="544" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
       </c>
       <c r="O1" s="545" t="n"/>
-      <c r="P1" s="546" t="inlineStr">
+      <c r="P1" s="542" t="inlineStr">
         <is>
           <t>VZ_DAI</t>
         </is>
       </c>
-      <c r="Q1" s="547" t="n"/>
+      <c r="Q1" s="543" t="n"/>
       <c r="R1" s="544" t="inlineStr">
         <is>
           <t>VZ_Esxx</t>
@@ -34366,9 +34366,9 @@
       <c r="S1" s="545" t="n"/>
     </row>
     <row r="2" ht="21.6" customFormat="1" customHeight="1" s="105">
-      <c r="A2" s="528" t="n"/>
-      <c r="B2" s="543" t="n"/>
-      <c r="C2" s="543" t="n"/>
+      <c r="A2" s="533" t="n"/>
+      <c r="B2" s="547" t="n"/>
+      <c r="C2" s="547" t="n"/>
       <c r="D2" s="395" t="inlineStr">
         <is>
           <t>File/Codice</t>
@@ -34409,12 +34409,12 @@
           <t>Rev</t>
         </is>
       </c>
-      <c r="L2" s="540" t="inlineStr">
+      <c r="L2" s="541" t="inlineStr">
         <is>
           <t>Codice</t>
         </is>
       </c>
-      <c r="M2" s="540" t="inlineStr">
+      <c r="M2" s="541" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
@@ -34475,7 +34475,7 @@
       <c r="R3" s="399" t="n"/>
       <c r="S3" s="400" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="592">
+    <row r="4" ht="30" customHeight="1" s="582">
       <c r="A4" s="114" t="inlineStr">
         <is>
           <t>Sviluppo regole (Algoritmi Diagnostici)</t>
@@ -34639,7 +34639,7 @@
       <c r="R6" s="109" t="n"/>
       <c r="S6" s="110" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="592">
+    <row r="7" ht="30" customHeight="1" s="582">
       <c r="A7" s="114" t="inlineStr">
         <is>
           <t>PropulsionDiagnosticDataset</t>
@@ -34905,8 +34905,8 @@
     <col width="14.85546875" customWidth="1" style="15" min="11" max="12"/>
     <col width="8.7109375" customWidth="1" style="103" min="13" max="13"/>
     <col width="33.140625" customWidth="1" style="103" min="14" max="14"/>
-    <col width="8.7109375" customWidth="1" style="103" min="15" max="21"/>
-    <col width="8.7109375" customWidth="1" style="103" min="22" max="16384"/>
+    <col width="8.7109375" customWidth="1" style="103" min="15" max="22"/>
+    <col width="8.7109375" customWidth="1" style="103" min="23" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customFormat="1" customHeight="1" s="105">
@@ -34920,18 +34920,18 @@
           <t>DESCRIZIONE FUNZIONE</t>
         </is>
       </c>
-      <c r="C1" s="526" t="inlineStr">
+      <c r="C1" s="531" t="inlineStr">
         <is>
           <t>DOC
 CARTELLA</t>
         </is>
       </c>
-      <c r="D1" s="526" t="inlineStr">
+      <c r="D1" s="531" t="inlineStr">
         <is>
           <t>DOC ID</t>
         </is>
       </c>
-      <c r="E1" s="526" t="inlineStr">
+      <c r="E1" s="531" t="inlineStr">
         <is>
           <t>Info DOC</t>
         </is>
@@ -34946,22 +34946,22 @@
           <t>VZI_New14</t>
         </is>
       </c>
-      <c r="H1" s="538" t="inlineStr">
+      <c r="H1" s="539" t="inlineStr">
         <is>
           <t>VZ_FR</t>
         </is>
       </c>
-      <c r="I1" s="538" t="inlineStr">
+      <c r="I1" s="539" t="inlineStr">
         <is>
           <t>VZ_ES</t>
         </is>
       </c>
-      <c r="J1" s="538" t="inlineStr">
+      <c r="J1" s="539" t="inlineStr">
         <is>
           <t>VZI-6_R1</t>
         </is>
       </c>
-      <c r="K1" s="538" t="inlineStr">
+      <c r="K1" s="539" t="inlineStr">
         <is>
           <t>VZI-4_R1</t>
         </is>
@@ -34997,7 +34997,7 @@
       <c r="K2" s="161" t="n"/>
       <c r="L2" s="162" t="n"/>
     </row>
-    <row r="3" outlineLevel="1" s="592">
+    <row r="3" outlineLevel="1" s="582">
       <c r="B3" s="144" t="n"/>
       <c r="C3" s="158" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
       <c r="K3" s="157" t="n"/>
       <c r="L3" s="158" t="n"/>
     </row>
-    <row r="4" outlineLevel="2" s="592">
+    <row r="4" outlineLevel="2" s="582">
       <c r="B4" s="144" t="n"/>
       <c r="D4" s="358" t="n"/>
       <c r="E4" s="186" t="inlineStr">
@@ -35050,7 +35050,7 @@
       <c r="K4" s="85" t="n"/>
       <c r="L4" s="50" t="n"/>
     </row>
-    <row r="5" outlineLevel="2" ht="75" customHeight="1" s="592">
+    <row r="5" outlineLevel="2" ht="75" customHeight="1" s="582">
       <c r="B5" s="144" t="n"/>
       <c r="D5" s="107" t="n"/>
       <c r="E5" s="186" t="inlineStr">
@@ -35079,7 +35079,7 @@
       <c r="K5" s="159" t="n"/>
       <c r="L5" s="50" t="n"/>
     </row>
-    <row r="6" outlineLevel="2" ht="330" customHeight="1" s="592">
+    <row r="6" outlineLevel="2" ht="330" customHeight="1" s="582">
       <c r="B6" s="144" t="n"/>
       <c r="D6" s="108" t="n"/>
       <c r="E6" s="186" t="inlineStr">
@@ -35106,7 +35106,7 @@
       <c r="K6" s="50" t="n"/>
       <c r="L6" s="50" t="n"/>
     </row>
-    <row r="7" outlineLevel="1" s="592">
+    <row r="7" outlineLevel="1" s="582">
       <c r="B7" s="144" t="n"/>
       <c r="C7" s="158" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
       <c r="K7" s="157" t="n"/>
       <c r="L7" s="158" t="n"/>
     </row>
-    <row r="8" outlineLevel="2" s="592">
+    <row r="8" outlineLevel="2" s="582">
       <c r="B8" s="144" t="n"/>
       <c r="D8" s="358" t="n"/>
       <c r="E8" s="186" t="inlineStr">
@@ -35157,7 +35157,7 @@
       <c r="K8" s="85" t="n"/>
       <c r="L8" s="50" t="n"/>
     </row>
-    <row r="9" outlineLevel="2" ht="120" customHeight="1" s="592">
+    <row r="9" outlineLevel="2" ht="120" customHeight="1" s="582">
       <c r="B9" s="144" t="n"/>
       <c r="D9" s="107" t="n"/>
       <c r="E9" s="186" t="inlineStr">
@@ -35188,7 +35188,7 @@
       <c r="K9" s="159" t="n"/>
       <c r="L9" s="50" t="n"/>
     </row>
-    <row r="10" outlineLevel="2" ht="270" customHeight="1" s="592">
+    <row r="10" outlineLevel="2" ht="270" customHeight="1" s="582">
       <c r="B10" s="144" t="n"/>
       <c r="D10" s="108" t="n"/>
       <c r="E10" s="186" t="inlineStr">
@@ -35212,7 +35212,7 @@
       <c r="K10" s="50" t="n"/>
       <c r="L10" s="50" t="n"/>
     </row>
-    <row r="11" outlineLevel="1" s="592">
+    <row r="11" outlineLevel="1" s="582">
       <c r="B11" s="144" t="n"/>
       <c r="C11" s="158" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
       <c r="K11" s="158" t="n"/>
       <c r="L11" s="158" t="n"/>
     </row>
-    <row r="12" outlineLevel="2" s="592">
+    <row r="12" outlineLevel="2" s="582">
       <c r="B12" s="144" t="n"/>
       <c r="D12" s="358" t="n"/>
       <c r="E12" s="186" t="inlineStr">
@@ -35263,7 +35263,7 @@
       <c r="K12" s="50" t="n"/>
       <c r="L12" s="50" t="n"/>
     </row>
-    <row r="13" outlineLevel="2" ht="240" customHeight="1" s="592">
+    <row r="13" outlineLevel="2" ht="240" customHeight="1" s="582">
       <c r="B13" s="144" t="n"/>
       <c r="D13" s="108" t="n"/>
       <c r="E13" s="186" t="inlineStr">
@@ -35288,7 +35288,7 @@
       <c r="K13" s="50" t="n"/>
       <c r="L13" s="50" t="n"/>
     </row>
-    <row r="14" outlineLevel="1" s="592">
+    <row r="14" outlineLevel="1" s="582">
       <c r="B14" s="144" t="n"/>
       <c r="C14" s="158" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
       <c r="K14" s="158" t="n"/>
       <c r="L14" s="158" t="n"/>
     </row>
-    <row r="15" outlineLevel="2" s="592">
+    <row r="15" outlineLevel="2" s="582">
       <c r="A15" s="116" t="n"/>
       <c r="B15" s="144" t="n"/>
       <c r="D15" s="50" t="n"/>
@@ -35365,7 +35365,7 @@
       <c r="K16" s="161" t="n"/>
       <c r="L16" s="162" t="n"/>
     </row>
-    <row r="17" outlineLevel="1" s="592">
+    <row r="17" outlineLevel="1" s="582">
       <c r="A17" s="177" t="n"/>
       <c r="B17" s="385" t="n"/>
       <c r="C17" s="158" t="inlineStr">
@@ -35397,7 +35397,7 @@
       <c r="K17" s="157" t="n"/>
       <c r="L17" s="158" t="n"/>
     </row>
-    <row r="18" outlineLevel="2" s="592">
+    <row r="18" outlineLevel="2" s="582">
       <c r="A18" s="179" t="n"/>
       <c r="B18" s="386" t="n"/>
       <c r="C18" s="180" t="n"/>
@@ -35419,7 +35419,7 @@
       <c r="K18" s="85" t="n"/>
       <c r="L18" s="50" t="n"/>
     </row>
-    <row r="19" outlineLevel="2" ht="150" customHeight="1" s="592">
+    <row r="19" outlineLevel="2" ht="150" customHeight="1" s="582">
       <c r="A19" s="179" t="n"/>
       <c r="B19" s="386" t="n"/>
       <c r="C19" s="180" t="n"/>
@@ -35456,7 +35456,7 @@
       <c r="K19" s="85" t="n"/>
       <c r="L19" s="50" t="n"/>
     </row>
-    <row r="20" outlineLevel="2" ht="345" customHeight="1" s="592">
+    <row r="20" outlineLevel="2" ht="345" customHeight="1" s="582">
       <c r="A20" s="179" t="n"/>
       <c r="B20" s="386" t="n"/>
       <c r="C20" s="180" t="n"/>
@@ -35485,7 +35485,7 @@
       <c r="K20" s="85" t="n"/>
       <c r="L20" s="50" t="n"/>
     </row>
-    <row r="21" outlineLevel="1" s="592">
+    <row r="21" outlineLevel="1" s="582">
       <c r="A21" s="179" t="n"/>
       <c r="B21" s="386" t="n"/>
       <c r="C21" s="158" t="inlineStr">
@@ -35520,7 +35520,7 @@
       <c r="K21" s="158" t="n"/>
       <c r="L21" s="158" t="n"/>
     </row>
-    <row r="22" outlineLevel="2" s="592">
+    <row r="22" outlineLevel="2" s="582">
       <c r="A22" s="179" t="n"/>
       <c r="C22" s="180" t="n"/>
       <c r="D22" s="358" t="n"/>
@@ -35543,7 +35543,7 @@
       <c r="K22" s="50" t="n"/>
       <c r="L22" s="50" t="n"/>
     </row>
-    <row r="23" outlineLevel="2" ht="409.5" customHeight="1" s="592">
+    <row r="23" outlineLevel="2" ht="409.5" customHeight="1" s="582">
       <c r="A23" s="179" t="n"/>
       <c r="B23" s="386" t="n"/>
       <c r="C23" s="180" t="n"/>
@@ -35581,7 +35581,7 @@
       <c r="K23" s="50" t="n"/>
       <c r="L23" s="50" t="n"/>
     </row>
-    <row r="24" outlineLevel="1" s="592">
+    <row r="24" outlineLevel="1" s="582">
       <c r="A24" s="179" t="n"/>
       <c r="B24" s="386" t="n"/>
       <c r="C24" s="158" t="inlineStr">
@@ -35613,7 +35613,7 @@
       <c r="K24" s="158" t="n"/>
       <c r="L24" s="158" t="n"/>
     </row>
-    <row r="25" outlineLevel="2" s="592">
+    <row r="25" outlineLevel="2" s="582">
       <c r="A25" s="179" t="n"/>
       <c r="B25" s="180" t="n"/>
       <c r="C25" s="180" t="n"/>
@@ -35665,7 +35665,7 @@
       <c r="K26" s="429" t="n"/>
       <c r="L26" s="430" t="n"/>
     </row>
-    <row r="27" outlineLevel="1" s="592">
+    <row r="27" outlineLevel="1" s="582">
       <c r="A27" s="181" t="n"/>
       <c r="B27" s="182" t="n"/>
       <c r="C27" s="158" t="inlineStr">
@@ -35697,7 +35697,7 @@
       <c r="K27" s="157" t="n"/>
       <c r="L27" s="158" t="n"/>
     </row>
-    <row r="28" outlineLevel="2" s="592">
+    <row r="28" outlineLevel="2" s="582">
       <c r="A28" s="183" t="n"/>
       <c r="B28" s="184">
         <f t="array" ref="B28">INDIRECT("'" &amp; $C33 &amp; "'!B5")</f>
@@ -35722,7 +35722,7 @@
       <c r="K28" s="85" t="n"/>
       <c r="L28" s="50" t="n"/>
     </row>
-    <row r="29" outlineLevel="1" s="592">
+    <row r="29" outlineLevel="1" s="582">
       <c r="A29" s="183" t="n"/>
       <c r="B29" s="184" t="n"/>
       <c r="C29" s="158" t="inlineStr">
@@ -35754,7 +35754,7 @@
       <c r="K29" s="158" t="n"/>
       <c r="L29" s="158" t="n"/>
     </row>
-    <row r="30" outlineLevel="2" s="592">
+    <row r="30" outlineLevel="2" s="582">
       <c r="A30" s="183" t="n"/>
       <c r="B30" s="184" t="n"/>
       <c r="C30" s="178" t="n"/>
@@ -35776,7 +35776,7 @@
       <c r="K30" s="50" t="n"/>
       <c r="L30" s="50" t="n"/>
     </row>
-    <row r="31" outlineLevel="1" s="592">
+    <row r="31" outlineLevel="1" s="582">
       <c r="A31" s="183" t="n"/>
       <c r="B31" s="184" t="n"/>
       <c r="C31" s="158" t="inlineStr">
@@ -35808,7 +35808,7 @@
       <c r="K31" s="158" t="n"/>
       <c r="L31" s="158" t="n"/>
     </row>
-    <row r="32" outlineLevel="2" s="592">
+    <row r="32" outlineLevel="2" s="582">
       <c r="A32" s="183" t="n"/>
       <c r="B32" s="184" t="n"/>
       <c r="C32" s="184" t="n"/>
@@ -35830,7 +35830,7 @@
       <c r="K32" s="50" t="n"/>
       <c r="L32" s="50" t="n"/>
     </row>
-    <row r="33" outlineLevel="1" s="592">
+    <row r="33" outlineLevel="1" s="582">
       <c r="A33" s="116" t="n"/>
       <c r="B33" s="144" t="n"/>
       <c r="C33" s="158" t="inlineStr">
@@ -35862,7 +35862,7 @@
       <c r="K33" s="158" t="n"/>
       <c r="L33" s="158" t="n"/>
     </row>
-    <row r="34" outlineLevel="2" s="592">
+    <row r="34" outlineLevel="2" s="582">
       <c r="A34" s="116" t="n"/>
       <c r="B34" s="144" t="n"/>
       <c r="D34" s="358" t="n"/>
@@ -35883,7 +35883,7 @@
       <c r="K34" s="50" t="n"/>
       <c r="L34" s="50" t="n"/>
     </row>
-    <row r="35" outlineLevel="2" s="592">
+    <row r="35" outlineLevel="2" s="582">
       <c r="A35" s="116" t="n"/>
       <c r="B35" s="144" t="n"/>
       <c r="D35" s="108" t="n"/>
@@ -35900,7 +35900,7 @@
       <c r="K35" s="50" t="n"/>
       <c r="L35" s="50" t="n"/>
     </row>
-    <row r="36" outlineLevel="1" s="592">
+    <row r="36" outlineLevel="1" s="582">
       <c r="A36" s="116" t="n"/>
       <c r="B36" s="144" t="n"/>
       <c r="C36" s="158" t="inlineStr">
@@ -35929,7 +35929,7 @@
       <c r="K36" s="158" t="n"/>
       <c r="L36" s="158" t="n"/>
     </row>
-    <row r="37" outlineLevel="2" s="592">
+    <row r="37" outlineLevel="2" s="582">
       <c r="A37" s="116" t="n"/>
       <c r="B37" s="144" t="n"/>
       <c r="D37" s="358" t="n"/>
@@ -35948,7 +35948,7 @@
       <c r="K37" s="50" t="n"/>
       <c r="L37" s="50" t="n"/>
     </row>
-    <row r="38" outlineLevel="1" s="592">
+    <row r="38" outlineLevel="1" s="582">
       <c r="A38" s="116" t="n"/>
       <c r="B38" s="387" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
       <c r="K38" s="158" t="n"/>
       <c r="L38" s="158" t="n"/>
     </row>
-    <row r="39" outlineLevel="2" s="592">
+    <row r="39" outlineLevel="2" s="582">
       <c r="A39" s="116" t="n"/>
       <c r="B39" s="144" t="n"/>
       <c r="D39" s="358" t="n"/>
@@ -36000,7 +36000,7 @@
       <c r="K39" s="50" t="n"/>
       <c r="L39" s="50" t="n"/>
     </row>
-    <row r="40" ht="30" customHeight="1" s="592">
+    <row r="40" ht="30" customHeight="1" s="582">
       <c r="A40" s="176" t="inlineStr">
         <is>
           <t>LV_Country_code_selection</t>
@@ -36026,7 +36026,7 @@
       <c r="K40" s="161" t="n"/>
       <c r="L40" s="162" t="n"/>
     </row>
-    <row r="41" outlineLevel="1" s="592">
+    <row r="41" outlineLevel="1" s="582">
       <c r="A41" s="181" t="n"/>
       <c r="B41" s="182" t="n"/>
       <c r="C41" s="158" t="inlineStr">
@@ -36064,7 +36064,7 @@
       <c r="K41" s="157" t="n"/>
       <c r="L41" s="158" t="n"/>
     </row>
-    <row r="42" outlineLevel="2" s="592">
+    <row r="42" outlineLevel="2" s="582">
       <c r="A42" s="183" t="n"/>
       <c r="B42" s="184" t="n"/>
       <c r="C42" s="184" t="n"/>
@@ -36090,7 +36090,7 @@
       <c r="K42" s="85" t="n"/>
       <c r="L42" s="50" t="n"/>
     </row>
-    <row r="43" outlineLevel="2" s="592">
+    <row r="43" outlineLevel="2" s="582">
       <c r="A43" s="183" t="n"/>
       <c r="B43" s="184" t="n"/>
       <c r="C43" s="184" t="n"/>
@@ -36102,7 +36102,7 @@
       </c>
       <c r="F43" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Country_code_selection è una selezione su IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema di controllo elettronico (IDU), il sistema di propulsione, i PCU della traine e il software di gestione del sistema. La funzione viene attivata quando il driver seleziona un paese corrente sul IDU, che viene poi inviato a tutti i PCU della traine. In caso di fallimento, il sistema deve essere riconosciuto e l'azione di ripristino prese.
+          <t>La funzione ferroviaria LV_Country_code_selection è una selezione su IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema di controllo elettronico (IDU), la PCU (Power Control Unit) e il sistema di propulsione. La funzione viene attivata quando il driver seleziona un paese corrente dal IDU, che viene poi inviato alle PCU del treno per configurare i pantografi appropriati. In caso di fallimento, la funzione è progettata per essere supervisionata e gestita dal sistema, con feedback al driver e azioni di sicurezza per garantire l'operazione in sicurezza.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina di riferimento: 7.</t>
         </is>
@@ -36110,21 +36110,21 @@
       <c r="G43" s="456" t="n"/>
       <c r="H43" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Country_code_selection è una selezione su IDU del paese corrente per informare la PCU sui pantografi selezionabili. È coinvolta nella gestione elettrica del treno, specificamente nella configurazione della tensione di linea e dei pantografi adatti al paese di operazione. La funzione è attivata quando il driver seleziona un paese dall'IDU, che viene poi inviato alle PCU per configurare la tensione di linea e i pantografi appropriati. In caso di fallimento, la funzione supervisiona l'errore e fornisce feedback al driver. La funzione è progettata con una sicurezza di SIL 2 e richiede la conferma del driver prima dell'attivazione.
+          <t>La funzione ferroviaria LV_Country_code_selection seleziona il paese corrente tramite l'IDU (Interface Device Unit) per informare la PCU (Power Control Unit) sui pantografi selezionabili. I componenti principali coinvolti sono l'IDU, la PCU e il sistema di propulsione. La funzione è attivata quando il driver seleziona un paese corrente dall'IDU, che viene poi inviato alle PCU per configurare i pantografi appropriati. In caso di fallimento, il sistema deve essere rilevato e l'azione del driver deve essere confermata. La funzione è progettata con una sicurezza SIL 2 e richiede la conferma del driver prima dell'avvio della propulsione.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina di riferimento: 7.</t>
         </is>
       </c>
       <c r="I43" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Country_code_selection seleziona l'IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema di gestione della velocità (TCMS), l'IDU e la PCU, con la logica di funzionamento basata sulla selezione di un codice di paese valido (1-8) che viene inviato alle PCU per configurare i pantografi. La funzione è progettata per garantire una sicurezza di livello SIL 2 e prevede la ridondanza nella comunicazione tra TCMS, IDU e PCU.
+          <t>La funzione ferroviaria LV_Country_code_selection seleziona l'IDU del paese corrente per informare la PCU sui pantografi selezionabili. Coinvolti sono il sistema IDU, la PCU e il software TCMS. La logica di funzionamento attiva la selezione del paese in base all'IDU selezionato, che viene poi inviato alle PCU per configurare i pantografi appropriati. La funzione è progettata con una sicurezza SIL 2 e prevede la deteczione di eventuali errori o fallimenti durante l'esecuzione della funzione.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina di riferimento: 7.</t>
         </is>
       </c>
       <c r="J43" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Country_code_selection seleziona l'IDU del paese corrente per informare la PCU sui pantografi selezionabili, utilizzando il codice di paese Italy come riferimento operativo. La funzione è coinvoltiva del sistema IDU e della PCU, ed è caratterizzata da due condizioni di attivazione: se un codice non disponibile viene selezionato o se un codice non definito viene selezionato, il sistema invia una messaggio al conducente. La funzione è progettata per garantire la sicurezza e l'efficienza del sistema, con requisiti di sicurezza SIL 2.
+          <t>La funzione ferroviaria LV_Country_code_selection seleziona l'IDU del paese corrente per informare la PCU sui pantografi selezionabili, utilizzando il codice di paese Italy come riferimento operativo. La funzione è coinvoltiva del sistema IDU e della PCU, ed è caratterizzata da due condizioni di attivazione: se un codice non disponibile viene selezionato o se un codice non definito viene selezionato, il sistema invia una messaggio di allarme al conducente. La funzione è progettata per garantire la sicurezza e la conformità alle normative, con un livello di sicurezza SIL 2.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina di riferimento: 12.</t>
         </is>
@@ -36132,7 +36132,7 @@
       <c r="K43" s="455" t="n"/>
       <c r="L43" s="457" t="n"/>
     </row>
-    <row r="44" ht="30" customHeight="1" s="592">
+    <row r="44" ht="30" customHeight="1" s="582">
       <c r="A44" s="176" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lifting</t>
@@ -36158,7 +36158,7 @@
       <c r="K44" s="161" t="n"/>
       <c r="L44" s="162" t="n"/>
     </row>
-    <row r="45" outlineLevel="1" s="592">
+    <row r="45" outlineLevel="1" s="582">
       <c r="A45" s="181" t="n"/>
       <c r="B45" s="182" t="n"/>
       <c r="C45" s="158" t="inlineStr">
@@ -36196,7 +36196,7 @@
       <c r="K45" s="157" t="n"/>
       <c r="L45" s="158" t="n"/>
     </row>
-    <row r="46" outlineLevel="2" s="592">
+    <row r="46" outlineLevel="2" s="582">
       <c r="A46" s="183" t="n"/>
       <c r="B46" s="184" t="n"/>
       <c r="C46" s="184" t="n"/>
@@ -36222,7 +36222,7 @@
       <c r="K46" s="85" t="n"/>
       <c r="L46" s="50" t="n"/>
     </row>
-    <row r="47" outlineLevel="2" s="592">
+    <row r="47" outlineLevel="2" s="582">
       <c r="A47" s="183" t="n"/>
       <c r="B47" s="184" t="n"/>
       <c r="C47" s="184" t="n"/>
@@ -36234,29 +36234,29 @@
       </c>
       <c r="F47" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che controlla l'alzamento dei pantografi 1 e/o 2 in base alla tensione di linea (switch) e al paese (IDU) selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, il sistema di gestione della tensione di linea e il sistema di comunicazione TCMS-PCU. La funzione è attivata quando il driver seleziona la line voltage system e il paese corretto, e viene disattivata se non si verifica l'alzamento del pantografo entro 35 secondi o se si verificano condizioni di fallimento come mancato alzamento o uso di un tipo di pantografo sbagliato.
+          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che regola l'alzamento del pantografo 1 o 2 in base alla tensione di linea e al paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, la console di guida (PCU) e il sistema di gestione della tensione di linea (TCMS). La funzione viene attivata quando il driver seleziona una line voltage system e un paese corretto, e viene disattivata se non si verifica l'alzamento del pantografo entro 35 secondi. In caso di fallimento, la funzione invia segnali di allarme e blocca il pantografo.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 8 — Pagina finale: 18.</t>
+Pagina iniziale: 8 — Pagina finale: 13.</t>
         </is>
       </c>
       <c r="G47" s="456" t="n"/>
       <c r="H47" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che regola l'alzamento del pantografo 1 o 2 in base alla tensione di linea e al paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, il sistema di gestione della tensione di linea e il sistema di comunicazione tra il Control Center e la Plataforma. La funzione è attivata quando il driver seleziona una line voltage system e un paese, e viene disattivata se non si verifica l'alzamento del pantografo entro 35 secondi o se si verificano condizioni di fallimento.
+          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che regola l'alzamento dei pantografi 1 e/o 2 in base alla tensione di linea (switch) e al paese (IDU) selezionati. La funzione coinvolge il sistema di controllo del pantografo, la TCMS (Traction Control and Management System), il PCU (Power Control Unit) e due DOs (Digital Output). La logica di funzionamento attiva il comando se il driver seleziona una line voltage system e specifica il tipo di pantografo da alzare. In caso di fallimento, la funzione invia segnali di allarme e blocca il pantografo.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina iniziale: 8 — Pagina finale: 15.</t>
         </is>
       </c>
       <c r="I47" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che controlla l'alzamento del pantografo 1 o 2 in base alla tensione di linea e al paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, la console del conducente (PCU) e il sistema di gestione della tensione di linea (TCMS). La funzione è attivata quando il conducente seleziona una line voltage system e un paese corretto, e viene eseguita automaticamente o manualmente. In caso di fallimento, la funzione verifica se il pantografo è stato alzato correttamente e se non ci sono errori di tipo hardware o software.
+          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che controlla l'alzamento del pantografo 1 o 2 in base alla tensione di linea e al paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, il sistema di gestione della tensione di linea, il sistema di identificazione del paese e il sistema di comunicazione tra il Control Center e la Unità di Comando (PCU). La funzione è attivata quando il driver seleziona una line voltage system e un paese, e viene disattivata se non si verifica l'alzamento del pantografo entro 35 secondi. In caso di fallimento, il sistema invia segnali di allarme e blocca il pantografo.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina iniziale: 8 — Pagina finale: 20.</t>
         </is>
       </c>
       <c r="J47" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lifting (Comando di alzamento pantografo 1 o 2 sulla base di tensione di linea e paese selezionati) è responsabile dell'alzamento del pantografo in base alle condizioni di linea e paese di operazione. I componenti principali coinvolti sono il sistema di controllo pantografico, il selector di tensione di linea e il software TCMS (Train Control and Management System). La funzione viene attivata quando il driver seleziona la tensione di linea e il paese di operazione, e in caso di emergenza, utilizza il paese più recentemente selezionato. La logica di funzionamento prevede l'invio di segnali al PCU (Pantograph Control Unit) e all'HVSP (High Voltage Switching Panel), con la possibilità di ridondanza per garantire la sicurezza.
+          <t>La funzione ferroviaria LV_Pantograph_Lifting è un comando che controlla l'alzamento del pantografo 1 o 2 sulla base di tensione di linea e paese selezionati. I componenti principali coinvolti sono il sistema di controllo del pantografo, la stazione di controllo (PCU) e il software TCMS. La funzione viene attivata quando il driver seleziona una line voltage system e attiva l'alzamento del pantografo 1 o 2, in base al paese di operazione selezionato. In caso di emergenza, la funzione utilizza il paese più recentemente selezionato e comunicato alla PCU. La logica di funzionamento prevede la validazione del paese selezionato per evitare l'uso di codici non disponibili.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina iniziale: 13 — Pagina finale: 21.</t>
         </is>
@@ -36264,7 +36264,7 @@
       <c r="K47" s="455" t="n"/>
       <c r="L47" s="457" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1" s="592">
+    <row r="48" ht="30" customHeight="1" s="582">
       <c r="A48" s="176" t="inlineStr">
         <is>
           <t>LV_Pantograph_Lowering</t>
@@ -36290,7 +36290,7 @@
       <c r="K48" s="161" t="n"/>
       <c r="L48" s="162" t="n"/>
     </row>
-    <row r="49" outlineLevel="1" s="592">
+    <row r="49" outlineLevel="1" s="582">
       <c r="A49" s="181" t="n"/>
       <c r="B49" s="182" t="n"/>
       <c r="C49" s="158" t="inlineStr">
@@ -36328,7 +36328,7 @@
       <c r="K49" s="157" t="n"/>
       <c r="L49" s="158" t="n"/>
     </row>
-    <row r="50" outlineLevel="2" s="592">
+    <row r="50" outlineLevel="2" s="582">
       <c r="A50" s="183" t="n"/>
       <c r="B50" s="184" t="n"/>
       <c r="C50" s="184" t="n"/>
@@ -36354,7 +36354,7 @@
       <c r="K50" s="85" t="n"/>
       <c r="L50" s="50" t="n"/>
     </row>
-    <row r="51" outlineLevel="2" s="592">
+    <row r="51" outlineLevel="2" s="582">
       <c r="A51" s="183" t="n"/>
       <c r="B51" s="184" t="n"/>
       <c r="C51" s="184" t="n"/>
@@ -36366,15 +36366,15 @@
       </c>
       <c r="F51" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lowering (Comando di abbassamento pantografo) è finalizzata a ridurre il pantografo in modo sicuro e controllato quando si deattiva la linea elettrica. La funzione coinvolge il sistema elettrico, il controllo del pantografo e il blocco della seconda pantografia in caso di interazione con la prima. La logica di funzionamento attiva il comando di abbassamento quando si verifica una delle seguenti condizioni: deattivazione della linea elettrica, pressione dell'Emergency push button o avvenuta una manovra di blocco del pantografo.
+          <t>La funzione ferroviaria LV_Pantograph_Lowering (Comando di abbassamento pantografo) è finalizzata a ridurre il pantografo in modo sicuro e controllato quando si deattiva la linea elettrica. La funzione coinvolge il sistema di controllo del pantografo, i circuiti di protezione e le interazioni software tra i vari componenti elettrici/meccanici. La logica di funzionamento attiva il comando di abbassamento quando si verifica una delle seguenti condizioni: deattivazione della linea elettrica, pressione dell'Emergency push button o avvenuta una critica falla del sistema. La funzione è progettata con un livello di sicurezza SIL 0 e prevede la bloccatura del pantografo in caso di mancato rispetto delle condizioni di abbassamento, per garantire la sicurezza dei passeggeri e del personale ferroviario.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
-Pagina iniziale: 14 — Pagina finale: 29.</t>
+Pagina iniziale: 14 — Pagina finale: 18.</t>
         </is>
       </c>
       <c r="G51" s="456" t="n"/>
       <c r="H51" s="625" t="inlineStr">
         <is>
-          <t>La funzione ferroviaria LV_Pantograph_Lowering (Comando di abbassamento pantografo) è un comando manuale/automatico che attiva l'abbassamento del pantografo in caso di deattivazione della linea elettrica o di emergenza. I componenti principali coinvolti sono il sistema di controllo del pantografo, i comandi di abbassamento (pantograph down) e l'impianto di sicurezza. La funzione viene attivata quando si verifica una delle seguenti condizioni: deattivazione della linea elettrica, pressione dell'emergenza o fallimento del sistema di controllo. In caso di fallimento, il pantografo viene bloccato per garantire la sicurezza.
+          <t>La funzione ferroviaria LV_Pantograph_Lowering (Comando di abbassamento pantografo) è una operazione manuale/automatica che attiva l'abbassamento del pantografo per spegnere la corrente elettrica. La funzione è caratterizzata dalla presenza dei seguenti componenti: il sistema di controllo elettronico, il pantografo con il suo sistema di levatura e il sistema di sicurezza. La logica di funzionamento attiva l'abbassamento del pantografo in caso di deattivazione della linea elettrica o in caso di emergenza, mentre la presenza di linee di sicurezza come i circuiti di spegnimento assicura una ridondanza e un alto livello di sicurezza.
 Analisi — Funzione equivalente tra le seguenti configurazioni: VZI_Base, VZ_FR, VZ_ES, VZI-6_R1.
 Pagina iniziale: 16 — Pagina finale: 20.</t>
         </is>
@@ -36449,7 +36449,7 @@
     </row>
     <row r="54" outlineLevel="2" customFormat="1" s="13">
       <c r="B54" s="103" t="n"/>
-      <c r="C54" s="543" t="n"/>
+      <c r="C54" s="547" t="n"/>
       <c r="D54" s="361" t="n"/>
       <c r="E54" s="321" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
     </row>
     <row r="55" outlineLevel="2" customFormat="1" s="13">
       <c r="B55" s="103" t="n"/>
-      <c r="C55" s="543" t="n"/>
+      <c r="C55" s="547" t="n"/>
       <c r="D55" s="458" t="n"/>
       <c r="E55" s="459" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
     </row>
     <row r="58" outlineLevel="2" customFormat="1" s="13">
       <c r="B58" s="103" t="n"/>
-      <c r="C58" s="543" t="n"/>
+      <c r="C58" s="547" t="n"/>
       <c r="D58" s="361" t="n"/>
       <c r="E58" s="321" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
     </row>
     <row r="59" outlineLevel="2" customFormat="1" s="13">
       <c r="B59" s="103" t="n"/>
-      <c r="C59" s="543" t="n"/>
+      <c r="C59" s="547" t="n"/>
       <c r="D59" s="458" t="n"/>
       <c r="E59" s="459" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
     </row>
     <row r="62" outlineLevel="2" customFormat="1" s="13">
       <c r="B62" s="103" t="n"/>
-      <c r="C62" s="543" t="n"/>
+      <c r="C62" s="547" t="n"/>
       <c r="D62" s="361" t="n"/>
       <c r="E62" s="321" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
     </row>
     <row r="63" outlineLevel="2" customFormat="1" s="13">
       <c r="B63" s="103" t="n"/>
-      <c r="C63" s="543" t="n"/>
+      <c r="C63" s="547" t="n"/>
       <c r="D63" s="458" t="n"/>
       <c r="E63" s="459" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
     </row>
     <row r="66" outlineLevel="2" customFormat="1" s="13">
       <c r="B66" s="103" t="n"/>
-      <c r="C66" s="543" t="n"/>
+      <c r="C66" s="547" t="n"/>
       <c r="D66" s="361" t="n"/>
       <c r="E66" s="321" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
     </row>
     <row r="67" outlineLevel="2" customFormat="1" s="13">
       <c r="B67" s="103" t="n"/>
-      <c r="C67" s="543" t="n"/>
+      <c r="C67" s="547" t="n"/>
       <c r="D67" s="458" t="n"/>
       <c r="E67" s="459" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
     </row>
     <row r="70" outlineLevel="2" customFormat="1" s="13">
       <c r="B70" s="103" t="n"/>
-      <c r="C70" s="543" t="n"/>
+      <c r="C70" s="547" t="n"/>
       <c r="D70" s="361" t="n"/>
       <c r="E70" s="321" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
     </row>
     <row r="71" outlineLevel="2" customFormat="1" s="13">
       <c r="B71" s="103" t="n"/>
-      <c r="C71" s="543" t="n"/>
+      <c r="C71" s="547" t="n"/>
       <c r="D71" s="458" t="n"/>
       <c r="E71" s="459" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
     </row>
     <row r="74" outlineLevel="2" customFormat="1" s="13">
       <c r="B74" s="103" t="n"/>
-      <c r="C74" s="543" t="n"/>
+      <c r="C74" s="547" t="n"/>
       <c r="D74" s="361" t="n"/>
       <c r="E74" s="321" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
     </row>
     <row r="75" outlineLevel="2" customFormat="1" s="13">
       <c r="B75" s="103" t="n"/>
-      <c r="C75" s="543" t="n"/>
+      <c r="C75" s="547" t="n"/>
       <c r="D75" s="458" t="n"/>
       <c r="E75" s="459" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
     </row>
     <row r="78" outlineLevel="2" customFormat="1" s="13">
       <c r="B78" s="103" t="n"/>
-      <c r="C78" s="543" t="n"/>
+      <c r="C78" s="547" t="n"/>
       <c r="D78" s="361" t="n"/>
       <c r="E78" s="321" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
     </row>
     <row r="79" outlineLevel="2" customFormat="1" s="13">
       <c r="B79" s="103" t="n"/>
-      <c r="C79" s="543" t="n"/>
+      <c r="C79" s="547" t="n"/>
       <c r="D79" s="458" t="n"/>
       <c r="E79" s="459" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
     </row>
     <row r="82" outlineLevel="2" customFormat="1" s="13">
       <c r="B82" s="103" t="n"/>
-      <c r="C82" s="543" t="n"/>
+      <c r="C82" s="547" t="n"/>
       <c r="D82" s="361" t="n"/>
       <c r="E82" s="321" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
     </row>
     <row r="83" outlineLevel="2" customFormat="1" s="13">
       <c r="B83" s="103" t="n"/>
-      <c r="C83" s="543" t="n"/>
+      <c r="C83" s="547" t="n"/>
       <c r="D83" s="458" t="n"/>
       <c r="E83" s="459" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
     </row>
     <row r="86" outlineLevel="2" customFormat="1" s="13">
       <c r="B86" s="103" t="n"/>
-      <c r="C86" s="543" t="n"/>
+      <c r="C86" s="547" t="n"/>
       <c r="D86" s="361" t="n"/>
       <c r="E86" s="321" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
     </row>
     <row r="87" outlineLevel="2" customFormat="1" s="13">
       <c r="B87" s="103" t="n"/>
-      <c r="C87" s="543" t="n"/>
+      <c r="C87" s="547" t="n"/>
       <c r="D87" s="458" t="n"/>
       <c r="E87" s="459" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
     </row>
     <row r="90" outlineLevel="2" customFormat="1" s="13">
       <c r="B90" s="103" t="n"/>
-      <c r="C90" s="543" t="n"/>
+      <c r="C90" s="547" t="n"/>
       <c r="D90" s="361" t="n"/>
       <c r="E90" s="321" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
     </row>
     <row r="91" outlineLevel="2" customFormat="1" s="13">
       <c r="B91" s="103" t="n"/>
-      <c r="C91" s="543" t="n"/>
+      <c r="C91" s="547" t="n"/>
       <c r="D91" s="458" t="n"/>
       <c r="E91" s="459" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
     </row>
     <row r="94" outlineLevel="2" customFormat="1" s="13">
       <c r="B94" s="103" t="n"/>
-      <c r="C94" s="543" t="n"/>
+      <c r="C94" s="547" t="n"/>
       <c r="D94" s="361" t="n"/>
       <c r="E94" s="321" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
     </row>
     <row r="95" outlineLevel="2" customFormat="1" s="13">
       <c r="B95" s="103" t="n"/>
-      <c r="C95" s="543" t="n"/>
+      <c r="C95" s="547" t="n"/>
       <c r="D95" s="458" t="n"/>
       <c r="E95" s="459" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
     </row>
     <row r="98" outlineLevel="2" customFormat="1" s="13">
       <c r="B98" s="103" t="n"/>
-      <c r="C98" s="543" t="n"/>
+      <c r="C98" s="547" t="n"/>
       <c r="D98" s="361" t="n"/>
       <c r="E98" s="321" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
     </row>
     <row r="99" outlineLevel="2" customFormat="1" s="13">
       <c r="B99" s="103" t="n"/>
-      <c r="C99" s="543" t="n"/>
+      <c r="C99" s="547" t="n"/>
       <c r="D99" s="458" t="n"/>
       <c r="E99" s="459" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
     </row>
     <row r="102" outlineLevel="2" customFormat="1" s="13">
       <c r="B102" s="103" t="n"/>
-      <c r="C102" s="543" t="n"/>
+      <c r="C102" s="547" t="n"/>
       <c r="D102" s="361" t="n"/>
       <c r="E102" s="321" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
     </row>
     <row r="103" outlineLevel="2" customFormat="1" s="13">
       <c r="B103" s="103" t="n"/>
-      <c r="C103" s="543" t="n"/>
+      <c r="C103" s="547" t="n"/>
       <c r="D103" s="458" t="n"/>
       <c r="E103" s="459" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
     </row>
     <row r="106" outlineLevel="2" customFormat="1" s="13">
       <c r="B106" s="103" t="n"/>
-      <c r="C106" s="543" t="n"/>
+      <c r="C106" s="547" t="n"/>
       <c r="D106" s="361" t="n"/>
       <c r="E106" s="321" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
     </row>
     <row r="107" outlineLevel="2" customFormat="1" s="13">
       <c r="B107" s="103" t="n"/>
-      <c r="C107" s="543" t="n"/>
+      <c r="C107" s="547" t="n"/>
       <c r="D107" s="458" t="n"/>
       <c r="E107" s="459" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
     </row>
     <row r="110" outlineLevel="2" customFormat="1" s="13">
       <c r="B110" s="103" t="n"/>
-      <c r="C110" s="543" t="n"/>
+      <c r="C110" s="547" t="n"/>
       <c r="D110" s="361" t="n"/>
       <c r="E110" s="321" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
     </row>
     <row r="111" outlineLevel="2" customFormat="1" s="13">
       <c r="B111" s="103" t="n"/>
-      <c r="C111" s="543" t="n"/>
+      <c r="C111" s="547" t="n"/>
       <c r="D111" s="458" t="n"/>
       <c r="E111" s="459" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
     </row>
     <row r="114" outlineLevel="2" customFormat="1" s="13">
       <c r="B114" s="103" t="n"/>
-      <c r="C114" s="543" t="n"/>
+      <c r="C114" s="547" t="n"/>
       <c r="D114" s="361" t="n"/>
       <c r="E114" s="321" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
     </row>
     <row r="115" outlineLevel="2" customFormat="1" s="13">
       <c r="B115" s="103" t="n"/>
-      <c r="C115" s="543" t="n"/>
+      <c r="C115" s="547" t="n"/>
       <c r="D115" s="458" t="n"/>
       <c r="E115" s="459" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
     </row>
     <row r="118" outlineLevel="2" customFormat="1" s="13">
       <c r="B118" s="103" t="n"/>
-      <c r="C118" s="543" t="n"/>
+      <c r="C118" s="547" t="n"/>
       <c r="D118" s="361" t="n"/>
       <c r="E118" s="321" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
     </row>
     <row r="119" outlineLevel="2" customFormat="1" s="13">
       <c r="B119" s="103" t="n"/>
-      <c r="C119" s="543" t="n"/>
+      <c r="C119" s="547" t="n"/>
       <c r="D119" s="458" t="n"/>
       <c r="E119" s="459" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
     </row>
     <row r="122" outlineLevel="2" customFormat="1" s="13">
       <c r="B122" s="103" t="n"/>
-      <c r="C122" s="543" t="n"/>
+      <c r="C122" s="547" t="n"/>
       <c r="D122" s="361" t="n"/>
       <c r="E122" s="321" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
     </row>
     <row r="123" outlineLevel="2" customFormat="1" s="13">
       <c r="B123" s="103" t="n"/>
-      <c r="C123" s="543" t="n"/>
+      <c r="C123" s="547" t="n"/>
       <c r="D123" s="458" t="n"/>
       <c r="E123" s="459" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
     </row>
     <row r="126" outlineLevel="2" customFormat="1" s="13">
       <c r="B126" s="103" t="n"/>
-      <c r="C126" s="543" t="n"/>
+      <c r="C126" s="547" t="n"/>
       <c r="D126" s="361" t="n"/>
       <c r="E126" s="321" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
     </row>
     <row r="127" outlineLevel="2" customFormat="1" s="13">
       <c r="B127" s="103" t="n"/>
-      <c r="C127" s="543" t="n"/>
+      <c r="C127" s="547" t="n"/>
       <c r="D127" s="458" t="n"/>
       <c r="E127" s="459" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
     </row>
     <row r="130" outlineLevel="2" customFormat="1" s="13">
       <c r="B130" s="103" t="n"/>
-      <c r="C130" s="543" t="n"/>
+      <c r="C130" s="547" t="n"/>
       <c r="D130" s="362" t="n"/>
       <c r="E130" s="324" t="inlineStr">
         <is>
@@ -38436,7 +38436,7 @@
     </row>
     <row r="131" outlineLevel="2" customFormat="1" s="13">
       <c r="B131" s="103" t="n"/>
-      <c r="C131" s="543" t="n"/>
+      <c r="C131" s="547" t="n"/>
       <c r="D131" s="458" t="n"/>
       <c r="E131" s="459" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
     </row>
     <row r="134" outlineLevel="2" customFormat="1" s="13">
       <c r="B134" s="103" t="n"/>
-      <c r="C134" s="611" t="n"/>
+      <c r="C134" s="618" t="n"/>
       <c r="D134" s="365" t="n"/>
       <c r="E134" s="331" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
     </row>
     <row r="135" outlineLevel="2" customFormat="1" s="13">
       <c r="B135" s="103" t="n"/>
-      <c r="C135" s="543" t="n"/>
+      <c r="C135" s="547" t="n"/>
       <c r="D135" s="458" t="n"/>
       <c r="E135" s="459" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
     </row>
     <row r="138" outlineLevel="2" customFormat="1" s="13">
       <c r="B138" s="103" t="n"/>
-      <c r="C138" s="611" t="n"/>
+      <c r="C138" s="618" t="n"/>
       <c r="D138" s="365" t="n"/>
       <c r="E138" s="331" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
     </row>
     <row r="139" outlineLevel="2" customFormat="1" s="13">
       <c r="B139" s="103" t="n"/>
-      <c r="C139" s="543" t="n"/>
+      <c r="C139" s="547" t="n"/>
       <c r="D139" s="458" t="n"/>
       <c r="E139" s="459" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
     </row>
     <row r="142" outlineLevel="2" customFormat="1" s="13">
       <c r="B142" s="103" t="n"/>
-      <c r="C142" s="611" t="n"/>
+      <c r="C142" s="618" t="n"/>
       <c r="D142" s="365" t="n"/>
       <c r="E142" s="331" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
     </row>
     <row r="143" outlineLevel="2" customFormat="1" s="13">
       <c r="B143" s="103" t="n"/>
-      <c r="C143" s="543" t="n"/>
+      <c r="C143" s="547" t="n"/>
       <c r="D143" s="458" t="n"/>
       <c r="E143" s="459" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
     </row>
     <row r="146" outlineLevel="2" customFormat="1" s="13">
       <c r="B146" s="103" t="n"/>
-      <c r="C146" s="611" t="n"/>
+      <c r="C146" s="618" t="n"/>
       <c r="D146" s="365" t="n"/>
       <c r="E146" s="331" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
     </row>
     <row r="147" outlineLevel="2" customFormat="1" s="13">
       <c r="B147" s="103" t="n"/>
-      <c r="C147" s="543" t="n"/>
+      <c r="C147" s="547" t="n"/>
       <c r="D147" s="458" t="n"/>
       <c r="E147" s="459" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
     </row>
     <row r="150" outlineLevel="2" customFormat="1" s="13">
       <c r="B150" s="103" t="n"/>
-      <c r="C150" s="611" t="n"/>
+      <c r="C150" s="618" t="n"/>
       <c r="D150" s="365" t="n"/>
       <c r="E150" s="331" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
     </row>
     <row r="151" outlineLevel="2" customFormat="1" s="13">
       <c r="B151" s="103" t="n"/>
-      <c r="C151" s="543" t="n"/>
+      <c r="C151" s="547" t="n"/>
       <c r="D151" s="458" t="n"/>
       <c r="E151" s="459" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
     </row>
     <row r="154" outlineLevel="2" customFormat="1" s="13">
       <c r="B154" s="103" t="n"/>
-      <c r="C154" s="611" t="n"/>
+      <c r="C154" s="618" t="n"/>
       <c r="D154" s="365" t="n"/>
       <c r="E154" s="331" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
     </row>
     <row r="155" outlineLevel="2" customFormat="1" s="13">
       <c r="B155" s="103" t="n"/>
-      <c r="C155" s="543" t="n"/>
+      <c r="C155" s="547" t="n"/>
       <c r="D155" s="458" t="n"/>
       <c r="E155" s="459" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
     </row>
     <row r="158" outlineLevel="2" customFormat="1" s="13">
       <c r="B158" s="103" t="n"/>
-      <c r="C158" s="611" t="n"/>
+      <c r="C158" s="618" t="n"/>
       <c r="D158" s="365" t="n"/>
       <c r="E158" s="331" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
     </row>
     <row r="159" outlineLevel="2" customFormat="1" s="13">
       <c r="B159" s="103" t="n"/>
-      <c r="C159" s="543" t="n"/>
+      <c r="C159" s="547" t="n"/>
       <c r="D159" s="458" t="n"/>
       <c r="E159" s="459" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
     </row>
     <row r="162" outlineLevel="2" customFormat="1" s="13">
       <c r="B162" s="103" t="n"/>
-      <c r="C162" s="543" t="n"/>
+      <c r="C162" s="547" t="n"/>
       <c r="D162" s="367" t="n"/>
       <c r="E162" s="337" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
     </row>
     <row r="163" outlineLevel="2" customFormat="1" s="13">
       <c r="B163" s="103" t="n"/>
-      <c r="C163" s="543" t="n"/>
+      <c r="C163" s="547" t="n"/>
       <c r="D163" s="458" t="n"/>
       <c r="E163" s="459" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
       <c r="K164" s="342" t="n"/>
       <c r="L164" s="343" t="n"/>
     </row>
-    <row r="165" outlineLevel="1" s="592">
+    <row r="165" outlineLevel="1" s="582">
       <c r="B165" s="376" t="n"/>
       <c r="C165" s="158" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
       <c r="K165" s="346" t="n"/>
       <c r="L165" s="346" t="n"/>
     </row>
-    <row r="166" outlineLevel="2" s="592">
+    <row r="166" outlineLevel="2" s="582">
       <c r="B166" s="376" t="n"/>
       <c r="D166" s="370" t="n"/>
       <c r="E166" s="348" t="inlineStr">
@@ -39342,7 +39342,7 @@
     </row>
     <row r="167" outlineLevel="2" customFormat="1" s="13">
       <c r="B167" s="103" t="n"/>
-      <c r="C167" s="543" t="n"/>
+      <c r="C167" s="547" t="n"/>
       <c r="D167" s="458" t="n"/>
       <c r="E167" s="459" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
       <c r="K168" s="352" t="n"/>
       <c r="L168" s="353" t="n"/>
     </row>
-    <row r="169" outlineLevel="1" s="592">
+    <row r="169" outlineLevel="1" s="582">
       <c r="B169" s="376" t="n"/>
       <c r="C169" s="158" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
       <c r="K169" s="346" t="n"/>
       <c r="L169" s="346" t="n"/>
     </row>
-    <row r="170" outlineLevel="2" s="592">
+    <row r="170" outlineLevel="2" s="582">
       <c r="B170" s="376" t="n"/>
       <c r="D170" s="370" t="n"/>
       <c r="E170" s="348" t="inlineStr">
@@ -39432,7 +39432,7 @@
     </row>
     <row r="171" outlineLevel="2" customFormat="1" s="13">
       <c r="B171" s="103" t="n"/>
-      <c r="C171" s="543" t="n"/>
+      <c r="C171" s="547" t="n"/>
       <c r="D171" s="458" t="n"/>
       <c r="E171" s="459" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
       <c r="K172" s="352" t="n"/>
       <c r="L172" s="353" t="n"/>
     </row>
-    <row r="173" outlineLevel="1" s="592">
+    <row r="173" outlineLevel="1" s="582">
       <c r="B173" s="376" t="n"/>
       <c r="C173" s="158" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
       <c r="K173" s="346" t="n"/>
       <c r="L173" s="346" t="n"/>
     </row>
-    <row r="174" outlineLevel="2" s="592">
+    <row r="174" outlineLevel="2" s="582">
       <c r="B174" s="376" t="n"/>
       <c r="D174" s="370" t="n"/>
       <c r="E174" s="348" t="inlineStr">
@@ -39522,7 +39522,7 @@
     </row>
     <row r="175" outlineLevel="2" customFormat="1" s="13">
       <c r="B175" s="103" t="n"/>
-      <c r="C175" s="543" t="n"/>
+      <c r="C175" s="547" t="n"/>
       <c r="D175" s="458" t="n"/>
       <c r="E175" s="459" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
       <c r="K176" s="352" t="n"/>
       <c r="L176" s="353" t="n"/>
     </row>
-    <row r="177" outlineLevel="1" s="592">
+    <row r="177" outlineLevel="1" s="582">
       <c r="B177" s="376" t="n"/>
       <c r="C177" s="158" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
       <c r="K177" s="346" t="n"/>
       <c r="L177" s="346" t="n"/>
     </row>
-    <row r="178" outlineLevel="2" s="592">
+    <row r="178" outlineLevel="2" s="582">
       <c r="B178" s="376" t="n"/>
       <c r="D178" s="370" t="n"/>
       <c r="E178" s="348" t="inlineStr">
@@ -39612,7 +39612,7 @@
     </row>
     <row r="179" outlineLevel="2" customFormat="1" s="13">
       <c r="B179" s="103" t="n"/>
-      <c r="C179" s="543" t="n"/>
+      <c r="C179" s="547" t="n"/>
       <c r="D179" s="458" t="n"/>
       <c r="E179" s="459" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
       <c r="K180" s="352" t="n"/>
       <c r="L180" s="353" t="n"/>
     </row>
-    <row r="181" outlineLevel="1" s="592">
+    <row r="181" outlineLevel="1" s="582">
       <c r="B181" s="376" t="n"/>
       <c r="C181" s="158" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
       <c r="K181" s="346" t="n"/>
       <c r="L181" s="346" t="n"/>
     </row>
-    <row r="182" outlineLevel="2" s="592">
+    <row r="182" outlineLevel="2" s="582">
       <c r="B182" s="376" t="n"/>
       <c r="D182" s="370" t="n"/>
       <c r="E182" s="348" t="inlineStr">
@@ -39702,7 +39702,7 @@
     </row>
     <row r="183" outlineLevel="2" customFormat="1" s="13">
       <c r="B183" s="103" t="n"/>
-      <c r="C183" s="543" t="n"/>
+      <c r="C183" s="547" t="n"/>
       <c r="D183" s="458" t="n"/>
       <c r="E183" s="459" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
       <c r="K184" s="352" t="n"/>
       <c r="L184" s="353" t="n"/>
     </row>
-    <row r="185" outlineLevel="1" s="592">
+    <row r="185" outlineLevel="1" s="582">
       <c r="B185" s="376" t="n"/>
       <c r="C185" s="158" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
       <c r="K185" s="346" t="n"/>
       <c r="L185" s="346" t="n"/>
     </row>
-    <row r="186" outlineLevel="2" s="592">
+    <row r="186" outlineLevel="2" s="582">
       <c r="B186" s="376" t="n"/>
       <c r="D186" s="372" t="n"/>
       <c r="E186" s="354" t="inlineStr">
@@ -39798,7 +39798,7 @@
     </row>
     <row r="187" outlineLevel="2" customFormat="1" s="13">
       <c r="B187" s="103" t="n"/>
-      <c r="C187" s="543" t="n"/>
+      <c r="C187" s="547" t="n"/>
       <c r="D187" s="458" t="n"/>
       <c r="E187" s="459" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
       <c r="K188" s="342" t="n"/>
       <c r="L188" s="343" t="n"/>
     </row>
-    <row r="189" outlineLevel="1" s="592">
+    <row r="189" outlineLevel="1" s="582">
       <c r="B189" s="376" t="n"/>
       <c r="C189" s="158" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
       <c r="K189" s="346" t="n"/>
       <c r="L189" s="346" t="n"/>
     </row>
-    <row r="190" outlineLevel="2" s="592">
+    <row r="190" outlineLevel="2" s="582">
       <c r="B190" s="376" t="n"/>
       <c r="D190" s="373" t="n"/>
       <c r="E190" s="356" t="inlineStr">
@@ -39897,7 +39897,7 @@
     </row>
     <row r="191" outlineLevel="2" customFormat="1" s="13">
       <c r="B191" s="103" t="n"/>
-      <c r="C191" s="543" t="n"/>
+      <c r="C191" s="547" t="n"/>
       <c r="D191" s="458" t="n"/>
       <c r="E191" s="459" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
       <c r="K192" s="352" t="n"/>
       <c r="L192" s="353" t="n"/>
     </row>
-    <row r="193" outlineLevel="1" s="592">
+    <row r="193" outlineLevel="1" s="582">
       <c r="B193" s="376" t="n"/>
       <c r="C193" s="158" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
       <c r="K193" s="346" t="n"/>
       <c r="L193" s="346" t="n"/>
     </row>
-    <row r="194" outlineLevel="2" s="592">
+    <row r="194" outlineLevel="2" s="582">
       <c r="B194" s="376" t="n"/>
       <c r="D194" s="373" t="n"/>
       <c r="E194" s="356" t="inlineStr">
@@ -39996,7 +39996,7 @@
     </row>
     <row r="195" outlineLevel="2" customFormat="1" s="13">
       <c r="B195" s="103" t="n"/>
-      <c r="C195" s="543" t="n"/>
+      <c r="C195" s="547" t="n"/>
       <c r="D195" s="458" t="n"/>
       <c r="E195" s="459" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
       <c r="K196" s="352" t="n"/>
       <c r="L196" s="353" t="n"/>
     </row>
-    <row r="197" outlineLevel="1" s="592">
+    <row r="197" outlineLevel="1" s="582">
       <c r="B197" s="376" t="n"/>
       <c r="C197" s="158" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
       <c r="K197" s="346" t="n"/>
       <c r="L197" s="346" t="n"/>
     </row>
-    <row r="198" outlineLevel="2" s="592">
+    <row r="198" outlineLevel="2" s="582">
       <c r="B198" s="376" t="n"/>
       <c r="D198" s="373" t="n"/>
       <c r="E198" s="356" t="inlineStr">
@@ -40095,7 +40095,7 @@
     </row>
     <row r="199" outlineLevel="2" customFormat="1" s="13">
       <c r="B199" s="103" t="n"/>
-      <c r="C199" s="543" t="n"/>
+      <c r="C199" s="547" t="n"/>
       <c r="D199" s="458" t="n"/>
       <c r="E199" s="459" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
       <c r="K200" s="352" t="n"/>
       <c r="L200" s="353" t="n"/>
     </row>
-    <row r="201" outlineLevel="1" s="592">
+    <row r="201" outlineLevel="1" s="582">
       <c r="B201" s="376" t="n"/>
       <c r="C201" s="158" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
       <c r="K201" s="346" t="n"/>
       <c r="L201" s="346" t="n"/>
     </row>
-    <row r="202" outlineLevel="2" s="592">
+    <row r="202" outlineLevel="2" s="582">
       <c r="B202" s="376" t="n"/>
       <c r="D202" s="373" t="n"/>
       <c r="E202" s="356" t="inlineStr">
@@ -40194,7 +40194,7 @@
     </row>
     <row r="203" outlineLevel="2" customFormat="1" s="13">
       <c r="B203" s="103" t="n"/>
-      <c r="C203" s="543" t="n"/>
+      <c r="C203" s="547" t="n"/>
       <c r="D203" s="458" t="n"/>
       <c r="E203" s="459" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
       <c r="K204" s="352" t="n"/>
       <c r="L204" s="353" t="n"/>
     </row>
-    <row r="205" outlineLevel="1" s="592">
+    <row r="205" outlineLevel="1" s="582">
       <c r="B205" s="376" t="n"/>
       <c r="C205" s="158" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
       <c r="K205" s="346" t="n"/>
       <c r="L205" s="346" t="n"/>
     </row>
-    <row r="206" outlineLevel="2" s="592">
+    <row r="206" outlineLevel="2" s="582">
       <c r="B206" s="376" t="n"/>
       <c r="D206" s="373" t="n"/>
       <c r="E206" s="356" t="inlineStr">
@@ -40293,7 +40293,7 @@
     </row>
     <row r="207" outlineLevel="2" customFormat="1" s="13">
       <c r="B207" s="103" t="n"/>
-      <c r="C207" s="543" t="n"/>
+      <c r="C207" s="547" t="n"/>
       <c r="D207" s="458" t="n"/>
       <c r="E207" s="459" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
       <c r="K208" s="352" t="n"/>
       <c r="L208" s="353" t="n"/>
     </row>
-    <row r="209" outlineLevel="1" s="592">
+    <row r="209" outlineLevel="1" s="582">
       <c r="B209" s="376" t="n"/>
       <c r="C209" s="158" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
       <c r="K209" s="346" t="n"/>
       <c r="L209" s="346" t="n"/>
     </row>
-    <row r="210" outlineLevel="2" s="592">
+    <row r="210" outlineLevel="2" s="582">
       <c r="B210" s="376" t="n"/>
       <c r="D210" s="373" t="n"/>
       <c r="E210" s="356" t="inlineStr">
@@ -40392,7 +40392,7 @@
     </row>
     <row r="211" outlineLevel="2" customFormat="1" s="13">
       <c r="B211" s="103" t="n"/>
-      <c r="C211" s="543" t="n"/>
+      <c r="C211" s="547" t="n"/>
       <c r="D211" s="458" t="n"/>
       <c r="E211" s="459" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
       <c r="K212" s="352" t="n"/>
       <c r="L212" s="353" t="n"/>
     </row>
-    <row r="213" outlineLevel="1" s="592">
+    <row r="213" outlineLevel="1" s="582">
       <c r="B213" s="376" t="n"/>
       <c r="C213" s="158" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
       <c r="K213" s="346" t="n"/>
       <c r="L213" s="346" t="n"/>
     </row>
-    <row r="214" outlineLevel="2" s="592">
+    <row r="214" outlineLevel="2" s="582">
       <c r="B214" s="376" t="n"/>
       <c r="D214" s="373" t="n"/>
       <c r="E214" s="356" t="inlineStr">
@@ -40491,7 +40491,7 @@
     </row>
     <row r="215" outlineLevel="2" customFormat="1" s="13">
       <c r="B215" s="103" t="n"/>
-      <c r="C215" s="543" t="n"/>
+      <c r="C215" s="547" t="n"/>
       <c r="D215" s="458" t="n"/>
       <c r="E215" s="459" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
       <c r="K216" s="352" t="n"/>
       <c r="L216" s="353" t="n"/>
     </row>
-    <row r="217" outlineLevel="1" s="592">
+    <row r="217" outlineLevel="1" s="582">
       <c r="B217" s="376" t="n"/>
       <c r="C217" s="158" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
       <c r="K217" s="346" t="n"/>
       <c r="L217" s="346" t="n"/>
     </row>
-    <row r="218" outlineLevel="2" s="592">
+    <row r="218" outlineLevel="2" s="582">
       <c r="B218" s="376" t="n"/>
       <c r="D218" s="372" t="n"/>
       <c r="E218" s="354" t="inlineStr">
@@ -40590,7 +40590,7 @@
     </row>
     <row r="219" outlineLevel="2" customFormat="1" s="13">
       <c r="B219" s="103" t="n"/>
-      <c r="C219" s="543" t="n"/>
+      <c r="C219" s="547" t="n"/>
       <c r="D219" s="458" t="n"/>
       <c r="E219" s="459" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
       <c r="K220" s="342" t="n"/>
       <c r="L220" s="343" t="n"/>
     </row>
-    <row r="221" outlineLevel="1" s="592">
+    <row r="221" outlineLevel="1" s="582">
       <c r="B221" s="376" t="n"/>
       <c r="C221" s="158" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
       <c r="K221" s="346" t="n"/>
       <c r="L221" s="346" t="n"/>
     </row>
-    <row r="222" outlineLevel="2" s="592">
+    <row r="222" outlineLevel="2" s="582">
       <c r="B222" s="376" t="n"/>
       <c r="D222" s="373" t="n"/>
       <c r="E222" s="356" t="inlineStr">
@@ -40690,7 +40690,7 @@
     </row>
     <row r="223" outlineLevel="2" customFormat="1" s="13">
       <c r="B223" s="103" t="n"/>
-      <c r="C223" s="543" t="n"/>
+      <c r="C223" s="547" t="n"/>
       <c r="D223" s="458" t="n"/>
       <c r="E223" s="459" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
       <c r="K224" s="352" t="n"/>
       <c r="L224" s="353" t="n"/>
     </row>
-    <row r="225" outlineLevel="1" s="592">
+    <row r="225" outlineLevel="1" s="582">
       <c r="B225" s="376" t="n"/>
       <c r="C225" s="158" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
       <c r="K225" s="346" t="n"/>
       <c r="L225" s="346" t="n"/>
     </row>
-    <row r="226" outlineLevel="2" s="592">
+    <row r="226" outlineLevel="2" s="582">
       <c r="B226" s="376" t="n"/>
       <c r="D226" s="373" t="n"/>
       <c r="E226" s="356" t="inlineStr">
@@ -40790,7 +40790,7 @@
     </row>
     <row r="227" outlineLevel="2" customFormat="1" s="13">
       <c r="B227" s="103" t="n"/>
-      <c r="C227" s="543" t="n"/>
+      <c r="C227" s="547" t="n"/>
       <c r="D227" s="458" t="n"/>
       <c r="E227" s="459" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
       <c r="K228" s="352" t="n"/>
       <c r="L228" s="353" t="n"/>
     </row>
-    <row r="229" outlineLevel="1" s="592">
+    <row r="229" outlineLevel="1" s="582">
       <c r="B229" s="376" t="n"/>
       <c r="C229" s="158" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
       <c r="K229" s="346" t="n"/>
       <c r="L229" s="346" t="n"/>
     </row>
-    <row r="230" outlineLevel="2" s="592">
+    <row r="230" outlineLevel="2" s="582">
       <c r="B230" s="376" t="n"/>
       <c r="D230" s="373" t="n"/>
       <c r="E230" s="356" t="inlineStr">
@@ -40890,7 +40890,7 @@
     </row>
     <row r="231" outlineLevel="2" customFormat="1" s="13">
       <c r="B231" s="103" t="n"/>
-      <c r="C231" s="543" t="n"/>
+      <c r="C231" s="547" t="n"/>
       <c r="D231" s="458" t="n"/>
       <c r="E231" s="459" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
       <c r="K232" s="352" t="n"/>
       <c r="L232" s="353" t="n"/>
     </row>
-    <row r="233" outlineLevel="1" s="592">
+    <row r="233" outlineLevel="1" s="582">
       <c r="B233" s="376" t="n"/>
       <c r="C233" s="158" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
       <c r="K233" s="346" t="n"/>
       <c r="L233" s="346" t="n"/>
     </row>
-    <row r="234" outlineLevel="2" s="592">
+    <row r="234" outlineLevel="2" s="582">
       <c r="B234" s="376" t="n"/>
       <c r="D234" s="373" t="n"/>
       <c r="E234" s="356" t="inlineStr">
@@ -40990,7 +40990,7 @@
     </row>
     <row r="235" outlineLevel="2" customFormat="1" s="13">
       <c r="B235" s="103" t="n"/>
-      <c r="C235" s="543" t="n"/>
+      <c r="C235" s="547" t="n"/>
       <c r="D235" s="458" t="n"/>
       <c r="E235" s="459" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
       <c r="K236" s="352" t="n"/>
       <c r="L236" s="353" t="n"/>
     </row>
-    <row r="237" outlineLevel="1" s="592">
+    <row r="237" outlineLevel="1" s="582">
       <c r="B237" s="376" t="n"/>
       <c r="C237" s="158" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
       <c r="K237" s="346" t="n"/>
       <c r="L237" s="346" t="n"/>
     </row>
-    <row r="238" outlineLevel="2" s="592">
+    <row r="238" outlineLevel="2" s="582">
       <c r="B238" s="376" t="n"/>
       <c r="D238" s="373" t="n"/>
       <c r="E238" s="356" t="inlineStr">
@@ -41088,7 +41088,7 @@
       <c r="K238" s="357" t="n"/>
       <c r="L238" s="357" t="n"/>
     </row>
-    <row r="239" outlineLevel="2" s="592">
+    <row r="239" outlineLevel="2" s="582">
       <c r="B239" s="376" t="n"/>
       <c r="D239" s="357" t="n"/>
       <c r="E239" s="459" t="inlineStr">
@@ -41126,7 +41126,7 @@
       <c r="K240" s="352" t="n"/>
       <c r="L240" s="353" t="n"/>
     </row>
-    <row r="241" outlineLevel="1" s="592">
+    <row r="241" outlineLevel="1" s="582">
       <c r="B241" s="376" t="n"/>
       <c r="C241" s="158" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
       <c r="K241" s="346" t="n"/>
       <c r="L241" s="346" t="n"/>
     </row>
-    <row r="242" outlineLevel="2" s="592">
+    <row r="242" outlineLevel="2" s="582">
       <c r="B242" s="376" t="n"/>
       <c r="D242" s="373" t="n"/>
       <c r="E242" s="356" t="inlineStr">
@@ -41187,7 +41187,7 @@
       <c r="K242" s="357" t="n"/>
       <c r="L242" s="357" t="n"/>
     </row>
-    <row r="243" outlineLevel="2" s="592">
+    <row r="243" outlineLevel="2" s="582">
       <c r="B243" s="376" t="n"/>
       <c r="D243" s="357" t="n"/>
       <c r="E243" s="459" t="inlineStr">
@@ -41225,7 +41225,7 @@
       <c r="K244" s="352" t="n"/>
       <c r="L244" s="353" t="n"/>
     </row>
-    <row r="245" outlineLevel="1" s="592">
+    <row r="245" outlineLevel="1" s="582">
       <c r="B245" s="376" t="n"/>
       <c r="C245" s="158" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
       <c r="K245" s="346" t="n"/>
       <c r="L245" s="346" t="n"/>
     </row>
-    <row r="246" outlineLevel="2" s="592">
+    <row r="246" outlineLevel="2" s="582">
       <c r="B246" s="376" t="n"/>
       <c r="D246" s="373" t="n"/>
       <c r="E246" s="356" t="inlineStr">
@@ -41286,7 +41286,7 @@
       <c r="K246" s="357" t="n"/>
       <c r="L246" s="357" t="n"/>
     </row>
-    <row r="247" outlineLevel="2" s="592">
+    <row r="247" outlineLevel="2" s="582">
       <c r="B247" s="376" t="n"/>
       <c r="D247" s="357" t="n"/>
       <c r="E247" s="459" t="inlineStr">
@@ -41324,7 +41324,7 @@
       <c r="K248" s="352" t="n"/>
       <c r="L248" s="353" t="n"/>
     </row>
-    <row r="249" outlineLevel="1" s="592">
+    <row r="249" outlineLevel="1" s="582">
       <c r="B249" s="376" t="n"/>
       <c r="C249" s="158" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
       <c r="K249" s="346" t="n"/>
       <c r="L249" s="346" t="n"/>
     </row>
-    <row r="250" outlineLevel="2" s="592">
+    <row r="250" outlineLevel="2" s="582">
       <c r="B250" s="376" t="n"/>
       <c r="D250" s="373" t="n"/>
       <c r="E250" s="356" t="inlineStr">
@@ -41385,7 +41385,7 @@
       <c r="K250" s="357" t="n"/>
       <c r="L250" s="357" t="n"/>
     </row>
-    <row r="251" outlineLevel="2" s="592">
+    <row r="251" outlineLevel="2" s="582">
       <c r="B251" s="376" t="n"/>
       <c r="D251" s="357" t="n"/>
       <c r="E251" s="459" t="inlineStr">
@@ -41423,7 +41423,7 @@
       <c r="K252" s="352" t="n"/>
       <c r="L252" s="353" t="n"/>
     </row>
-    <row r="253" outlineLevel="1" s="592">
+    <row r="253" outlineLevel="1" s="582">
       <c r="B253" s="376" t="n"/>
       <c r="C253" s="158" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
       <c r="K253" s="346" t="n"/>
       <c r="L253" s="346" t="n"/>
     </row>
-    <row r="254" outlineLevel="2" s="592">
+    <row r="254" outlineLevel="2" s="582">
       <c r="B254" s="376" t="n"/>
       <c r="D254" s="373" t="n"/>
       <c r="E254" s="356" t="inlineStr">
@@ -41484,7 +41484,7 @@
       <c r="K254" s="357" t="n"/>
       <c r="L254" s="357" t="n"/>
     </row>
-    <row r="255" outlineLevel="2" s="592">
+    <row r="255" outlineLevel="2" s="582">
       <c r="B255" s="376" t="n"/>
       <c r="D255" s="357" t="n"/>
       <c r="E255" s="459" t="inlineStr">
@@ -41522,7 +41522,7 @@
       <c r="K256" s="352" t="n"/>
       <c r="L256" s="353" t="n"/>
     </row>
-    <row r="257" outlineLevel="1" s="592">
+    <row r="257" outlineLevel="1" s="582">
       <c r="B257" s="376" t="n"/>
       <c r="C257" s="158" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
       <c r="K257" s="346" t="n"/>
       <c r="L257" s="346" t="n"/>
     </row>
-    <row r="258" outlineLevel="2" s="592">
+    <row r="258" outlineLevel="2" s="582">
       <c r="B258" s="376" t="n"/>
       <c r="D258" s="373" t="n"/>
       <c r="E258" s="356" t="inlineStr">
@@ -41583,7 +41583,7 @@
       <c r="K258" s="357" t="n"/>
       <c r="L258" s="357" t="n"/>
     </row>
-    <row r="259" outlineLevel="2" s="592">
+    <row r="259" outlineLevel="2" s="582">
       <c r="B259" s="376" t="n"/>
       <c r="D259" s="357" t="n"/>
       <c r="E259" s="459" t="inlineStr">
@@ -41621,7 +41621,7 @@
       <c r="K260" s="352" t="n"/>
       <c r="L260" s="353" t="n"/>
     </row>
-    <row r="261" outlineLevel="1" s="592">
+    <row r="261" outlineLevel="1" s="582">
       <c r="B261" s="376" t="n"/>
       <c r="C261" s="158" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
       <c r="K261" s="346" t="n"/>
       <c r="L261" s="346" t="n"/>
     </row>
-    <row r="262" outlineLevel="2" s="592">
+    <row r="262" outlineLevel="2" s="582">
       <c r="B262" s="376" t="n"/>
       <c r="D262" s="373" t="n"/>
       <c r="E262" s="356" t="inlineStr">
@@ -41682,7 +41682,7 @@
       <c r="K262" s="357" t="n"/>
       <c r="L262" s="357" t="n"/>
     </row>
-    <row r="263" outlineLevel="2" s="592">
+    <row r="263" outlineLevel="2" s="582">
       <c r="B263" s="376" t="n"/>
       <c r="D263" s="357" t="n"/>
       <c r="E263" s="459" t="inlineStr">
@@ -41720,7 +41720,7 @@
       <c r="K264" s="352" t="n"/>
       <c r="L264" s="353" t="n"/>
     </row>
-    <row r="265" outlineLevel="1" s="592">
+    <row r="265" outlineLevel="1" s="582">
       <c r="B265" s="376" t="n"/>
       <c r="C265" s="158" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
       <c r="K265" s="346" t="n"/>
       <c r="L265" s="346" t="n"/>
     </row>
-    <row r="266" outlineLevel="2" s="592">
+    <row r="266" outlineLevel="2" s="582">
       <c r="B266" s="376" t="n"/>
       <c r="D266" s="373" t="n"/>
       <c r="E266" s="356" t="inlineStr">
@@ -41781,7 +41781,7 @@
       <c r="K266" s="357" t="n"/>
       <c r="L266" s="357" t="n"/>
     </row>
-    <row r="267" outlineLevel="2" s="592">
+    <row r="267" outlineLevel="2" s="582">
       <c r="B267" s="376" t="n"/>
       <c r="D267" s="357" t="n"/>
       <c r="E267" s="459" t="inlineStr">
@@ -41819,7 +41819,7 @@
       <c r="K268" s="352" t="n"/>
       <c r="L268" s="353" t="n"/>
     </row>
-    <row r="269" outlineLevel="1" s="592">
+    <row r="269" outlineLevel="1" s="582">
       <c r="B269" s="376" t="n"/>
       <c r="C269" s="158" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
       <c r="K269" s="346" t="n"/>
       <c r="L269" s="346" t="n"/>
     </row>
-    <row r="270" outlineLevel="2" s="592">
+    <row r="270" outlineLevel="2" s="582">
       <c r="B270" s="376" t="n"/>
       <c r="D270" s="373" t="n"/>
       <c r="E270" s="356" t="inlineStr">
@@ -41880,7 +41880,7 @@
       <c r="K270" s="357" t="n"/>
       <c r="L270" s="357" t="n"/>
     </row>
-    <row r="271" outlineLevel="2" s="592">
+    <row r="271" outlineLevel="2" s="582">
       <c r="B271" s="376" t="n"/>
       <c r="D271" s="357" t="n"/>
       <c r="E271" s="459" t="inlineStr">
@@ -41918,7 +41918,7 @@
       <c r="K272" s="352" t="n"/>
       <c r="L272" s="353" t="n"/>
     </row>
-    <row r="273" outlineLevel="1" s="592">
+    <row r="273" outlineLevel="1" s="582">
       <c r="B273" s="376" t="n"/>
       <c r="C273" s="158" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
       <c r="K273" s="346" t="n"/>
       <c r="L273" s="346" t="n"/>
     </row>
-    <row r="274" outlineLevel="2" s="592">
+    <row r="274" outlineLevel="2" s="582">
       <c r="B274" s="376" t="n"/>
       <c r="D274" s="372" t="n"/>
       <c r="E274" s="354" t="inlineStr">
@@ -41975,7 +41975,7 @@
       <c r="K274" s="355" t="n"/>
       <c r="L274" s="355" t="n"/>
     </row>
-    <row r="275" outlineLevel="2" s="592">
+    <row r="275" outlineLevel="2" s="582">
       <c r="B275" s="376" t="n"/>
       <c r="D275" s="357" t="n"/>
       <c r="E275" s="459" t="inlineStr">
@@ -42013,7 +42013,7 @@
       <c r="K276" s="342" t="n"/>
       <c r="L276" s="343" t="n"/>
     </row>
-    <row r="277" outlineLevel="1" s="592">
+    <row r="277" outlineLevel="1" s="582">
       <c r="B277" s="376" t="n"/>
       <c r="C277" s="158" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
       <c r="K277" s="346" t="n"/>
       <c r="L277" s="346" t="n"/>
     </row>
-    <row r="278" outlineLevel="2" s="592">
+    <row r="278" outlineLevel="2" s="582">
       <c r="B278" s="376" t="n"/>
       <c r="D278" s="373" t="n"/>
       <c r="E278" s="356" t="inlineStr">
@@ -42069,7 +42069,7 @@
       <c r="K278" s="357" t="n"/>
       <c r="L278" s="357" t="n"/>
     </row>
-    <row r="279" outlineLevel="2" s="592">
+    <row r="279" outlineLevel="2" s="582">
       <c r="B279" s="376" t="n"/>
       <c r="D279" s="357" t="n"/>
       <c r="E279" s="459" t="inlineStr">
@@ -42107,7 +42107,7 @@
       <c r="K280" s="352" t="n"/>
       <c r="L280" s="353" t="n"/>
     </row>
-    <row r="281" outlineLevel="1" s="592">
+    <row r="281" outlineLevel="1" s="582">
       <c r="B281" s="376" t="n"/>
       <c r="C281" s="158" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
       <c r="K281" s="346" t="n"/>
       <c r="L281" s="346" t="n"/>
     </row>
-    <row r="282" outlineLevel="2" s="592">
+    <row r="282" outlineLevel="2" s="582">
       <c r="B282" s="376" t="n"/>
       <c r="D282" s="373" t="n"/>
       <c r="E282" s="356" t="inlineStr">
@@ -42163,7 +42163,7 @@
       <c r="K282" s="357" t="n"/>
       <c r="L282" s="357" t="n"/>
     </row>
-    <row r="283" outlineLevel="2" s="592">
+    <row r="283" outlineLevel="2" s="582">
       <c r="B283" s="376" t="n"/>
       <c r="D283" s="357" t="n"/>
       <c r="E283" s="459" t="inlineStr">
@@ -42201,7 +42201,7 @@
       <c r="K284" s="352" t="n"/>
       <c r="L284" s="353" t="n"/>
     </row>
-    <row r="285" outlineLevel="1" s="592">
+    <row r="285" outlineLevel="1" s="582">
       <c r="B285" s="376" t="n"/>
       <c r="C285" s="158" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
       <c r="K285" s="346" t="n"/>
       <c r="L285" s="346" t="n"/>
     </row>
-    <row r="286" outlineLevel="2" s="592">
+    <row r="286" outlineLevel="2" s="582">
       <c r="B286" s="376" t="n"/>
       <c r="D286" s="373" t="n"/>
       <c r="E286" s="356" t="inlineStr">
@@ -42257,7 +42257,7 @@
       <c r="K286" s="357" t="n"/>
       <c r="L286" s="357" t="n"/>
     </row>
-    <row r="287" outlineLevel="2" s="592">
+    <row r="287" outlineLevel="2" s="582">
       <c r="B287" s="376" t="n"/>
       <c r="D287" s="357" t="n"/>
       <c r="E287" s="459" t="inlineStr">
@@ -42295,7 +42295,7 @@
       <c r="K288" s="352" t="n"/>
       <c r="L288" s="353" t="n"/>
     </row>
-    <row r="289" outlineLevel="1" s="592">
+    <row r="289" outlineLevel="1" s="582">
       <c r="B289" s="376" t="n"/>
       <c r="C289" s="158" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
       <c r="K289" s="346" t="n"/>
       <c r="L289" s="346" t="n"/>
     </row>
-    <row r="290" outlineLevel="2" s="592">
+    <row r="290" outlineLevel="2" s="582">
       <c r="B290" s="376" t="n"/>
       <c r="D290" s="373" t="n"/>
       <c r="E290" s="356" t="inlineStr">
@@ -42351,7 +42351,7 @@
       <c r="K290" s="357" t="n"/>
       <c r="L290" s="357" t="n"/>
     </row>
-    <row r="291" outlineLevel="2" s="592">
+    <row r="291" outlineLevel="2" s="582">
       <c r="B291" s="376" t="n"/>
       <c r="D291" s="357" t="n"/>
       <c r="E291" s="459" t="inlineStr">
@@ -42389,7 +42389,7 @@
       <c r="K292" s="352" t="n"/>
       <c r="L292" s="353" t="n"/>
     </row>
-    <row r="293" outlineLevel="1" s="592">
+    <row r="293" outlineLevel="1" s="582">
       <c r="B293" s="376" t="n"/>
       <c r="C293" s="158" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
       <c r="K293" s="346" t="n"/>
       <c r="L293" s="346" t="n"/>
     </row>
-    <row r="294" outlineLevel="2" s="592">
+    <row r="294" outlineLevel="2" s="582">
       <c r="B294" s="376" t="n"/>
       <c r="D294" s="372" t="n"/>
       <c r="E294" s="354" t="inlineStr">
@@ -42447,7 +42447,7 @@
       <c r="K294" s="355" t="n"/>
       <c r="L294" s="355" t="n"/>
     </row>
-    <row r="295" outlineLevel="2" s="592">
+    <row r="295" outlineLevel="2" s="582">
       <c r="B295" s="376" t="n"/>
       <c r="D295" s="357" t="n"/>
       <c r="E295" s="459" t="inlineStr">
